--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:H32"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,19 +421,19 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אוליביה דין The Art of Loving</v>
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-09</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
+        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E2" t="str">
-        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
+        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
       </c>
       <c r="F2" t="str">
         <v>אלבומים חדשים</v>
@@ -441,587 +441,787 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Geese Getting Killed</v>
+        <v>אוליביה דין The Art of Loving</v>
       </c>
       <c r="B3" t="str">
-        <v>2025-12-29</v>
+        <v>2026-01-04</v>
       </c>
       <c r="C3" t="str">
-        <v>https://yosmusic.com/geese-getting-killed/</v>
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E3" t="str">
-        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
+        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
       </c>
       <c r="F3" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>רוסליה Lux</v>
+        <v>Geese Getting Killed</v>
       </c>
       <c r="B4" t="str">
-        <v>2025-12-25</v>
+        <v>2025-12-29</v>
       </c>
       <c r="C4" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
+        <v>https://yosmusic.com/geese-getting-killed/</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E4" t="str">
-        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
+        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
       </c>
       <c r="F4" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>יאנגבלאד אירוסמית' one more time</v>
+        <v>רוסליה Lux</v>
       </c>
       <c r="B5" t="str">
-        <v>2025-12-17</v>
+        <v>2025-12-25</v>
       </c>
       <c r="C5" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E5" t="str">
-        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
+        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
       </c>
       <c r="F5" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>פינק פלויד Wish You Were Here 50</v>
+        <v>יאנגבלאד אירוסמית' one more time</v>
       </c>
       <c r="B6" t="str">
-        <v>2025-12-14</v>
+        <v>2025-12-17</v>
       </c>
       <c r="C6" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
+        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E6" t="str">
-        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
+        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
       </c>
       <c r="F6" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+        <v>פינק פלויד Wish You Were Here 50</v>
       </c>
       <c r="B7" t="str">
-        <v>2025-12-08</v>
+        <v>2025-12-14</v>
       </c>
       <c r="C7" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E7" t="str">
-        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
+        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
       </c>
       <c r="F7" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>סטריי קידס DO IT (EP)</v>
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
       </c>
       <c r="B8" t="str">
-        <v>2025-12-04</v>
+        <v>2025-12-08</v>
       </c>
       <c r="C8" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
+        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E8" t="str">
-        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
+        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
       </c>
       <c r="F8" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>דויד ברוזה BROZAJAZZ</v>
+        <v>סטריי קידס DO IT (EP)</v>
       </c>
       <c r="B9" t="str">
-        <v>2025-11-30</v>
+        <v>2025-12-04</v>
       </c>
       <c r="C9" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
+        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E9" t="str">
-        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
+        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
       </c>
       <c r="F9" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Five Seconds of Summer – Everyone's A Star</v>
+        <v>דויד ברוזה BROZAJAZZ</v>
       </c>
       <c r="B10" t="str">
-        <v>2025-11-24</v>
+        <v>2025-11-30</v>
       </c>
       <c r="C10" t="str">
-        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E10" t="str">
-        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
+        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
       </c>
       <c r="F10" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>התקווה 6 – ויהי אור</v>
+        <v>Five Seconds of Summer – Everyone's A Star</v>
       </c>
       <c r="B11" t="str">
-        <v>2025-11-20</v>
+        <v>2025-11-24</v>
       </c>
       <c r="C11" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
+        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E11" t="str">
-        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
+        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
       </c>
       <c r="F11" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>פלורנס אנד דה משין Everybody Scream</v>
+        <v>התקווה 6 – ויהי אור</v>
       </c>
       <c r="B12" t="str">
-        <v>2025-11-13</v>
+        <v>2025-11-20</v>
       </c>
       <c r="C12" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
+        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E12" t="str">
-        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
+        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
       </c>
       <c r="F12" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>טיים אימפלה Deadbeat</v>
+        <v>פלורנס אנד דה משין Everybody Scream</v>
       </c>
       <c r="B13" t="str">
-        <v>2025-11-03</v>
+        <v>2025-11-13</v>
       </c>
       <c r="C13" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E13" t="str">
-        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
+        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
       </c>
       <c r="F13" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+        <v>טיים אימפלה Deadbeat</v>
       </c>
       <c r="B14" t="str">
-        <v>2025-10-20</v>
+        <v>2025-11-03</v>
       </c>
       <c r="C14" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E14" t="str">
-        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
+        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
       </c>
       <c r="F14" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>שלמה גרוניך – תודה אהבה</v>
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
       </c>
       <c r="B15" t="str">
-        <v>2025-10-18</v>
+        <v>2025-10-20</v>
       </c>
       <c r="C15" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
+        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E15" t="str">
-        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
+        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
       </c>
       <c r="F15" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>טיילור סוויפט The Life Of A Showgirl</v>
+        <v>שלמה גרוניך – תודה אהבה</v>
       </c>
       <c r="B16" t="str">
-        <v>2025-10-11</v>
+        <v>2025-10-18</v>
       </c>
       <c r="C16" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E16" t="str">
-        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
+        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
       </c>
       <c r="F16" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>דוג'ה קאט Vie</v>
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
       </c>
       <c r="B17" t="str">
-        <v>2025-10-04</v>
+        <v>2025-10-11</v>
       </c>
       <c r="C17" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E17" t="str">
-        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
+        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
       </c>
       <c r="F17" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ג'וי קרוקס Juniper</v>
+        <v>דוג'ה קאט Vie</v>
       </c>
       <c r="B18" t="str">
-        <v>2025-10-03</v>
+        <v>2025-10-04</v>
       </c>
       <c r="C18" t="str">
-        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E18" t="str">
-        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
+        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
       </c>
       <c r="F18" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ביפי קליירו Futique</v>
+        <v>ג'וי קרוקס Juniper</v>
       </c>
       <c r="B19" t="str">
-        <v>2025-09-30</v>
+        <v>2025-10-03</v>
       </c>
       <c r="C19" t="str">
-        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
+        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E19" t="str">
-        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
+        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
       </c>
       <c r="F19" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>אד שירן Play</v>
+        <v>ביפי קליירו Futique</v>
       </c>
       <c r="B20" t="str">
-        <v>2025-09-24</v>
+        <v>2025-09-30</v>
       </c>
       <c r="C20" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
+        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E20" t="str">
-        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
+        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
       </c>
       <c r="F20" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+        <v>אד שירן Play</v>
       </c>
       <c r="B21" t="str">
-        <v>2025-09-21</v>
+        <v>2025-09-24</v>
       </c>
       <c r="C21" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E21" t="str">
-        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
+        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
       </c>
       <c r="F21" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>סוויד Antidepressants</v>
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
       </c>
       <c r="B22" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-21</v>
       </c>
       <c r="C22" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E22" t="str">
-        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
+        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
       </c>
       <c r="F22" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>וולף אליס The Clearing</v>
+        <v>סוויד Antidepressants</v>
       </c>
       <c r="B23" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-12</v>
       </c>
       <c r="C23" t="str">
-        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
+        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E23" t="str">
-        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
+        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
       </c>
       <c r="F23" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+        <v>וולף אליס The Clearing</v>
       </c>
       <c r="B24" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-01</v>
       </c>
       <c r="C24" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
+        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E24" t="str">
-        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
+        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
       </c>
       <c r="F24" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
       </c>
       <c r="B25" t="str">
-        <v>2025-08-24</v>
+        <v>2025-08-29</v>
       </c>
       <c r="C25" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
+        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E25" t="str">
-        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
+        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
       </c>
       <c r="F25" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
       </c>
       <c r="B26" t="str">
-        <v>2025-08-21</v>
+        <v>2025-08-24</v>
       </c>
       <c r="C26" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
+        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E26" t="str">
-        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
+        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
       </c>
       <c r="F26" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>אברהם טל – חי</v>
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
       </c>
       <c r="B27" t="str">
-        <v>2025-08-17</v>
+        <v>2025-08-21</v>
       </c>
       <c r="C27" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E27" t="str">
-        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
+        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
       </c>
       <c r="F27" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>רנה ראפ Bite Me</v>
+        <v>אברהם טל – חי</v>
       </c>
       <c r="B28" t="str">
-        <v>2025-08-12</v>
+        <v>2025-08-17</v>
       </c>
       <c r="C28" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E28" t="str">
-        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
+        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
       </c>
       <c r="F28" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>The K's – Pretty On The Internet</v>
+        <v>רנה ראפ Bite Me</v>
       </c>
       <c r="B29" t="str">
-        <v>2025-08-03</v>
+        <v>2025-08-12</v>
       </c>
       <c r="C29" t="str">
-        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
+        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E29" t="str">
-        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
+        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
       </c>
       <c r="F29" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>פליטווד מק Fifty Years – Don’t Stop</v>
+        <v>The K's – Pretty On The Internet</v>
       </c>
       <c r="B30" t="str">
-        <v>2025-07-30</v>
+        <v>2025-08-03</v>
       </c>
       <c r="C30" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%99%d7%98%d7%95%d7%95%d7%93-%d7%9e%d7%a7-fifty-years-dont-stop/</v>
+        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E30" t="str">
-        <v>פליטווד מק (Fleetwood Mac) חוגגים חצי מאה של מוזיקה עם אוסף חדש בן 50 שירים, שמתפרש על כל הקריירה של הלהקה, מימיה הראשונים בסגנון בלוז, ועד להצלחתה העולמית כאחת מלהקות הגדולות בהיסטוריה של הרוק. פליטווד מק הם לא רק להקה</v>
+        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
       </c>
       <c r="F30" t="str">
         <v>אלבומים חדשים</v>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
+        <v>פליטווד מק Fifty Years – Don’t Stop</v>
+      </c>
+      <c r="B31" t="str">
+        <v>2025-07-30</v>
+      </c>
+      <c r="C31" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%99%d7%98%d7%95%d7%95%d7%93-%d7%9e%d7%a7-fifty-years-dont-stop/</v>
+      </c>
+      <c r="D31" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E31" t="str">
+        <v>פליטווד מק (Fleetwood Mac) חוגגים חצי מאה של מוזיקה עם אוסף חדש בן 50 שירים, שמתפרש על כל הקריירה של הלהקה, מימיה הראשונים בסגנון בלוז, ועד להצלחתה העולמית כאחת מלהקות הגדולות בהיסטוריה של הרוק. פליטווד מק הם לא רק להקה</v>
+      </c>
+      <c r="F31" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
         <v>Wet Leg Moisturizer</v>
       </c>
-      <c r="B31" t="str">
+      <c r="B32" t="str">
         <v>2025-07-25</v>
       </c>
-      <c r="C31" t="str">
+      <c r="C32" t="str">
         <v>https://yosmusic.com/wet-leg-moisturizer/</v>
       </c>
-      <c r="D31" t="str">
-        <v>2026-01-08</v>
-      </c>
-      <c r="E31" t="str">
+      <c r="D32" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E32" t="str">
         <v>להקת Wet Leg לא הוציאה קרם לחות (Moisturizer) כמוצר טיפוח. במקום זאת, "Moisturizer" הוא שמו של האלבום השני והחדש שלהם. במרכז –  צמד אינדי-רוק המורכב מהחברות ריין טיסדייל והסטר צ'יימברס. אלבום הבכורה הנושא את שמה, הגיע למקום הראשון במצעד האלבומים</v>
       </c>
-      <c r="F31" t="str">
-        <v>אלבומים חדשים</v>
+      <c r="F32" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H32"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:J33"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,19 +421,19 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מארינה מקסימיליאן – ריק בחלל</v>
+        <v>פטריק סבג Hotel Mogador</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-13</v>
       </c>
       <c r="E2" t="str">
-        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
+        <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
       </c>
       <c r="F2" t="str">
         <v>אלבומים חדשים</v>
@@ -441,19 +441,19 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אוליביה דין The Art of Loving</v>
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-09</v>
       </c>
       <c r="C3" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
+        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E3" t="str">
-        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
+        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
       </c>
       <c r="F3" t="str">
         <v>אלבומים חדשים</v>
@@ -467,19 +467,19 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Geese Getting Killed</v>
+        <v>אוליביה דין The Art of Loving</v>
       </c>
       <c r="B4" t="str">
-        <v>2025-12-29</v>
+        <v>2026-01-04</v>
       </c>
       <c r="C4" t="str">
-        <v>https://yosmusic.com/geese-getting-killed/</v>
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E4" t="str">
-        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
+        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
       </c>
       <c r="F4" t="str">
         <v>אלבומים חדשים</v>
@@ -488,24 +488,30 @@
         <v/>
       </c>
       <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>רוסליה Lux</v>
+        <v>Geese Getting Killed</v>
       </c>
       <c r="B5" t="str">
-        <v>2025-12-25</v>
+        <v>2025-12-29</v>
       </c>
       <c r="C5" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
+        <v>https://yosmusic.com/geese-getting-killed/</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E5" t="str">
-        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
+        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
       </c>
       <c r="F5" t="str">
         <v>אלבומים חדשים</v>
@@ -514,24 +520,30 @@
         <v/>
       </c>
       <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>יאנגבלאד אירוסמית' one more time</v>
+        <v>רוסליה Lux</v>
       </c>
       <c r="B6" t="str">
-        <v>2025-12-17</v>
+        <v>2025-12-25</v>
       </c>
       <c r="C6" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E6" t="str">
-        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
+        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
       </c>
       <c r="F6" t="str">
         <v>אלבומים חדשים</v>
@@ -540,24 +552,30 @@
         <v/>
       </c>
       <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>פינק פלויד Wish You Were Here 50</v>
+        <v>יאנגבלאד אירוסמית' one more time</v>
       </c>
       <c r="B7" t="str">
-        <v>2025-12-14</v>
+        <v>2025-12-17</v>
       </c>
       <c r="C7" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
+        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E7" t="str">
-        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
+        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
       </c>
       <c r="F7" t="str">
         <v>אלבומים חדשים</v>
@@ -566,24 +584,30 @@
         <v/>
       </c>
       <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+        <v>פינק פלויד Wish You Were Here 50</v>
       </c>
       <c r="B8" t="str">
-        <v>2025-12-08</v>
+        <v>2025-12-14</v>
       </c>
       <c r="C8" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E8" t="str">
-        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
+        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
       </c>
       <c r="F8" t="str">
         <v>אלבומים חדשים</v>
@@ -592,24 +616,30 @@
         <v/>
       </c>
       <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>סטריי קידס DO IT (EP)</v>
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
       </c>
       <c r="B9" t="str">
-        <v>2025-12-04</v>
+        <v>2025-12-08</v>
       </c>
       <c r="C9" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
+        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E9" t="str">
-        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
+        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
       </c>
       <c r="F9" t="str">
         <v>אלבומים חדשים</v>
@@ -618,24 +648,30 @@
         <v/>
       </c>
       <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>דויד ברוזה BROZAJAZZ</v>
+        <v>סטריי קידס DO IT (EP)</v>
       </c>
       <c r="B10" t="str">
-        <v>2025-11-30</v>
+        <v>2025-12-04</v>
       </c>
       <c r="C10" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
+        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E10" t="str">
-        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
+        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
       </c>
       <c r="F10" t="str">
         <v>אלבומים חדשים</v>
@@ -644,24 +680,30 @@
         <v/>
       </c>
       <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Five Seconds of Summer – Everyone's A Star</v>
+        <v>דויד ברוזה BROZAJAZZ</v>
       </c>
       <c r="B11" t="str">
-        <v>2025-11-24</v>
+        <v>2025-11-30</v>
       </c>
       <c r="C11" t="str">
-        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E11" t="str">
-        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
+        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
       </c>
       <c r="F11" t="str">
         <v>אלבומים חדשים</v>
@@ -670,24 +712,30 @@
         <v/>
       </c>
       <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>התקווה 6 – ויהי אור</v>
+        <v>Five Seconds of Summer – Everyone's A Star</v>
       </c>
       <c r="B12" t="str">
-        <v>2025-11-20</v>
+        <v>2025-11-24</v>
       </c>
       <c r="C12" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
+        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E12" t="str">
-        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
+        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
       </c>
       <c r="F12" t="str">
         <v>אלבומים חדשים</v>
@@ -696,24 +744,30 @@
         <v/>
       </c>
       <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>פלורנס אנד דה משין Everybody Scream</v>
+        <v>התקווה 6 – ויהי אור</v>
       </c>
       <c r="B13" t="str">
-        <v>2025-11-13</v>
+        <v>2025-11-20</v>
       </c>
       <c r="C13" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
+        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E13" t="str">
-        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
+        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
       </c>
       <c r="F13" t="str">
         <v>אלבומים חדשים</v>
@@ -722,24 +776,30 @@
         <v/>
       </c>
       <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>טיים אימפלה Deadbeat</v>
+        <v>פלורנס אנד דה משין Everybody Scream</v>
       </c>
       <c r="B14" t="str">
-        <v>2025-11-03</v>
+        <v>2025-11-13</v>
       </c>
       <c r="C14" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E14" t="str">
-        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
+        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
       </c>
       <c r="F14" t="str">
         <v>אלבומים חדשים</v>
@@ -748,24 +808,30 @@
         <v/>
       </c>
       <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14" t="str">
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+        <v>טיים אימפלה Deadbeat</v>
       </c>
       <c r="B15" t="str">
-        <v>2025-10-20</v>
+        <v>2025-11-03</v>
       </c>
       <c r="C15" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E15" t="str">
-        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
+        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
       </c>
       <c r="F15" t="str">
         <v>אלבומים חדשים</v>
@@ -774,24 +840,30 @@
         <v/>
       </c>
       <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15" t="str">
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>שלמה גרוניך – תודה אהבה</v>
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
       </c>
       <c r="B16" t="str">
-        <v>2025-10-18</v>
+        <v>2025-10-20</v>
       </c>
       <c r="C16" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
+        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E16" t="str">
-        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
+        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
       </c>
       <c r="F16" t="str">
         <v>אלבומים חדשים</v>
@@ -800,24 +872,30 @@
         <v/>
       </c>
       <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16" t="str">
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>טיילור סוויפט The Life Of A Showgirl</v>
+        <v>שלמה גרוניך – תודה אהבה</v>
       </c>
       <c r="B17" t="str">
-        <v>2025-10-11</v>
+        <v>2025-10-18</v>
       </c>
       <c r="C17" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E17" t="str">
-        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
+        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
       </c>
       <c r="F17" t="str">
         <v>אלבומים חדשים</v>
@@ -826,24 +904,30 @@
         <v/>
       </c>
       <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17" t="str">
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>דוג'ה קאט Vie</v>
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
       </c>
       <c r="B18" t="str">
-        <v>2025-10-04</v>
+        <v>2025-10-11</v>
       </c>
       <c r="C18" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E18" t="str">
-        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
+        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
       </c>
       <c r="F18" t="str">
         <v>אלבומים חדשים</v>
@@ -852,24 +936,30 @@
         <v/>
       </c>
       <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ג'וי קרוקס Juniper</v>
+        <v>דוג'ה קאט Vie</v>
       </c>
       <c r="B19" t="str">
-        <v>2025-10-03</v>
+        <v>2025-10-04</v>
       </c>
       <c r="C19" t="str">
-        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E19" t="str">
-        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
+        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
       </c>
       <c r="F19" t="str">
         <v>אלבומים חדשים</v>
@@ -878,24 +968,30 @@
         <v/>
       </c>
       <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19" t="str">
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ביפי קליירו Futique</v>
+        <v>ג'וי קרוקס Juniper</v>
       </c>
       <c r="B20" t="str">
-        <v>2025-09-30</v>
+        <v>2025-10-03</v>
       </c>
       <c r="C20" t="str">
-        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
+        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E20" t="str">
-        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
+        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
       </c>
       <c r="F20" t="str">
         <v>אלבומים חדשים</v>
@@ -904,24 +1000,30 @@
         <v/>
       </c>
       <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>אד שירן Play</v>
+        <v>ביפי קליירו Futique</v>
       </c>
       <c r="B21" t="str">
-        <v>2025-09-24</v>
+        <v>2025-09-30</v>
       </c>
       <c r="C21" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
+        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E21" t="str">
-        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
+        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
       </c>
       <c r="F21" t="str">
         <v>אלבומים חדשים</v>
@@ -930,24 +1032,30 @@
         <v/>
       </c>
       <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+        <v>אד שירן Play</v>
       </c>
       <c r="B22" t="str">
-        <v>2025-09-21</v>
+        <v>2025-09-24</v>
       </c>
       <c r="C22" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E22" t="str">
-        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
+        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
       </c>
       <c r="F22" t="str">
         <v>אלבומים חדשים</v>
@@ -956,24 +1064,30 @@
         <v/>
       </c>
       <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
+      <c r="J22" t="str">
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>סוויד Antidepressants</v>
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
       </c>
       <c r="B23" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-21</v>
       </c>
       <c r="C23" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E23" t="str">
-        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
+        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
       </c>
       <c r="F23" t="str">
         <v>אלבומים חדשים</v>
@@ -982,24 +1096,30 @@
         <v/>
       </c>
       <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+      <c r="J23" t="str">
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>וולף אליס The Clearing</v>
+        <v>סוויד Antidepressants</v>
       </c>
       <c r="B24" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-12</v>
       </c>
       <c r="C24" t="str">
-        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
+        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E24" t="str">
-        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
+        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
       </c>
       <c r="F24" t="str">
         <v>אלבומים חדשים</v>
@@ -1008,24 +1128,30 @@
         <v/>
       </c>
       <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
+      <c r="J24" t="str">
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+        <v>וולף אליס The Clearing</v>
       </c>
       <c r="B25" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-01</v>
       </c>
       <c r="C25" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
+        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E25" t="str">
-        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
+        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
       </c>
       <c r="F25" t="str">
         <v>אלבומים חדשים</v>
@@ -1034,24 +1160,30 @@
         <v/>
       </c>
       <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="J25" t="str">
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
       </c>
       <c r="B26" t="str">
-        <v>2025-08-24</v>
+        <v>2025-08-29</v>
       </c>
       <c r="C26" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
+        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E26" t="str">
-        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
+        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
       </c>
       <c r="F26" t="str">
         <v>אלבומים חדשים</v>
@@ -1060,24 +1192,30 @@
         <v/>
       </c>
       <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v/>
+      </c>
+      <c r="J26" t="str">
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
       </c>
       <c r="B27" t="str">
-        <v>2025-08-21</v>
+        <v>2025-08-24</v>
       </c>
       <c r="C27" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
+        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E27" t="str">
-        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
+        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
       </c>
       <c r="F27" t="str">
         <v>אלבומים חדשים</v>
@@ -1086,24 +1224,30 @@
         <v/>
       </c>
       <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v/>
+      </c>
+      <c r="J27" t="str">
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>אברהם טל – חי</v>
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
       </c>
       <c r="B28" t="str">
-        <v>2025-08-17</v>
+        <v>2025-08-21</v>
       </c>
       <c r="C28" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E28" t="str">
-        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
+        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
       </c>
       <c r="F28" t="str">
         <v>אלבומים חדשים</v>
@@ -1112,24 +1256,30 @@
         <v/>
       </c>
       <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v/>
+      </c>
+      <c r="J28" t="str">
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>רנה ראפ Bite Me</v>
+        <v>אברהם טל – חי</v>
       </c>
       <c r="B29" t="str">
-        <v>2025-08-12</v>
+        <v>2025-08-17</v>
       </c>
       <c r="C29" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E29" t="str">
-        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
+        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
       </c>
       <c r="F29" t="str">
         <v>אלבומים חדשים</v>
@@ -1138,24 +1288,30 @@
         <v/>
       </c>
       <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v/>
+      </c>
+      <c r="J29" t="str">
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>The K's – Pretty On The Internet</v>
+        <v>רנה ראפ Bite Me</v>
       </c>
       <c r="B30" t="str">
-        <v>2025-08-03</v>
+        <v>2025-08-12</v>
       </c>
       <c r="C30" t="str">
-        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
+        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E30" t="str">
-        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
+        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
       </c>
       <c r="F30" t="str">
         <v>אלבומים חדשים</v>
@@ -1164,24 +1320,30 @@
         <v/>
       </c>
       <c r="H30" t="str">
+        <v/>
+      </c>
+      <c r="I30" t="str">
+        <v/>
+      </c>
+      <c r="J30" t="str">
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>פליטווד מק Fifty Years – Don’t Stop</v>
+        <v>The K's – Pretty On The Internet</v>
       </c>
       <c r="B31" t="str">
-        <v>2025-07-30</v>
+        <v>2025-08-03</v>
       </c>
       <c r="C31" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%99%d7%98%d7%95%d7%95%d7%93-%d7%9e%d7%a7-fifty-years-dont-stop/</v>
+        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="E31" t="str">
-        <v>פליטווד מק (Fleetwood Mac) חוגגים חצי מאה של מוזיקה עם אוסף חדש בן 50 שירים, שמתפרש על כל הקריירה של הלהקה, מימיה הראשונים בסגנון בלוז, ועד להצלחתה העולמית כאחת מלהקות הגדולות בהיסטוריה של הרוק. פליטווד מק הם לא רק להקה</v>
+        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
       </c>
       <c r="F31" t="str">
         <v>אלבומים חדשים</v>
@@ -1190,38 +1352,82 @@
         <v/>
       </c>
       <c r="H31" t="str">
+        <v/>
+      </c>
+      <c r="I31" t="str">
+        <v/>
+      </c>
+      <c r="J31" t="str">
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
+        <v>פליטווד מק Fifty Years – Don’t Stop</v>
+      </c>
+      <c r="B32" t="str">
+        <v>2025-07-30</v>
+      </c>
+      <c r="C32" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%99%d7%98%d7%95%d7%95%d7%93-%d7%9e%d7%a7-fifty-years-dont-stop/</v>
+      </c>
+      <c r="D32" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E32" t="str">
+        <v>פליטווד מק (Fleetwood Mac) חוגגים חצי מאה של מוזיקה עם אוסף חדש בן 50 שירים, שמתפרש על כל הקריירה של הלהקה, מימיה הראשונים בסגנון בלוז, ועד להצלחתה העולמית כאחת מלהקות הגדולות בהיסטוריה של הרוק. פליטווד מק הם לא רק להקה</v>
+      </c>
+      <c r="F32" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <v/>
+      </c>
+      <c r="I32" t="str">
+        <v/>
+      </c>
+      <c r="J32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
         <v>Wet Leg Moisturizer</v>
       </c>
-      <c r="B32" t="str">
+      <c r="B33" t="str">
         <v>2025-07-25</v>
       </c>
-      <c r="C32" t="str">
+      <c r="C33" t="str">
         <v>https://yosmusic.com/wet-leg-moisturizer/</v>
       </c>
-      <c r="D32" t="str">
-        <v>2026-01-08</v>
-      </c>
-      <c r="E32" t="str">
+      <c r="D33" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E33" t="str">
         <v>להקת Wet Leg לא הוציאה קרם לחות (Moisturizer) כמוצר טיפוח. במקום זאת, "Moisturizer" הוא שמו של האלבום השני והחדש שלהם. במרכז –  צמד אינדי-רוק המורכב מהחברות ריין טיסדייל והסטר צ'יימברס. אלבום הבכורה הנושא את שמה, הגיע למקום הראשון במצעד האלבומים</v>
       </c>
-      <c r="F32" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="G32" t="str">
-        <v/>
-      </c>
-      <c r="H32" t="str">
+      <c r="F33" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
+      <c r="I33" t="str">
+        <v/>
+      </c>
+      <c r="J33" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H32"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J33"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:N63"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -416,7 +416,22 @@
         <v>תיאור</v>
       </c>
       <c r="F1" t="str">
+        <v>משך</v>
+      </c>
+      <c r="G1" t="str">
+        <v>ערוץ</v>
+      </c>
+      <c r="H1" t="str">
         <v>תגית</v>
+      </c>
+      <c r="I1" t="str">
+        <v>קישור אמן</v>
+      </c>
+      <c r="J1" t="str">
+        <v>קישור אלבום</v>
+      </c>
+      <c r="K1" t="str">
+        <v>שיר - אמן</v>
       </c>
     </row>
     <row r="2">
@@ -430,13 +445,28 @@
         <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-13</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E2" t="str">
         <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
       </c>
       <c r="F2" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v>פטריק סבג Hotel Mogador</v>
       </c>
     </row>
     <row r="3">
@@ -450,19 +480,28 @@
         <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E3" t="str">
         <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
       </c>
       <c r="F3" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
       </c>
     </row>
     <row r="4">
@@ -476,25 +515,28 @@
         <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E4" t="str">
         <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
       </c>
       <c r="F4" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I4" t="str">
         <v/>
       </c>
       <c r="J4" t="str">
         <v/>
+      </c>
+      <c r="K4" t="str">
+        <v>אוליביה דין The Art of Loving</v>
       </c>
     </row>
     <row r="5">
@@ -508,25 +550,28 @@
         <v>https://yosmusic.com/geese-getting-killed/</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E5" t="str">
         <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
       </c>
       <c r="F5" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I5" t="str">
         <v/>
       </c>
       <c r="J5" t="str">
         <v/>
+      </c>
+      <c r="K5" t="str">
+        <v>Geese Getting Killed</v>
       </c>
     </row>
     <row r="6">
@@ -540,25 +585,28 @@
         <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E6" t="str">
         <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
       </c>
       <c r="F6" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I6" t="str">
         <v/>
       </c>
       <c r="J6" t="str">
         <v/>
+      </c>
+      <c r="K6" t="str">
+        <v>רוסליה Lux</v>
       </c>
     </row>
     <row r="7">
@@ -572,25 +620,28 @@
         <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E7" t="str">
         <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
       </c>
       <c r="F7" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I7" t="str">
         <v/>
       </c>
       <c r="J7" t="str">
         <v/>
+      </c>
+      <c r="K7" t="str">
+        <v>יאנגבלאד אירוסמית' one more time</v>
       </c>
     </row>
     <row r="8">
@@ -604,25 +655,28 @@
         <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E8" t="str">
         <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
       </c>
       <c r="F8" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I8" t="str">
         <v/>
       </c>
       <c r="J8" t="str">
         <v/>
+      </c>
+      <c r="K8" t="str">
+        <v>פינק פלויד Wish You Were Here 50</v>
       </c>
     </row>
     <row r="9">
@@ -636,25 +690,28 @@
         <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E9" t="str">
         <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
       </c>
       <c r="F9" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I9" t="str">
         <v/>
       </c>
       <c r="J9" t="str">
         <v/>
+      </c>
+      <c r="K9" t="str">
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
       </c>
     </row>
     <row r="10">
@@ -668,25 +725,28 @@
         <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E10" t="str">
         <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
       </c>
       <c r="F10" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I10" t="str">
         <v/>
       </c>
       <c r="J10" t="str">
         <v/>
+      </c>
+      <c r="K10" t="str">
+        <v>סטריי קידס DO IT (EP)</v>
       </c>
     </row>
     <row r="11">
@@ -700,25 +760,28 @@
         <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E11" t="str">
         <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
       </c>
       <c r="F11" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I11" t="str">
         <v/>
       </c>
       <c r="J11" t="str">
         <v/>
+      </c>
+      <c r="K11" t="str">
+        <v>דויד ברוזה BROZAJAZZ</v>
       </c>
     </row>
     <row r="12">
@@ -732,25 +795,28 @@
         <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E12" t="str">
         <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
       </c>
       <c r="F12" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I12" t="str">
         <v/>
       </c>
       <c r="J12" t="str">
         <v/>
+      </c>
+      <c r="K12" t="str">
+        <v>Five Seconds of Summer – Everyone's A Star</v>
       </c>
     </row>
     <row r="13">
@@ -764,25 +830,28 @@
         <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E13" t="str">
         <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
       </c>
       <c r="F13" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I13" t="str">
         <v/>
       </c>
       <c r="J13" t="str">
         <v/>
+      </c>
+      <c r="K13" t="str">
+        <v>התקווה 6 – ויהי אור</v>
       </c>
     </row>
     <row r="14">
@@ -796,25 +865,28 @@
         <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E14" t="str">
         <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
       </c>
       <c r="F14" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I14" t="str">
         <v/>
       </c>
       <c r="J14" t="str">
         <v/>
+      </c>
+      <c r="K14" t="str">
+        <v>פלורנס אנד דה משין Everybody Scream</v>
       </c>
     </row>
     <row r="15">
@@ -828,25 +900,28 @@
         <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E15" t="str">
         <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
       </c>
       <c r="F15" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I15" t="str">
         <v/>
       </c>
       <c r="J15" t="str">
         <v/>
+      </c>
+      <c r="K15" t="str">
+        <v>טיים אימפלה Deadbeat</v>
       </c>
     </row>
     <row r="16">
@@ -860,25 +935,28 @@
         <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E16" t="str">
         <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
       </c>
       <c r="F16" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I16" t="str">
         <v/>
       </c>
       <c r="J16" t="str">
         <v/>
+      </c>
+      <c r="K16" t="str">
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
       </c>
     </row>
     <row r="17">
@@ -892,25 +970,28 @@
         <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E17" t="str">
         <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
       </c>
       <c r="F17" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I17" t="str">
         <v/>
       </c>
       <c r="J17" t="str">
         <v/>
+      </c>
+      <c r="K17" t="str">
+        <v>שלמה גרוניך – תודה אהבה</v>
       </c>
     </row>
     <row r="18">
@@ -924,25 +1005,28 @@
         <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E18" t="str">
         <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
       </c>
       <c r="F18" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I18" t="str">
         <v/>
       </c>
       <c r="J18" t="str">
         <v/>
+      </c>
+      <c r="K18" t="str">
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
       </c>
     </row>
     <row r="19">
@@ -956,25 +1040,28 @@
         <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E19" t="str">
         <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
       </c>
       <c r="F19" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I19" t="str">
         <v/>
       </c>
       <c r="J19" t="str">
         <v/>
+      </c>
+      <c r="K19" t="str">
+        <v>דוג'ה קאט Vie</v>
       </c>
     </row>
     <row r="20">
@@ -988,25 +1075,28 @@
         <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E20" t="str">
         <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
       </c>
       <c r="F20" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I20" t="str">
         <v/>
       </c>
       <c r="J20" t="str">
         <v/>
+      </c>
+      <c r="K20" t="str">
+        <v>ג'וי קרוקס Juniper</v>
       </c>
     </row>
     <row r="21">
@@ -1020,25 +1110,28 @@
         <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E21" t="str">
         <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
       </c>
       <c r="F21" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I21" t="str">
         <v/>
       </c>
       <c r="J21" t="str">
         <v/>
+      </c>
+      <c r="K21" t="str">
+        <v>ביפי קליירו Futique</v>
       </c>
     </row>
     <row r="22">
@@ -1052,25 +1145,28 @@
         <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E22" t="str">
         <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
       </c>
       <c r="F22" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I22" t="str">
         <v/>
       </c>
       <c r="J22" t="str">
         <v/>
+      </c>
+      <c r="K22" t="str">
+        <v>אד שירן Play</v>
       </c>
     </row>
     <row r="23">
@@ -1084,25 +1180,28 @@
         <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E23" t="str">
         <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
       </c>
       <c r="F23" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I23" t="str">
         <v/>
       </c>
       <c r="J23" t="str">
         <v/>
+      </c>
+      <c r="K23" t="str">
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
       </c>
     </row>
     <row r="24">
@@ -1116,25 +1215,28 @@
         <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E24" t="str">
         <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
       </c>
       <c r="F24" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I24" t="str">
         <v/>
       </c>
       <c r="J24" t="str">
         <v/>
+      </c>
+      <c r="K24" t="str">
+        <v>סוויד Antidepressants</v>
       </c>
     </row>
     <row r="25">
@@ -1148,25 +1250,28 @@
         <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E25" t="str">
         <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
       </c>
       <c r="F25" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I25" t="str">
         <v/>
       </c>
       <c r="J25" t="str">
         <v/>
+      </c>
+      <c r="K25" t="str">
+        <v>וולף אליס The Clearing</v>
       </c>
     </row>
     <row r="26">
@@ -1180,25 +1285,28 @@
         <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E26" t="str">
         <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
       </c>
       <c r="F26" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I26" t="str">
         <v/>
       </c>
       <c r="J26" t="str">
         <v/>
+      </c>
+      <c r="K26" t="str">
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
       </c>
     </row>
     <row r="27">
@@ -1212,25 +1320,28 @@
         <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E27" t="str">
         <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
       </c>
       <c r="F27" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I27" t="str">
         <v/>
       </c>
       <c r="J27" t="str">
         <v/>
+      </c>
+      <c r="K27" t="str">
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
       </c>
     </row>
     <row r="28">
@@ -1244,25 +1355,28 @@
         <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E28" t="str">
         <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
       </c>
       <c r="F28" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I28" t="str">
         <v/>
       </c>
       <c r="J28" t="str">
         <v/>
+      </c>
+      <c r="K28" t="str">
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
       </c>
     </row>
     <row r="29">
@@ -1276,25 +1390,28 @@
         <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E29" t="str">
         <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
       </c>
       <c r="F29" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I29" t="str">
         <v/>
       </c>
       <c r="J29" t="str">
         <v/>
+      </c>
+      <c r="K29" t="str">
+        <v>אברהם טל – חי</v>
       </c>
     </row>
     <row r="30">
@@ -1308,25 +1425,28 @@
         <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E30" t="str">
         <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
       </c>
       <c r="F30" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I30" t="str">
         <v/>
       </c>
       <c r="J30" t="str">
         <v/>
+      </c>
+      <c r="K30" t="str">
+        <v>רנה ראפ Bite Me</v>
       </c>
     </row>
     <row r="31">
@@ -1340,42 +1460,45 @@
         <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E31" t="str">
         <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
       </c>
       <c r="F31" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I31" t="str">
         <v/>
       </c>
       <c r="J31" t="str">
         <v/>
+      </c>
+      <c r="K31" t="str">
+        <v>The K's – Pretty On The Internet</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>פליטווד מק Fifty Years – Don’t Stop</v>
+        <v>פטריק סבג Hotel Mogador</v>
       </c>
       <c r="B32" t="str">
-        <v>2025-07-30</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C32" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%99%d7%98%d7%95%d7%95%d7%93-%d7%9e%d7%a7-fifty-years-dont-stop/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-13</v>
       </c>
       <c r="E32" t="str">
-        <v>פליטווד מק (Fleetwood Mac) חוגגים חצי מאה של מוזיקה עם אוסף חדש בן 50 שירים, שמתפרש על כל הקריירה של הלהקה, מימיה הראשונים בסגנון בלוז, ועד להצלחתה העולמית כאחת מלהקות הגדולות בהיסטוריה של הרוק. פליטווד מק הם לא רק להקה</v>
+        <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
       </c>
       <c r="F32" t="str">
         <v>אלבומים חדשים</v>
@@ -1395,39 +1518,1365 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
+      </c>
+      <c r="B33" t="str">
+        <v>2026-01-09</v>
+      </c>
+      <c r="C33" t="str">
+        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
+      </c>
+      <c r="D33" t="str">
+        <v>2026-01-09</v>
+      </c>
+      <c r="E33" t="str">
+        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
+      </c>
+      <c r="F33" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
+      <c r="I33" t="str">
+        <v/>
+      </c>
+      <c r="J33" t="str">
+        <v/>
+      </c>
+      <c r="K33" t="str">
+        <v/>
+      </c>
+      <c r="L33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>אוליביה דין The Art of Loving</v>
+      </c>
+      <c r="B34" t="str">
+        <v>2026-01-04</v>
+      </c>
+      <c r="C34" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
+      </c>
+      <c r="D34" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E34" t="str">
+        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
+      </c>
+      <c r="F34" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+      <c r="I34" t="str">
+        <v/>
+      </c>
+      <c r="J34" t="str">
+        <v/>
+      </c>
+      <c r="K34" t="str">
+        <v/>
+      </c>
+      <c r="L34" t="str">
+        <v/>
+      </c>
+      <c r="M34" t="str">
+        <v/>
+      </c>
+      <c r="N34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Geese Getting Killed</v>
+      </c>
+      <c r="B35" t="str">
+        <v>2025-12-29</v>
+      </c>
+      <c r="C35" t="str">
+        <v>https://yosmusic.com/geese-getting-killed/</v>
+      </c>
+      <c r="D35" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E35" t="str">
+        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
+      </c>
+      <c r="F35" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+      <c r="H35" t="str">
+        <v/>
+      </c>
+      <c r="I35" t="str">
+        <v/>
+      </c>
+      <c r="J35" t="str">
+        <v/>
+      </c>
+      <c r="K35" t="str">
+        <v/>
+      </c>
+      <c r="L35" t="str">
+        <v/>
+      </c>
+      <c r="M35" t="str">
+        <v/>
+      </c>
+      <c r="N35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>רוסליה Lux</v>
+      </c>
+      <c r="B36" t="str">
+        <v>2025-12-25</v>
+      </c>
+      <c r="C36" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
+      </c>
+      <c r="D36" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E36" t="str">
+        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
+      </c>
+      <c r="F36" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
+      <c r="I36" t="str">
+        <v/>
+      </c>
+      <c r="J36" t="str">
+        <v/>
+      </c>
+      <c r="K36" t="str">
+        <v/>
+      </c>
+      <c r="L36" t="str">
+        <v/>
+      </c>
+      <c r="M36" t="str">
+        <v/>
+      </c>
+      <c r="N36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>יאנגבלאד אירוסמית' one more time</v>
+      </c>
+      <c r="B37" t="str">
+        <v>2025-12-17</v>
+      </c>
+      <c r="C37" t="str">
+        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
+      </c>
+      <c r="D37" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E37" t="str">
+        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
+      </c>
+      <c r="F37" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+      <c r="I37" t="str">
+        <v/>
+      </c>
+      <c r="J37" t="str">
+        <v/>
+      </c>
+      <c r="K37" t="str">
+        <v/>
+      </c>
+      <c r="L37" t="str">
+        <v/>
+      </c>
+      <c r="M37" t="str">
+        <v/>
+      </c>
+      <c r="N37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>פינק פלויד Wish You Were Here 50</v>
+      </c>
+      <c r="B38" t="str">
+        <v>2025-12-14</v>
+      </c>
+      <c r="C38" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
+      </c>
+      <c r="D38" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E38" t="str">
+        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
+      </c>
+      <c r="F38" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+      <c r="I38" t="str">
+        <v/>
+      </c>
+      <c r="J38" t="str">
+        <v/>
+      </c>
+      <c r="K38" t="str">
+        <v/>
+      </c>
+      <c r="L38" t="str">
+        <v/>
+      </c>
+      <c r="M38" t="str">
+        <v/>
+      </c>
+      <c r="N38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+      </c>
+      <c r="B39" t="str">
+        <v>2025-12-08</v>
+      </c>
+      <c r="C39" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
+      </c>
+      <c r="D39" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E39" t="str">
+        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
+      </c>
+      <c r="F39" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+      <c r="I39" t="str">
+        <v/>
+      </c>
+      <c r="J39" t="str">
+        <v/>
+      </c>
+      <c r="K39" t="str">
+        <v/>
+      </c>
+      <c r="L39" t="str">
+        <v/>
+      </c>
+      <c r="M39" t="str">
+        <v/>
+      </c>
+      <c r="N39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>סטריי קידס DO IT (EP)</v>
+      </c>
+      <c r="B40" t="str">
+        <v>2025-12-04</v>
+      </c>
+      <c r="C40" t="str">
+        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
+      </c>
+      <c r="D40" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E40" t="str">
+        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
+      </c>
+      <c r="F40" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
+      <c r="I40" t="str">
+        <v/>
+      </c>
+      <c r="J40" t="str">
+        <v/>
+      </c>
+      <c r="K40" t="str">
+        <v/>
+      </c>
+      <c r="L40" t="str">
+        <v/>
+      </c>
+      <c r="M40" t="str">
+        <v/>
+      </c>
+      <c r="N40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>דויד ברוזה BROZAJAZZ</v>
+      </c>
+      <c r="B41" t="str">
+        <v>2025-11-30</v>
+      </c>
+      <c r="C41" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
+      </c>
+      <c r="D41" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E41" t="str">
+        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
+      </c>
+      <c r="F41" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+      <c r="I41" t="str">
+        <v/>
+      </c>
+      <c r="J41" t="str">
+        <v/>
+      </c>
+      <c r="K41" t="str">
+        <v/>
+      </c>
+      <c r="L41" t="str">
+        <v/>
+      </c>
+      <c r="M41" t="str">
+        <v/>
+      </c>
+      <c r="N41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>Five Seconds of Summer – Everyone's A Star</v>
+      </c>
+      <c r="B42" t="str">
+        <v>2025-11-24</v>
+      </c>
+      <c r="C42" t="str">
+        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
+      </c>
+      <c r="D42" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E42" t="str">
+        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
+      </c>
+      <c r="F42" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+      <c r="I42" t="str">
+        <v/>
+      </c>
+      <c r="J42" t="str">
+        <v/>
+      </c>
+      <c r="K42" t="str">
+        <v/>
+      </c>
+      <c r="L42" t="str">
+        <v/>
+      </c>
+      <c r="M42" t="str">
+        <v/>
+      </c>
+      <c r="N42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>התקווה 6 – ויהי אור</v>
+      </c>
+      <c r="B43" t="str">
+        <v>2025-11-20</v>
+      </c>
+      <c r="C43" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
+      </c>
+      <c r="D43" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E43" t="str">
+        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
+      </c>
+      <c r="F43" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="str">
+        <v/>
+      </c>
+      <c r="J43" t="str">
+        <v/>
+      </c>
+      <c r="K43" t="str">
+        <v/>
+      </c>
+      <c r="L43" t="str">
+        <v/>
+      </c>
+      <c r="M43" t="str">
+        <v/>
+      </c>
+      <c r="N43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>פלורנס אנד דה משין Everybody Scream</v>
+      </c>
+      <c r="B44" t="str">
+        <v>2025-11-13</v>
+      </c>
+      <c r="C44" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
+      </c>
+      <c r="D44" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E44" t="str">
+        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
+      </c>
+      <c r="F44" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+      <c r="I44" t="str">
+        <v/>
+      </c>
+      <c r="J44" t="str">
+        <v/>
+      </c>
+      <c r="K44" t="str">
+        <v/>
+      </c>
+      <c r="L44" t="str">
+        <v/>
+      </c>
+      <c r="M44" t="str">
+        <v/>
+      </c>
+      <c r="N44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>טיים אימפלה Deadbeat</v>
+      </c>
+      <c r="B45" t="str">
+        <v>2025-11-03</v>
+      </c>
+      <c r="C45" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
+      </c>
+      <c r="D45" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E45" t="str">
+        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
+      </c>
+      <c r="F45" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
+      <c r="I45" t="str">
+        <v/>
+      </c>
+      <c r="J45" t="str">
+        <v/>
+      </c>
+      <c r="K45" t="str">
+        <v/>
+      </c>
+      <c r="L45" t="str">
+        <v/>
+      </c>
+      <c r="M45" t="str">
+        <v/>
+      </c>
+      <c r="N45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+      </c>
+      <c r="B46" t="str">
+        <v>2025-10-20</v>
+      </c>
+      <c r="C46" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
+      </c>
+      <c r="D46" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E46" t="str">
+        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
+      </c>
+      <c r="F46" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
+      <c r="I46" t="str">
+        <v/>
+      </c>
+      <c r="J46" t="str">
+        <v/>
+      </c>
+      <c r="K46" t="str">
+        <v/>
+      </c>
+      <c r="L46" t="str">
+        <v/>
+      </c>
+      <c r="M46" t="str">
+        <v/>
+      </c>
+      <c r="N46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>שלמה גרוניך – תודה אהבה</v>
+      </c>
+      <c r="B47" t="str">
+        <v>2025-10-18</v>
+      </c>
+      <c r="C47" t="str">
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
+      </c>
+      <c r="D47" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E47" t="str">
+        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
+      </c>
+      <c r="F47" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
+      <c r="H47" t="str">
+        <v/>
+      </c>
+      <c r="I47" t="str">
+        <v/>
+      </c>
+      <c r="J47" t="str">
+        <v/>
+      </c>
+      <c r="K47" t="str">
+        <v/>
+      </c>
+      <c r="L47" t="str">
+        <v/>
+      </c>
+      <c r="M47" t="str">
+        <v/>
+      </c>
+      <c r="N47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
+      </c>
+      <c r="B48" t="str">
+        <v>2025-10-11</v>
+      </c>
+      <c r="C48" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
+      </c>
+      <c r="D48" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E48" t="str">
+        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
+      </c>
+      <c r="F48" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
+      <c r="H48" t="str">
+        <v/>
+      </c>
+      <c r="I48" t="str">
+        <v/>
+      </c>
+      <c r="J48" t="str">
+        <v/>
+      </c>
+      <c r="K48" t="str">
+        <v/>
+      </c>
+      <c r="L48" t="str">
+        <v/>
+      </c>
+      <c r="M48" t="str">
+        <v/>
+      </c>
+      <c r="N48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>דוג'ה קאט Vie</v>
+      </c>
+      <c r="B49" t="str">
+        <v>2025-10-04</v>
+      </c>
+      <c r="C49" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
+      </c>
+      <c r="D49" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E49" t="str">
+        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
+      </c>
+      <c r="F49" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
+      <c r="H49" t="str">
+        <v/>
+      </c>
+      <c r="I49" t="str">
+        <v/>
+      </c>
+      <c r="J49" t="str">
+        <v/>
+      </c>
+      <c r="K49" t="str">
+        <v/>
+      </c>
+      <c r="L49" t="str">
+        <v/>
+      </c>
+      <c r="M49" t="str">
+        <v/>
+      </c>
+      <c r="N49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>ג'וי קרוקס Juniper</v>
+      </c>
+      <c r="B50" t="str">
+        <v>2025-10-03</v>
+      </c>
+      <c r="C50" t="str">
+        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
+      </c>
+      <c r="D50" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E50" t="str">
+        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
+      </c>
+      <c r="F50" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G50" t="str">
+        <v/>
+      </c>
+      <c r="H50" t="str">
+        <v/>
+      </c>
+      <c r="I50" t="str">
+        <v/>
+      </c>
+      <c r="J50" t="str">
+        <v/>
+      </c>
+      <c r="K50" t="str">
+        <v/>
+      </c>
+      <c r="L50" t="str">
+        <v/>
+      </c>
+      <c r="M50" t="str">
+        <v/>
+      </c>
+      <c r="N50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>ביפי קליירו Futique</v>
+      </c>
+      <c r="B51" t="str">
+        <v>2025-09-30</v>
+      </c>
+      <c r="C51" t="str">
+        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
+      </c>
+      <c r="D51" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E51" t="str">
+        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
+      </c>
+      <c r="F51" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
+      <c r="H51" t="str">
+        <v/>
+      </c>
+      <c r="I51" t="str">
+        <v/>
+      </c>
+      <c r="J51" t="str">
+        <v/>
+      </c>
+      <c r="K51" t="str">
+        <v/>
+      </c>
+      <c r="L51" t="str">
+        <v/>
+      </c>
+      <c r="M51" t="str">
+        <v/>
+      </c>
+      <c r="N51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>אד שירן Play</v>
+      </c>
+      <c r="B52" t="str">
+        <v>2025-09-24</v>
+      </c>
+      <c r="C52" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
+      </c>
+      <c r="D52" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E52" t="str">
+        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
+      </c>
+      <c r="F52" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G52" t="str">
+        <v/>
+      </c>
+      <c r="H52" t="str">
+        <v/>
+      </c>
+      <c r="I52" t="str">
+        <v/>
+      </c>
+      <c r="J52" t="str">
+        <v/>
+      </c>
+      <c r="K52" t="str">
+        <v/>
+      </c>
+      <c r="L52" t="str">
+        <v/>
+      </c>
+      <c r="M52" t="str">
+        <v/>
+      </c>
+      <c r="N52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+      </c>
+      <c r="B53" t="str">
+        <v>2025-09-21</v>
+      </c>
+      <c r="C53" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
+      </c>
+      <c r="D53" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E53" t="str">
+        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
+      </c>
+      <c r="F53" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G53" t="str">
+        <v/>
+      </c>
+      <c r="H53" t="str">
+        <v/>
+      </c>
+      <c r="I53" t="str">
+        <v/>
+      </c>
+      <c r="J53" t="str">
+        <v/>
+      </c>
+      <c r="K53" t="str">
+        <v/>
+      </c>
+      <c r="L53" t="str">
+        <v/>
+      </c>
+      <c r="M53" t="str">
+        <v/>
+      </c>
+      <c r="N53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>סוויד Antidepressants</v>
+      </c>
+      <c r="B54" t="str">
+        <v>2025-09-12</v>
+      </c>
+      <c r="C54" t="str">
+        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
+      </c>
+      <c r="D54" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E54" t="str">
+        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
+      </c>
+      <c r="F54" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G54" t="str">
+        <v/>
+      </c>
+      <c r="H54" t="str">
+        <v/>
+      </c>
+      <c r="I54" t="str">
+        <v/>
+      </c>
+      <c r="J54" t="str">
+        <v/>
+      </c>
+      <c r="K54" t="str">
+        <v/>
+      </c>
+      <c r="L54" t="str">
+        <v/>
+      </c>
+      <c r="M54" t="str">
+        <v/>
+      </c>
+      <c r="N54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>וולף אליס The Clearing</v>
+      </c>
+      <c r="B55" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="C55" t="str">
+        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
+      </c>
+      <c r="D55" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E55" t="str">
+        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
+      </c>
+      <c r="F55" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G55" t="str">
+        <v/>
+      </c>
+      <c r="H55" t="str">
+        <v/>
+      </c>
+      <c r="I55" t="str">
+        <v/>
+      </c>
+      <c r="J55" t="str">
+        <v/>
+      </c>
+      <c r="K55" t="str">
+        <v/>
+      </c>
+      <c r="L55" t="str">
+        <v/>
+      </c>
+      <c r="M55" t="str">
+        <v/>
+      </c>
+      <c r="N55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+      </c>
+      <c r="B56" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="C56" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
+      </c>
+      <c r="D56" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E56" t="str">
+        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
+      </c>
+      <c r="F56" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G56" t="str">
+        <v/>
+      </c>
+      <c r="H56" t="str">
+        <v/>
+      </c>
+      <c r="I56" t="str">
+        <v/>
+      </c>
+      <c r="J56" t="str">
+        <v/>
+      </c>
+      <c r="K56" t="str">
+        <v/>
+      </c>
+      <c r="L56" t="str">
+        <v/>
+      </c>
+      <c r="M56" t="str">
+        <v/>
+      </c>
+      <c r="N56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+      </c>
+      <c r="B57" t="str">
+        <v>2025-08-24</v>
+      </c>
+      <c r="C57" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
+      </c>
+      <c r="D57" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E57" t="str">
+        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
+      </c>
+      <c r="F57" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G57" t="str">
+        <v/>
+      </c>
+      <c r="H57" t="str">
+        <v/>
+      </c>
+      <c r="I57" t="str">
+        <v/>
+      </c>
+      <c r="J57" t="str">
+        <v/>
+      </c>
+      <c r="K57" t="str">
+        <v/>
+      </c>
+      <c r="L57" t="str">
+        <v/>
+      </c>
+      <c r="M57" t="str">
+        <v/>
+      </c>
+      <c r="N57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+      </c>
+      <c r="B58" t="str">
+        <v>2025-08-21</v>
+      </c>
+      <c r="C58" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
+      </c>
+      <c r="D58" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E58" t="str">
+        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
+      </c>
+      <c r="F58" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+      <c r="H58" t="str">
+        <v/>
+      </c>
+      <c r="I58" t="str">
+        <v/>
+      </c>
+      <c r="J58" t="str">
+        <v/>
+      </c>
+      <c r="K58" t="str">
+        <v/>
+      </c>
+      <c r="L58" t="str">
+        <v/>
+      </c>
+      <c r="M58" t="str">
+        <v/>
+      </c>
+      <c r="N58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>אברהם טל – חי</v>
+      </c>
+      <c r="B59" t="str">
+        <v>2025-08-17</v>
+      </c>
+      <c r="C59" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
+      </c>
+      <c r="D59" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E59" t="str">
+        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
+      </c>
+      <c r="F59" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G59" t="str">
+        <v/>
+      </c>
+      <c r="H59" t="str">
+        <v/>
+      </c>
+      <c r="I59" t="str">
+        <v/>
+      </c>
+      <c r="J59" t="str">
+        <v/>
+      </c>
+      <c r="K59" t="str">
+        <v/>
+      </c>
+      <c r="L59" t="str">
+        <v/>
+      </c>
+      <c r="M59" t="str">
+        <v/>
+      </c>
+      <c r="N59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>רנה ראפ Bite Me</v>
+      </c>
+      <c r="B60" t="str">
+        <v>2025-08-12</v>
+      </c>
+      <c r="C60" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
+      </c>
+      <c r="D60" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E60" t="str">
+        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
+      </c>
+      <c r="F60" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G60" t="str">
+        <v/>
+      </c>
+      <c r="H60" t="str">
+        <v/>
+      </c>
+      <c r="I60" t="str">
+        <v/>
+      </c>
+      <c r="J60" t="str">
+        <v/>
+      </c>
+      <c r="K60" t="str">
+        <v/>
+      </c>
+      <c r="L60" t="str">
+        <v/>
+      </c>
+      <c r="M60" t="str">
+        <v/>
+      </c>
+      <c r="N60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>The K's – Pretty On The Internet</v>
+      </c>
+      <c r="B61" t="str">
+        <v>2025-08-03</v>
+      </c>
+      <c r="C61" t="str">
+        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
+      </c>
+      <c r="D61" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E61" t="str">
+        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
+      </c>
+      <c r="F61" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G61" t="str">
+        <v/>
+      </c>
+      <c r="H61" t="str">
+        <v/>
+      </c>
+      <c r="I61" t="str">
+        <v/>
+      </c>
+      <c r="J61" t="str">
+        <v/>
+      </c>
+      <c r="K61" t="str">
+        <v/>
+      </c>
+      <c r="L61" t="str">
+        <v/>
+      </c>
+      <c r="M61" t="str">
+        <v/>
+      </c>
+      <c r="N61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>פליטווד מק Fifty Years – Don’t Stop</v>
+      </c>
+      <c r="B62" t="str">
+        <v>2025-07-30</v>
+      </c>
+      <c r="C62" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%99%d7%98%d7%95%d7%95%d7%93-%d7%9e%d7%a7-fifty-years-dont-stop/</v>
+      </c>
+      <c r="D62" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E62" t="str">
+        <v>פליטווד מק (Fleetwood Mac) חוגגים חצי מאה של מוזיקה עם אוסף חדש בן 50 שירים, שמתפרש על כל הקריירה של הלהקה, מימיה הראשונים בסגנון בלוז, ועד להצלחתה העולמית כאחת מלהקות הגדולות בהיסטוריה של הרוק. פליטווד מק הם לא רק להקה</v>
+      </c>
+      <c r="F62" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G62" t="str">
+        <v/>
+      </c>
+      <c r="H62" t="str">
+        <v/>
+      </c>
+      <c r="I62" t="str">
+        <v/>
+      </c>
+      <c r="J62" t="str">
+        <v/>
+      </c>
+      <c r="K62" t="str">
+        <v/>
+      </c>
+      <c r="L62" t="str">
+        <v/>
+      </c>
+      <c r="M62" t="str">
+        <v/>
+      </c>
+      <c r="N62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
         <v>Wet Leg Moisturizer</v>
       </c>
-      <c r="B33" t="str">
+      <c r="B63" t="str">
         <v>2025-07-25</v>
       </c>
-      <c r="C33" t="str">
+      <c r="C63" t="str">
         <v>https://yosmusic.com/wet-leg-moisturizer/</v>
       </c>
-      <c r="D33" t="str">
-        <v>2026-01-08</v>
-      </c>
-      <c r="E33" t="str">
+      <c r="D63" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E63" t="str">
         <v>להקת Wet Leg לא הוציאה קרם לחות (Moisturizer) כמוצר טיפוח. במקום זאת, "Moisturizer" הוא שמו של האלבום השני והחדש שלהם. במרכז –  צמד אינדי-רוק המורכב מהחברות ריין טיסדייל והסטר צ'יימברס. אלבום הבכורה הנושא את שמה, הגיע למקום הראשון במצעד האלבומים</v>
       </c>
-      <c r="F33" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="G33" t="str">
-        <v/>
-      </c>
-      <c r="H33" t="str">
-        <v/>
-      </c>
-      <c r="I33" t="str">
-        <v/>
-      </c>
-      <c r="J33" t="str">
+      <c r="F63" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G63" t="str">
+        <v/>
+      </c>
+      <c r="H63" t="str">
+        <v/>
+      </c>
+      <c r="I63" t="str">
+        <v/>
+      </c>
+      <c r="J63" t="str">
+        <v/>
+      </c>
+      <c r="K63" t="str">
+        <v/>
+      </c>
+      <c r="L63" t="str">
+        <v/>
+      </c>
+      <c r="M63" t="str">
+        <v/>
+      </c>
+      <c r="N63" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J33"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N63"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N63"/>
+  <dimension ref="A1:R93"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1495,24 +1495,39 @@
         <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-01-13</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E32" t="str">
         <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
       </c>
       <c r="F32" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I32" t="str">
         <v/>
       </c>
       <c r="J32" t="str">
+        <v/>
+      </c>
+      <c r="K32" t="str">
+        <v>פטריק סבג Hotel Mogador</v>
+      </c>
+      <c r="L32" t="str">
+        <v/>
+      </c>
+      <c r="M32" t="str">
+        <v/>
+      </c>
+      <c r="N32" t="str">
+        <v/>
+      </c>
+      <c r="O32" t="str">
         <v/>
       </c>
     </row>
@@ -1527,19 +1542,19 @@
         <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E33" t="str">
         <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
       </c>
       <c r="F33" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I33" t="str">
         <v/>
@@ -1548,9 +1563,18 @@
         <v/>
       </c>
       <c r="K33" t="str">
-        <v/>
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
       </c>
       <c r="L33" t="str">
+        <v/>
+      </c>
+      <c r="M33" t="str">
+        <v/>
+      </c>
+      <c r="N33" t="str">
+        <v/>
+      </c>
+      <c r="O33" t="str">
         <v/>
       </c>
     </row>
@@ -1565,19 +1589,19 @@
         <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E34" t="str">
         <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
       </c>
       <c r="F34" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I34" t="str">
         <v/>
@@ -1586,7 +1610,7 @@
         <v/>
       </c>
       <c r="K34" t="str">
-        <v/>
+        <v>אוליביה דין The Art of Loving</v>
       </c>
       <c r="L34" t="str">
         <v/>
@@ -1595,6 +1619,9 @@
         <v/>
       </c>
       <c r="N34" t="str">
+        <v/>
+      </c>
+      <c r="O34" t="str">
         <v/>
       </c>
     </row>
@@ -1609,19 +1636,19 @@
         <v>https://yosmusic.com/geese-getting-killed/</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E35" t="str">
         <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
       </c>
       <c r="F35" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I35" t="str">
         <v/>
@@ -1630,7 +1657,7 @@
         <v/>
       </c>
       <c r="K35" t="str">
-        <v/>
+        <v>Geese Getting Killed</v>
       </c>
       <c r="L35" t="str">
         <v/>
@@ -1639,6 +1666,9 @@
         <v/>
       </c>
       <c r="N35" t="str">
+        <v/>
+      </c>
+      <c r="O35" t="str">
         <v/>
       </c>
     </row>
@@ -1653,19 +1683,19 @@
         <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E36" t="str">
         <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
       </c>
       <c r="F36" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I36" t="str">
         <v/>
@@ -1674,7 +1704,7 @@
         <v/>
       </c>
       <c r="K36" t="str">
-        <v/>
+        <v>רוסליה Lux</v>
       </c>
       <c r="L36" t="str">
         <v/>
@@ -1683,6 +1713,9 @@
         <v/>
       </c>
       <c r="N36" t="str">
+        <v/>
+      </c>
+      <c r="O36" t="str">
         <v/>
       </c>
     </row>
@@ -1697,19 +1730,19 @@
         <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E37" t="str">
         <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
       </c>
       <c r="F37" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I37" t="str">
         <v/>
@@ -1718,7 +1751,7 @@
         <v/>
       </c>
       <c r="K37" t="str">
-        <v/>
+        <v>יאנגבלאד אירוסמית' one more time</v>
       </c>
       <c r="L37" t="str">
         <v/>
@@ -1727,6 +1760,9 @@
         <v/>
       </c>
       <c r="N37" t="str">
+        <v/>
+      </c>
+      <c r="O37" t="str">
         <v/>
       </c>
     </row>
@@ -1741,19 +1777,19 @@
         <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E38" t="str">
         <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
       </c>
       <c r="F38" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I38" t="str">
         <v/>
@@ -1762,7 +1798,7 @@
         <v/>
       </c>
       <c r="K38" t="str">
-        <v/>
+        <v>פינק פלויד Wish You Were Here 50</v>
       </c>
       <c r="L38" t="str">
         <v/>
@@ -1771,6 +1807,9 @@
         <v/>
       </c>
       <c r="N38" t="str">
+        <v/>
+      </c>
+      <c r="O38" t="str">
         <v/>
       </c>
     </row>
@@ -1785,19 +1824,19 @@
         <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E39" t="str">
         <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
       </c>
       <c r="F39" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I39" t="str">
         <v/>
@@ -1806,7 +1845,7 @@
         <v/>
       </c>
       <c r="K39" t="str">
-        <v/>
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
       </c>
       <c r="L39" t="str">
         <v/>
@@ -1815,6 +1854,9 @@
         <v/>
       </c>
       <c r="N39" t="str">
+        <v/>
+      </c>
+      <c r="O39" t="str">
         <v/>
       </c>
     </row>
@@ -1829,19 +1871,19 @@
         <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E40" t="str">
         <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
       </c>
       <c r="F40" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I40" t="str">
         <v/>
@@ -1850,7 +1892,7 @@
         <v/>
       </c>
       <c r="K40" t="str">
-        <v/>
+        <v>סטריי קידס DO IT (EP)</v>
       </c>
       <c r="L40" t="str">
         <v/>
@@ -1859,6 +1901,9 @@
         <v/>
       </c>
       <c r="N40" t="str">
+        <v/>
+      </c>
+      <c r="O40" t="str">
         <v/>
       </c>
     </row>
@@ -1873,19 +1918,19 @@
         <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E41" t="str">
         <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
       </c>
       <c r="F41" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I41" t="str">
         <v/>
@@ -1894,7 +1939,7 @@
         <v/>
       </c>
       <c r="K41" t="str">
-        <v/>
+        <v>דויד ברוזה BROZAJAZZ</v>
       </c>
       <c r="L41" t="str">
         <v/>
@@ -1903,6 +1948,9 @@
         <v/>
       </c>
       <c r="N41" t="str">
+        <v/>
+      </c>
+      <c r="O41" t="str">
         <v/>
       </c>
     </row>
@@ -1917,19 +1965,19 @@
         <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E42" t="str">
         <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
       </c>
       <c r="F42" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I42" t="str">
         <v/>
@@ -1938,7 +1986,7 @@
         <v/>
       </c>
       <c r="K42" t="str">
-        <v/>
+        <v>Five Seconds of Summer – Everyone's A Star</v>
       </c>
       <c r="L42" t="str">
         <v/>
@@ -1947,6 +1995,9 @@
         <v/>
       </c>
       <c r="N42" t="str">
+        <v/>
+      </c>
+      <c r="O42" t="str">
         <v/>
       </c>
     </row>
@@ -1961,19 +2012,19 @@
         <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E43" t="str">
         <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
       </c>
       <c r="F43" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I43" t="str">
         <v/>
@@ -1982,7 +2033,7 @@
         <v/>
       </c>
       <c r="K43" t="str">
-        <v/>
+        <v>התקווה 6 – ויהי אור</v>
       </c>
       <c r="L43" t="str">
         <v/>
@@ -1991,6 +2042,9 @@
         <v/>
       </c>
       <c r="N43" t="str">
+        <v/>
+      </c>
+      <c r="O43" t="str">
         <v/>
       </c>
     </row>
@@ -2005,19 +2059,19 @@
         <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E44" t="str">
         <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
       </c>
       <c r="F44" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I44" t="str">
         <v/>
@@ -2026,7 +2080,7 @@
         <v/>
       </c>
       <c r="K44" t="str">
-        <v/>
+        <v>פלורנס אנד דה משין Everybody Scream</v>
       </c>
       <c r="L44" t="str">
         <v/>
@@ -2035,6 +2089,9 @@
         <v/>
       </c>
       <c r="N44" t="str">
+        <v/>
+      </c>
+      <c r="O44" t="str">
         <v/>
       </c>
     </row>
@@ -2049,19 +2106,19 @@
         <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E45" t="str">
         <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
       </c>
       <c r="F45" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I45" t="str">
         <v/>
@@ -2070,7 +2127,7 @@
         <v/>
       </c>
       <c r="K45" t="str">
-        <v/>
+        <v>טיים אימפלה Deadbeat</v>
       </c>
       <c r="L45" t="str">
         <v/>
@@ -2079,6 +2136,9 @@
         <v/>
       </c>
       <c r="N45" t="str">
+        <v/>
+      </c>
+      <c r="O45" t="str">
         <v/>
       </c>
     </row>
@@ -2093,19 +2153,19 @@
         <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E46" t="str">
         <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
       </c>
       <c r="F46" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I46" t="str">
         <v/>
@@ -2114,7 +2174,7 @@
         <v/>
       </c>
       <c r="K46" t="str">
-        <v/>
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
       </c>
       <c r="L46" t="str">
         <v/>
@@ -2123,6 +2183,9 @@
         <v/>
       </c>
       <c r="N46" t="str">
+        <v/>
+      </c>
+      <c r="O46" t="str">
         <v/>
       </c>
     </row>
@@ -2137,19 +2200,19 @@
         <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E47" t="str">
         <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
       </c>
       <c r="F47" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I47" t="str">
         <v/>
@@ -2158,7 +2221,7 @@
         <v/>
       </c>
       <c r="K47" t="str">
-        <v/>
+        <v>שלמה גרוניך – תודה אהבה</v>
       </c>
       <c r="L47" t="str">
         <v/>
@@ -2167,6 +2230,9 @@
         <v/>
       </c>
       <c r="N47" t="str">
+        <v/>
+      </c>
+      <c r="O47" t="str">
         <v/>
       </c>
     </row>
@@ -2181,19 +2247,19 @@
         <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E48" t="str">
         <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
       </c>
       <c r="F48" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I48" t="str">
         <v/>
@@ -2202,7 +2268,7 @@
         <v/>
       </c>
       <c r="K48" t="str">
-        <v/>
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
       </c>
       <c r="L48" t="str">
         <v/>
@@ -2211,6 +2277,9 @@
         <v/>
       </c>
       <c r="N48" t="str">
+        <v/>
+      </c>
+      <c r="O48" t="str">
         <v/>
       </c>
     </row>
@@ -2225,19 +2294,19 @@
         <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E49" t="str">
         <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
       </c>
       <c r="F49" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I49" t="str">
         <v/>
@@ -2246,7 +2315,7 @@
         <v/>
       </c>
       <c r="K49" t="str">
-        <v/>
+        <v>דוג'ה קאט Vie</v>
       </c>
       <c r="L49" t="str">
         <v/>
@@ -2255,6 +2324,9 @@
         <v/>
       </c>
       <c r="N49" t="str">
+        <v/>
+      </c>
+      <c r="O49" t="str">
         <v/>
       </c>
     </row>
@@ -2269,19 +2341,19 @@
         <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E50" t="str">
         <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
       </c>
       <c r="F50" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -2290,7 +2362,7 @@
         <v/>
       </c>
       <c r="K50" t="str">
-        <v/>
+        <v>ג'וי קרוקס Juniper</v>
       </c>
       <c r="L50" t="str">
         <v/>
@@ -2299,6 +2371,9 @@
         <v/>
       </c>
       <c r="N50" t="str">
+        <v/>
+      </c>
+      <c r="O50" t="str">
         <v/>
       </c>
     </row>
@@ -2313,19 +2388,19 @@
         <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E51" t="str">
         <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
       </c>
       <c r="F51" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I51" t="str">
         <v/>
@@ -2334,7 +2409,7 @@
         <v/>
       </c>
       <c r="K51" t="str">
-        <v/>
+        <v>ביפי קליירו Futique</v>
       </c>
       <c r="L51" t="str">
         <v/>
@@ -2343,6 +2418,9 @@
         <v/>
       </c>
       <c r="N51" t="str">
+        <v/>
+      </c>
+      <c r="O51" t="str">
         <v/>
       </c>
     </row>
@@ -2357,19 +2435,19 @@
         <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E52" t="str">
         <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
       </c>
       <c r="F52" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -2378,7 +2456,7 @@
         <v/>
       </c>
       <c r="K52" t="str">
-        <v/>
+        <v>אד שירן Play</v>
       </c>
       <c r="L52" t="str">
         <v/>
@@ -2387,6 +2465,9 @@
         <v/>
       </c>
       <c r="N52" t="str">
+        <v/>
+      </c>
+      <c r="O52" t="str">
         <v/>
       </c>
     </row>
@@ -2401,19 +2482,19 @@
         <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E53" t="str">
         <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
       </c>
       <c r="F53" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I53" t="str">
         <v/>
@@ -2422,7 +2503,7 @@
         <v/>
       </c>
       <c r="K53" t="str">
-        <v/>
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
       </c>
       <c r="L53" t="str">
         <v/>
@@ -2431,6 +2512,9 @@
         <v/>
       </c>
       <c r="N53" t="str">
+        <v/>
+      </c>
+      <c r="O53" t="str">
         <v/>
       </c>
     </row>
@@ -2445,19 +2529,19 @@
         <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E54" t="str">
         <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
       </c>
       <c r="F54" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I54" t="str">
         <v/>
@@ -2466,7 +2550,7 @@
         <v/>
       </c>
       <c r="K54" t="str">
-        <v/>
+        <v>סוויד Antidepressants</v>
       </c>
       <c r="L54" t="str">
         <v/>
@@ -2475,6 +2559,9 @@
         <v/>
       </c>
       <c r="N54" t="str">
+        <v/>
+      </c>
+      <c r="O54" t="str">
         <v/>
       </c>
     </row>
@@ -2489,19 +2576,19 @@
         <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E55" t="str">
         <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
       </c>
       <c r="F55" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I55" t="str">
         <v/>
@@ -2510,7 +2597,7 @@
         <v/>
       </c>
       <c r="K55" t="str">
-        <v/>
+        <v>וולף אליס The Clearing</v>
       </c>
       <c r="L55" t="str">
         <v/>
@@ -2519,6 +2606,9 @@
         <v/>
       </c>
       <c r="N55" t="str">
+        <v/>
+      </c>
+      <c r="O55" t="str">
         <v/>
       </c>
     </row>
@@ -2533,19 +2623,19 @@
         <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E56" t="str">
         <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
       </c>
       <c r="F56" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I56" t="str">
         <v/>
@@ -2554,7 +2644,7 @@
         <v/>
       </c>
       <c r="K56" t="str">
-        <v/>
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
       </c>
       <c r="L56" t="str">
         <v/>
@@ -2563,6 +2653,9 @@
         <v/>
       </c>
       <c r="N56" t="str">
+        <v/>
+      </c>
+      <c r="O56" t="str">
         <v/>
       </c>
     </row>
@@ -2577,19 +2670,19 @@
         <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E57" t="str">
         <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
       </c>
       <c r="F57" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I57" t="str">
         <v/>
@@ -2598,7 +2691,7 @@
         <v/>
       </c>
       <c r="K57" t="str">
-        <v/>
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
       </c>
       <c r="L57" t="str">
         <v/>
@@ -2607,6 +2700,9 @@
         <v/>
       </c>
       <c r="N57" t="str">
+        <v/>
+      </c>
+      <c r="O57" t="str">
         <v/>
       </c>
     </row>
@@ -2621,19 +2717,19 @@
         <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E58" t="str">
         <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
       </c>
       <c r="F58" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I58" t="str">
         <v/>
@@ -2642,7 +2738,7 @@
         <v/>
       </c>
       <c r="K58" t="str">
-        <v/>
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
       </c>
       <c r="L58" t="str">
         <v/>
@@ -2651,6 +2747,9 @@
         <v/>
       </c>
       <c r="N58" t="str">
+        <v/>
+      </c>
+      <c r="O58" t="str">
         <v/>
       </c>
     </row>
@@ -2665,19 +2764,19 @@
         <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E59" t="str">
         <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
       </c>
       <c r="F59" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I59" t="str">
         <v/>
@@ -2686,7 +2785,7 @@
         <v/>
       </c>
       <c r="K59" t="str">
-        <v/>
+        <v>אברהם טל – חי</v>
       </c>
       <c r="L59" t="str">
         <v/>
@@ -2695,6 +2794,9 @@
         <v/>
       </c>
       <c r="N59" t="str">
+        <v/>
+      </c>
+      <c r="O59" t="str">
         <v/>
       </c>
     </row>
@@ -2709,19 +2811,19 @@
         <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E60" t="str">
         <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
       </c>
       <c r="F60" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I60" t="str">
         <v/>
@@ -2730,7 +2832,7 @@
         <v/>
       </c>
       <c r="K60" t="str">
-        <v/>
+        <v>רנה ראפ Bite Me</v>
       </c>
       <c r="L60" t="str">
         <v/>
@@ -2739,6 +2841,9 @@
         <v/>
       </c>
       <c r="N60" t="str">
+        <v/>
+      </c>
+      <c r="O60" t="str">
         <v/>
       </c>
     </row>
@@ -2753,19 +2858,19 @@
         <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E61" t="str">
         <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
       </c>
       <c r="F61" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="I61" t="str">
         <v/>
@@ -2774,7 +2879,7 @@
         <v/>
       </c>
       <c r="K61" t="str">
-        <v/>
+        <v>The K's – Pretty On The Internet</v>
       </c>
       <c r="L61" t="str">
         <v/>
@@ -2783,24 +2888,27 @@
         <v/>
       </c>
       <c r="N61" t="str">
+        <v/>
+      </c>
+      <c r="O61" t="str">
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>פליטווד מק Fifty Years – Don’t Stop</v>
+        <v>פטריק סבג Hotel Mogador</v>
       </c>
       <c r="B62" t="str">
-        <v>2025-07-30</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C62" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%99%d7%98%d7%95%d7%95%d7%93-%d7%9e%d7%a7-fifty-years-dont-stop/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-13</v>
       </c>
       <c r="E62" t="str">
-        <v>פליטווד מק (Fleetwood Mac) חוגגים חצי מאה של מוזיקה עם אוסף חדש בן 50 שירים, שמתפרש על כל הקריירה של הלהקה, מימיה הראשונים בסגנון בלוז, ועד להצלחתה העולמית כאחת מלהקות הגדולות בהיסטוריה של הרוק. פליטווד מק הם לא רק להקה</v>
+        <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
       </c>
       <c r="F62" t="str">
         <v>אלבומים חדשים</v>
@@ -2832,51 +2940,1737 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
+      </c>
+      <c r="B63" t="str">
+        <v>2026-01-09</v>
+      </c>
+      <c r="C63" t="str">
+        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
+      </c>
+      <c r="D63" t="str">
+        <v>2026-01-09</v>
+      </c>
+      <c r="E63" t="str">
+        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
+      </c>
+      <c r="F63" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G63" t="str">
+        <v/>
+      </c>
+      <c r="H63" t="str">
+        <v/>
+      </c>
+      <c r="I63" t="str">
+        <v/>
+      </c>
+      <c r="J63" t="str">
+        <v/>
+      </c>
+      <c r="K63" t="str">
+        <v/>
+      </c>
+      <c r="L63" t="str">
+        <v/>
+      </c>
+      <c r="M63" t="str">
+        <v/>
+      </c>
+      <c r="N63" t="str">
+        <v/>
+      </c>
+      <c r="O63" t="str">
+        <v/>
+      </c>
+      <c r="P63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>אוליביה דין The Art of Loving</v>
+      </c>
+      <c r="B64" t="str">
+        <v>2026-01-04</v>
+      </c>
+      <c r="C64" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
+      </c>
+      <c r="D64" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E64" t="str">
+        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
+      </c>
+      <c r="F64" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G64" t="str">
+        <v/>
+      </c>
+      <c r="H64" t="str">
+        <v/>
+      </c>
+      <c r="I64" t="str">
+        <v/>
+      </c>
+      <c r="J64" t="str">
+        <v/>
+      </c>
+      <c r="K64" t="str">
+        <v/>
+      </c>
+      <c r="L64" t="str">
+        <v/>
+      </c>
+      <c r="M64" t="str">
+        <v/>
+      </c>
+      <c r="N64" t="str">
+        <v/>
+      </c>
+      <c r="O64" t="str">
+        <v/>
+      </c>
+      <c r="P64" t="str">
+        <v/>
+      </c>
+      <c r="Q64" t="str">
+        <v/>
+      </c>
+      <c r="R64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>Geese Getting Killed</v>
+      </c>
+      <c r="B65" t="str">
+        <v>2025-12-29</v>
+      </c>
+      <c r="C65" t="str">
+        <v>https://yosmusic.com/geese-getting-killed/</v>
+      </c>
+      <c r="D65" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E65" t="str">
+        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
+      </c>
+      <c r="F65" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G65" t="str">
+        <v/>
+      </c>
+      <c r="H65" t="str">
+        <v/>
+      </c>
+      <c r="I65" t="str">
+        <v/>
+      </c>
+      <c r="J65" t="str">
+        <v/>
+      </c>
+      <c r="K65" t="str">
+        <v/>
+      </c>
+      <c r="L65" t="str">
+        <v/>
+      </c>
+      <c r="M65" t="str">
+        <v/>
+      </c>
+      <c r="N65" t="str">
+        <v/>
+      </c>
+      <c r="O65" t="str">
+        <v/>
+      </c>
+      <c r="P65" t="str">
+        <v/>
+      </c>
+      <c r="Q65" t="str">
+        <v/>
+      </c>
+      <c r="R65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>רוסליה Lux</v>
+      </c>
+      <c r="B66" t="str">
+        <v>2025-12-25</v>
+      </c>
+      <c r="C66" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
+      </c>
+      <c r="D66" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E66" t="str">
+        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
+      </c>
+      <c r="F66" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G66" t="str">
+        <v/>
+      </c>
+      <c r="H66" t="str">
+        <v/>
+      </c>
+      <c r="I66" t="str">
+        <v/>
+      </c>
+      <c r="J66" t="str">
+        <v/>
+      </c>
+      <c r="K66" t="str">
+        <v/>
+      </c>
+      <c r="L66" t="str">
+        <v/>
+      </c>
+      <c r="M66" t="str">
+        <v/>
+      </c>
+      <c r="N66" t="str">
+        <v/>
+      </c>
+      <c r="O66" t="str">
+        <v/>
+      </c>
+      <c r="P66" t="str">
+        <v/>
+      </c>
+      <c r="Q66" t="str">
+        <v/>
+      </c>
+      <c r="R66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>יאנגבלאד אירוסמית' one more time</v>
+      </c>
+      <c r="B67" t="str">
+        <v>2025-12-17</v>
+      </c>
+      <c r="C67" t="str">
+        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
+      </c>
+      <c r="D67" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E67" t="str">
+        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
+      </c>
+      <c r="F67" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G67" t="str">
+        <v/>
+      </c>
+      <c r="H67" t="str">
+        <v/>
+      </c>
+      <c r="I67" t="str">
+        <v/>
+      </c>
+      <c r="J67" t="str">
+        <v/>
+      </c>
+      <c r="K67" t="str">
+        <v/>
+      </c>
+      <c r="L67" t="str">
+        <v/>
+      </c>
+      <c r="M67" t="str">
+        <v/>
+      </c>
+      <c r="N67" t="str">
+        <v/>
+      </c>
+      <c r="O67" t="str">
+        <v/>
+      </c>
+      <c r="P67" t="str">
+        <v/>
+      </c>
+      <c r="Q67" t="str">
+        <v/>
+      </c>
+      <c r="R67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>פינק פלויד Wish You Were Here 50</v>
+      </c>
+      <c r="B68" t="str">
+        <v>2025-12-14</v>
+      </c>
+      <c r="C68" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
+      </c>
+      <c r="D68" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E68" t="str">
+        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
+      </c>
+      <c r="F68" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G68" t="str">
+        <v/>
+      </c>
+      <c r="H68" t="str">
+        <v/>
+      </c>
+      <c r="I68" t="str">
+        <v/>
+      </c>
+      <c r="J68" t="str">
+        <v/>
+      </c>
+      <c r="K68" t="str">
+        <v/>
+      </c>
+      <c r="L68" t="str">
+        <v/>
+      </c>
+      <c r="M68" t="str">
+        <v/>
+      </c>
+      <c r="N68" t="str">
+        <v/>
+      </c>
+      <c r="O68" t="str">
+        <v/>
+      </c>
+      <c r="P68" t="str">
+        <v/>
+      </c>
+      <c r="Q68" t="str">
+        <v/>
+      </c>
+      <c r="R68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+      </c>
+      <c r="B69" t="str">
+        <v>2025-12-08</v>
+      </c>
+      <c r="C69" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
+      </c>
+      <c r="D69" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E69" t="str">
+        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
+      </c>
+      <c r="F69" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G69" t="str">
+        <v/>
+      </c>
+      <c r="H69" t="str">
+        <v/>
+      </c>
+      <c r="I69" t="str">
+        <v/>
+      </c>
+      <c r="J69" t="str">
+        <v/>
+      </c>
+      <c r="K69" t="str">
+        <v/>
+      </c>
+      <c r="L69" t="str">
+        <v/>
+      </c>
+      <c r="M69" t="str">
+        <v/>
+      </c>
+      <c r="N69" t="str">
+        <v/>
+      </c>
+      <c r="O69" t="str">
+        <v/>
+      </c>
+      <c r="P69" t="str">
+        <v/>
+      </c>
+      <c r="Q69" t="str">
+        <v/>
+      </c>
+      <c r="R69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>סטריי קידס DO IT (EP)</v>
+      </c>
+      <c r="B70" t="str">
+        <v>2025-12-04</v>
+      </c>
+      <c r="C70" t="str">
+        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
+      </c>
+      <c r="D70" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E70" t="str">
+        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
+      </c>
+      <c r="F70" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G70" t="str">
+        <v/>
+      </c>
+      <c r="H70" t="str">
+        <v/>
+      </c>
+      <c r="I70" t="str">
+        <v/>
+      </c>
+      <c r="J70" t="str">
+        <v/>
+      </c>
+      <c r="K70" t="str">
+        <v/>
+      </c>
+      <c r="L70" t="str">
+        <v/>
+      </c>
+      <c r="M70" t="str">
+        <v/>
+      </c>
+      <c r="N70" t="str">
+        <v/>
+      </c>
+      <c r="O70" t="str">
+        <v/>
+      </c>
+      <c r="P70" t="str">
+        <v/>
+      </c>
+      <c r="Q70" t="str">
+        <v/>
+      </c>
+      <c r="R70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>דויד ברוזה BROZAJAZZ</v>
+      </c>
+      <c r="B71" t="str">
+        <v>2025-11-30</v>
+      </c>
+      <c r="C71" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
+      </c>
+      <c r="D71" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E71" t="str">
+        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
+      </c>
+      <c r="F71" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G71" t="str">
+        <v/>
+      </c>
+      <c r="H71" t="str">
+        <v/>
+      </c>
+      <c r="I71" t="str">
+        <v/>
+      </c>
+      <c r="J71" t="str">
+        <v/>
+      </c>
+      <c r="K71" t="str">
+        <v/>
+      </c>
+      <c r="L71" t="str">
+        <v/>
+      </c>
+      <c r="M71" t="str">
+        <v/>
+      </c>
+      <c r="N71" t="str">
+        <v/>
+      </c>
+      <c r="O71" t="str">
+        <v/>
+      </c>
+      <c r="P71" t="str">
+        <v/>
+      </c>
+      <c r="Q71" t="str">
+        <v/>
+      </c>
+      <c r="R71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>Five Seconds of Summer – Everyone's A Star</v>
+      </c>
+      <c r="B72" t="str">
+        <v>2025-11-24</v>
+      </c>
+      <c r="C72" t="str">
+        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
+      </c>
+      <c r="D72" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E72" t="str">
+        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
+      </c>
+      <c r="F72" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G72" t="str">
+        <v/>
+      </c>
+      <c r="H72" t="str">
+        <v/>
+      </c>
+      <c r="I72" t="str">
+        <v/>
+      </c>
+      <c r="J72" t="str">
+        <v/>
+      </c>
+      <c r="K72" t="str">
+        <v/>
+      </c>
+      <c r="L72" t="str">
+        <v/>
+      </c>
+      <c r="M72" t="str">
+        <v/>
+      </c>
+      <c r="N72" t="str">
+        <v/>
+      </c>
+      <c r="O72" t="str">
+        <v/>
+      </c>
+      <c r="P72" t="str">
+        <v/>
+      </c>
+      <c r="Q72" t="str">
+        <v/>
+      </c>
+      <c r="R72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>התקווה 6 – ויהי אור</v>
+      </c>
+      <c r="B73" t="str">
+        <v>2025-11-20</v>
+      </c>
+      <c r="C73" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
+      </c>
+      <c r="D73" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E73" t="str">
+        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
+      </c>
+      <c r="F73" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G73" t="str">
+        <v/>
+      </c>
+      <c r="H73" t="str">
+        <v/>
+      </c>
+      <c r="I73" t="str">
+        <v/>
+      </c>
+      <c r="J73" t="str">
+        <v/>
+      </c>
+      <c r="K73" t="str">
+        <v/>
+      </c>
+      <c r="L73" t="str">
+        <v/>
+      </c>
+      <c r="M73" t="str">
+        <v/>
+      </c>
+      <c r="N73" t="str">
+        <v/>
+      </c>
+      <c r="O73" t="str">
+        <v/>
+      </c>
+      <c r="P73" t="str">
+        <v/>
+      </c>
+      <c r="Q73" t="str">
+        <v/>
+      </c>
+      <c r="R73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>פלורנס אנד דה משין Everybody Scream</v>
+      </c>
+      <c r="B74" t="str">
+        <v>2025-11-13</v>
+      </c>
+      <c r="C74" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
+      </c>
+      <c r="D74" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E74" t="str">
+        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
+      </c>
+      <c r="F74" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G74" t="str">
+        <v/>
+      </c>
+      <c r="H74" t="str">
+        <v/>
+      </c>
+      <c r="I74" t="str">
+        <v/>
+      </c>
+      <c r="J74" t="str">
+        <v/>
+      </c>
+      <c r="K74" t="str">
+        <v/>
+      </c>
+      <c r="L74" t="str">
+        <v/>
+      </c>
+      <c r="M74" t="str">
+        <v/>
+      </c>
+      <c r="N74" t="str">
+        <v/>
+      </c>
+      <c r="O74" t="str">
+        <v/>
+      </c>
+      <c r="P74" t="str">
+        <v/>
+      </c>
+      <c r="Q74" t="str">
+        <v/>
+      </c>
+      <c r="R74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>טיים אימפלה Deadbeat</v>
+      </c>
+      <c r="B75" t="str">
+        <v>2025-11-03</v>
+      </c>
+      <c r="C75" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
+      </c>
+      <c r="D75" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E75" t="str">
+        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
+      </c>
+      <c r="F75" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G75" t="str">
+        <v/>
+      </c>
+      <c r="H75" t="str">
+        <v/>
+      </c>
+      <c r="I75" t="str">
+        <v/>
+      </c>
+      <c r="J75" t="str">
+        <v/>
+      </c>
+      <c r="K75" t="str">
+        <v/>
+      </c>
+      <c r="L75" t="str">
+        <v/>
+      </c>
+      <c r="M75" t="str">
+        <v/>
+      </c>
+      <c r="N75" t="str">
+        <v/>
+      </c>
+      <c r="O75" t="str">
+        <v/>
+      </c>
+      <c r="P75" t="str">
+        <v/>
+      </c>
+      <c r="Q75" t="str">
+        <v/>
+      </c>
+      <c r="R75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+      </c>
+      <c r="B76" t="str">
+        <v>2025-10-20</v>
+      </c>
+      <c r="C76" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
+      </c>
+      <c r="D76" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E76" t="str">
+        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
+      </c>
+      <c r="F76" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G76" t="str">
+        <v/>
+      </c>
+      <c r="H76" t="str">
+        <v/>
+      </c>
+      <c r="I76" t="str">
+        <v/>
+      </c>
+      <c r="J76" t="str">
+        <v/>
+      </c>
+      <c r="K76" t="str">
+        <v/>
+      </c>
+      <c r="L76" t="str">
+        <v/>
+      </c>
+      <c r="M76" t="str">
+        <v/>
+      </c>
+      <c r="N76" t="str">
+        <v/>
+      </c>
+      <c r="O76" t="str">
+        <v/>
+      </c>
+      <c r="P76" t="str">
+        <v/>
+      </c>
+      <c r="Q76" t="str">
+        <v/>
+      </c>
+      <c r="R76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>שלמה גרוניך – תודה אהבה</v>
+      </c>
+      <c r="B77" t="str">
+        <v>2025-10-18</v>
+      </c>
+      <c r="C77" t="str">
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
+      </c>
+      <c r="D77" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E77" t="str">
+        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
+      </c>
+      <c r="F77" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G77" t="str">
+        <v/>
+      </c>
+      <c r="H77" t="str">
+        <v/>
+      </c>
+      <c r="I77" t="str">
+        <v/>
+      </c>
+      <c r="J77" t="str">
+        <v/>
+      </c>
+      <c r="K77" t="str">
+        <v/>
+      </c>
+      <c r="L77" t="str">
+        <v/>
+      </c>
+      <c r="M77" t="str">
+        <v/>
+      </c>
+      <c r="N77" t="str">
+        <v/>
+      </c>
+      <c r="O77" t="str">
+        <v/>
+      </c>
+      <c r="P77" t="str">
+        <v/>
+      </c>
+      <c r="Q77" t="str">
+        <v/>
+      </c>
+      <c r="R77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
+      </c>
+      <c r="B78" t="str">
+        <v>2025-10-11</v>
+      </c>
+      <c r="C78" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
+      </c>
+      <c r="D78" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E78" t="str">
+        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
+      </c>
+      <c r="F78" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G78" t="str">
+        <v/>
+      </c>
+      <c r="H78" t="str">
+        <v/>
+      </c>
+      <c r="I78" t="str">
+        <v/>
+      </c>
+      <c r="J78" t="str">
+        <v/>
+      </c>
+      <c r="K78" t="str">
+        <v/>
+      </c>
+      <c r="L78" t="str">
+        <v/>
+      </c>
+      <c r="M78" t="str">
+        <v/>
+      </c>
+      <c r="N78" t="str">
+        <v/>
+      </c>
+      <c r="O78" t="str">
+        <v/>
+      </c>
+      <c r="P78" t="str">
+        <v/>
+      </c>
+      <c r="Q78" t="str">
+        <v/>
+      </c>
+      <c r="R78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>דוג'ה קאט Vie</v>
+      </c>
+      <c r="B79" t="str">
+        <v>2025-10-04</v>
+      </c>
+      <c r="C79" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
+      </c>
+      <c r="D79" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E79" t="str">
+        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
+      </c>
+      <c r="F79" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G79" t="str">
+        <v/>
+      </c>
+      <c r="H79" t="str">
+        <v/>
+      </c>
+      <c r="I79" t="str">
+        <v/>
+      </c>
+      <c r="J79" t="str">
+        <v/>
+      </c>
+      <c r="K79" t="str">
+        <v/>
+      </c>
+      <c r="L79" t="str">
+        <v/>
+      </c>
+      <c r="M79" t="str">
+        <v/>
+      </c>
+      <c r="N79" t="str">
+        <v/>
+      </c>
+      <c r="O79" t="str">
+        <v/>
+      </c>
+      <c r="P79" t="str">
+        <v/>
+      </c>
+      <c r="Q79" t="str">
+        <v/>
+      </c>
+      <c r="R79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>ג'וי קרוקס Juniper</v>
+      </c>
+      <c r="B80" t="str">
+        <v>2025-10-03</v>
+      </c>
+      <c r="C80" t="str">
+        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
+      </c>
+      <c r="D80" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E80" t="str">
+        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
+      </c>
+      <c r="F80" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G80" t="str">
+        <v/>
+      </c>
+      <c r="H80" t="str">
+        <v/>
+      </c>
+      <c r="I80" t="str">
+        <v/>
+      </c>
+      <c r="J80" t="str">
+        <v/>
+      </c>
+      <c r="K80" t="str">
+        <v/>
+      </c>
+      <c r="L80" t="str">
+        <v/>
+      </c>
+      <c r="M80" t="str">
+        <v/>
+      </c>
+      <c r="N80" t="str">
+        <v/>
+      </c>
+      <c r="O80" t="str">
+        <v/>
+      </c>
+      <c r="P80" t="str">
+        <v/>
+      </c>
+      <c r="Q80" t="str">
+        <v/>
+      </c>
+      <c r="R80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>ביפי קליירו Futique</v>
+      </c>
+      <c r="B81" t="str">
+        <v>2025-09-30</v>
+      </c>
+      <c r="C81" t="str">
+        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
+      </c>
+      <c r="D81" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E81" t="str">
+        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
+      </c>
+      <c r="F81" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G81" t="str">
+        <v/>
+      </c>
+      <c r="H81" t="str">
+        <v/>
+      </c>
+      <c r="I81" t="str">
+        <v/>
+      </c>
+      <c r="J81" t="str">
+        <v/>
+      </c>
+      <c r="K81" t="str">
+        <v/>
+      </c>
+      <c r="L81" t="str">
+        <v/>
+      </c>
+      <c r="M81" t="str">
+        <v/>
+      </c>
+      <c r="N81" t="str">
+        <v/>
+      </c>
+      <c r="O81" t="str">
+        <v/>
+      </c>
+      <c r="P81" t="str">
+        <v/>
+      </c>
+      <c r="Q81" t="str">
+        <v/>
+      </c>
+      <c r="R81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>אד שירן Play</v>
+      </c>
+      <c r="B82" t="str">
+        <v>2025-09-24</v>
+      </c>
+      <c r="C82" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
+      </c>
+      <c r="D82" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E82" t="str">
+        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
+      </c>
+      <c r="F82" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G82" t="str">
+        <v/>
+      </c>
+      <c r="H82" t="str">
+        <v/>
+      </c>
+      <c r="I82" t="str">
+        <v/>
+      </c>
+      <c r="J82" t="str">
+        <v/>
+      </c>
+      <c r="K82" t="str">
+        <v/>
+      </c>
+      <c r="L82" t="str">
+        <v/>
+      </c>
+      <c r="M82" t="str">
+        <v/>
+      </c>
+      <c r="N82" t="str">
+        <v/>
+      </c>
+      <c r="O82" t="str">
+        <v/>
+      </c>
+      <c r="P82" t="str">
+        <v/>
+      </c>
+      <c r="Q82" t="str">
+        <v/>
+      </c>
+      <c r="R82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+      </c>
+      <c r="B83" t="str">
+        <v>2025-09-21</v>
+      </c>
+      <c r="C83" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
+      </c>
+      <c r="D83" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E83" t="str">
+        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
+      </c>
+      <c r="F83" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G83" t="str">
+        <v/>
+      </c>
+      <c r="H83" t="str">
+        <v/>
+      </c>
+      <c r="I83" t="str">
+        <v/>
+      </c>
+      <c r="J83" t="str">
+        <v/>
+      </c>
+      <c r="K83" t="str">
+        <v/>
+      </c>
+      <c r="L83" t="str">
+        <v/>
+      </c>
+      <c r="M83" t="str">
+        <v/>
+      </c>
+      <c r="N83" t="str">
+        <v/>
+      </c>
+      <c r="O83" t="str">
+        <v/>
+      </c>
+      <c r="P83" t="str">
+        <v/>
+      </c>
+      <c r="Q83" t="str">
+        <v/>
+      </c>
+      <c r="R83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>סוויד Antidepressants</v>
+      </c>
+      <c r="B84" t="str">
+        <v>2025-09-12</v>
+      </c>
+      <c r="C84" t="str">
+        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
+      </c>
+      <c r="D84" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E84" t="str">
+        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
+      </c>
+      <c r="F84" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G84" t="str">
+        <v/>
+      </c>
+      <c r="H84" t="str">
+        <v/>
+      </c>
+      <c r="I84" t="str">
+        <v/>
+      </c>
+      <c r="J84" t="str">
+        <v/>
+      </c>
+      <c r="K84" t="str">
+        <v/>
+      </c>
+      <c r="L84" t="str">
+        <v/>
+      </c>
+      <c r="M84" t="str">
+        <v/>
+      </c>
+      <c r="N84" t="str">
+        <v/>
+      </c>
+      <c r="O84" t="str">
+        <v/>
+      </c>
+      <c r="P84" t="str">
+        <v/>
+      </c>
+      <c r="Q84" t="str">
+        <v/>
+      </c>
+      <c r="R84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>וולף אליס The Clearing</v>
+      </c>
+      <c r="B85" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="C85" t="str">
+        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
+      </c>
+      <c r="D85" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E85" t="str">
+        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
+      </c>
+      <c r="F85" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G85" t="str">
+        <v/>
+      </c>
+      <c r="H85" t="str">
+        <v/>
+      </c>
+      <c r="I85" t="str">
+        <v/>
+      </c>
+      <c r="J85" t="str">
+        <v/>
+      </c>
+      <c r="K85" t="str">
+        <v/>
+      </c>
+      <c r="L85" t="str">
+        <v/>
+      </c>
+      <c r="M85" t="str">
+        <v/>
+      </c>
+      <c r="N85" t="str">
+        <v/>
+      </c>
+      <c r="O85" t="str">
+        <v/>
+      </c>
+      <c r="P85" t="str">
+        <v/>
+      </c>
+      <c r="Q85" t="str">
+        <v/>
+      </c>
+      <c r="R85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+      </c>
+      <c r="B86" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="C86" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
+      </c>
+      <c r="D86" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E86" t="str">
+        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
+      </c>
+      <c r="F86" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G86" t="str">
+        <v/>
+      </c>
+      <c r="H86" t="str">
+        <v/>
+      </c>
+      <c r="I86" t="str">
+        <v/>
+      </c>
+      <c r="J86" t="str">
+        <v/>
+      </c>
+      <c r="K86" t="str">
+        <v/>
+      </c>
+      <c r="L86" t="str">
+        <v/>
+      </c>
+      <c r="M86" t="str">
+        <v/>
+      </c>
+      <c r="N86" t="str">
+        <v/>
+      </c>
+      <c r="O86" t="str">
+        <v/>
+      </c>
+      <c r="P86" t="str">
+        <v/>
+      </c>
+      <c r="Q86" t="str">
+        <v/>
+      </c>
+      <c r="R86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+      </c>
+      <c r="B87" t="str">
+        <v>2025-08-24</v>
+      </c>
+      <c r="C87" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
+      </c>
+      <c r="D87" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E87" t="str">
+        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
+      </c>
+      <c r="F87" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G87" t="str">
+        <v/>
+      </c>
+      <c r="H87" t="str">
+        <v/>
+      </c>
+      <c r="I87" t="str">
+        <v/>
+      </c>
+      <c r="J87" t="str">
+        <v/>
+      </c>
+      <c r="K87" t="str">
+        <v/>
+      </c>
+      <c r="L87" t="str">
+        <v/>
+      </c>
+      <c r="M87" t="str">
+        <v/>
+      </c>
+      <c r="N87" t="str">
+        <v/>
+      </c>
+      <c r="O87" t="str">
+        <v/>
+      </c>
+      <c r="P87" t="str">
+        <v/>
+      </c>
+      <c r="Q87" t="str">
+        <v/>
+      </c>
+      <c r="R87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+      </c>
+      <c r="B88" t="str">
+        <v>2025-08-21</v>
+      </c>
+      <c r="C88" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
+      </c>
+      <c r="D88" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E88" t="str">
+        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
+      </c>
+      <c r="F88" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G88" t="str">
+        <v/>
+      </c>
+      <c r="H88" t="str">
+        <v/>
+      </c>
+      <c r="I88" t="str">
+        <v/>
+      </c>
+      <c r="J88" t="str">
+        <v/>
+      </c>
+      <c r="K88" t="str">
+        <v/>
+      </c>
+      <c r="L88" t="str">
+        <v/>
+      </c>
+      <c r="M88" t="str">
+        <v/>
+      </c>
+      <c r="N88" t="str">
+        <v/>
+      </c>
+      <c r="O88" t="str">
+        <v/>
+      </c>
+      <c r="P88" t="str">
+        <v/>
+      </c>
+      <c r="Q88" t="str">
+        <v/>
+      </c>
+      <c r="R88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>אברהם טל – חי</v>
+      </c>
+      <c r="B89" t="str">
+        <v>2025-08-17</v>
+      </c>
+      <c r="C89" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
+      </c>
+      <c r="D89" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E89" t="str">
+        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
+      </c>
+      <c r="F89" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G89" t="str">
+        <v/>
+      </c>
+      <c r="H89" t="str">
+        <v/>
+      </c>
+      <c r="I89" t="str">
+        <v/>
+      </c>
+      <c r="J89" t="str">
+        <v/>
+      </c>
+      <c r="K89" t="str">
+        <v/>
+      </c>
+      <c r="L89" t="str">
+        <v/>
+      </c>
+      <c r="M89" t="str">
+        <v/>
+      </c>
+      <c r="N89" t="str">
+        <v/>
+      </c>
+      <c r="O89" t="str">
+        <v/>
+      </c>
+      <c r="P89" t="str">
+        <v/>
+      </c>
+      <c r="Q89" t="str">
+        <v/>
+      </c>
+      <c r="R89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>רנה ראפ Bite Me</v>
+      </c>
+      <c r="B90" t="str">
+        <v>2025-08-12</v>
+      </c>
+      <c r="C90" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
+      </c>
+      <c r="D90" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E90" t="str">
+        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
+      </c>
+      <c r="F90" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G90" t="str">
+        <v/>
+      </c>
+      <c r="H90" t="str">
+        <v/>
+      </c>
+      <c r="I90" t="str">
+        <v/>
+      </c>
+      <c r="J90" t="str">
+        <v/>
+      </c>
+      <c r="K90" t="str">
+        <v/>
+      </c>
+      <c r="L90" t="str">
+        <v/>
+      </c>
+      <c r="M90" t="str">
+        <v/>
+      </c>
+      <c r="N90" t="str">
+        <v/>
+      </c>
+      <c r="O90" t="str">
+        <v/>
+      </c>
+      <c r="P90" t="str">
+        <v/>
+      </c>
+      <c r="Q90" t="str">
+        <v/>
+      </c>
+      <c r="R90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>The K's – Pretty On The Internet</v>
+      </c>
+      <c r="B91" t="str">
+        <v>2025-08-03</v>
+      </c>
+      <c r="C91" t="str">
+        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
+      </c>
+      <c r="D91" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E91" t="str">
+        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
+      </c>
+      <c r="F91" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G91" t="str">
+        <v/>
+      </c>
+      <c r="H91" t="str">
+        <v/>
+      </c>
+      <c r="I91" t="str">
+        <v/>
+      </c>
+      <c r="J91" t="str">
+        <v/>
+      </c>
+      <c r="K91" t="str">
+        <v/>
+      </c>
+      <c r="L91" t="str">
+        <v/>
+      </c>
+      <c r="M91" t="str">
+        <v/>
+      </c>
+      <c r="N91" t="str">
+        <v/>
+      </c>
+      <c r="O91" t="str">
+        <v/>
+      </c>
+      <c r="P91" t="str">
+        <v/>
+      </c>
+      <c r="Q91" t="str">
+        <v/>
+      </c>
+      <c r="R91" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>פליטווד מק Fifty Years – Don’t Stop</v>
+      </c>
+      <c r="B92" t="str">
+        <v>2025-07-30</v>
+      </c>
+      <c r="C92" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%99%d7%98%d7%95%d7%95%d7%93-%d7%9e%d7%a7-fifty-years-dont-stop/</v>
+      </c>
+      <c r="D92" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E92" t="str">
+        <v>פליטווד מק (Fleetwood Mac) חוגגים חצי מאה של מוזיקה עם אוסף חדש בן 50 שירים, שמתפרש על כל הקריירה של הלהקה, מימיה הראשונים בסגנון בלוז, ועד להצלחתה העולמית כאחת מלהקות הגדולות בהיסטוריה של הרוק. פליטווד מק הם לא רק להקה</v>
+      </c>
+      <c r="F92" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G92" t="str">
+        <v/>
+      </c>
+      <c r="H92" t="str">
+        <v/>
+      </c>
+      <c r="I92" t="str">
+        <v/>
+      </c>
+      <c r="J92" t="str">
+        <v/>
+      </c>
+      <c r="K92" t="str">
+        <v/>
+      </c>
+      <c r="L92" t="str">
+        <v/>
+      </c>
+      <c r="M92" t="str">
+        <v/>
+      </c>
+      <c r="N92" t="str">
+        <v/>
+      </c>
+      <c r="O92" t="str">
+        <v/>
+      </c>
+      <c r="P92" t="str">
+        <v/>
+      </c>
+      <c r="Q92" t="str">
+        <v/>
+      </c>
+      <c r="R92" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
         <v>Wet Leg Moisturizer</v>
       </c>
-      <c r="B63" t="str">
+      <c r="B93" t="str">
         <v>2025-07-25</v>
       </c>
-      <c r="C63" t="str">
+      <c r="C93" t="str">
         <v>https://yosmusic.com/wet-leg-moisturizer/</v>
       </c>
-      <c r="D63" t="str">
+      <c r="D93" t="str">
         <v>2026-01-08</v>
       </c>
-      <c r="E63" t="str">
+      <c r="E93" t="str">
         <v>להקת Wet Leg לא הוציאה קרם לחות (Moisturizer) כמוצר טיפוח. במקום זאת, "Moisturizer" הוא שמו של האלבום השני והחדש שלהם. במרכז –  צמד אינדי-רוק המורכב מהחברות ריין טיסדייל והסטר צ'יימברס. אלבום הבכורה הנושא את שמה, הגיע למקום הראשון במצעד האלבומים</v>
       </c>
-      <c r="F63" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="G63" t="str">
-        <v/>
-      </c>
-      <c r="H63" t="str">
-        <v/>
-      </c>
-      <c r="I63" t="str">
-        <v/>
-      </c>
-      <c r="J63" t="str">
-        <v/>
-      </c>
-      <c r="K63" t="str">
-        <v/>
-      </c>
-      <c r="L63" t="str">
-        <v/>
-      </c>
-      <c r="M63" t="str">
-        <v/>
-      </c>
-      <c r="N63" t="str">
+      <c r="F93" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="G93" t="str">
+        <v/>
+      </c>
+      <c r="H93" t="str">
+        <v/>
+      </c>
+      <c r="I93" t="str">
+        <v/>
+      </c>
+      <c r="J93" t="str">
+        <v/>
+      </c>
+      <c r="K93" t="str">
+        <v/>
+      </c>
+      <c r="L93" t="str">
+        <v/>
+      </c>
+      <c r="M93" t="str">
+        <v/>
+      </c>
+      <c r="N93" t="str">
+        <v/>
+      </c>
+      <c r="O93" t="str">
+        <v/>
+      </c>
+      <c r="P93" t="str">
+        <v/>
+      </c>
+      <c r="Q93" t="str">
+        <v/>
+      </c>
+      <c r="R93" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N63"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R93"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:O61"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1484,9 +1484,1419 @@
         <v>The K's – Pretty On The Internet</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>פטריק סבג Hotel Mogador</v>
+      </c>
+      <c r="B32" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C32" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
+      </c>
+      <c r="D32" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E32" t="str">
+        <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
+      </c>
+      <c r="F32" t="str">
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I32" t="str">
+        <v/>
+      </c>
+      <c r="J32" t="str">
+        <v/>
+      </c>
+      <c r="K32" t="str">
+        <v>פטריק סבג Hotel Mogador</v>
+      </c>
+      <c r="L32" t="str">
+        <v/>
+      </c>
+      <c r="M32" t="str">
+        <v/>
+      </c>
+      <c r="N32" t="str">
+        <v/>
+      </c>
+      <c r="O32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
+      </c>
+      <c r="B33" t="str">
+        <v>2026-01-09</v>
+      </c>
+      <c r="C33" t="str">
+        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
+      </c>
+      <c r="D33" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E33" t="str">
+        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
+      </c>
+      <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I33" t="str">
+        <v/>
+      </c>
+      <c r="J33" t="str">
+        <v/>
+      </c>
+      <c r="K33" t="str">
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
+      </c>
+      <c r="L33" t="str">
+        <v/>
+      </c>
+      <c r="M33" t="str">
+        <v/>
+      </c>
+      <c r="N33" t="str">
+        <v/>
+      </c>
+      <c r="O33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>אוליביה דין The Art of Loving</v>
+      </c>
+      <c r="B34" t="str">
+        <v>2026-01-04</v>
+      </c>
+      <c r="C34" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
+      </c>
+      <c r="D34" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E34" t="str">
+        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
+      </c>
+      <c r="F34" t="str">
+        <v/>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+      <c r="H34" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I34" t="str">
+        <v/>
+      </c>
+      <c r="J34" t="str">
+        <v/>
+      </c>
+      <c r="K34" t="str">
+        <v>אוליביה דין The Art of Loving</v>
+      </c>
+      <c r="L34" t="str">
+        <v/>
+      </c>
+      <c r="M34" t="str">
+        <v/>
+      </c>
+      <c r="N34" t="str">
+        <v/>
+      </c>
+      <c r="O34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Geese Getting Killed</v>
+      </c>
+      <c r="B35" t="str">
+        <v>2025-12-29</v>
+      </c>
+      <c r="C35" t="str">
+        <v>https://yosmusic.com/geese-getting-killed/</v>
+      </c>
+      <c r="D35" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E35" t="str">
+        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
+      </c>
+      <c r="F35" t="str">
+        <v/>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+      <c r="H35" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I35" t="str">
+        <v/>
+      </c>
+      <c r="J35" t="str">
+        <v/>
+      </c>
+      <c r="K35" t="str">
+        <v>Geese Getting Killed</v>
+      </c>
+      <c r="L35" t="str">
+        <v/>
+      </c>
+      <c r="M35" t="str">
+        <v/>
+      </c>
+      <c r="N35" t="str">
+        <v/>
+      </c>
+      <c r="O35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>רוסליה Lux</v>
+      </c>
+      <c r="B36" t="str">
+        <v>2025-12-25</v>
+      </c>
+      <c r="C36" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
+      </c>
+      <c r="D36" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E36" t="str">
+        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
+      </c>
+      <c r="F36" t="str">
+        <v/>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I36" t="str">
+        <v/>
+      </c>
+      <c r="J36" t="str">
+        <v/>
+      </c>
+      <c r="K36" t="str">
+        <v>רוסליה Lux</v>
+      </c>
+      <c r="L36" t="str">
+        <v/>
+      </c>
+      <c r="M36" t="str">
+        <v/>
+      </c>
+      <c r="N36" t="str">
+        <v/>
+      </c>
+      <c r="O36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>יאנגבלאד אירוסמית' one more time</v>
+      </c>
+      <c r="B37" t="str">
+        <v>2025-12-17</v>
+      </c>
+      <c r="C37" t="str">
+        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
+      </c>
+      <c r="D37" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E37" t="str">
+        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
+      </c>
+      <c r="F37" t="str">
+        <v/>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I37" t="str">
+        <v/>
+      </c>
+      <c r="J37" t="str">
+        <v/>
+      </c>
+      <c r="K37" t="str">
+        <v>יאנגבלאד אירוסמית' one more time</v>
+      </c>
+      <c r="L37" t="str">
+        <v/>
+      </c>
+      <c r="M37" t="str">
+        <v/>
+      </c>
+      <c r="N37" t="str">
+        <v/>
+      </c>
+      <c r="O37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>פינק פלויד Wish You Were Here 50</v>
+      </c>
+      <c r="B38" t="str">
+        <v>2025-12-14</v>
+      </c>
+      <c r="C38" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
+      </c>
+      <c r="D38" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E38" t="str">
+        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
+      </c>
+      <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I38" t="str">
+        <v/>
+      </c>
+      <c r="J38" t="str">
+        <v/>
+      </c>
+      <c r="K38" t="str">
+        <v>פינק פלויד Wish You Were Here 50</v>
+      </c>
+      <c r="L38" t="str">
+        <v/>
+      </c>
+      <c r="M38" t="str">
+        <v/>
+      </c>
+      <c r="N38" t="str">
+        <v/>
+      </c>
+      <c r="O38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+      </c>
+      <c r="B39" t="str">
+        <v>2025-12-08</v>
+      </c>
+      <c r="C39" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
+      </c>
+      <c r="D39" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E39" t="str">
+        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
+      </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I39" t="str">
+        <v/>
+      </c>
+      <c r="J39" t="str">
+        <v/>
+      </c>
+      <c r="K39" t="str">
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+      </c>
+      <c r="L39" t="str">
+        <v/>
+      </c>
+      <c r="M39" t="str">
+        <v/>
+      </c>
+      <c r="N39" t="str">
+        <v/>
+      </c>
+      <c r="O39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>סטריי קידס DO IT EP</v>
+      </c>
+      <c r="B40" t="str">
+        <v>2025-12-04</v>
+      </c>
+      <c r="C40" t="str">
+        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
+      </c>
+      <c r="D40" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E40" t="str">
+        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
+      </c>
+      <c r="F40" t="str">
+        <v/>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I40" t="str">
+        <v/>
+      </c>
+      <c r="J40" t="str">
+        <v/>
+      </c>
+      <c r="K40" t="str">
+        <v>סטריי קידס DO IT EP</v>
+      </c>
+      <c r="L40" t="str">
+        <v/>
+      </c>
+      <c r="M40" t="str">
+        <v/>
+      </c>
+      <c r="N40" t="str">
+        <v/>
+      </c>
+      <c r="O40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>דויד ברוזה BROZAJAZZ</v>
+      </c>
+      <c r="B41" t="str">
+        <v>2025-11-30</v>
+      </c>
+      <c r="C41" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
+      </c>
+      <c r="D41" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E41" t="str">
+        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
+      </c>
+      <c r="F41" t="str">
+        <v/>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I41" t="str">
+        <v/>
+      </c>
+      <c r="J41" t="str">
+        <v/>
+      </c>
+      <c r="K41" t="str">
+        <v>דויד ברוזה BROZAJAZZ</v>
+      </c>
+      <c r="L41" t="str">
+        <v/>
+      </c>
+      <c r="M41" t="str">
+        <v/>
+      </c>
+      <c r="N41" t="str">
+        <v/>
+      </c>
+      <c r="O41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>Five Seconds of Summer – Everyone's A Star</v>
+      </c>
+      <c r="B42" t="str">
+        <v>2025-11-24</v>
+      </c>
+      <c r="C42" t="str">
+        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
+      </c>
+      <c r="D42" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E42" t="str">
+        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
+      </c>
+      <c r="F42" t="str">
+        <v/>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I42" t="str">
+        <v/>
+      </c>
+      <c r="J42" t="str">
+        <v/>
+      </c>
+      <c r="K42" t="str">
+        <v>Five Seconds of Summer – Everyone's A Star</v>
+      </c>
+      <c r="L42" t="str">
+        <v/>
+      </c>
+      <c r="M42" t="str">
+        <v/>
+      </c>
+      <c r="N42" t="str">
+        <v/>
+      </c>
+      <c r="O42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>התקווה 6 – ויהי אור</v>
+      </c>
+      <c r="B43" t="str">
+        <v>2025-11-20</v>
+      </c>
+      <c r="C43" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
+      </c>
+      <c r="D43" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E43" t="str">
+        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I43" t="str">
+        <v/>
+      </c>
+      <c r="J43" t="str">
+        <v/>
+      </c>
+      <c r="K43" t="str">
+        <v>התקווה 6 – ויהי אור</v>
+      </c>
+      <c r="L43" t="str">
+        <v/>
+      </c>
+      <c r="M43" t="str">
+        <v/>
+      </c>
+      <c r="N43" t="str">
+        <v/>
+      </c>
+      <c r="O43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>פלורנס אנד דה משין Everybody Scream</v>
+      </c>
+      <c r="B44" t="str">
+        <v>2025-11-13</v>
+      </c>
+      <c r="C44" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
+      </c>
+      <c r="D44" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E44" t="str">
+        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
+      </c>
+      <c r="F44" t="str">
+        <v/>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I44" t="str">
+        <v/>
+      </c>
+      <c r="J44" t="str">
+        <v/>
+      </c>
+      <c r="K44" t="str">
+        <v>פלורנס אנד דה משין Everybody Scream</v>
+      </c>
+      <c r="L44" t="str">
+        <v/>
+      </c>
+      <c r="M44" t="str">
+        <v/>
+      </c>
+      <c r="N44" t="str">
+        <v/>
+      </c>
+      <c r="O44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>טיים אימפלה Deadbeat</v>
+      </c>
+      <c r="B45" t="str">
+        <v>2025-11-03</v>
+      </c>
+      <c r="C45" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
+      </c>
+      <c r="D45" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E45" t="str">
+        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
+      </c>
+      <c r="F45" t="str">
+        <v/>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I45" t="str">
+        <v/>
+      </c>
+      <c r="J45" t="str">
+        <v/>
+      </c>
+      <c r="K45" t="str">
+        <v>טיים אימפלה Deadbeat</v>
+      </c>
+      <c r="L45" t="str">
+        <v/>
+      </c>
+      <c r="M45" t="str">
+        <v/>
+      </c>
+      <c r="N45" t="str">
+        <v/>
+      </c>
+      <c r="O45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+      </c>
+      <c r="B46" t="str">
+        <v>2025-10-20</v>
+      </c>
+      <c r="C46" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
+      </c>
+      <c r="D46" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E46" t="str">
+        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
+      </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I46" t="str">
+        <v/>
+      </c>
+      <c r="J46" t="str">
+        <v/>
+      </c>
+      <c r="K46" t="str">
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+      </c>
+      <c r="L46" t="str">
+        <v/>
+      </c>
+      <c r="M46" t="str">
+        <v/>
+      </c>
+      <c r="N46" t="str">
+        <v/>
+      </c>
+      <c r="O46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>שלמה גרוניך – תודה אהבה</v>
+      </c>
+      <c r="B47" t="str">
+        <v>2025-10-18</v>
+      </c>
+      <c r="C47" t="str">
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
+      </c>
+      <c r="D47" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E47" t="str">
+        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
+      </c>
+      <c r="F47" t="str">
+        <v/>
+      </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
+      <c r="H47" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I47" t="str">
+        <v/>
+      </c>
+      <c r="J47" t="str">
+        <v/>
+      </c>
+      <c r="K47" t="str">
+        <v>שלמה גרוניך – תודה אהבה</v>
+      </c>
+      <c r="L47" t="str">
+        <v/>
+      </c>
+      <c r="M47" t="str">
+        <v/>
+      </c>
+      <c r="N47" t="str">
+        <v/>
+      </c>
+      <c r="O47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
+      </c>
+      <c r="B48" t="str">
+        <v>2025-10-11</v>
+      </c>
+      <c r="C48" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
+      </c>
+      <c r="D48" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E48" t="str">
+        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
+      </c>
+      <c r="F48" t="str">
+        <v/>
+      </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
+      <c r="H48" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I48" t="str">
+        <v/>
+      </c>
+      <c r="J48" t="str">
+        <v/>
+      </c>
+      <c r="K48" t="str">
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
+      </c>
+      <c r="L48" t="str">
+        <v/>
+      </c>
+      <c r="M48" t="str">
+        <v/>
+      </c>
+      <c r="N48" t="str">
+        <v/>
+      </c>
+      <c r="O48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>דוג'ה קאט Vie</v>
+      </c>
+      <c r="B49" t="str">
+        <v>2025-10-04</v>
+      </c>
+      <c r="C49" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
+      </c>
+      <c r="D49" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E49" t="str">
+        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
+      </c>
+      <c r="F49" t="str">
+        <v/>
+      </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
+      <c r="H49" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I49" t="str">
+        <v/>
+      </c>
+      <c r="J49" t="str">
+        <v/>
+      </c>
+      <c r="K49" t="str">
+        <v>דוג'ה קאט Vie</v>
+      </c>
+      <c r="L49" t="str">
+        <v/>
+      </c>
+      <c r="M49" t="str">
+        <v/>
+      </c>
+      <c r="N49" t="str">
+        <v/>
+      </c>
+      <c r="O49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>ג'וי קרוקס Juniper</v>
+      </c>
+      <c r="B50" t="str">
+        <v>2025-10-03</v>
+      </c>
+      <c r="C50" t="str">
+        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
+      </c>
+      <c r="D50" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E50" t="str">
+        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
+      </c>
+      <c r="F50" t="str">
+        <v/>
+      </c>
+      <c r="G50" t="str">
+        <v/>
+      </c>
+      <c r="H50" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I50" t="str">
+        <v/>
+      </c>
+      <c r="J50" t="str">
+        <v/>
+      </c>
+      <c r="K50" t="str">
+        <v>ג'וי קרוקס Juniper</v>
+      </c>
+      <c r="L50" t="str">
+        <v/>
+      </c>
+      <c r="M50" t="str">
+        <v/>
+      </c>
+      <c r="N50" t="str">
+        <v/>
+      </c>
+      <c r="O50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>ביפי קליירו Futique</v>
+      </c>
+      <c r="B51" t="str">
+        <v>2025-09-30</v>
+      </c>
+      <c r="C51" t="str">
+        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
+      </c>
+      <c r="D51" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E51" t="str">
+        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
+      </c>
+      <c r="F51" t="str">
+        <v/>
+      </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
+      <c r="H51" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I51" t="str">
+        <v/>
+      </c>
+      <c r="J51" t="str">
+        <v/>
+      </c>
+      <c r="K51" t="str">
+        <v>ביפי קליירו Futique</v>
+      </c>
+      <c r="L51" t="str">
+        <v/>
+      </c>
+      <c r="M51" t="str">
+        <v/>
+      </c>
+      <c r="N51" t="str">
+        <v/>
+      </c>
+      <c r="O51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>אד שירן Play</v>
+      </c>
+      <c r="B52" t="str">
+        <v>2025-09-24</v>
+      </c>
+      <c r="C52" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
+      </c>
+      <c r="D52" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E52" t="str">
+        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
+      </c>
+      <c r="F52" t="str">
+        <v/>
+      </c>
+      <c r="G52" t="str">
+        <v/>
+      </c>
+      <c r="H52" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I52" t="str">
+        <v/>
+      </c>
+      <c r="J52" t="str">
+        <v/>
+      </c>
+      <c r="K52" t="str">
+        <v>אד שירן Play</v>
+      </c>
+      <c r="L52" t="str">
+        <v/>
+      </c>
+      <c r="M52" t="str">
+        <v/>
+      </c>
+      <c r="N52" t="str">
+        <v/>
+      </c>
+      <c r="O52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+      </c>
+      <c r="B53" t="str">
+        <v>2025-09-21</v>
+      </c>
+      <c r="C53" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
+      </c>
+      <c r="D53" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E53" t="str">
+        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
+      </c>
+      <c r="F53" t="str">
+        <v/>
+      </c>
+      <c r="G53" t="str">
+        <v/>
+      </c>
+      <c r="H53" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I53" t="str">
+        <v/>
+      </c>
+      <c r="J53" t="str">
+        <v/>
+      </c>
+      <c r="K53" t="str">
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+      </c>
+      <c r="L53" t="str">
+        <v/>
+      </c>
+      <c r="M53" t="str">
+        <v/>
+      </c>
+      <c r="N53" t="str">
+        <v/>
+      </c>
+      <c r="O53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>סוויד Antidepressants</v>
+      </c>
+      <c r="B54" t="str">
+        <v>2025-09-12</v>
+      </c>
+      <c r="C54" t="str">
+        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
+      </c>
+      <c r="D54" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E54" t="str">
+        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
+      </c>
+      <c r="F54" t="str">
+        <v/>
+      </c>
+      <c r="G54" t="str">
+        <v/>
+      </c>
+      <c r="H54" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I54" t="str">
+        <v/>
+      </c>
+      <c r="J54" t="str">
+        <v/>
+      </c>
+      <c r="K54" t="str">
+        <v>סוויד Antidepressants</v>
+      </c>
+      <c r="L54" t="str">
+        <v/>
+      </c>
+      <c r="M54" t="str">
+        <v/>
+      </c>
+      <c r="N54" t="str">
+        <v/>
+      </c>
+      <c r="O54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>וולף אליס The Clearing</v>
+      </c>
+      <c r="B55" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="C55" t="str">
+        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
+      </c>
+      <c r="D55" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E55" t="str">
+        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
+      </c>
+      <c r="F55" t="str">
+        <v/>
+      </c>
+      <c r="G55" t="str">
+        <v/>
+      </c>
+      <c r="H55" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I55" t="str">
+        <v/>
+      </c>
+      <c r="J55" t="str">
+        <v/>
+      </c>
+      <c r="K55" t="str">
+        <v>וולף אליס The Clearing</v>
+      </c>
+      <c r="L55" t="str">
+        <v/>
+      </c>
+      <c r="M55" t="str">
+        <v/>
+      </c>
+      <c r="N55" t="str">
+        <v/>
+      </c>
+      <c r="O55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+      </c>
+      <c r="B56" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="C56" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
+      </c>
+      <c r="D56" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E56" t="str">
+        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
+      </c>
+      <c r="F56" t="str">
+        <v/>
+      </c>
+      <c r="G56" t="str">
+        <v/>
+      </c>
+      <c r="H56" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I56" t="str">
+        <v/>
+      </c>
+      <c r="J56" t="str">
+        <v/>
+      </c>
+      <c r="K56" t="str">
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+      </c>
+      <c r="L56" t="str">
+        <v/>
+      </c>
+      <c r="M56" t="str">
+        <v/>
+      </c>
+      <c r="N56" t="str">
+        <v/>
+      </c>
+      <c r="O56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+      </c>
+      <c r="B57" t="str">
+        <v>2025-08-24</v>
+      </c>
+      <c r="C57" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
+      </c>
+      <c r="D57" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E57" t="str">
+        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
+      </c>
+      <c r="F57" t="str">
+        <v/>
+      </c>
+      <c r="G57" t="str">
+        <v/>
+      </c>
+      <c r="H57" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I57" t="str">
+        <v/>
+      </c>
+      <c r="J57" t="str">
+        <v/>
+      </c>
+      <c r="K57" t="str">
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+      </c>
+      <c r="L57" t="str">
+        <v/>
+      </c>
+      <c r="M57" t="str">
+        <v/>
+      </c>
+      <c r="N57" t="str">
+        <v/>
+      </c>
+      <c r="O57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+      </c>
+      <c r="B58" t="str">
+        <v>2025-08-21</v>
+      </c>
+      <c r="C58" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
+      </c>
+      <c r="D58" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E58" t="str">
+        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
+      </c>
+      <c r="F58" t="str">
+        <v/>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+      <c r="H58" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I58" t="str">
+        <v/>
+      </c>
+      <c r="J58" t="str">
+        <v/>
+      </c>
+      <c r="K58" t="str">
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+      </c>
+      <c r="L58" t="str">
+        <v/>
+      </c>
+      <c r="M58" t="str">
+        <v/>
+      </c>
+      <c r="N58" t="str">
+        <v/>
+      </c>
+      <c r="O58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>אברהם טל – חי</v>
+      </c>
+      <c r="B59" t="str">
+        <v>2025-08-17</v>
+      </c>
+      <c r="C59" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
+      </c>
+      <c r="D59" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E59" t="str">
+        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
+      </c>
+      <c r="F59" t="str">
+        <v/>
+      </c>
+      <c r="G59" t="str">
+        <v/>
+      </c>
+      <c r="H59" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I59" t="str">
+        <v/>
+      </c>
+      <c r="J59" t="str">
+        <v/>
+      </c>
+      <c r="K59" t="str">
+        <v>אברהם טל – חי</v>
+      </c>
+      <c r="L59" t="str">
+        <v/>
+      </c>
+      <c r="M59" t="str">
+        <v/>
+      </c>
+      <c r="N59" t="str">
+        <v/>
+      </c>
+      <c r="O59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>רנה ראפ Bite Me</v>
+      </c>
+      <c r="B60" t="str">
+        <v>2025-08-12</v>
+      </c>
+      <c r="C60" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
+      </c>
+      <c r="D60" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E60" t="str">
+        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
+      </c>
+      <c r="F60" t="str">
+        <v/>
+      </c>
+      <c r="G60" t="str">
+        <v/>
+      </c>
+      <c r="H60" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I60" t="str">
+        <v/>
+      </c>
+      <c r="J60" t="str">
+        <v/>
+      </c>
+      <c r="K60" t="str">
+        <v>רנה ראפ Bite Me</v>
+      </c>
+      <c r="L60" t="str">
+        <v/>
+      </c>
+      <c r="M60" t="str">
+        <v/>
+      </c>
+      <c r="N60" t="str">
+        <v/>
+      </c>
+      <c r="O60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>The K's – Pretty On The Internet</v>
+      </c>
+      <c r="B61" t="str">
+        <v>2025-08-03</v>
+      </c>
+      <c r="C61" t="str">
+        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
+      </c>
+      <c r="D61" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E61" t="str">
+        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
+      </c>
+      <c r="F61" t="str">
+        <v/>
+      </c>
+      <c r="G61" t="str">
+        <v/>
+      </c>
+      <c r="H61" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I61" t="str">
+        <v/>
+      </c>
+      <c r="J61" t="str">
+        <v/>
+      </c>
+      <c r="K61" t="str">
+        <v>The K's – Pretty On The Internet</v>
+      </c>
+      <c r="L61" t="str">
+        <v/>
+      </c>
+      <c r="M61" t="str">
+        <v/>
+      </c>
+      <c r="N61" t="str">
+        <v/>
+      </c>
+      <c r="O61" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O61"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O61"/>
+  <dimension ref="A1:S91"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2894,9 +2894,1779 @@
         <v/>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>פטריק סבג Hotel Mogador</v>
+      </c>
+      <c r="B62" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C62" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
+      </c>
+      <c r="D62" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E62" t="str">
+        <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
+      </c>
+      <c r="F62" t="str">
+        <v/>
+      </c>
+      <c r="G62" t="str">
+        <v/>
+      </c>
+      <c r="H62" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I62" t="str">
+        <v/>
+      </c>
+      <c r="J62" t="str">
+        <v/>
+      </c>
+      <c r="K62" t="str">
+        <v>פטריק סבג Hotel Mogador</v>
+      </c>
+      <c r="L62" t="str">
+        <v/>
+      </c>
+      <c r="M62" t="str">
+        <v/>
+      </c>
+      <c r="N62" t="str">
+        <v/>
+      </c>
+      <c r="O62" t="str">
+        <v/>
+      </c>
+      <c r="P62" t="str">
+        <v/>
+      </c>
+      <c r="Q62" t="str">
+        <v/>
+      </c>
+      <c r="R62" t="str">
+        <v/>
+      </c>
+      <c r="S62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
+      </c>
+      <c r="B63" t="str">
+        <v>2026-01-09</v>
+      </c>
+      <c r="C63" t="str">
+        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
+      </c>
+      <c r="D63" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E63" t="str">
+        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
+      </c>
+      <c r="F63" t="str">
+        <v/>
+      </c>
+      <c r="G63" t="str">
+        <v/>
+      </c>
+      <c r="H63" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I63" t="str">
+        <v/>
+      </c>
+      <c r="J63" t="str">
+        <v/>
+      </c>
+      <c r="K63" t="str">
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
+      </c>
+      <c r="L63" t="str">
+        <v/>
+      </c>
+      <c r="M63" t="str">
+        <v/>
+      </c>
+      <c r="N63" t="str">
+        <v/>
+      </c>
+      <c r="O63" t="str">
+        <v/>
+      </c>
+      <c r="P63" t="str">
+        <v/>
+      </c>
+      <c r="Q63" t="str">
+        <v/>
+      </c>
+      <c r="R63" t="str">
+        <v/>
+      </c>
+      <c r="S63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>אוליביה דין The Art of Loving</v>
+      </c>
+      <c r="B64" t="str">
+        <v>2026-01-04</v>
+      </c>
+      <c r="C64" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
+      </c>
+      <c r="D64" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E64" t="str">
+        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
+      </c>
+      <c r="F64" t="str">
+        <v/>
+      </c>
+      <c r="G64" t="str">
+        <v/>
+      </c>
+      <c r="H64" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I64" t="str">
+        <v/>
+      </c>
+      <c r="J64" t="str">
+        <v/>
+      </c>
+      <c r="K64" t="str">
+        <v>אוליביה דין The Art of Loving</v>
+      </c>
+      <c r="L64" t="str">
+        <v/>
+      </c>
+      <c r="M64" t="str">
+        <v/>
+      </c>
+      <c r="N64" t="str">
+        <v/>
+      </c>
+      <c r="O64" t="str">
+        <v/>
+      </c>
+      <c r="P64" t="str">
+        <v/>
+      </c>
+      <c r="Q64" t="str">
+        <v/>
+      </c>
+      <c r="R64" t="str">
+        <v/>
+      </c>
+      <c r="S64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>Geese Getting Killed</v>
+      </c>
+      <c r="B65" t="str">
+        <v>2025-12-29</v>
+      </c>
+      <c r="C65" t="str">
+        <v>https://yosmusic.com/geese-getting-killed/</v>
+      </c>
+      <c r="D65" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E65" t="str">
+        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
+      </c>
+      <c r="F65" t="str">
+        <v/>
+      </c>
+      <c r="G65" t="str">
+        <v/>
+      </c>
+      <c r="H65" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I65" t="str">
+        <v/>
+      </c>
+      <c r="J65" t="str">
+        <v/>
+      </c>
+      <c r="K65" t="str">
+        <v>Geese Getting Killed</v>
+      </c>
+      <c r="L65" t="str">
+        <v/>
+      </c>
+      <c r="M65" t="str">
+        <v/>
+      </c>
+      <c r="N65" t="str">
+        <v/>
+      </c>
+      <c r="O65" t="str">
+        <v/>
+      </c>
+      <c r="P65" t="str">
+        <v/>
+      </c>
+      <c r="Q65" t="str">
+        <v/>
+      </c>
+      <c r="R65" t="str">
+        <v/>
+      </c>
+      <c r="S65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>רוסליה Lux</v>
+      </c>
+      <c r="B66" t="str">
+        <v>2025-12-25</v>
+      </c>
+      <c r="C66" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
+      </c>
+      <c r="D66" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E66" t="str">
+        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
+      </c>
+      <c r="F66" t="str">
+        <v/>
+      </c>
+      <c r="G66" t="str">
+        <v/>
+      </c>
+      <c r="H66" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I66" t="str">
+        <v/>
+      </c>
+      <c r="J66" t="str">
+        <v/>
+      </c>
+      <c r="K66" t="str">
+        <v>רוסליה Lux</v>
+      </c>
+      <c r="L66" t="str">
+        <v/>
+      </c>
+      <c r="M66" t="str">
+        <v/>
+      </c>
+      <c r="N66" t="str">
+        <v/>
+      </c>
+      <c r="O66" t="str">
+        <v/>
+      </c>
+      <c r="P66" t="str">
+        <v/>
+      </c>
+      <c r="Q66" t="str">
+        <v/>
+      </c>
+      <c r="R66" t="str">
+        <v/>
+      </c>
+      <c r="S66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>יאנגבלאד אירוסמית' one more time</v>
+      </c>
+      <c r="B67" t="str">
+        <v>2025-12-17</v>
+      </c>
+      <c r="C67" t="str">
+        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
+      </c>
+      <c r="D67" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E67" t="str">
+        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
+      </c>
+      <c r="F67" t="str">
+        <v/>
+      </c>
+      <c r="G67" t="str">
+        <v/>
+      </c>
+      <c r="H67" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I67" t="str">
+        <v/>
+      </c>
+      <c r="J67" t="str">
+        <v/>
+      </c>
+      <c r="K67" t="str">
+        <v>יאנגבלאד אירוסמית' one more time</v>
+      </c>
+      <c r="L67" t="str">
+        <v/>
+      </c>
+      <c r="M67" t="str">
+        <v/>
+      </c>
+      <c r="N67" t="str">
+        <v/>
+      </c>
+      <c r="O67" t="str">
+        <v/>
+      </c>
+      <c r="P67" t="str">
+        <v/>
+      </c>
+      <c r="Q67" t="str">
+        <v/>
+      </c>
+      <c r="R67" t="str">
+        <v/>
+      </c>
+      <c r="S67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>פינק פלויד Wish You Were Here 50</v>
+      </c>
+      <c r="B68" t="str">
+        <v>2025-12-14</v>
+      </c>
+      <c r="C68" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
+      </c>
+      <c r="D68" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E68" t="str">
+        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
+      </c>
+      <c r="F68" t="str">
+        <v/>
+      </c>
+      <c r="G68" t="str">
+        <v/>
+      </c>
+      <c r="H68" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I68" t="str">
+        <v/>
+      </c>
+      <c r="J68" t="str">
+        <v/>
+      </c>
+      <c r="K68" t="str">
+        <v>פינק פלויד Wish You Were Here 50</v>
+      </c>
+      <c r="L68" t="str">
+        <v/>
+      </c>
+      <c r="M68" t="str">
+        <v/>
+      </c>
+      <c r="N68" t="str">
+        <v/>
+      </c>
+      <c r="O68" t="str">
+        <v/>
+      </c>
+      <c r="P68" t="str">
+        <v/>
+      </c>
+      <c r="Q68" t="str">
+        <v/>
+      </c>
+      <c r="R68" t="str">
+        <v/>
+      </c>
+      <c r="S68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+      </c>
+      <c r="B69" t="str">
+        <v>2025-12-08</v>
+      </c>
+      <c r="C69" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
+      </c>
+      <c r="D69" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E69" t="str">
+        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
+      </c>
+      <c r="F69" t="str">
+        <v/>
+      </c>
+      <c r="G69" t="str">
+        <v/>
+      </c>
+      <c r="H69" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I69" t="str">
+        <v/>
+      </c>
+      <c r="J69" t="str">
+        <v/>
+      </c>
+      <c r="K69" t="str">
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+      </c>
+      <c r="L69" t="str">
+        <v/>
+      </c>
+      <c r="M69" t="str">
+        <v/>
+      </c>
+      <c r="N69" t="str">
+        <v/>
+      </c>
+      <c r="O69" t="str">
+        <v/>
+      </c>
+      <c r="P69" t="str">
+        <v/>
+      </c>
+      <c r="Q69" t="str">
+        <v/>
+      </c>
+      <c r="R69" t="str">
+        <v/>
+      </c>
+      <c r="S69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>סטריי קידס DO IT EP</v>
+      </c>
+      <c r="B70" t="str">
+        <v>2025-12-04</v>
+      </c>
+      <c r="C70" t="str">
+        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
+      </c>
+      <c r="D70" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E70" t="str">
+        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
+      </c>
+      <c r="F70" t="str">
+        <v/>
+      </c>
+      <c r="G70" t="str">
+        <v/>
+      </c>
+      <c r="H70" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I70" t="str">
+        <v/>
+      </c>
+      <c r="J70" t="str">
+        <v/>
+      </c>
+      <c r="K70" t="str">
+        <v>סטריי קידס DO IT EP</v>
+      </c>
+      <c r="L70" t="str">
+        <v/>
+      </c>
+      <c r="M70" t="str">
+        <v/>
+      </c>
+      <c r="N70" t="str">
+        <v/>
+      </c>
+      <c r="O70" t="str">
+        <v/>
+      </c>
+      <c r="P70" t="str">
+        <v/>
+      </c>
+      <c r="Q70" t="str">
+        <v/>
+      </c>
+      <c r="R70" t="str">
+        <v/>
+      </c>
+      <c r="S70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>דויד ברוזה BROZAJAZZ</v>
+      </c>
+      <c r="B71" t="str">
+        <v>2025-11-30</v>
+      </c>
+      <c r="C71" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
+      </c>
+      <c r="D71" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E71" t="str">
+        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
+      </c>
+      <c r="F71" t="str">
+        <v/>
+      </c>
+      <c r="G71" t="str">
+        <v/>
+      </c>
+      <c r="H71" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I71" t="str">
+        <v/>
+      </c>
+      <c r="J71" t="str">
+        <v/>
+      </c>
+      <c r="K71" t="str">
+        <v>דויד ברוזה BROZAJAZZ</v>
+      </c>
+      <c r="L71" t="str">
+        <v/>
+      </c>
+      <c r="M71" t="str">
+        <v/>
+      </c>
+      <c r="N71" t="str">
+        <v/>
+      </c>
+      <c r="O71" t="str">
+        <v/>
+      </c>
+      <c r="P71" t="str">
+        <v/>
+      </c>
+      <c r="Q71" t="str">
+        <v/>
+      </c>
+      <c r="R71" t="str">
+        <v/>
+      </c>
+      <c r="S71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>Five Seconds of Summer – Everyone's A Star</v>
+      </c>
+      <c r="B72" t="str">
+        <v>2025-11-24</v>
+      </c>
+      <c r="C72" t="str">
+        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
+      </c>
+      <c r="D72" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E72" t="str">
+        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
+      </c>
+      <c r="F72" t="str">
+        <v/>
+      </c>
+      <c r="G72" t="str">
+        <v/>
+      </c>
+      <c r="H72" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I72" t="str">
+        <v/>
+      </c>
+      <c r="J72" t="str">
+        <v/>
+      </c>
+      <c r="K72" t="str">
+        <v>Five Seconds of Summer – Everyone's A Star</v>
+      </c>
+      <c r="L72" t="str">
+        <v/>
+      </c>
+      <c r="M72" t="str">
+        <v/>
+      </c>
+      <c r="N72" t="str">
+        <v/>
+      </c>
+      <c r="O72" t="str">
+        <v/>
+      </c>
+      <c r="P72" t="str">
+        <v/>
+      </c>
+      <c r="Q72" t="str">
+        <v/>
+      </c>
+      <c r="R72" t="str">
+        <v/>
+      </c>
+      <c r="S72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>התקווה 6 – ויהי אור</v>
+      </c>
+      <c r="B73" t="str">
+        <v>2025-11-20</v>
+      </c>
+      <c r="C73" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
+      </c>
+      <c r="D73" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E73" t="str">
+        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
+      </c>
+      <c r="F73" t="str">
+        <v/>
+      </c>
+      <c r="G73" t="str">
+        <v/>
+      </c>
+      <c r="H73" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I73" t="str">
+        <v/>
+      </c>
+      <c r="J73" t="str">
+        <v/>
+      </c>
+      <c r="K73" t="str">
+        <v>התקווה 6 – ויהי אור</v>
+      </c>
+      <c r="L73" t="str">
+        <v/>
+      </c>
+      <c r="M73" t="str">
+        <v/>
+      </c>
+      <c r="N73" t="str">
+        <v/>
+      </c>
+      <c r="O73" t="str">
+        <v/>
+      </c>
+      <c r="P73" t="str">
+        <v/>
+      </c>
+      <c r="Q73" t="str">
+        <v/>
+      </c>
+      <c r="R73" t="str">
+        <v/>
+      </c>
+      <c r="S73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>פלורנס אנד דה משין Everybody Scream</v>
+      </c>
+      <c r="B74" t="str">
+        <v>2025-11-13</v>
+      </c>
+      <c r="C74" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
+      </c>
+      <c r="D74" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E74" t="str">
+        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
+      </c>
+      <c r="F74" t="str">
+        <v/>
+      </c>
+      <c r="G74" t="str">
+        <v/>
+      </c>
+      <c r="H74" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I74" t="str">
+        <v/>
+      </c>
+      <c r="J74" t="str">
+        <v/>
+      </c>
+      <c r="K74" t="str">
+        <v>פלורנס אנד דה משין Everybody Scream</v>
+      </c>
+      <c r="L74" t="str">
+        <v/>
+      </c>
+      <c r="M74" t="str">
+        <v/>
+      </c>
+      <c r="N74" t="str">
+        <v/>
+      </c>
+      <c r="O74" t="str">
+        <v/>
+      </c>
+      <c r="P74" t="str">
+        <v/>
+      </c>
+      <c r="Q74" t="str">
+        <v/>
+      </c>
+      <c r="R74" t="str">
+        <v/>
+      </c>
+      <c r="S74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>טיים אימפלה Deadbeat</v>
+      </c>
+      <c r="B75" t="str">
+        <v>2025-11-03</v>
+      </c>
+      <c r="C75" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
+      </c>
+      <c r="D75" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E75" t="str">
+        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
+      </c>
+      <c r="F75" t="str">
+        <v/>
+      </c>
+      <c r="G75" t="str">
+        <v/>
+      </c>
+      <c r="H75" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I75" t="str">
+        <v/>
+      </c>
+      <c r="J75" t="str">
+        <v/>
+      </c>
+      <c r="K75" t="str">
+        <v>טיים אימפלה Deadbeat</v>
+      </c>
+      <c r="L75" t="str">
+        <v/>
+      </c>
+      <c r="M75" t="str">
+        <v/>
+      </c>
+      <c r="N75" t="str">
+        <v/>
+      </c>
+      <c r="O75" t="str">
+        <v/>
+      </c>
+      <c r="P75" t="str">
+        <v/>
+      </c>
+      <c r="Q75" t="str">
+        <v/>
+      </c>
+      <c r="R75" t="str">
+        <v/>
+      </c>
+      <c r="S75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+      </c>
+      <c r="B76" t="str">
+        <v>2025-10-20</v>
+      </c>
+      <c r="C76" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
+      </c>
+      <c r="D76" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E76" t="str">
+        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
+      </c>
+      <c r="F76" t="str">
+        <v/>
+      </c>
+      <c r="G76" t="str">
+        <v/>
+      </c>
+      <c r="H76" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I76" t="str">
+        <v/>
+      </c>
+      <c r="J76" t="str">
+        <v/>
+      </c>
+      <c r="K76" t="str">
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+      </c>
+      <c r="L76" t="str">
+        <v/>
+      </c>
+      <c r="M76" t="str">
+        <v/>
+      </c>
+      <c r="N76" t="str">
+        <v/>
+      </c>
+      <c r="O76" t="str">
+        <v/>
+      </c>
+      <c r="P76" t="str">
+        <v/>
+      </c>
+      <c r="Q76" t="str">
+        <v/>
+      </c>
+      <c r="R76" t="str">
+        <v/>
+      </c>
+      <c r="S76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>שלמה גרוניך – תודה אהבה</v>
+      </c>
+      <c r="B77" t="str">
+        <v>2025-10-18</v>
+      </c>
+      <c r="C77" t="str">
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
+      </c>
+      <c r="D77" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E77" t="str">
+        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
+      </c>
+      <c r="F77" t="str">
+        <v/>
+      </c>
+      <c r="G77" t="str">
+        <v/>
+      </c>
+      <c r="H77" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I77" t="str">
+        <v/>
+      </c>
+      <c r="J77" t="str">
+        <v/>
+      </c>
+      <c r="K77" t="str">
+        <v>שלמה גרוניך – תודה אהבה</v>
+      </c>
+      <c r="L77" t="str">
+        <v/>
+      </c>
+      <c r="M77" t="str">
+        <v/>
+      </c>
+      <c r="N77" t="str">
+        <v/>
+      </c>
+      <c r="O77" t="str">
+        <v/>
+      </c>
+      <c r="P77" t="str">
+        <v/>
+      </c>
+      <c r="Q77" t="str">
+        <v/>
+      </c>
+      <c r="R77" t="str">
+        <v/>
+      </c>
+      <c r="S77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
+      </c>
+      <c r="B78" t="str">
+        <v>2025-10-11</v>
+      </c>
+      <c r="C78" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
+      </c>
+      <c r="D78" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E78" t="str">
+        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
+      </c>
+      <c r="F78" t="str">
+        <v/>
+      </c>
+      <c r="G78" t="str">
+        <v/>
+      </c>
+      <c r="H78" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I78" t="str">
+        <v/>
+      </c>
+      <c r="J78" t="str">
+        <v/>
+      </c>
+      <c r="K78" t="str">
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
+      </c>
+      <c r="L78" t="str">
+        <v/>
+      </c>
+      <c r="M78" t="str">
+        <v/>
+      </c>
+      <c r="N78" t="str">
+        <v/>
+      </c>
+      <c r="O78" t="str">
+        <v/>
+      </c>
+      <c r="P78" t="str">
+        <v/>
+      </c>
+      <c r="Q78" t="str">
+        <v/>
+      </c>
+      <c r="R78" t="str">
+        <v/>
+      </c>
+      <c r="S78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>דוג'ה קאט Vie</v>
+      </c>
+      <c r="B79" t="str">
+        <v>2025-10-04</v>
+      </c>
+      <c r="C79" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
+      </c>
+      <c r="D79" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E79" t="str">
+        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
+      </c>
+      <c r="F79" t="str">
+        <v/>
+      </c>
+      <c r="G79" t="str">
+        <v/>
+      </c>
+      <c r="H79" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I79" t="str">
+        <v/>
+      </c>
+      <c r="J79" t="str">
+        <v/>
+      </c>
+      <c r="K79" t="str">
+        <v>דוג'ה קאט Vie</v>
+      </c>
+      <c r="L79" t="str">
+        <v/>
+      </c>
+      <c r="M79" t="str">
+        <v/>
+      </c>
+      <c r="N79" t="str">
+        <v/>
+      </c>
+      <c r="O79" t="str">
+        <v/>
+      </c>
+      <c r="P79" t="str">
+        <v/>
+      </c>
+      <c r="Q79" t="str">
+        <v/>
+      </c>
+      <c r="R79" t="str">
+        <v/>
+      </c>
+      <c r="S79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>ג'וי קרוקס Juniper</v>
+      </c>
+      <c r="B80" t="str">
+        <v>2025-10-03</v>
+      </c>
+      <c r="C80" t="str">
+        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
+      </c>
+      <c r="D80" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E80" t="str">
+        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
+      </c>
+      <c r="F80" t="str">
+        <v/>
+      </c>
+      <c r="G80" t="str">
+        <v/>
+      </c>
+      <c r="H80" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I80" t="str">
+        <v/>
+      </c>
+      <c r="J80" t="str">
+        <v/>
+      </c>
+      <c r="K80" t="str">
+        <v>ג'וי קרוקס Juniper</v>
+      </c>
+      <c r="L80" t="str">
+        <v/>
+      </c>
+      <c r="M80" t="str">
+        <v/>
+      </c>
+      <c r="N80" t="str">
+        <v/>
+      </c>
+      <c r="O80" t="str">
+        <v/>
+      </c>
+      <c r="P80" t="str">
+        <v/>
+      </c>
+      <c r="Q80" t="str">
+        <v/>
+      </c>
+      <c r="R80" t="str">
+        <v/>
+      </c>
+      <c r="S80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>ביפי קליירו Futique</v>
+      </c>
+      <c r="B81" t="str">
+        <v>2025-09-30</v>
+      </c>
+      <c r="C81" t="str">
+        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
+      </c>
+      <c r="D81" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E81" t="str">
+        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
+      </c>
+      <c r="F81" t="str">
+        <v/>
+      </c>
+      <c r="G81" t="str">
+        <v/>
+      </c>
+      <c r="H81" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I81" t="str">
+        <v/>
+      </c>
+      <c r="J81" t="str">
+        <v/>
+      </c>
+      <c r="K81" t="str">
+        <v>ביפי קליירו Futique</v>
+      </c>
+      <c r="L81" t="str">
+        <v/>
+      </c>
+      <c r="M81" t="str">
+        <v/>
+      </c>
+      <c r="N81" t="str">
+        <v/>
+      </c>
+      <c r="O81" t="str">
+        <v/>
+      </c>
+      <c r="P81" t="str">
+        <v/>
+      </c>
+      <c r="Q81" t="str">
+        <v/>
+      </c>
+      <c r="R81" t="str">
+        <v/>
+      </c>
+      <c r="S81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>אד שירן Play</v>
+      </c>
+      <c r="B82" t="str">
+        <v>2025-09-24</v>
+      </c>
+      <c r="C82" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
+      </c>
+      <c r="D82" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E82" t="str">
+        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
+      </c>
+      <c r="F82" t="str">
+        <v/>
+      </c>
+      <c r="G82" t="str">
+        <v/>
+      </c>
+      <c r="H82" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I82" t="str">
+        <v/>
+      </c>
+      <c r="J82" t="str">
+        <v/>
+      </c>
+      <c r="K82" t="str">
+        <v>אד שירן Play</v>
+      </c>
+      <c r="L82" t="str">
+        <v/>
+      </c>
+      <c r="M82" t="str">
+        <v/>
+      </c>
+      <c r="N82" t="str">
+        <v/>
+      </c>
+      <c r="O82" t="str">
+        <v/>
+      </c>
+      <c r="P82" t="str">
+        <v/>
+      </c>
+      <c r="Q82" t="str">
+        <v/>
+      </c>
+      <c r="R82" t="str">
+        <v/>
+      </c>
+      <c r="S82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+      </c>
+      <c r="B83" t="str">
+        <v>2025-09-21</v>
+      </c>
+      <c r="C83" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
+      </c>
+      <c r="D83" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E83" t="str">
+        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
+      </c>
+      <c r="F83" t="str">
+        <v/>
+      </c>
+      <c r="G83" t="str">
+        <v/>
+      </c>
+      <c r="H83" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I83" t="str">
+        <v/>
+      </c>
+      <c r="J83" t="str">
+        <v/>
+      </c>
+      <c r="K83" t="str">
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+      </c>
+      <c r="L83" t="str">
+        <v/>
+      </c>
+      <c r="M83" t="str">
+        <v/>
+      </c>
+      <c r="N83" t="str">
+        <v/>
+      </c>
+      <c r="O83" t="str">
+        <v/>
+      </c>
+      <c r="P83" t="str">
+        <v/>
+      </c>
+      <c r="Q83" t="str">
+        <v/>
+      </c>
+      <c r="R83" t="str">
+        <v/>
+      </c>
+      <c r="S83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>סוויד Antidepressants</v>
+      </c>
+      <c r="B84" t="str">
+        <v>2025-09-12</v>
+      </c>
+      <c r="C84" t="str">
+        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
+      </c>
+      <c r="D84" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E84" t="str">
+        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
+      </c>
+      <c r="F84" t="str">
+        <v/>
+      </c>
+      <c r="G84" t="str">
+        <v/>
+      </c>
+      <c r="H84" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I84" t="str">
+        <v/>
+      </c>
+      <c r="J84" t="str">
+        <v/>
+      </c>
+      <c r="K84" t="str">
+        <v>סוויד Antidepressants</v>
+      </c>
+      <c r="L84" t="str">
+        <v/>
+      </c>
+      <c r="M84" t="str">
+        <v/>
+      </c>
+      <c r="N84" t="str">
+        <v/>
+      </c>
+      <c r="O84" t="str">
+        <v/>
+      </c>
+      <c r="P84" t="str">
+        <v/>
+      </c>
+      <c r="Q84" t="str">
+        <v/>
+      </c>
+      <c r="R84" t="str">
+        <v/>
+      </c>
+      <c r="S84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>וולף אליס The Clearing</v>
+      </c>
+      <c r="B85" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="C85" t="str">
+        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
+      </c>
+      <c r="D85" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E85" t="str">
+        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
+      </c>
+      <c r="F85" t="str">
+        <v/>
+      </c>
+      <c r="G85" t="str">
+        <v/>
+      </c>
+      <c r="H85" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I85" t="str">
+        <v/>
+      </c>
+      <c r="J85" t="str">
+        <v/>
+      </c>
+      <c r="K85" t="str">
+        <v>וולף אליס The Clearing</v>
+      </c>
+      <c r="L85" t="str">
+        <v/>
+      </c>
+      <c r="M85" t="str">
+        <v/>
+      </c>
+      <c r="N85" t="str">
+        <v/>
+      </c>
+      <c r="O85" t="str">
+        <v/>
+      </c>
+      <c r="P85" t="str">
+        <v/>
+      </c>
+      <c r="Q85" t="str">
+        <v/>
+      </c>
+      <c r="R85" t="str">
+        <v/>
+      </c>
+      <c r="S85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+      </c>
+      <c r="B86" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="C86" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
+      </c>
+      <c r="D86" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E86" t="str">
+        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
+      </c>
+      <c r="F86" t="str">
+        <v/>
+      </c>
+      <c r="G86" t="str">
+        <v/>
+      </c>
+      <c r="H86" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I86" t="str">
+        <v/>
+      </c>
+      <c r="J86" t="str">
+        <v/>
+      </c>
+      <c r="K86" t="str">
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+      </c>
+      <c r="L86" t="str">
+        <v/>
+      </c>
+      <c r="M86" t="str">
+        <v/>
+      </c>
+      <c r="N86" t="str">
+        <v/>
+      </c>
+      <c r="O86" t="str">
+        <v/>
+      </c>
+      <c r="P86" t="str">
+        <v/>
+      </c>
+      <c r="Q86" t="str">
+        <v/>
+      </c>
+      <c r="R86" t="str">
+        <v/>
+      </c>
+      <c r="S86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+      </c>
+      <c r="B87" t="str">
+        <v>2025-08-24</v>
+      </c>
+      <c r="C87" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
+      </c>
+      <c r="D87" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E87" t="str">
+        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
+      </c>
+      <c r="F87" t="str">
+        <v/>
+      </c>
+      <c r="G87" t="str">
+        <v/>
+      </c>
+      <c r="H87" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I87" t="str">
+        <v/>
+      </c>
+      <c r="J87" t="str">
+        <v/>
+      </c>
+      <c r="K87" t="str">
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+      </c>
+      <c r="L87" t="str">
+        <v/>
+      </c>
+      <c r="M87" t="str">
+        <v/>
+      </c>
+      <c r="N87" t="str">
+        <v/>
+      </c>
+      <c r="O87" t="str">
+        <v/>
+      </c>
+      <c r="P87" t="str">
+        <v/>
+      </c>
+      <c r="Q87" t="str">
+        <v/>
+      </c>
+      <c r="R87" t="str">
+        <v/>
+      </c>
+      <c r="S87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+      </c>
+      <c r="B88" t="str">
+        <v>2025-08-21</v>
+      </c>
+      <c r="C88" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
+      </c>
+      <c r="D88" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E88" t="str">
+        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
+      </c>
+      <c r="F88" t="str">
+        <v/>
+      </c>
+      <c r="G88" t="str">
+        <v/>
+      </c>
+      <c r="H88" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I88" t="str">
+        <v/>
+      </c>
+      <c r="J88" t="str">
+        <v/>
+      </c>
+      <c r="K88" t="str">
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+      </c>
+      <c r="L88" t="str">
+        <v/>
+      </c>
+      <c r="M88" t="str">
+        <v/>
+      </c>
+      <c r="N88" t="str">
+        <v/>
+      </c>
+      <c r="O88" t="str">
+        <v/>
+      </c>
+      <c r="P88" t="str">
+        <v/>
+      </c>
+      <c r="Q88" t="str">
+        <v/>
+      </c>
+      <c r="R88" t="str">
+        <v/>
+      </c>
+      <c r="S88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>אברהם טל – חי</v>
+      </c>
+      <c r="B89" t="str">
+        <v>2025-08-17</v>
+      </c>
+      <c r="C89" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
+      </c>
+      <c r="D89" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E89" t="str">
+        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
+      </c>
+      <c r="F89" t="str">
+        <v/>
+      </c>
+      <c r="G89" t="str">
+        <v/>
+      </c>
+      <c r="H89" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I89" t="str">
+        <v/>
+      </c>
+      <c r="J89" t="str">
+        <v/>
+      </c>
+      <c r="K89" t="str">
+        <v>אברהם טל – חי</v>
+      </c>
+      <c r="L89" t="str">
+        <v/>
+      </c>
+      <c r="M89" t="str">
+        <v/>
+      </c>
+      <c r="N89" t="str">
+        <v/>
+      </c>
+      <c r="O89" t="str">
+        <v/>
+      </c>
+      <c r="P89" t="str">
+        <v/>
+      </c>
+      <c r="Q89" t="str">
+        <v/>
+      </c>
+      <c r="R89" t="str">
+        <v/>
+      </c>
+      <c r="S89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>רנה ראפ Bite Me</v>
+      </c>
+      <c r="B90" t="str">
+        <v>2025-08-12</v>
+      </c>
+      <c r="C90" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
+      </c>
+      <c r="D90" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E90" t="str">
+        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
+      </c>
+      <c r="F90" t="str">
+        <v/>
+      </c>
+      <c r="G90" t="str">
+        <v/>
+      </c>
+      <c r="H90" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I90" t="str">
+        <v/>
+      </c>
+      <c r="J90" t="str">
+        <v/>
+      </c>
+      <c r="K90" t="str">
+        <v>רנה ראפ Bite Me</v>
+      </c>
+      <c r="L90" t="str">
+        <v/>
+      </c>
+      <c r="M90" t="str">
+        <v/>
+      </c>
+      <c r="N90" t="str">
+        <v/>
+      </c>
+      <c r="O90" t="str">
+        <v/>
+      </c>
+      <c r="P90" t="str">
+        <v/>
+      </c>
+      <c r="Q90" t="str">
+        <v/>
+      </c>
+      <c r="R90" t="str">
+        <v/>
+      </c>
+      <c r="S90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>The K's – Pretty On The Internet</v>
+      </c>
+      <c r="B91" t="str">
+        <v>2025-08-03</v>
+      </c>
+      <c r="C91" t="str">
+        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
+      </c>
+      <c r="D91" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E91" t="str">
+        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
+      </c>
+      <c r="F91" t="str">
+        <v/>
+      </c>
+      <c r="G91" t="str">
+        <v/>
+      </c>
+      <c r="H91" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I91" t="str">
+        <v/>
+      </c>
+      <c r="J91" t="str">
+        <v/>
+      </c>
+      <c r="K91" t="str">
+        <v>The K's – Pretty On The Internet</v>
+      </c>
+      <c r="L91" t="str">
+        <v/>
+      </c>
+      <c r="M91" t="str">
+        <v/>
+      </c>
+      <c r="N91" t="str">
+        <v/>
+      </c>
+      <c r="O91" t="str">
+        <v/>
+      </c>
+      <c r="P91" t="str">
+        <v/>
+      </c>
+      <c r="Q91" t="str">
+        <v/>
+      </c>
+      <c r="R91" t="str">
+        <v/>
+      </c>
+      <c r="S91" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S91"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S91"/>
+  <dimension ref="A1:W121"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4664,9 +4664,2139 @@
         <v/>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>פטריק סבג Hotel Mogador</v>
+      </c>
+      <c r="B92" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C92" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
+      </c>
+      <c r="D92" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E92" t="str">
+        <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
+      </c>
+      <c r="F92" t="str">
+        <v/>
+      </c>
+      <c r="G92" t="str">
+        <v/>
+      </c>
+      <c r="H92" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I92" t="str">
+        <v/>
+      </c>
+      <c r="J92" t="str">
+        <v/>
+      </c>
+      <c r="K92" t="str">
+        <v>פטריק סבג Hotel Mogador</v>
+      </c>
+      <c r="L92" t="str">
+        <v/>
+      </c>
+      <c r="M92" t="str">
+        <v/>
+      </c>
+      <c r="N92" t="str">
+        <v/>
+      </c>
+      <c r="O92" t="str">
+        <v/>
+      </c>
+      <c r="P92" t="str">
+        <v/>
+      </c>
+      <c r="Q92" t="str">
+        <v/>
+      </c>
+      <c r="R92" t="str">
+        <v/>
+      </c>
+      <c r="S92" t="str">
+        <v/>
+      </c>
+      <c r="T92" t="str">
+        <v/>
+      </c>
+      <c r="U92" t="str">
+        <v/>
+      </c>
+      <c r="V92" t="str">
+        <v/>
+      </c>
+      <c r="W92" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
+      </c>
+      <c r="B93" t="str">
+        <v>2026-01-09</v>
+      </c>
+      <c r="C93" t="str">
+        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
+      </c>
+      <c r="D93" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E93" t="str">
+        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
+      </c>
+      <c r="F93" t="str">
+        <v/>
+      </c>
+      <c r="G93" t="str">
+        <v/>
+      </c>
+      <c r="H93" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I93" t="str">
+        <v/>
+      </c>
+      <c r="J93" t="str">
+        <v/>
+      </c>
+      <c r="K93" t="str">
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
+      </c>
+      <c r="L93" t="str">
+        <v/>
+      </c>
+      <c r="M93" t="str">
+        <v/>
+      </c>
+      <c r="N93" t="str">
+        <v/>
+      </c>
+      <c r="O93" t="str">
+        <v/>
+      </c>
+      <c r="P93" t="str">
+        <v/>
+      </c>
+      <c r="Q93" t="str">
+        <v/>
+      </c>
+      <c r="R93" t="str">
+        <v/>
+      </c>
+      <c r="S93" t="str">
+        <v/>
+      </c>
+      <c r="T93" t="str">
+        <v/>
+      </c>
+      <c r="U93" t="str">
+        <v/>
+      </c>
+      <c r="V93" t="str">
+        <v/>
+      </c>
+      <c r="W93" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>אוליביה דין The Art of Loving</v>
+      </c>
+      <c r="B94" t="str">
+        <v>2026-01-04</v>
+      </c>
+      <c r="C94" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
+      </c>
+      <c r="D94" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E94" t="str">
+        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
+      </c>
+      <c r="F94" t="str">
+        <v/>
+      </c>
+      <c r="G94" t="str">
+        <v/>
+      </c>
+      <c r="H94" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I94" t="str">
+        <v/>
+      </c>
+      <c r="J94" t="str">
+        <v/>
+      </c>
+      <c r="K94" t="str">
+        <v>אוליביה דין The Art of Loving</v>
+      </c>
+      <c r="L94" t="str">
+        <v/>
+      </c>
+      <c r="M94" t="str">
+        <v/>
+      </c>
+      <c r="N94" t="str">
+        <v/>
+      </c>
+      <c r="O94" t="str">
+        <v/>
+      </c>
+      <c r="P94" t="str">
+        <v/>
+      </c>
+      <c r="Q94" t="str">
+        <v/>
+      </c>
+      <c r="R94" t="str">
+        <v/>
+      </c>
+      <c r="S94" t="str">
+        <v/>
+      </c>
+      <c r="T94" t="str">
+        <v/>
+      </c>
+      <c r="U94" t="str">
+        <v/>
+      </c>
+      <c r="V94" t="str">
+        <v/>
+      </c>
+      <c r="W94" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>Geese Getting Killed</v>
+      </c>
+      <c r="B95" t="str">
+        <v>2025-12-29</v>
+      </c>
+      <c r="C95" t="str">
+        <v>https://yosmusic.com/geese-getting-killed/</v>
+      </c>
+      <c r="D95" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E95" t="str">
+        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
+      </c>
+      <c r="F95" t="str">
+        <v/>
+      </c>
+      <c r="G95" t="str">
+        <v/>
+      </c>
+      <c r="H95" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I95" t="str">
+        <v/>
+      </c>
+      <c r="J95" t="str">
+        <v/>
+      </c>
+      <c r="K95" t="str">
+        <v>Geese Getting Killed</v>
+      </c>
+      <c r="L95" t="str">
+        <v/>
+      </c>
+      <c r="M95" t="str">
+        <v/>
+      </c>
+      <c r="N95" t="str">
+        <v/>
+      </c>
+      <c r="O95" t="str">
+        <v/>
+      </c>
+      <c r="P95" t="str">
+        <v/>
+      </c>
+      <c r="Q95" t="str">
+        <v/>
+      </c>
+      <c r="R95" t="str">
+        <v/>
+      </c>
+      <c r="S95" t="str">
+        <v/>
+      </c>
+      <c r="T95" t="str">
+        <v/>
+      </c>
+      <c r="U95" t="str">
+        <v/>
+      </c>
+      <c r="V95" t="str">
+        <v/>
+      </c>
+      <c r="W95" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>רוסליה Lux</v>
+      </c>
+      <c r="B96" t="str">
+        <v>2025-12-25</v>
+      </c>
+      <c r="C96" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
+      </c>
+      <c r="D96" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E96" t="str">
+        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
+      </c>
+      <c r="F96" t="str">
+        <v/>
+      </c>
+      <c r="G96" t="str">
+        <v/>
+      </c>
+      <c r="H96" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I96" t="str">
+        <v/>
+      </c>
+      <c r="J96" t="str">
+        <v/>
+      </c>
+      <c r="K96" t="str">
+        <v>רוסליה Lux</v>
+      </c>
+      <c r="L96" t="str">
+        <v/>
+      </c>
+      <c r="M96" t="str">
+        <v/>
+      </c>
+      <c r="N96" t="str">
+        <v/>
+      </c>
+      <c r="O96" t="str">
+        <v/>
+      </c>
+      <c r="P96" t="str">
+        <v/>
+      </c>
+      <c r="Q96" t="str">
+        <v/>
+      </c>
+      <c r="R96" t="str">
+        <v/>
+      </c>
+      <c r="S96" t="str">
+        <v/>
+      </c>
+      <c r="T96" t="str">
+        <v/>
+      </c>
+      <c r="U96" t="str">
+        <v/>
+      </c>
+      <c r="V96" t="str">
+        <v/>
+      </c>
+      <c r="W96" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>יאנגבלאד אירוסמית' one more time</v>
+      </c>
+      <c r="B97" t="str">
+        <v>2025-12-17</v>
+      </c>
+      <c r="C97" t="str">
+        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
+      </c>
+      <c r="D97" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E97" t="str">
+        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
+      </c>
+      <c r="F97" t="str">
+        <v/>
+      </c>
+      <c r="G97" t="str">
+        <v/>
+      </c>
+      <c r="H97" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I97" t="str">
+        <v/>
+      </c>
+      <c r="J97" t="str">
+        <v/>
+      </c>
+      <c r="K97" t="str">
+        <v>יאנגבלאד אירוסמית' one more time</v>
+      </c>
+      <c r="L97" t="str">
+        <v/>
+      </c>
+      <c r="M97" t="str">
+        <v/>
+      </c>
+      <c r="N97" t="str">
+        <v/>
+      </c>
+      <c r="O97" t="str">
+        <v/>
+      </c>
+      <c r="P97" t="str">
+        <v/>
+      </c>
+      <c r="Q97" t="str">
+        <v/>
+      </c>
+      <c r="R97" t="str">
+        <v/>
+      </c>
+      <c r="S97" t="str">
+        <v/>
+      </c>
+      <c r="T97" t="str">
+        <v/>
+      </c>
+      <c r="U97" t="str">
+        <v/>
+      </c>
+      <c r="V97" t="str">
+        <v/>
+      </c>
+      <c r="W97" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>פינק פלויד Wish You Were Here 50</v>
+      </c>
+      <c r="B98" t="str">
+        <v>2025-12-14</v>
+      </c>
+      <c r="C98" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
+      </c>
+      <c r="D98" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E98" t="str">
+        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
+      </c>
+      <c r="F98" t="str">
+        <v/>
+      </c>
+      <c r="G98" t="str">
+        <v/>
+      </c>
+      <c r="H98" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I98" t="str">
+        <v/>
+      </c>
+      <c r="J98" t="str">
+        <v/>
+      </c>
+      <c r="K98" t="str">
+        <v>פינק פלויד Wish You Were Here 50</v>
+      </c>
+      <c r="L98" t="str">
+        <v/>
+      </c>
+      <c r="M98" t="str">
+        <v/>
+      </c>
+      <c r="N98" t="str">
+        <v/>
+      </c>
+      <c r="O98" t="str">
+        <v/>
+      </c>
+      <c r="P98" t="str">
+        <v/>
+      </c>
+      <c r="Q98" t="str">
+        <v/>
+      </c>
+      <c r="R98" t="str">
+        <v/>
+      </c>
+      <c r="S98" t="str">
+        <v/>
+      </c>
+      <c r="T98" t="str">
+        <v/>
+      </c>
+      <c r="U98" t="str">
+        <v/>
+      </c>
+      <c r="V98" t="str">
+        <v/>
+      </c>
+      <c r="W98" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+      </c>
+      <c r="B99" t="str">
+        <v>2025-12-08</v>
+      </c>
+      <c r="C99" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
+      </c>
+      <c r="D99" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E99" t="str">
+        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
+      </c>
+      <c r="F99" t="str">
+        <v/>
+      </c>
+      <c r="G99" t="str">
+        <v/>
+      </c>
+      <c r="H99" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I99" t="str">
+        <v/>
+      </c>
+      <c r="J99" t="str">
+        <v/>
+      </c>
+      <c r="K99" t="str">
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+      </c>
+      <c r="L99" t="str">
+        <v/>
+      </c>
+      <c r="M99" t="str">
+        <v/>
+      </c>
+      <c r="N99" t="str">
+        <v/>
+      </c>
+      <c r="O99" t="str">
+        <v/>
+      </c>
+      <c r="P99" t="str">
+        <v/>
+      </c>
+      <c r="Q99" t="str">
+        <v/>
+      </c>
+      <c r="R99" t="str">
+        <v/>
+      </c>
+      <c r="S99" t="str">
+        <v/>
+      </c>
+      <c r="T99" t="str">
+        <v/>
+      </c>
+      <c r="U99" t="str">
+        <v/>
+      </c>
+      <c r="V99" t="str">
+        <v/>
+      </c>
+      <c r="W99" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>סטריי קידס DO IT EP</v>
+      </c>
+      <c r="B100" t="str">
+        <v>2025-12-04</v>
+      </c>
+      <c r="C100" t="str">
+        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
+      </c>
+      <c r="D100" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E100" t="str">
+        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
+      </c>
+      <c r="F100" t="str">
+        <v/>
+      </c>
+      <c r="G100" t="str">
+        <v/>
+      </c>
+      <c r="H100" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I100" t="str">
+        <v/>
+      </c>
+      <c r="J100" t="str">
+        <v/>
+      </c>
+      <c r="K100" t="str">
+        <v>סטריי קידס DO IT EP</v>
+      </c>
+      <c r="L100" t="str">
+        <v/>
+      </c>
+      <c r="M100" t="str">
+        <v/>
+      </c>
+      <c r="N100" t="str">
+        <v/>
+      </c>
+      <c r="O100" t="str">
+        <v/>
+      </c>
+      <c r="P100" t="str">
+        <v/>
+      </c>
+      <c r="Q100" t="str">
+        <v/>
+      </c>
+      <c r="R100" t="str">
+        <v/>
+      </c>
+      <c r="S100" t="str">
+        <v/>
+      </c>
+      <c r="T100" t="str">
+        <v/>
+      </c>
+      <c r="U100" t="str">
+        <v/>
+      </c>
+      <c r="V100" t="str">
+        <v/>
+      </c>
+      <c r="W100" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>דויד ברוזה BROZAJAZZ</v>
+      </c>
+      <c r="B101" t="str">
+        <v>2025-11-30</v>
+      </c>
+      <c r="C101" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
+      </c>
+      <c r="D101" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E101" t="str">
+        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
+      </c>
+      <c r="F101" t="str">
+        <v/>
+      </c>
+      <c r="G101" t="str">
+        <v/>
+      </c>
+      <c r="H101" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I101" t="str">
+        <v/>
+      </c>
+      <c r="J101" t="str">
+        <v/>
+      </c>
+      <c r="K101" t="str">
+        <v>דויד ברוזה BROZAJAZZ</v>
+      </c>
+      <c r="L101" t="str">
+        <v/>
+      </c>
+      <c r="M101" t="str">
+        <v/>
+      </c>
+      <c r="N101" t="str">
+        <v/>
+      </c>
+      <c r="O101" t="str">
+        <v/>
+      </c>
+      <c r="P101" t="str">
+        <v/>
+      </c>
+      <c r="Q101" t="str">
+        <v/>
+      </c>
+      <c r="R101" t="str">
+        <v/>
+      </c>
+      <c r="S101" t="str">
+        <v/>
+      </c>
+      <c r="T101" t="str">
+        <v/>
+      </c>
+      <c r="U101" t="str">
+        <v/>
+      </c>
+      <c r="V101" t="str">
+        <v/>
+      </c>
+      <c r="W101" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>Five Seconds of Summer – Everyone's A Star</v>
+      </c>
+      <c r="B102" t="str">
+        <v>2025-11-24</v>
+      </c>
+      <c r="C102" t="str">
+        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
+      </c>
+      <c r="D102" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E102" t="str">
+        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
+      </c>
+      <c r="F102" t="str">
+        <v/>
+      </c>
+      <c r="G102" t="str">
+        <v/>
+      </c>
+      <c r="H102" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I102" t="str">
+        <v/>
+      </c>
+      <c r="J102" t="str">
+        <v/>
+      </c>
+      <c r="K102" t="str">
+        <v>Five Seconds of Summer – Everyone's A Star</v>
+      </c>
+      <c r="L102" t="str">
+        <v/>
+      </c>
+      <c r="M102" t="str">
+        <v/>
+      </c>
+      <c r="N102" t="str">
+        <v/>
+      </c>
+      <c r="O102" t="str">
+        <v/>
+      </c>
+      <c r="P102" t="str">
+        <v/>
+      </c>
+      <c r="Q102" t="str">
+        <v/>
+      </c>
+      <c r="R102" t="str">
+        <v/>
+      </c>
+      <c r="S102" t="str">
+        <v/>
+      </c>
+      <c r="T102" t="str">
+        <v/>
+      </c>
+      <c r="U102" t="str">
+        <v/>
+      </c>
+      <c r="V102" t="str">
+        <v/>
+      </c>
+      <c r="W102" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>התקווה 6 – ויהי אור</v>
+      </c>
+      <c r="B103" t="str">
+        <v>2025-11-20</v>
+      </c>
+      <c r="C103" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
+      </c>
+      <c r="D103" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E103" t="str">
+        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
+      </c>
+      <c r="F103" t="str">
+        <v/>
+      </c>
+      <c r="G103" t="str">
+        <v/>
+      </c>
+      <c r="H103" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I103" t="str">
+        <v/>
+      </c>
+      <c r="J103" t="str">
+        <v/>
+      </c>
+      <c r="K103" t="str">
+        <v>התקווה 6 – ויהי אור</v>
+      </c>
+      <c r="L103" t="str">
+        <v/>
+      </c>
+      <c r="M103" t="str">
+        <v/>
+      </c>
+      <c r="N103" t="str">
+        <v/>
+      </c>
+      <c r="O103" t="str">
+        <v/>
+      </c>
+      <c r="P103" t="str">
+        <v/>
+      </c>
+      <c r="Q103" t="str">
+        <v/>
+      </c>
+      <c r="R103" t="str">
+        <v/>
+      </c>
+      <c r="S103" t="str">
+        <v/>
+      </c>
+      <c r="T103" t="str">
+        <v/>
+      </c>
+      <c r="U103" t="str">
+        <v/>
+      </c>
+      <c r="V103" t="str">
+        <v/>
+      </c>
+      <c r="W103" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>פלורנס אנד דה משין Everybody Scream</v>
+      </c>
+      <c r="B104" t="str">
+        <v>2025-11-13</v>
+      </c>
+      <c r="C104" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
+      </c>
+      <c r="D104" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E104" t="str">
+        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
+      </c>
+      <c r="F104" t="str">
+        <v/>
+      </c>
+      <c r="G104" t="str">
+        <v/>
+      </c>
+      <c r="H104" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I104" t="str">
+        <v/>
+      </c>
+      <c r="J104" t="str">
+        <v/>
+      </c>
+      <c r="K104" t="str">
+        <v>פלורנס אנד דה משין Everybody Scream</v>
+      </c>
+      <c r="L104" t="str">
+        <v/>
+      </c>
+      <c r="M104" t="str">
+        <v/>
+      </c>
+      <c r="N104" t="str">
+        <v/>
+      </c>
+      <c r="O104" t="str">
+        <v/>
+      </c>
+      <c r="P104" t="str">
+        <v/>
+      </c>
+      <c r="Q104" t="str">
+        <v/>
+      </c>
+      <c r="R104" t="str">
+        <v/>
+      </c>
+      <c r="S104" t="str">
+        <v/>
+      </c>
+      <c r="T104" t="str">
+        <v/>
+      </c>
+      <c r="U104" t="str">
+        <v/>
+      </c>
+      <c r="V104" t="str">
+        <v/>
+      </c>
+      <c r="W104" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>טיים אימפלה Deadbeat</v>
+      </c>
+      <c r="B105" t="str">
+        <v>2025-11-03</v>
+      </c>
+      <c r="C105" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
+      </c>
+      <c r="D105" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E105" t="str">
+        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
+      </c>
+      <c r="F105" t="str">
+        <v/>
+      </c>
+      <c r="G105" t="str">
+        <v/>
+      </c>
+      <c r="H105" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I105" t="str">
+        <v/>
+      </c>
+      <c r="J105" t="str">
+        <v/>
+      </c>
+      <c r="K105" t="str">
+        <v>טיים אימפלה Deadbeat</v>
+      </c>
+      <c r="L105" t="str">
+        <v/>
+      </c>
+      <c r="M105" t="str">
+        <v/>
+      </c>
+      <c r="N105" t="str">
+        <v/>
+      </c>
+      <c r="O105" t="str">
+        <v/>
+      </c>
+      <c r="P105" t="str">
+        <v/>
+      </c>
+      <c r="Q105" t="str">
+        <v/>
+      </c>
+      <c r="R105" t="str">
+        <v/>
+      </c>
+      <c r="S105" t="str">
+        <v/>
+      </c>
+      <c r="T105" t="str">
+        <v/>
+      </c>
+      <c r="U105" t="str">
+        <v/>
+      </c>
+      <c r="V105" t="str">
+        <v/>
+      </c>
+      <c r="W105" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+      </c>
+      <c r="B106" t="str">
+        <v>2025-10-20</v>
+      </c>
+      <c r="C106" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
+      </c>
+      <c r="D106" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E106" t="str">
+        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
+      </c>
+      <c r="F106" t="str">
+        <v/>
+      </c>
+      <c r="G106" t="str">
+        <v/>
+      </c>
+      <c r="H106" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I106" t="str">
+        <v/>
+      </c>
+      <c r="J106" t="str">
+        <v/>
+      </c>
+      <c r="K106" t="str">
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+      </c>
+      <c r="L106" t="str">
+        <v/>
+      </c>
+      <c r="M106" t="str">
+        <v/>
+      </c>
+      <c r="N106" t="str">
+        <v/>
+      </c>
+      <c r="O106" t="str">
+        <v/>
+      </c>
+      <c r="P106" t="str">
+        <v/>
+      </c>
+      <c r="Q106" t="str">
+        <v/>
+      </c>
+      <c r="R106" t="str">
+        <v/>
+      </c>
+      <c r="S106" t="str">
+        <v/>
+      </c>
+      <c r="T106" t="str">
+        <v/>
+      </c>
+      <c r="U106" t="str">
+        <v/>
+      </c>
+      <c r="V106" t="str">
+        <v/>
+      </c>
+      <c r="W106" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>שלמה גרוניך – תודה אהבה</v>
+      </c>
+      <c r="B107" t="str">
+        <v>2025-10-18</v>
+      </c>
+      <c r="C107" t="str">
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
+      </c>
+      <c r="D107" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E107" t="str">
+        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
+      </c>
+      <c r="F107" t="str">
+        <v/>
+      </c>
+      <c r="G107" t="str">
+        <v/>
+      </c>
+      <c r="H107" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I107" t="str">
+        <v/>
+      </c>
+      <c r="J107" t="str">
+        <v/>
+      </c>
+      <c r="K107" t="str">
+        <v>שלמה גרוניך – תודה אהבה</v>
+      </c>
+      <c r="L107" t="str">
+        <v/>
+      </c>
+      <c r="M107" t="str">
+        <v/>
+      </c>
+      <c r="N107" t="str">
+        <v/>
+      </c>
+      <c r="O107" t="str">
+        <v/>
+      </c>
+      <c r="P107" t="str">
+        <v/>
+      </c>
+      <c r="Q107" t="str">
+        <v/>
+      </c>
+      <c r="R107" t="str">
+        <v/>
+      </c>
+      <c r="S107" t="str">
+        <v/>
+      </c>
+      <c r="T107" t="str">
+        <v/>
+      </c>
+      <c r="U107" t="str">
+        <v/>
+      </c>
+      <c r="V107" t="str">
+        <v/>
+      </c>
+      <c r="W107" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
+      </c>
+      <c r="B108" t="str">
+        <v>2025-10-11</v>
+      </c>
+      <c r="C108" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
+      </c>
+      <c r="D108" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E108" t="str">
+        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
+      </c>
+      <c r="F108" t="str">
+        <v/>
+      </c>
+      <c r="G108" t="str">
+        <v/>
+      </c>
+      <c r="H108" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I108" t="str">
+        <v/>
+      </c>
+      <c r="J108" t="str">
+        <v/>
+      </c>
+      <c r="K108" t="str">
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
+      </c>
+      <c r="L108" t="str">
+        <v/>
+      </c>
+      <c r="M108" t="str">
+        <v/>
+      </c>
+      <c r="N108" t="str">
+        <v/>
+      </c>
+      <c r="O108" t="str">
+        <v/>
+      </c>
+      <c r="P108" t="str">
+        <v/>
+      </c>
+      <c r="Q108" t="str">
+        <v/>
+      </c>
+      <c r="R108" t="str">
+        <v/>
+      </c>
+      <c r="S108" t="str">
+        <v/>
+      </c>
+      <c r="T108" t="str">
+        <v/>
+      </c>
+      <c r="U108" t="str">
+        <v/>
+      </c>
+      <c r="V108" t="str">
+        <v/>
+      </c>
+      <c r="W108" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>דוג'ה קאט Vie</v>
+      </c>
+      <c r="B109" t="str">
+        <v>2025-10-04</v>
+      </c>
+      <c r="C109" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
+      </c>
+      <c r="D109" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E109" t="str">
+        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
+      </c>
+      <c r="F109" t="str">
+        <v/>
+      </c>
+      <c r="G109" t="str">
+        <v/>
+      </c>
+      <c r="H109" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I109" t="str">
+        <v/>
+      </c>
+      <c r="J109" t="str">
+        <v/>
+      </c>
+      <c r="K109" t="str">
+        <v>דוג'ה קאט Vie</v>
+      </c>
+      <c r="L109" t="str">
+        <v/>
+      </c>
+      <c r="M109" t="str">
+        <v/>
+      </c>
+      <c r="N109" t="str">
+        <v/>
+      </c>
+      <c r="O109" t="str">
+        <v/>
+      </c>
+      <c r="P109" t="str">
+        <v/>
+      </c>
+      <c r="Q109" t="str">
+        <v/>
+      </c>
+      <c r="R109" t="str">
+        <v/>
+      </c>
+      <c r="S109" t="str">
+        <v/>
+      </c>
+      <c r="T109" t="str">
+        <v/>
+      </c>
+      <c r="U109" t="str">
+        <v/>
+      </c>
+      <c r="V109" t="str">
+        <v/>
+      </c>
+      <c r="W109" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>ג'וי קרוקס Juniper</v>
+      </c>
+      <c r="B110" t="str">
+        <v>2025-10-03</v>
+      </c>
+      <c r="C110" t="str">
+        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
+      </c>
+      <c r="D110" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E110" t="str">
+        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
+      </c>
+      <c r="F110" t="str">
+        <v/>
+      </c>
+      <c r="G110" t="str">
+        <v/>
+      </c>
+      <c r="H110" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I110" t="str">
+        <v/>
+      </c>
+      <c r="J110" t="str">
+        <v/>
+      </c>
+      <c r="K110" t="str">
+        <v>ג'וי קרוקס Juniper</v>
+      </c>
+      <c r="L110" t="str">
+        <v/>
+      </c>
+      <c r="M110" t="str">
+        <v/>
+      </c>
+      <c r="N110" t="str">
+        <v/>
+      </c>
+      <c r="O110" t="str">
+        <v/>
+      </c>
+      <c r="P110" t="str">
+        <v/>
+      </c>
+      <c r="Q110" t="str">
+        <v/>
+      </c>
+      <c r="R110" t="str">
+        <v/>
+      </c>
+      <c r="S110" t="str">
+        <v/>
+      </c>
+      <c r="T110" t="str">
+        <v/>
+      </c>
+      <c r="U110" t="str">
+        <v/>
+      </c>
+      <c r="V110" t="str">
+        <v/>
+      </c>
+      <c r="W110" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>ביפי קליירו Futique</v>
+      </c>
+      <c r="B111" t="str">
+        <v>2025-09-30</v>
+      </c>
+      <c r="C111" t="str">
+        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
+      </c>
+      <c r="D111" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E111" t="str">
+        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
+      </c>
+      <c r="F111" t="str">
+        <v/>
+      </c>
+      <c r="G111" t="str">
+        <v/>
+      </c>
+      <c r="H111" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I111" t="str">
+        <v/>
+      </c>
+      <c r="J111" t="str">
+        <v/>
+      </c>
+      <c r="K111" t="str">
+        <v>ביפי קליירו Futique</v>
+      </c>
+      <c r="L111" t="str">
+        <v/>
+      </c>
+      <c r="M111" t="str">
+        <v/>
+      </c>
+      <c r="N111" t="str">
+        <v/>
+      </c>
+      <c r="O111" t="str">
+        <v/>
+      </c>
+      <c r="P111" t="str">
+        <v/>
+      </c>
+      <c r="Q111" t="str">
+        <v/>
+      </c>
+      <c r="R111" t="str">
+        <v/>
+      </c>
+      <c r="S111" t="str">
+        <v/>
+      </c>
+      <c r="T111" t="str">
+        <v/>
+      </c>
+      <c r="U111" t="str">
+        <v/>
+      </c>
+      <c r="V111" t="str">
+        <v/>
+      </c>
+      <c r="W111" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>אד שירן Play</v>
+      </c>
+      <c r="B112" t="str">
+        <v>2025-09-24</v>
+      </c>
+      <c r="C112" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
+      </c>
+      <c r="D112" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E112" t="str">
+        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
+      </c>
+      <c r="F112" t="str">
+        <v/>
+      </c>
+      <c r="G112" t="str">
+        <v/>
+      </c>
+      <c r="H112" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I112" t="str">
+        <v/>
+      </c>
+      <c r="J112" t="str">
+        <v/>
+      </c>
+      <c r="K112" t="str">
+        <v>אד שירן Play</v>
+      </c>
+      <c r="L112" t="str">
+        <v/>
+      </c>
+      <c r="M112" t="str">
+        <v/>
+      </c>
+      <c r="N112" t="str">
+        <v/>
+      </c>
+      <c r="O112" t="str">
+        <v/>
+      </c>
+      <c r="P112" t="str">
+        <v/>
+      </c>
+      <c r="Q112" t="str">
+        <v/>
+      </c>
+      <c r="R112" t="str">
+        <v/>
+      </c>
+      <c r="S112" t="str">
+        <v/>
+      </c>
+      <c r="T112" t="str">
+        <v/>
+      </c>
+      <c r="U112" t="str">
+        <v/>
+      </c>
+      <c r="V112" t="str">
+        <v/>
+      </c>
+      <c r="W112" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+      </c>
+      <c r="B113" t="str">
+        <v>2025-09-21</v>
+      </c>
+      <c r="C113" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
+      </c>
+      <c r="D113" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E113" t="str">
+        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
+      </c>
+      <c r="F113" t="str">
+        <v/>
+      </c>
+      <c r="G113" t="str">
+        <v/>
+      </c>
+      <c r="H113" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I113" t="str">
+        <v/>
+      </c>
+      <c r="J113" t="str">
+        <v/>
+      </c>
+      <c r="K113" t="str">
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+      </c>
+      <c r="L113" t="str">
+        <v/>
+      </c>
+      <c r="M113" t="str">
+        <v/>
+      </c>
+      <c r="N113" t="str">
+        <v/>
+      </c>
+      <c r="O113" t="str">
+        <v/>
+      </c>
+      <c r="P113" t="str">
+        <v/>
+      </c>
+      <c r="Q113" t="str">
+        <v/>
+      </c>
+      <c r="R113" t="str">
+        <v/>
+      </c>
+      <c r="S113" t="str">
+        <v/>
+      </c>
+      <c r="T113" t="str">
+        <v/>
+      </c>
+      <c r="U113" t="str">
+        <v/>
+      </c>
+      <c r="V113" t="str">
+        <v/>
+      </c>
+      <c r="W113" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>סוויד Antidepressants</v>
+      </c>
+      <c r="B114" t="str">
+        <v>2025-09-12</v>
+      </c>
+      <c r="C114" t="str">
+        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
+      </c>
+      <c r="D114" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E114" t="str">
+        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
+      </c>
+      <c r="F114" t="str">
+        <v/>
+      </c>
+      <c r="G114" t="str">
+        <v/>
+      </c>
+      <c r="H114" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I114" t="str">
+        <v/>
+      </c>
+      <c r="J114" t="str">
+        <v/>
+      </c>
+      <c r="K114" t="str">
+        <v>סוויד Antidepressants</v>
+      </c>
+      <c r="L114" t="str">
+        <v/>
+      </c>
+      <c r="M114" t="str">
+        <v/>
+      </c>
+      <c r="N114" t="str">
+        <v/>
+      </c>
+      <c r="O114" t="str">
+        <v/>
+      </c>
+      <c r="P114" t="str">
+        <v/>
+      </c>
+      <c r="Q114" t="str">
+        <v/>
+      </c>
+      <c r="R114" t="str">
+        <v/>
+      </c>
+      <c r="S114" t="str">
+        <v/>
+      </c>
+      <c r="T114" t="str">
+        <v/>
+      </c>
+      <c r="U114" t="str">
+        <v/>
+      </c>
+      <c r="V114" t="str">
+        <v/>
+      </c>
+      <c r="W114" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>וולף אליס The Clearing</v>
+      </c>
+      <c r="B115" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="C115" t="str">
+        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
+      </c>
+      <c r="D115" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E115" t="str">
+        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
+      </c>
+      <c r="F115" t="str">
+        <v/>
+      </c>
+      <c r="G115" t="str">
+        <v/>
+      </c>
+      <c r="H115" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I115" t="str">
+        <v/>
+      </c>
+      <c r="J115" t="str">
+        <v/>
+      </c>
+      <c r="K115" t="str">
+        <v>וולף אליס The Clearing</v>
+      </c>
+      <c r="L115" t="str">
+        <v/>
+      </c>
+      <c r="M115" t="str">
+        <v/>
+      </c>
+      <c r="N115" t="str">
+        <v/>
+      </c>
+      <c r="O115" t="str">
+        <v/>
+      </c>
+      <c r="P115" t="str">
+        <v/>
+      </c>
+      <c r="Q115" t="str">
+        <v/>
+      </c>
+      <c r="R115" t="str">
+        <v/>
+      </c>
+      <c r="S115" t="str">
+        <v/>
+      </c>
+      <c r="T115" t="str">
+        <v/>
+      </c>
+      <c r="U115" t="str">
+        <v/>
+      </c>
+      <c r="V115" t="str">
+        <v/>
+      </c>
+      <c r="W115" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+      </c>
+      <c r="B116" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="C116" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
+      </c>
+      <c r="D116" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E116" t="str">
+        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
+      </c>
+      <c r="F116" t="str">
+        <v/>
+      </c>
+      <c r="G116" t="str">
+        <v/>
+      </c>
+      <c r="H116" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I116" t="str">
+        <v/>
+      </c>
+      <c r="J116" t="str">
+        <v/>
+      </c>
+      <c r="K116" t="str">
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+      </c>
+      <c r="L116" t="str">
+        <v/>
+      </c>
+      <c r="M116" t="str">
+        <v/>
+      </c>
+      <c r="N116" t="str">
+        <v/>
+      </c>
+      <c r="O116" t="str">
+        <v/>
+      </c>
+      <c r="P116" t="str">
+        <v/>
+      </c>
+      <c r="Q116" t="str">
+        <v/>
+      </c>
+      <c r="R116" t="str">
+        <v/>
+      </c>
+      <c r="S116" t="str">
+        <v/>
+      </c>
+      <c r="T116" t="str">
+        <v/>
+      </c>
+      <c r="U116" t="str">
+        <v/>
+      </c>
+      <c r="V116" t="str">
+        <v/>
+      </c>
+      <c r="W116" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+      </c>
+      <c r="B117" t="str">
+        <v>2025-08-24</v>
+      </c>
+      <c r="C117" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
+      </c>
+      <c r="D117" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E117" t="str">
+        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
+      </c>
+      <c r="F117" t="str">
+        <v/>
+      </c>
+      <c r="G117" t="str">
+        <v/>
+      </c>
+      <c r="H117" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I117" t="str">
+        <v/>
+      </c>
+      <c r="J117" t="str">
+        <v/>
+      </c>
+      <c r="K117" t="str">
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+      </c>
+      <c r="L117" t="str">
+        <v/>
+      </c>
+      <c r="M117" t="str">
+        <v/>
+      </c>
+      <c r="N117" t="str">
+        <v/>
+      </c>
+      <c r="O117" t="str">
+        <v/>
+      </c>
+      <c r="P117" t="str">
+        <v/>
+      </c>
+      <c r="Q117" t="str">
+        <v/>
+      </c>
+      <c r="R117" t="str">
+        <v/>
+      </c>
+      <c r="S117" t="str">
+        <v/>
+      </c>
+      <c r="T117" t="str">
+        <v/>
+      </c>
+      <c r="U117" t="str">
+        <v/>
+      </c>
+      <c r="V117" t="str">
+        <v/>
+      </c>
+      <c r="W117" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+      </c>
+      <c r="B118" t="str">
+        <v>2025-08-21</v>
+      </c>
+      <c r="C118" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
+      </c>
+      <c r="D118" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E118" t="str">
+        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
+      </c>
+      <c r="F118" t="str">
+        <v/>
+      </c>
+      <c r="G118" t="str">
+        <v/>
+      </c>
+      <c r="H118" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I118" t="str">
+        <v/>
+      </c>
+      <c r="J118" t="str">
+        <v/>
+      </c>
+      <c r="K118" t="str">
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+      </c>
+      <c r="L118" t="str">
+        <v/>
+      </c>
+      <c r="M118" t="str">
+        <v/>
+      </c>
+      <c r="N118" t="str">
+        <v/>
+      </c>
+      <c r="O118" t="str">
+        <v/>
+      </c>
+      <c r="P118" t="str">
+        <v/>
+      </c>
+      <c r="Q118" t="str">
+        <v/>
+      </c>
+      <c r="R118" t="str">
+        <v/>
+      </c>
+      <c r="S118" t="str">
+        <v/>
+      </c>
+      <c r="T118" t="str">
+        <v/>
+      </c>
+      <c r="U118" t="str">
+        <v/>
+      </c>
+      <c r="V118" t="str">
+        <v/>
+      </c>
+      <c r="W118" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>אברהם טל – חי</v>
+      </c>
+      <c r="B119" t="str">
+        <v>2025-08-17</v>
+      </c>
+      <c r="C119" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
+      </c>
+      <c r="D119" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E119" t="str">
+        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
+      </c>
+      <c r="F119" t="str">
+        <v/>
+      </c>
+      <c r="G119" t="str">
+        <v/>
+      </c>
+      <c r="H119" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I119" t="str">
+        <v/>
+      </c>
+      <c r="J119" t="str">
+        <v/>
+      </c>
+      <c r="K119" t="str">
+        <v>אברהם טל – חי</v>
+      </c>
+      <c r="L119" t="str">
+        <v/>
+      </c>
+      <c r="M119" t="str">
+        <v/>
+      </c>
+      <c r="N119" t="str">
+        <v/>
+      </c>
+      <c r="O119" t="str">
+        <v/>
+      </c>
+      <c r="P119" t="str">
+        <v/>
+      </c>
+      <c r="Q119" t="str">
+        <v/>
+      </c>
+      <c r="R119" t="str">
+        <v/>
+      </c>
+      <c r="S119" t="str">
+        <v/>
+      </c>
+      <c r="T119" t="str">
+        <v/>
+      </c>
+      <c r="U119" t="str">
+        <v/>
+      </c>
+      <c r="V119" t="str">
+        <v/>
+      </c>
+      <c r="W119" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>רנה ראפ Bite Me</v>
+      </c>
+      <c r="B120" t="str">
+        <v>2025-08-12</v>
+      </c>
+      <c r="C120" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
+      </c>
+      <c r="D120" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E120" t="str">
+        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
+      </c>
+      <c r="F120" t="str">
+        <v/>
+      </c>
+      <c r="G120" t="str">
+        <v/>
+      </c>
+      <c r="H120" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I120" t="str">
+        <v/>
+      </c>
+      <c r="J120" t="str">
+        <v/>
+      </c>
+      <c r="K120" t="str">
+        <v>רנה ראפ Bite Me</v>
+      </c>
+      <c r="L120" t="str">
+        <v/>
+      </c>
+      <c r="M120" t="str">
+        <v/>
+      </c>
+      <c r="N120" t="str">
+        <v/>
+      </c>
+      <c r="O120" t="str">
+        <v/>
+      </c>
+      <c r="P120" t="str">
+        <v/>
+      </c>
+      <c r="Q120" t="str">
+        <v/>
+      </c>
+      <c r="R120" t="str">
+        <v/>
+      </c>
+      <c r="S120" t="str">
+        <v/>
+      </c>
+      <c r="T120" t="str">
+        <v/>
+      </c>
+      <c r="U120" t="str">
+        <v/>
+      </c>
+      <c r="V120" t="str">
+        <v/>
+      </c>
+      <c r="W120" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>The K's – Pretty On The Internet</v>
+      </c>
+      <c r="B121" t="str">
+        <v>2025-08-03</v>
+      </c>
+      <c r="C121" t="str">
+        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
+      </c>
+      <c r="D121" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E121" t="str">
+        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
+      </c>
+      <c r="F121" t="str">
+        <v/>
+      </c>
+      <c r="G121" t="str">
+        <v/>
+      </c>
+      <c r="H121" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I121" t="str">
+        <v/>
+      </c>
+      <c r="J121" t="str">
+        <v/>
+      </c>
+      <c r="K121" t="str">
+        <v>The K's – Pretty On The Internet</v>
+      </c>
+      <c r="L121" t="str">
+        <v/>
+      </c>
+      <c r="M121" t="str">
+        <v/>
+      </c>
+      <c r="N121" t="str">
+        <v/>
+      </c>
+      <c r="O121" t="str">
+        <v/>
+      </c>
+      <c r="P121" t="str">
+        <v/>
+      </c>
+      <c r="Q121" t="str">
+        <v/>
+      </c>
+      <c r="R121" t="str">
+        <v/>
+      </c>
+      <c r="S121" t="str">
+        <v/>
+      </c>
+      <c r="T121" t="str">
+        <v/>
+      </c>
+      <c r="U121" t="str">
+        <v/>
+      </c>
+      <c r="V121" t="str">
+        <v/>
+      </c>
+      <c r="W121" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S91"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:W121"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W121"/>
+  <dimension ref="A1:AA151"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6794,9 +6794,2499 @@
         <v/>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>פטריק סבג Hotel Mogador</v>
+      </c>
+      <c r="B122" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C122" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
+      </c>
+      <c r="D122" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E122" t="str">
+        <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
+      </c>
+      <c r="F122" t="str">
+        <v/>
+      </c>
+      <c r="G122" t="str">
+        <v/>
+      </c>
+      <c r="H122" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I122" t="str">
+        <v/>
+      </c>
+      <c r="J122" t="str">
+        <v/>
+      </c>
+      <c r="K122" t="str">
+        <v>פטריק סבג Hotel Mogador</v>
+      </c>
+      <c r="L122" t="str">
+        <v/>
+      </c>
+      <c r="M122" t="str">
+        <v/>
+      </c>
+      <c r="N122" t="str">
+        <v/>
+      </c>
+      <c r="O122" t="str">
+        <v/>
+      </c>
+      <c r="P122" t="str">
+        <v/>
+      </c>
+      <c r="Q122" t="str">
+        <v/>
+      </c>
+      <c r="R122" t="str">
+        <v/>
+      </c>
+      <c r="S122" t="str">
+        <v/>
+      </c>
+      <c r="T122" t="str">
+        <v/>
+      </c>
+      <c r="U122" t="str">
+        <v/>
+      </c>
+      <c r="V122" t="str">
+        <v/>
+      </c>
+      <c r="W122" t="str">
+        <v/>
+      </c>
+      <c r="X122" t="str">
+        <v/>
+      </c>
+      <c r="Y122" t="str">
+        <v/>
+      </c>
+      <c r="Z122" t="str">
+        <v/>
+      </c>
+      <c r="AA122" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
+      </c>
+      <c r="B123" t="str">
+        <v>2026-01-09</v>
+      </c>
+      <c r="C123" t="str">
+        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
+      </c>
+      <c r="D123" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E123" t="str">
+        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
+      </c>
+      <c r="F123" t="str">
+        <v/>
+      </c>
+      <c r="G123" t="str">
+        <v/>
+      </c>
+      <c r="H123" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I123" t="str">
+        <v/>
+      </c>
+      <c r="J123" t="str">
+        <v/>
+      </c>
+      <c r="K123" t="str">
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
+      </c>
+      <c r="L123" t="str">
+        <v/>
+      </c>
+      <c r="M123" t="str">
+        <v/>
+      </c>
+      <c r="N123" t="str">
+        <v/>
+      </c>
+      <c r="O123" t="str">
+        <v/>
+      </c>
+      <c r="P123" t="str">
+        <v/>
+      </c>
+      <c r="Q123" t="str">
+        <v/>
+      </c>
+      <c r="R123" t="str">
+        <v/>
+      </c>
+      <c r="S123" t="str">
+        <v/>
+      </c>
+      <c r="T123" t="str">
+        <v/>
+      </c>
+      <c r="U123" t="str">
+        <v/>
+      </c>
+      <c r="V123" t="str">
+        <v/>
+      </c>
+      <c r="W123" t="str">
+        <v/>
+      </c>
+      <c r="X123" t="str">
+        <v/>
+      </c>
+      <c r="Y123" t="str">
+        <v/>
+      </c>
+      <c r="Z123" t="str">
+        <v/>
+      </c>
+      <c r="AA123" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>אוליביה דין The Art of Loving</v>
+      </c>
+      <c r="B124" t="str">
+        <v>2026-01-04</v>
+      </c>
+      <c r="C124" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
+      </c>
+      <c r="D124" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E124" t="str">
+        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
+      </c>
+      <c r="F124" t="str">
+        <v/>
+      </c>
+      <c r="G124" t="str">
+        <v/>
+      </c>
+      <c r="H124" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I124" t="str">
+        <v/>
+      </c>
+      <c r="J124" t="str">
+        <v/>
+      </c>
+      <c r="K124" t="str">
+        <v>אוליביה דין The Art of Loving</v>
+      </c>
+      <c r="L124" t="str">
+        <v/>
+      </c>
+      <c r="M124" t="str">
+        <v/>
+      </c>
+      <c r="N124" t="str">
+        <v/>
+      </c>
+      <c r="O124" t="str">
+        <v/>
+      </c>
+      <c r="P124" t="str">
+        <v/>
+      </c>
+      <c r="Q124" t="str">
+        <v/>
+      </c>
+      <c r="R124" t="str">
+        <v/>
+      </c>
+      <c r="S124" t="str">
+        <v/>
+      </c>
+      <c r="T124" t="str">
+        <v/>
+      </c>
+      <c r="U124" t="str">
+        <v/>
+      </c>
+      <c r="V124" t="str">
+        <v/>
+      </c>
+      <c r="W124" t="str">
+        <v/>
+      </c>
+      <c r="X124" t="str">
+        <v/>
+      </c>
+      <c r="Y124" t="str">
+        <v/>
+      </c>
+      <c r="Z124" t="str">
+        <v/>
+      </c>
+      <c r="AA124" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>Geese Getting Killed</v>
+      </c>
+      <c r="B125" t="str">
+        <v>2025-12-29</v>
+      </c>
+      <c r="C125" t="str">
+        <v>https://yosmusic.com/geese-getting-killed/</v>
+      </c>
+      <c r="D125" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E125" t="str">
+        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
+      </c>
+      <c r="F125" t="str">
+        <v/>
+      </c>
+      <c r="G125" t="str">
+        <v/>
+      </c>
+      <c r="H125" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I125" t="str">
+        <v/>
+      </c>
+      <c r="J125" t="str">
+        <v/>
+      </c>
+      <c r="K125" t="str">
+        <v>Geese Getting Killed</v>
+      </c>
+      <c r="L125" t="str">
+        <v/>
+      </c>
+      <c r="M125" t="str">
+        <v/>
+      </c>
+      <c r="N125" t="str">
+        <v/>
+      </c>
+      <c r="O125" t="str">
+        <v/>
+      </c>
+      <c r="P125" t="str">
+        <v/>
+      </c>
+      <c r="Q125" t="str">
+        <v/>
+      </c>
+      <c r="R125" t="str">
+        <v/>
+      </c>
+      <c r="S125" t="str">
+        <v/>
+      </c>
+      <c r="T125" t="str">
+        <v/>
+      </c>
+      <c r="U125" t="str">
+        <v/>
+      </c>
+      <c r="V125" t="str">
+        <v/>
+      </c>
+      <c r="W125" t="str">
+        <v/>
+      </c>
+      <c r="X125" t="str">
+        <v/>
+      </c>
+      <c r="Y125" t="str">
+        <v/>
+      </c>
+      <c r="Z125" t="str">
+        <v/>
+      </c>
+      <c r="AA125" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>רוסליה Lux</v>
+      </c>
+      <c r="B126" t="str">
+        <v>2025-12-25</v>
+      </c>
+      <c r="C126" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
+      </c>
+      <c r="D126" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E126" t="str">
+        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
+      </c>
+      <c r="F126" t="str">
+        <v/>
+      </c>
+      <c r="G126" t="str">
+        <v/>
+      </c>
+      <c r="H126" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I126" t="str">
+        <v/>
+      </c>
+      <c r="J126" t="str">
+        <v/>
+      </c>
+      <c r="K126" t="str">
+        <v>רוסליה Lux</v>
+      </c>
+      <c r="L126" t="str">
+        <v/>
+      </c>
+      <c r="M126" t="str">
+        <v/>
+      </c>
+      <c r="N126" t="str">
+        <v/>
+      </c>
+      <c r="O126" t="str">
+        <v/>
+      </c>
+      <c r="P126" t="str">
+        <v/>
+      </c>
+      <c r="Q126" t="str">
+        <v/>
+      </c>
+      <c r="R126" t="str">
+        <v/>
+      </c>
+      <c r="S126" t="str">
+        <v/>
+      </c>
+      <c r="T126" t="str">
+        <v/>
+      </c>
+      <c r="U126" t="str">
+        <v/>
+      </c>
+      <c r="V126" t="str">
+        <v/>
+      </c>
+      <c r="W126" t="str">
+        <v/>
+      </c>
+      <c r="X126" t="str">
+        <v/>
+      </c>
+      <c r="Y126" t="str">
+        <v/>
+      </c>
+      <c r="Z126" t="str">
+        <v/>
+      </c>
+      <c r="AA126" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>יאנגבלאד אירוסמית' one more time</v>
+      </c>
+      <c r="B127" t="str">
+        <v>2025-12-17</v>
+      </c>
+      <c r="C127" t="str">
+        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
+      </c>
+      <c r="D127" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E127" t="str">
+        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
+      </c>
+      <c r="F127" t="str">
+        <v/>
+      </c>
+      <c r="G127" t="str">
+        <v/>
+      </c>
+      <c r="H127" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I127" t="str">
+        <v/>
+      </c>
+      <c r="J127" t="str">
+        <v/>
+      </c>
+      <c r="K127" t="str">
+        <v>יאנגבלאד אירוסמית' one more time</v>
+      </c>
+      <c r="L127" t="str">
+        <v/>
+      </c>
+      <c r="M127" t="str">
+        <v/>
+      </c>
+      <c r="N127" t="str">
+        <v/>
+      </c>
+      <c r="O127" t="str">
+        <v/>
+      </c>
+      <c r="P127" t="str">
+        <v/>
+      </c>
+      <c r="Q127" t="str">
+        <v/>
+      </c>
+      <c r="R127" t="str">
+        <v/>
+      </c>
+      <c r="S127" t="str">
+        <v/>
+      </c>
+      <c r="T127" t="str">
+        <v/>
+      </c>
+      <c r="U127" t="str">
+        <v/>
+      </c>
+      <c r="V127" t="str">
+        <v/>
+      </c>
+      <c r="W127" t="str">
+        <v/>
+      </c>
+      <c r="X127" t="str">
+        <v/>
+      </c>
+      <c r="Y127" t="str">
+        <v/>
+      </c>
+      <c r="Z127" t="str">
+        <v/>
+      </c>
+      <c r="AA127" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>פינק פלויד Wish You Were Here 50</v>
+      </c>
+      <c r="B128" t="str">
+        <v>2025-12-14</v>
+      </c>
+      <c r="C128" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
+      </c>
+      <c r="D128" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E128" t="str">
+        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
+      </c>
+      <c r="F128" t="str">
+        <v/>
+      </c>
+      <c r="G128" t="str">
+        <v/>
+      </c>
+      <c r="H128" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I128" t="str">
+        <v/>
+      </c>
+      <c r="J128" t="str">
+        <v/>
+      </c>
+      <c r="K128" t="str">
+        <v>פינק פלויד Wish You Were Here 50</v>
+      </c>
+      <c r="L128" t="str">
+        <v/>
+      </c>
+      <c r="M128" t="str">
+        <v/>
+      </c>
+      <c r="N128" t="str">
+        <v/>
+      </c>
+      <c r="O128" t="str">
+        <v/>
+      </c>
+      <c r="P128" t="str">
+        <v/>
+      </c>
+      <c r="Q128" t="str">
+        <v/>
+      </c>
+      <c r="R128" t="str">
+        <v/>
+      </c>
+      <c r="S128" t="str">
+        <v/>
+      </c>
+      <c r="T128" t="str">
+        <v/>
+      </c>
+      <c r="U128" t="str">
+        <v/>
+      </c>
+      <c r="V128" t="str">
+        <v/>
+      </c>
+      <c r="W128" t="str">
+        <v/>
+      </c>
+      <c r="X128" t="str">
+        <v/>
+      </c>
+      <c r="Y128" t="str">
+        <v/>
+      </c>
+      <c r="Z128" t="str">
+        <v/>
+      </c>
+      <c r="AA128" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+      </c>
+      <c r="B129" t="str">
+        <v>2025-12-08</v>
+      </c>
+      <c r="C129" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
+      </c>
+      <c r="D129" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E129" t="str">
+        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
+      </c>
+      <c r="F129" t="str">
+        <v/>
+      </c>
+      <c r="G129" t="str">
+        <v/>
+      </c>
+      <c r="H129" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I129" t="str">
+        <v/>
+      </c>
+      <c r="J129" t="str">
+        <v/>
+      </c>
+      <c r="K129" t="str">
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+      </c>
+      <c r="L129" t="str">
+        <v/>
+      </c>
+      <c r="M129" t="str">
+        <v/>
+      </c>
+      <c r="N129" t="str">
+        <v/>
+      </c>
+      <c r="O129" t="str">
+        <v/>
+      </c>
+      <c r="P129" t="str">
+        <v/>
+      </c>
+      <c r="Q129" t="str">
+        <v/>
+      </c>
+      <c r="R129" t="str">
+        <v/>
+      </c>
+      <c r="S129" t="str">
+        <v/>
+      </c>
+      <c r="T129" t="str">
+        <v/>
+      </c>
+      <c r="U129" t="str">
+        <v/>
+      </c>
+      <c r="V129" t="str">
+        <v/>
+      </c>
+      <c r="W129" t="str">
+        <v/>
+      </c>
+      <c r="X129" t="str">
+        <v/>
+      </c>
+      <c r="Y129" t="str">
+        <v/>
+      </c>
+      <c r="Z129" t="str">
+        <v/>
+      </c>
+      <c r="AA129" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>סטריי קידס DO IT EP</v>
+      </c>
+      <c r="B130" t="str">
+        <v>2025-12-04</v>
+      </c>
+      <c r="C130" t="str">
+        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
+      </c>
+      <c r="D130" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E130" t="str">
+        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
+      </c>
+      <c r="F130" t="str">
+        <v/>
+      </c>
+      <c r="G130" t="str">
+        <v/>
+      </c>
+      <c r="H130" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I130" t="str">
+        <v/>
+      </c>
+      <c r="J130" t="str">
+        <v/>
+      </c>
+      <c r="K130" t="str">
+        <v>סטריי קידס DO IT EP</v>
+      </c>
+      <c r="L130" t="str">
+        <v/>
+      </c>
+      <c r="M130" t="str">
+        <v/>
+      </c>
+      <c r="N130" t="str">
+        <v/>
+      </c>
+      <c r="O130" t="str">
+        <v/>
+      </c>
+      <c r="P130" t="str">
+        <v/>
+      </c>
+      <c r="Q130" t="str">
+        <v/>
+      </c>
+      <c r="R130" t="str">
+        <v/>
+      </c>
+      <c r="S130" t="str">
+        <v/>
+      </c>
+      <c r="T130" t="str">
+        <v/>
+      </c>
+      <c r="U130" t="str">
+        <v/>
+      </c>
+      <c r="V130" t="str">
+        <v/>
+      </c>
+      <c r="W130" t="str">
+        <v/>
+      </c>
+      <c r="X130" t="str">
+        <v/>
+      </c>
+      <c r="Y130" t="str">
+        <v/>
+      </c>
+      <c r="Z130" t="str">
+        <v/>
+      </c>
+      <c r="AA130" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>דויד ברוזה BROZAJAZZ</v>
+      </c>
+      <c r="B131" t="str">
+        <v>2025-11-30</v>
+      </c>
+      <c r="C131" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
+      </c>
+      <c r="D131" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E131" t="str">
+        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
+      </c>
+      <c r="F131" t="str">
+        <v/>
+      </c>
+      <c r="G131" t="str">
+        <v/>
+      </c>
+      <c r="H131" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I131" t="str">
+        <v/>
+      </c>
+      <c r="J131" t="str">
+        <v/>
+      </c>
+      <c r="K131" t="str">
+        <v>דויד ברוזה BROZAJAZZ</v>
+      </c>
+      <c r="L131" t="str">
+        <v/>
+      </c>
+      <c r="M131" t="str">
+        <v/>
+      </c>
+      <c r="N131" t="str">
+        <v/>
+      </c>
+      <c r="O131" t="str">
+        <v/>
+      </c>
+      <c r="P131" t="str">
+        <v/>
+      </c>
+      <c r="Q131" t="str">
+        <v/>
+      </c>
+      <c r="R131" t="str">
+        <v/>
+      </c>
+      <c r="S131" t="str">
+        <v/>
+      </c>
+      <c r="T131" t="str">
+        <v/>
+      </c>
+      <c r="U131" t="str">
+        <v/>
+      </c>
+      <c r="V131" t="str">
+        <v/>
+      </c>
+      <c r="W131" t="str">
+        <v/>
+      </c>
+      <c r="X131" t="str">
+        <v/>
+      </c>
+      <c r="Y131" t="str">
+        <v/>
+      </c>
+      <c r="Z131" t="str">
+        <v/>
+      </c>
+      <c r="AA131" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>Five Seconds of Summer – Everyone's A Star</v>
+      </c>
+      <c r="B132" t="str">
+        <v>2025-11-24</v>
+      </c>
+      <c r="C132" t="str">
+        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
+      </c>
+      <c r="D132" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E132" t="str">
+        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
+      </c>
+      <c r="F132" t="str">
+        <v/>
+      </c>
+      <c r="G132" t="str">
+        <v/>
+      </c>
+      <c r="H132" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I132" t="str">
+        <v/>
+      </c>
+      <c r="J132" t="str">
+        <v/>
+      </c>
+      <c r="K132" t="str">
+        <v>Five Seconds of Summer – Everyone's A Star</v>
+      </c>
+      <c r="L132" t="str">
+        <v/>
+      </c>
+      <c r="M132" t="str">
+        <v/>
+      </c>
+      <c r="N132" t="str">
+        <v/>
+      </c>
+      <c r="O132" t="str">
+        <v/>
+      </c>
+      <c r="P132" t="str">
+        <v/>
+      </c>
+      <c r="Q132" t="str">
+        <v/>
+      </c>
+      <c r="R132" t="str">
+        <v/>
+      </c>
+      <c r="S132" t="str">
+        <v/>
+      </c>
+      <c r="T132" t="str">
+        <v/>
+      </c>
+      <c r="U132" t="str">
+        <v/>
+      </c>
+      <c r="V132" t="str">
+        <v/>
+      </c>
+      <c r="W132" t="str">
+        <v/>
+      </c>
+      <c r="X132" t="str">
+        <v/>
+      </c>
+      <c r="Y132" t="str">
+        <v/>
+      </c>
+      <c r="Z132" t="str">
+        <v/>
+      </c>
+      <c r="AA132" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>התקווה 6 – ויהי אור</v>
+      </c>
+      <c r="B133" t="str">
+        <v>2025-11-20</v>
+      </c>
+      <c r="C133" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
+      </c>
+      <c r="D133" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E133" t="str">
+        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
+      </c>
+      <c r="F133" t="str">
+        <v/>
+      </c>
+      <c r="G133" t="str">
+        <v/>
+      </c>
+      <c r="H133" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I133" t="str">
+        <v/>
+      </c>
+      <c r="J133" t="str">
+        <v/>
+      </c>
+      <c r="K133" t="str">
+        <v>התקווה 6 – ויהי אור</v>
+      </c>
+      <c r="L133" t="str">
+        <v/>
+      </c>
+      <c r="M133" t="str">
+        <v/>
+      </c>
+      <c r="N133" t="str">
+        <v/>
+      </c>
+      <c r="O133" t="str">
+        <v/>
+      </c>
+      <c r="P133" t="str">
+        <v/>
+      </c>
+      <c r="Q133" t="str">
+        <v/>
+      </c>
+      <c r="R133" t="str">
+        <v/>
+      </c>
+      <c r="S133" t="str">
+        <v/>
+      </c>
+      <c r="T133" t="str">
+        <v/>
+      </c>
+      <c r="U133" t="str">
+        <v/>
+      </c>
+      <c r="V133" t="str">
+        <v/>
+      </c>
+      <c r="W133" t="str">
+        <v/>
+      </c>
+      <c r="X133" t="str">
+        <v/>
+      </c>
+      <c r="Y133" t="str">
+        <v/>
+      </c>
+      <c r="Z133" t="str">
+        <v/>
+      </c>
+      <c r="AA133" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>פלורנס אנד דה משין Everybody Scream</v>
+      </c>
+      <c r="B134" t="str">
+        <v>2025-11-13</v>
+      </c>
+      <c r="C134" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
+      </c>
+      <c r="D134" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E134" t="str">
+        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
+      </c>
+      <c r="F134" t="str">
+        <v/>
+      </c>
+      <c r="G134" t="str">
+        <v/>
+      </c>
+      <c r="H134" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I134" t="str">
+        <v/>
+      </c>
+      <c r="J134" t="str">
+        <v/>
+      </c>
+      <c r="K134" t="str">
+        <v>פלורנס אנד דה משין Everybody Scream</v>
+      </c>
+      <c r="L134" t="str">
+        <v/>
+      </c>
+      <c r="M134" t="str">
+        <v/>
+      </c>
+      <c r="N134" t="str">
+        <v/>
+      </c>
+      <c r="O134" t="str">
+        <v/>
+      </c>
+      <c r="P134" t="str">
+        <v/>
+      </c>
+      <c r="Q134" t="str">
+        <v/>
+      </c>
+      <c r="R134" t="str">
+        <v/>
+      </c>
+      <c r="S134" t="str">
+        <v/>
+      </c>
+      <c r="T134" t="str">
+        <v/>
+      </c>
+      <c r="U134" t="str">
+        <v/>
+      </c>
+      <c r="V134" t="str">
+        <v/>
+      </c>
+      <c r="W134" t="str">
+        <v/>
+      </c>
+      <c r="X134" t="str">
+        <v/>
+      </c>
+      <c r="Y134" t="str">
+        <v/>
+      </c>
+      <c r="Z134" t="str">
+        <v/>
+      </c>
+      <c r="AA134" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>טיים אימפלה Deadbeat</v>
+      </c>
+      <c r="B135" t="str">
+        <v>2025-11-03</v>
+      </c>
+      <c r="C135" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
+      </c>
+      <c r="D135" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E135" t="str">
+        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
+      </c>
+      <c r="F135" t="str">
+        <v/>
+      </c>
+      <c r="G135" t="str">
+        <v/>
+      </c>
+      <c r="H135" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I135" t="str">
+        <v/>
+      </c>
+      <c r="J135" t="str">
+        <v/>
+      </c>
+      <c r="K135" t="str">
+        <v>טיים אימפלה Deadbeat</v>
+      </c>
+      <c r="L135" t="str">
+        <v/>
+      </c>
+      <c r="M135" t="str">
+        <v/>
+      </c>
+      <c r="N135" t="str">
+        <v/>
+      </c>
+      <c r="O135" t="str">
+        <v/>
+      </c>
+      <c r="P135" t="str">
+        <v/>
+      </c>
+      <c r="Q135" t="str">
+        <v/>
+      </c>
+      <c r="R135" t="str">
+        <v/>
+      </c>
+      <c r="S135" t="str">
+        <v/>
+      </c>
+      <c r="T135" t="str">
+        <v/>
+      </c>
+      <c r="U135" t="str">
+        <v/>
+      </c>
+      <c r="V135" t="str">
+        <v/>
+      </c>
+      <c r="W135" t="str">
+        <v/>
+      </c>
+      <c r="X135" t="str">
+        <v/>
+      </c>
+      <c r="Y135" t="str">
+        <v/>
+      </c>
+      <c r="Z135" t="str">
+        <v/>
+      </c>
+      <c r="AA135" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+      </c>
+      <c r="B136" t="str">
+        <v>2025-10-20</v>
+      </c>
+      <c r="C136" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
+      </c>
+      <c r="D136" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E136" t="str">
+        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
+      </c>
+      <c r="F136" t="str">
+        <v/>
+      </c>
+      <c r="G136" t="str">
+        <v/>
+      </c>
+      <c r="H136" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I136" t="str">
+        <v/>
+      </c>
+      <c r="J136" t="str">
+        <v/>
+      </c>
+      <c r="K136" t="str">
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+      </c>
+      <c r="L136" t="str">
+        <v/>
+      </c>
+      <c r="M136" t="str">
+        <v/>
+      </c>
+      <c r="N136" t="str">
+        <v/>
+      </c>
+      <c r="O136" t="str">
+        <v/>
+      </c>
+      <c r="P136" t="str">
+        <v/>
+      </c>
+      <c r="Q136" t="str">
+        <v/>
+      </c>
+      <c r="R136" t="str">
+        <v/>
+      </c>
+      <c r="S136" t="str">
+        <v/>
+      </c>
+      <c r="T136" t="str">
+        <v/>
+      </c>
+      <c r="U136" t="str">
+        <v/>
+      </c>
+      <c r="V136" t="str">
+        <v/>
+      </c>
+      <c r="W136" t="str">
+        <v/>
+      </c>
+      <c r="X136" t="str">
+        <v/>
+      </c>
+      <c r="Y136" t="str">
+        <v/>
+      </c>
+      <c r="Z136" t="str">
+        <v/>
+      </c>
+      <c r="AA136" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>שלמה גרוניך – תודה אהבה</v>
+      </c>
+      <c r="B137" t="str">
+        <v>2025-10-18</v>
+      </c>
+      <c r="C137" t="str">
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
+      </c>
+      <c r="D137" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E137" t="str">
+        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
+      </c>
+      <c r="F137" t="str">
+        <v/>
+      </c>
+      <c r="G137" t="str">
+        <v/>
+      </c>
+      <c r="H137" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I137" t="str">
+        <v/>
+      </c>
+      <c r="J137" t="str">
+        <v/>
+      </c>
+      <c r="K137" t="str">
+        <v>שלמה גרוניך – תודה אהבה</v>
+      </c>
+      <c r="L137" t="str">
+        <v/>
+      </c>
+      <c r="M137" t="str">
+        <v/>
+      </c>
+      <c r="N137" t="str">
+        <v/>
+      </c>
+      <c r="O137" t="str">
+        <v/>
+      </c>
+      <c r="P137" t="str">
+        <v/>
+      </c>
+      <c r="Q137" t="str">
+        <v/>
+      </c>
+      <c r="R137" t="str">
+        <v/>
+      </c>
+      <c r="S137" t="str">
+        <v/>
+      </c>
+      <c r="T137" t="str">
+        <v/>
+      </c>
+      <c r="U137" t="str">
+        <v/>
+      </c>
+      <c r="V137" t="str">
+        <v/>
+      </c>
+      <c r="W137" t="str">
+        <v/>
+      </c>
+      <c r="X137" t="str">
+        <v/>
+      </c>
+      <c r="Y137" t="str">
+        <v/>
+      </c>
+      <c r="Z137" t="str">
+        <v/>
+      </c>
+      <c r="AA137" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
+      </c>
+      <c r="B138" t="str">
+        <v>2025-10-11</v>
+      </c>
+      <c r="C138" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
+      </c>
+      <c r="D138" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E138" t="str">
+        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
+      </c>
+      <c r="F138" t="str">
+        <v/>
+      </c>
+      <c r="G138" t="str">
+        <v/>
+      </c>
+      <c r="H138" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I138" t="str">
+        <v/>
+      </c>
+      <c r="J138" t="str">
+        <v/>
+      </c>
+      <c r="K138" t="str">
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
+      </c>
+      <c r="L138" t="str">
+        <v/>
+      </c>
+      <c r="M138" t="str">
+        <v/>
+      </c>
+      <c r="N138" t="str">
+        <v/>
+      </c>
+      <c r="O138" t="str">
+        <v/>
+      </c>
+      <c r="P138" t="str">
+        <v/>
+      </c>
+      <c r="Q138" t="str">
+        <v/>
+      </c>
+      <c r="R138" t="str">
+        <v/>
+      </c>
+      <c r="S138" t="str">
+        <v/>
+      </c>
+      <c r="T138" t="str">
+        <v/>
+      </c>
+      <c r="U138" t="str">
+        <v/>
+      </c>
+      <c r="V138" t="str">
+        <v/>
+      </c>
+      <c r="W138" t="str">
+        <v/>
+      </c>
+      <c r="X138" t="str">
+        <v/>
+      </c>
+      <c r="Y138" t="str">
+        <v/>
+      </c>
+      <c r="Z138" t="str">
+        <v/>
+      </c>
+      <c r="AA138" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>דוג'ה קאט Vie</v>
+      </c>
+      <c r="B139" t="str">
+        <v>2025-10-04</v>
+      </c>
+      <c r="C139" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
+      </c>
+      <c r="D139" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E139" t="str">
+        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
+      </c>
+      <c r="F139" t="str">
+        <v/>
+      </c>
+      <c r="G139" t="str">
+        <v/>
+      </c>
+      <c r="H139" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I139" t="str">
+        <v/>
+      </c>
+      <c r="J139" t="str">
+        <v/>
+      </c>
+      <c r="K139" t="str">
+        <v>דוג'ה קאט Vie</v>
+      </c>
+      <c r="L139" t="str">
+        <v/>
+      </c>
+      <c r="M139" t="str">
+        <v/>
+      </c>
+      <c r="N139" t="str">
+        <v/>
+      </c>
+      <c r="O139" t="str">
+        <v/>
+      </c>
+      <c r="P139" t="str">
+        <v/>
+      </c>
+      <c r="Q139" t="str">
+        <v/>
+      </c>
+      <c r="R139" t="str">
+        <v/>
+      </c>
+      <c r="S139" t="str">
+        <v/>
+      </c>
+      <c r="T139" t="str">
+        <v/>
+      </c>
+      <c r="U139" t="str">
+        <v/>
+      </c>
+      <c r="V139" t="str">
+        <v/>
+      </c>
+      <c r="W139" t="str">
+        <v/>
+      </c>
+      <c r="X139" t="str">
+        <v/>
+      </c>
+      <c r="Y139" t="str">
+        <v/>
+      </c>
+      <c r="Z139" t="str">
+        <v/>
+      </c>
+      <c r="AA139" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>ג'וי קרוקס Juniper</v>
+      </c>
+      <c r="B140" t="str">
+        <v>2025-10-03</v>
+      </c>
+      <c r="C140" t="str">
+        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
+      </c>
+      <c r="D140" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E140" t="str">
+        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
+      </c>
+      <c r="F140" t="str">
+        <v/>
+      </c>
+      <c r="G140" t="str">
+        <v/>
+      </c>
+      <c r="H140" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I140" t="str">
+        <v/>
+      </c>
+      <c r="J140" t="str">
+        <v/>
+      </c>
+      <c r="K140" t="str">
+        <v>ג'וי קרוקס Juniper</v>
+      </c>
+      <c r="L140" t="str">
+        <v/>
+      </c>
+      <c r="M140" t="str">
+        <v/>
+      </c>
+      <c r="N140" t="str">
+        <v/>
+      </c>
+      <c r="O140" t="str">
+        <v/>
+      </c>
+      <c r="P140" t="str">
+        <v/>
+      </c>
+      <c r="Q140" t="str">
+        <v/>
+      </c>
+      <c r="R140" t="str">
+        <v/>
+      </c>
+      <c r="S140" t="str">
+        <v/>
+      </c>
+      <c r="T140" t="str">
+        <v/>
+      </c>
+      <c r="U140" t="str">
+        <v/>
+      </c>
+      <c r="V140" t="str">
+        <v/>
+      </c>
+      <c r="W140" t="str">
+        <v/>
+      </c>
+      <c r="X140" t="str">
+        <v/>
+      </c>
+      <c r="Y140" t="str">
+        <v/>
+      </c>
+      <c r="Z140" t="str">
+        <v/>
+      </c>
+      <c r="AA140" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>ביפי קליירו Futique</v>
+      </c>
+      <c r="B141" t="str">
+        <v>2025-09-30</v>
+      </c>
+      <c r="C141" t="str">
+        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
+      </c>
+      <c r="D141" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E141" t="str">
+        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
+      </c>
+      <c r="F141" t="str">
+        <v/>
+      </c>
+      <c r="G141" t="str">
+        <v/>
+      </c>
+      <c r="H141" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I141" t="str">
+        <v/>
+      </c>
+      <c r="J141" t="str">
+        <v/>
+      </c>
+      <c r="K141" t="str">
+        <v>ביפי קליירו Futique</v>
+      </c>
+      <c r="L141" t="str">
+        <v/>
+      </c>
+      <c r="M141" t="str">
+        <v/>
+      </c>
+      <c r="N141" t="str">
+        <v/>
+      </c>
+      <c r="O141" t="str">
+        <v/>
+      </c>
+      <c r="P141" t="str">
+        <v/>
+      </c>
+      <c r="Q141" t="str">
+        <v/>
+      </c>
+      <c r="R141" t="str">
+        <v/>
+      </c>
+      <c r="S141" t="str">
+        <v/>
+      </c>
+      <c r="T141" t="str">
+        <v/>
+      </c>
+      <c r="U141" t="str">
+        <v/>
+      </c>
+      <c r="V141" t="str">
+        <v/>
+      </c>
+      <c r="W141" t="str">
+        <v/>
+      </c>
+      <c r="X141" t="str">
+        <v/>
+      </c>
+      <c r="Y141" t="str">
+        <v/>
+      </c>
+      <c r="Z141" t="str">
+        <v/>
+      </c>
+      <c r="AA141" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>אד שירן Play</v>
+      </c>
+      <c r="B142" t="str">
+        <v>2025-09-24</v>
+      </c>
+      <c r="C142" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
+      </c>
+      <c r="D142" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E142" t="str">
+        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
+      </c>
+      <c r="F142" t="str">
+        <v/>
+      </c>
+      <c r="G142" t="str">
+        <v/>
+      </c>
+      <c r="H142" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I142" t="str">
+        <v/>
+      </c>
+      <c r="J142" t="str">
+        <v/>
+      </c>
+      <c r="K142" t="str">
+        <v>אד שירן Play</v>
+      </c>
+      <c r="L142" t="str">
+        <v/>
+      </c>
+      <c r="M142" t="str">
+        <v/>
+      </c>
+      <c r="N142" t="str">
+        <v/>
+      </c>
+      <c r="O142" t="str">
+        <v/>
+      </c>
+      <c r="P142" t="str">
+        <v/>
+      </c>
+      <c r="Q142" t="str">
+        <v/>
+      </c>
+      <c r="R142" t="str">
+        <v/>
+      </c>
+      <c r="S142" t="str">
+        <v/>
+      </c>
+      <c r="T142" t="str">
+        <v/>
+      </c>
+      <c r="U142" t="str">
+        <v/>
+      </c>
+      <c r="V142" t="str">
+        <v/>
+      </c>
+      <c r="W142" t="str">
+        <v/>
+      </c>
+      <c r="X142" t="str">
+        <v/>
+      </c>
+      <c r="Y142" t="str">
+        <v/>
+      </c>
+      <c r="Z142" t="str">
+        <v/>
+      </c>
+      <c r="AA142" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+      </c>
+      <c r="B143" t="str">
+        <v>2025-09-21</v>
+      </c>
+      <c r="C143" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
+      </c>
+      <c r="D143" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E143" t="str">
+        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
+      </c>
+      <c r="F143" t="str">
+        <v/>
+      </c>
+      <c r="G143" t="str">
+        <v/>
+      </c>
+      <c r="H143" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I143" t="str">
+        <v/>
+      </c>
+      <c r="J143" t="str">
+        <v/>
+      </c>
+      <c r="K143" t="str">
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+      </c>
+      <c r="L143" t="str">
+        <v/>
+      </c>
+      <c r="M143" t="str">
+        <v/>
+      </c>
+      <c r="N143" t="str">
+        <v/>
+      </c>
+      <c r="O143" t="str">
+        <v/>
+      </c>
+      <c r="P143" t="str">
+        <v/>
+      </c>
+      <c r="Q143" t="str">
+        <v/>
+      </c>
+      <c r="R143" t="str">
+        <v/>
+      </c>
+      <c r="S143" t="str">
+        <v/>
+      </c>
+      <c r="T143" t="str">
+        <v/>
+      </c>
+      <c r="U143" t="str">
+        <v/>
+      </c>
+      <c r="V143" t="str">
+        <v/>
+      </c>
+      <c r="W143" t="str">
+        <v/>
+      </c>
+      <c r="X143" t="str">
+        <v/>
+      </c>
+      <c r="Y143" t="str">
+        <v/>
+      </c>
+      <c r="Z143" t="str">
+        <v/>
+      </c>
+      <c r="AA143" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>סוויד Antidepressants</v>
+      </c>
+      <c r="B144" t="str">
+        <v>2025-09-12</v>
+      </c>
+      <c r="C144" t="str">
+        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
+      </c>
+      <c r="D144" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E144" t="str">
+        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
+      </c>
+      <c r="F144" t="str">
+        <v/>
+      </c>
+      <c r="G144" t="str">
+        <v/>
+      </c>
+      <c r="H144" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I144" t="str">
+        <v/>
+      </c>
+      <c r="J144" t="str">
+        <v/>
+      </c>
+      <c r="K144" t="str">
+        <v>סוויד Antidepressants</v>
+      </c>
+      <c r="L144" t="str">
+        <v/>
+      </c>
+      <c r="M144" t="str">
+        <v/>
+      </c>
+      <c r="N144" t="str">
+        <v/>
+      </c>
+      <c r="O144" t="str">
+        <v/>
+      </c>
+      <c r="P144" t="str">
+        <v/>
+      </c>
+      <c r="Q144" t="str">
+        <v/>
+      </c>
+      <c r="R144" t="str">
+        <v/>
+      </c>
+      <c r="S144" t="str">
+        <v/>
+      </c>
+      <c r="T144" t="str">
+        <v/>
+      </c>
+      <c r="U144" t="str">
+        <v/>
+      </c>
+      <c r="V144" t="str">
+        <v/>
+      </c>
+      <c r="W144" t="str">
+        <v/>
+      </c>
+      <c r="X144" t="str">
+        <v/>
+      </c>
+      <c r="Y144" t="str">
+        <v/>
+      </c>
+      <c r="Z144" t="str">
+        <v/>
+      </c>
+      <c r="AA144" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>וולף אליס The Clearing</v>
+      </c>
+      <c r="B145" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="C145" t="str">
+        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
+      </c>
+      <c r="D145" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E145" t="str">
+        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
+      </c>
+      <c r="F145" t="str">
+        <v/>
+      </c>
+      <c r="G145" t="str">
+        <v/>
+      </c>
+      <c r="H145" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I145" t="str">
+        <v/>
+      </c>
+      <c r="J145" t="str">
+        <v/>
+      </c>
+      <c r="K145" t="str">
+        <v>וולף אליס The Clearing</v>
+      </c>
+      <c r="L145" t="str">
+        <v/>
+      </c>
+      <c r="M145" t="str">
+        <v/>
+      </c>
+      <c r="N145" t="str">
+        <v/>
+      </c>
+      <c r="O145" t="str">
+        <v/>
+      </c>
+      <c r="P145" t="str">
+        <v/>
+      </c>
+      <c r="Q145" t="str">
+        <v/>
+      </c>
+      <c r="R145" t="str">
+        <v/>
+      </c>
+      <c r="S145" t="str">
+        <v/>
+      </c>
+      <c r="T145" t="str">
+        <v/>
+      </c>
+      <c r="U145" t="str">
+        <v/>
+      </c>
+      <c r="V145" t="str">
+        <v/>
+      </c>
+      <c r="W145" t="str">
+        <v/>
+      </c>
+      <c r="X145" t="str">
+        <v/>
+      </c>
+      <c r="Y145" t="str">
+        <v/>
+      </c>
+      <c r="Z145" t="str">
+        <v/>
+      </c>
+      <c r="AA145" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+      </c>
+      <c r="B146" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="C146" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
+      </c>
+      <c r="D146" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E146" t="str">
+        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
+      </c>
+      <c r="F146" t="str">
+        <v/>
+      </c>
+      <c r="G146" t="str">
+        <v/>
+      </c>
+      <c r="H146" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I146" t="str">
+        <v/>
+      </c>
+      <c r="J146" t="str">
+        <v/>
+      </c>
+      <c r="K146" t="str">
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+      </c>
+      <c r="L146" t="str">
+        <v/>
+      </c>
+      <c r="M146" t="str">
+        <v/>
+      </c>
+      <c r="N146" t="str">
+        <v/>
+      </c>
+      <c r="O146" t="str">
+        <v/>
+      </c>
+      <c r="P146" t="str">
+        <v/>
+      </c>
+      <c r="Q146" t="str">
+        <v/>
+      </c>
+      <c r="R146" t="str">
+        <v/>
+      </c>
+      <c r="S146" t="str">
+        <v/>
+      </c>
+      <c r="T146" t="str">
+        <v/>
+      </c>
+      <c r="U146" t="str">
+        <v/>
+      </c>
+      <c r="V146" t="str">
+        <v/>
+      </c>
+      <c r="W146" t="str">
+        <v/>
+      </c>
+      <c r="X146" t="str">
+        <v/>
+      </c>
+      <c r="Y146" t="str">
+        <v/>
+      </c>
+      <c r="Z146" t="str">
+        <v/>
+      </c>
+      <c r="AA146" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+      </c>
+      <c r="B147" t="str">
+        <v>2025-08-24</v>
+      </c>
+      <c r="C147" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
+      </c>
+      <c r="D147" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E147" t="str">
+        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
+      </c>
+      <c r="F147" t="str">
+        <v/>
+      </c>
+      <c r="G147" t="str">
+        <v/>
+      </c>
+      <c r="H147" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I147" t="str">
+        <v/>
+      </c>
+      <c r="J147" t="str">
+        <v/>
+      </c>
+      <c r="K147" t="str">
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+      </c>
+      <c r="L147" t="str">
+        <v/>
+      </c>
+      <c r="M147" t="str">
+        <v/>
+      </c>
+      <c r="N147" t="str">
+        <v/>
+      </c>
+      <c r="O147" t="str">
+        <v/>
+      </c>
+      <c r="P147" t="str">
+        <v/>
+      </c>
+      <c r="Q147" t="str">
+        <v/>
+      </c>
+      <c r="R147" t="str">
+        <v/>
+      </c>
+      <c r="S147" t="str">
+        <v/>
+      </c>
+      <c r="T147" t="str">
+        <v/>
+      </c>
+      <c r="U147" t="str">
+        <v/>
+      </c>
+      <c r="V147" t="str">
+        <v/>
+      </c>
+      <c r="W147" t="str">
+        <v/>
+      </c>
+      <c r="X147" t="str">
+        <v/>
+      </c>
+      <c r="Y147" t="str">
+        <v/>
+      </c>
+      <c r="Z147" t="str">
+        <v/>
+      </c>
+      <c r="AA147" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+      </c>
+      <c r="B148" t="str">
+        <v>2025-08-21</v>
+      </c>
+      <c r="C148" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
+      </c>
+      <c r="D148" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E148" t="str">
+        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
+      </c>
+      <c r="F148" t="str">
+        <v/>
+      </c>
+      <c r="G148" t="str">
+        <v/>
+      </c>
+      <c r="H148" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I148" t="str">
+        <v/>
+      </c>
+      <c r="J148" t="str">
+        <v/>
+      </c>
+      <c r="K148" t="str">
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+      </c>
+      <c r="L148" t="str">
+        <v/>
+      </c>
+      <c r="M148" t="str">
+        <v/>
+      </c>
+      <c r="N148" t="str">
+        <v/>
+      </c>
+      <c r="O148" t="str">
+        <v/>
+      </c>
+      <c r="P148" t="str">
+        <v/>
+      </c>
+      <c r="Q148" t="str">
+        <v/>
+      </c>
+      <c r="R148" t="str">
+        <v/>
+      </c>
+      <c r="S148" t="str">
+        <v/>
+      </c>
+      <c r="T148" t="str">
+        <v/>
+      </c>
+      <c r="U148" t="str">
+        <v/>
+      </c>
+      <c r="V148" t="str">
+        <v/>
+      </c>
+      <c r="W148" t="str">
+        <v/>
+      </c>
+      <c r="X148" t="str">
+        <v/>
+      </c>
+      <c r="Y148" t="str">
+        <v/>
+      </c>
+      <c r="Z148" t="str">
+        <v/>
+      </c>
+      <c r="AA148" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>אברהם טל – חי</v>
+      </c>
+      <c r="B149" t="str">
+        <v>2025-08-17</v>
+      </c>
+      <c r="C149" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
+      </c>
+      <c r="D149" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E149" t="str">
+        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
+      </c>
+      <c r="F149" t="str">
+        <v/>
+      </c>
+      <c r="G149" t="str">
+        <v/>
+      </c>
+      <c r="H149" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I149" t="str">
+        <v/>
+      </c>
+      <c r="J149" t="str">
+        <v/>
+      </c>
+      <c r="K149" t="str">
+        <v>אברהם טל – חי</v>
+      </c>
+      <c r="L149" t="str">
+        <v/>
+      </c>
+      <c r="M149" t="str">
+        <v/>
+      </c>
+      <c r="N149" t="str">
+        <v/>
+      </c>
+      <c r="O149" t="str">
+        <v/>
+      </c>
+      <c r="P149" t="str">
+        <v/>
+      </c>
+      <c r="Q149" t="str">
+        <v/>
+      </c>
+      <c r="R149" t="str">
+        <v/>
+      </c>
+      <c r="S149" t="str">
+        <v/>
+      </c>
+      <c r="T149" t="str">
+        <v/>
+      </c>
+      <c r="U149" t="str">
+        <v/>
+      </c>
+      <c r="V149" t="str">
+        <v/>
+      </c>
+      <c r="W149" t="str">
+        <v/>
+      </c>
+      <c r="X149" t="str">
+        <v/>
+      </c>
+      <c r="Y149" t="str">
+        <v/>
+      </c>
+      <c r="Z149" t="str">
+        <v/>
+      </c>
+      <c r="AA149" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>רנה ראפ Bite Me</v>
+      </c>
+      <c r="B150" t="str">
+        <v>2025-08-12</v>
+      </c>
+      <c r="C150" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
+      </c>
+      <c r="D150" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E150" t="str">
+        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
+      </c>
+      <c r="F150" t="str">
+        <v/>
+      </c>
+      <c r="G150" t="str">
+        <v/>
+      </c>
+      <c r="H150" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I150" t="str">
+        <v/>
+      </c>
+      <c r="J150" t="str">
+        <v/>
+      </c>
+      <c r="K150" t="str">
+        <v>רנה ראפ Bite Me</v>
+      </c>
+      <c r="L150" t="str">
+        <v/>
+      </c>
+      <c r="M150" t="str">
+        <v/>
+      </c>
+      <c r="N150" t="str">
+        <v/>
+      </c>
+      <c r="O150" t="str">
+        <v/>
+      </c>
+      <c r="P150" t="str">
+        <v/>
+      </c>
+      <c r="Q150" t="str">
+        <v/>
+      </c>
+      <c r="R150" t="str">
+        <v/>
+      </c>
+      <c r="S150" t="str">
+        <v/>
+      </c>
+      <c r="T150" t="str">
+        <v/>
+      </c>
+      <c r="U150" t="str">
+        <v/>
+      </c>
+      <c r="V150" t="str">
+        <v/>
+      </c>
+      <c r="W150" t="str">
+        <v/>
+      </c>
+      <c r="X150" t="str">
+        <v/>
+      </c>
+      <c r="Y150" t="str">
+        <v/>
+      </c>
+      <c r="Z150" t="str">
+        <v/>
+      </c>
+      <c r="AA150" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>The K's – Pretty On The Internet</v>
+      </c>
+      <c r="B151" t="str">
+        <v>2025-08-03</v>
+      </c>
+      <c r="C151" t="str">
+        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
+      </c>
+      <c r="D151" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E151" t="str">
+        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
+      </c>
+      <c r="F151" t="str">
+        <v/>
+      </c>
+      <c r="G151" t="str">
+        <v/>
+      </c>
+      <c r="H151" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I151" t="str">
+        <v/>
+      </c>
+      <c r="J151" t="str">
+        <v/>
+      </c>
+      <c r="K151" t="str">
+        <v>The K's – Pretty On The Internet</v>
+      </c>
+      <c r="L151" t="str">
+        <v/>
+      </c>
+      <c r="M151" t="str">
+        <v/>
+      </c>
+      <c r="N151" t="str">
+        <v/>
+      </c>
+      <c r="O151" t="str">
+        <v/>
+      </c>
+      <c r="P151" t="str">
+        <v/>
+      </c>
+      <c r="Q151" t="str">
+        <v/>
+      </c>
+      <c r="R151" t="str">
+        <v/>
+      </c>
+      <c r="S151" t="str">
+        <v/>
+      </c>
+      <c r="T151" t="str">
+        <v/>
+      </c>
+      <c r="U151" t="str">
+        <v/>
+      </c>
+      <c r="V151" t="str">
+        <v/>
+      </c>
+      <c r="W151" t="str">
+        <v/>
+      </c>
+      <c r="X151" t="str">
+        <v/>
+      </c>
+      <c r="Y151" t="str">
+        <v/>
+      </c>
+      <c r="Z151" t="str">
+        <v/>
+      </c>
+      <c r="AA151" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:W121"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AA151"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA151"/>
+  <dimension ref="A1:AE181"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -9284,9 +9284,2859 @@
         <v/>
       </c>
     </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>פטריק סבג Hotel Mogador</v>
+      </c>
+      <c r="B152" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C152" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
+      </c>
+      <c r="D152" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E152" t="str">
+        <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
+      </c>
+      <c r="F152" t="str">
+        <v/>
+      </c>
+      <c r="G152" t="str">
+        <v/>
+      </c>
+      <c r="H152" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I152" t="str">
+        <v/>
+      </c>
+      <c r="J152" t="str">
+        <v/>
+      </c>
+      <c r="K152" t="str">
+        <v>פטריק סבג Hotel Mogador</v>
+      </c>
+      <c r="L152" t="str">
+        <v/>
+      </c>
+      <c r="M152" t="str">
+        <v/>
+      </c>
+      <c r="N152" t="str">
+        <v/>
+      </c>
+      <c r="O152" t="str">
+        <v/>
+      </c>
+      <c r="P152" t="str">
+        <v/>
+      </c>
+      <c r="Q152" t="str">
+        <v/>
+      </c>
+      <c r="R152" t="str">
+        <v/>
+      </c>
+      <c r="S152" t="str">
+        <v/>
+      </c>
+      <c r="T152" t="str">
+        <v/>
+      </c>
+      <c r="U152" t="str">
+        <v/>
+      </c>
+      <c r="V152" t="str">
+        <v/>
+      </c>
+      <c r="W152" t="str">
+        <v/>
+      </c>
+      <c r="X152" t="str">
+        <v/>
+      </c>
+      <c r="Y152" t="str">
+        <v/>
+      </c>
+      <c r="Z152" t="str">
+        <v/>
+      </c>
+      <c r="AA152" t="str">
+        <v/>
+      </c>
+      <c r="AB152" t="str">
+        <v/>
+      </c>
+      <c r="AC152" t="str">
+        <v/>
+      </c>
+      <c r="AD152" t="str">
+        <v/>
+      </c>
+      <c r="AE152" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
+      </c>
+      <c r="B153" t="str">
+        <v>2026-01-09</v>
+      </c>
+      <c r="C153" t="str">
+        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
+      </c>
+      <c r="D153" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E153" t="str">
+        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
+      </c>
+      <c r="F153" t="str">
+        <v/>
+      </c>
+      <c r="G153" t="str">
+        <v/>
+      </c>
+      <c r="H153" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I153" t="str">
+        <v/>
+      </c>
+      <c r="J153" t="str">
+        <v/>
+      </c>
+      <c r="K153" t="str">
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
+      </c>
+      <c r="L153" t="str">
+        <v/>
+      </c>
+      <c r="M153" t="str">
+        <v/>
+      </c>
+      <c r="N153" t="str">
+        <v/>
+      </c>
+      <c r="O153" t="str">
+        <v/>
+      </c>
+      <c r="P153" t="str">
+        <v/>
+      </c>
+      <c r="Q153" t="str">
+        <v/>
+      </c>
+      <c r="R153" t="str">
+        <v/>
+      </c>
+      <c r="S153" t="str">
+        <v/>
+      </c>
+      <c r="T153" t="str">
+        <v/>
+      </c>
+      <c r="U153" t="str">
+        <v/>
+      </c>
+      <c r="V153" t="str">
+        <v/>
+      </c>
+      <c r="W153" t="str">
+        <v/>
+      </c>
+      <c r="X153" t="str">
+        <v/>
+      </c>
+      <c r="Y153" t="str">
+        <v/>
+      </c>
+      <c r="Z153" t="str">
+        <v/>
+      </c>
+      <c r="AA153" t="str">
+        <v/>
+      </c>
+      <c r="AB153" t="str">
+        <v/>
+      </c>
+      <c r="AC153" t="str">
+        <v/>
+      </c>
+      <c r="AD153" t="str">
+        <v/>
+      </c>
+      <c r="AE153" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>אוליביה דין The Art of Loving</v>
+      </c>
+      <c r="B154" t="str">
+        <v>2026-01-04</v>
+      </c>
+      <c r="C154" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
+      </c>
+      <c r="D154" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E154" t="str">
+        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
+      </c>
+      <c r="F154" t="str">
+        <v/>
+      </c>
+      <c r="G154" t="str">
+        <v/>
+      </c>
+      <c r="H154" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I154" t="str">
+        <v/>
+      </c>
+      <c r="J154" t="str">
+        <v/>
+      </c>
+      <c r="K154" t="str">
+        <v>אוליביה דין The Art of Loving</v>
+      </c>
+      <c r="L154" t="str">
+        <v/>
+      </c>
+      <c r="M154" t="str">
+        <v/>
+      </c>
+      <c r="N154" t="str">
+        <v/>
+      </c>
+      <c r="O154" t="str">
+        <v/>
+      </c>
+      <c r="P154" t="str">
+        <v/>
+      </c>
+      <c r="Q154" t="str">
+        <v/>
+      </c>
+      <c r="R154" t="str">
+        <v/>
+      </c>
+      <c r="S154" t="str">
+        <v/>
+      </c>
+      <c r="T154" t="str">
+        <v/>
+      </c>
+      <c r="U154" t="str">
+        <v/>
+      </c>
+      <c r="V154" t="str">
+        <v/>
+      </c>
+      <c r="W154" t="str">
+        <v/>
+      </c>
+      <c r="X154" t="str">
+        <v/>
+      </c>
+      <c r="Y154" t="str">
+        <v/>
+      </c>
+      <c r="Z154" t="str">
+        <v/>
+      </c>
+      <c r="AA154" t="str">
+        <v/>
+      </c>
+      <c r="AB154" t="str">
+        <v/>
+      </c>
+      <c r="AC154" t="str">
+        <v/>
+      </c>
+      <c r="AD154" t="str">
+        <v/>
+      </c>
+      <c r="AE154" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>Geese Getting Killed</v>
+      </c>
+      <c r="B155" t="str">
+        <v>2025-12-29</v>
+      </c>
+      <c r="C155" t="str">
+        <v>https://yosmusic.com/geese-getting-killed/</v>
+      </c>
+      <c r="D155" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E155" t="str">
+        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
+      </c>
+      <c r="F155" t="str">
+        <v/>
+      </c>
+      <c r="G155" t="str">
+        <v/>
+      </c>
+      <c r="H155" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I155" t="str">
+        <v/>
+      </c>
+      <c r="J155" t="str">
+        <v/>
+      </c>
+      <c r="K155" t="str">
+        <v>Geese Getting Killed</v>
+      </c>
+      <c r="L155" t="str">
+        <v/>
+      </c>
+      <c r="M155" t="str">
+        <v/>
+      </c>
+      <c r="N155" t="str">
+        <v/>
+      </c>
+      <c r="O155" t="str">
+        <v/>
+      </c>
+      <c r="P155" t="str">
+        <v/>
+      </c>
+      <c r="Q155" t="str">
+        <v/>
+      </c>
+      <c r="R155" t="str">
+        <v/>
+      </c>
+      <c r="S155" t="str">
+        <v/>
+      </c>
+      <c r="T155" t="str">
+        <v/>
+      </c>
+      <c r="U155" t="str">
+        <v/>
+      </c>
+      <c r="V155" t="str">
+        <v/>
+      </c>
+      <c r="W155" t="str">
+        <v/>
+      </c>
+      <c r="X155" t="str">
+        <v/>
+      </c>
+      <c r="Y155" t="str">
+        <v/>
+      </c>
+      <c r="Z155" t="str">
+        <v/>
+      </c>
+      <c r="AA155" t="str">
+        <v/>
+      </c>
+      <c r="AB155" t="str">
+        <v/>
+      </c>
+      <c r="AC155" t="str">
+        <v/>
+      </c>
+      <c r="AD155" t="str">
+        <v/>
+      </c>
+      <c r="AE155" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>רוסליה Lux</v>
+      </c>
+      <c r="B156" t="str">
+        <v>2025-12-25</v>
+      </c>
+      <c r="C156" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
+      </c>
+      <c r="D156" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E156" t="str">
+        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
+      </c>
+      <c r="F156" t="str">
+        <v/>
+      </c>
+      <c r="G156" t="str">
+        <v/>
+      </c>
+      <c r="H156" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I156" t="str">
+        <v/>
+      </c>
+      <c r="J156" t="str">
+        <v/>
+      </c>
+      <c r="K156" t="str">
+        <v>רוסליה Lux</v>
+      </c>
+      <c r="L156" t="str">
+        <v/>
+      </c>
+      <c r="M156" t="str">
+        <v/>
+      </c>
+      <c r="N156" t="str">
+        <v/>
+      </c>
+      <c r="O156" t="str">
+        <v/>
+      </c>
+      <c r="P156" t="str">
+        <v/>
+      </c>
+      <c r="Q156" t="str">
+        <v/>
+      </c>
+      <c r="R156" t="str">
+        <v/>
+      </c>
+      <c r="S156" t="str">
+        <v/>
+      </c>
+      <c r="T156" t="str">
+        <v/>
+      </c>
+      <c r="U156" t="str">
+        <v/>
+      </c>
+      <c r="V156" t="str">
+        <v/>
+      </c>
+      <c r="W156" t="str">
+        <v/>
+      </c>
+      <c r="X156" t="str">
+        <v/>
+      </c>
+      <c r="Y156" t="str">
+        <v/>
+      </c>
+      <c r="Z156" t="str">
+        <v/>
+      </c>
+      <c r="AA156" t="str">
+        <v/>
+      </c>
+      <c r="AB156" t="str">
+        <v/>
+      </c>
+      <c r="AC156" t="str">
+        <v/>
+      </c>
+      <c r="AD156" t="str">
+        <v/>
+      </c>
+      <c r="AE156" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>יאנגבלאד אירוסמית' one more time</v>
+      </c>
+      <c r="B157" t="str">
+        <v>2025-12-17</v>
+      </c>
+      <c r="C157" t="str">
+        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
+      </c>
+      <c r="D157" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E157" t="str">
+        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
+      </c>
+      <c r="F157" t="str">
+        <v/>
+      </c>
+      <c r="G157" t="str">
+        <v/>
+      </c>
+      <c r="H157" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I157" t="str">
+        <v/>
+      </c>
+      <c r="J157" t="str">
+        <v/>
+      </c>
+      <c r="K157" t="str">
+        <v>יאנגבלאד אירוסמית' one more time</v>
+      </c>
+      <c r="L157" t="str">
+        <v/>
+      </c>
+      <c r="M157" t="str">
+        <v/>
+      </c>
+      <c r="N157" t="str">
+        <v/>
+      </c>
+      <c r="O157" t="str">
+        <v/>
+      </c>
+      <c r="P157" t="str">
+        <v/>
+      </c>
+      <c r="Q157" t="str">
+        <v/>
+      </c>
+      <c r="R157" t="str">
+        <v/>
+      </c>
+      <c r="S157" t="str">
+        <v/>
+      </c>
+      <c r="T157" t="str">
+        <v/>
+      </c>
+      <c r="U157" t="str">
+        <v/>
+      </c>
+      <c r="V157" t="str">
+        <v/>
+      </c>
+      <c r="W157" t="str">
+        <v/>
+      </c>
+      <c r="X157" t="str">
+        <v/>
+      </c>
+      <c r="Y157" t="str">
+        <v/>
+      </c>
+      <c r="Z157" t="str">
+        <v/>
+      </c>
+      <c r="AA157" t="str">
+        <v/>
+      </c>
+      <c r="AB157" t="str">
+        <v/>
+      </c>
+      <c r="AC157" t="str">
+        <v/>
+      </c>
+      <c r="AD157" t="str">
+        <v/>
+      </c>
+      <c r="AE157" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>פינק פלויד Wish You Were Here 50</v>
+      </c>
+      <c r="B158" t="str">
+        <v>2025-12-14</v>
+      </c>
+      <c r="C158" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
+      </c>
+      <c r="D158" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E158" t="str">
+        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
+      </c>
+      <c r="F158" t="str">
+        <v/>
+      </c>
+      <c r="G158" t="str">
+        <v/>
+      </c>
+      <c r="H158" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I158" t="str">
+        <v/>
+      </c>
+      <c r="J158" t="str">
+        <v/>
+      </c>
+      <c r="K158" t="str">
+        <v>פינק פלויד Wish You Were Here 50</v>
+      </c>
+      <c r="L158" t="str">
+        <v/>
+      </c>
+      <c r="M158" t="str">
+        <v/>
+      </c>
+      <c r="N158" t="str">
+        <v/>
+      </c>
+      <c r="O158" t="str">
+        <v/>
+      </c>
+      <c r="P158" t="str">
+        <v/>
+      </c>
+      <c r="Q158" t="str">
+        <v/>
+      </c>
+      <c r="R158" t="str">
+        <v/>
+      </c>
+      <c r="S158" t="str">
+        <v/>
+      </c>
+      <c r="T158" t="str">
+        <v/>
+      </c>
+      <c r="U158" t="str">
+        <v/>
+      </c>
+      <c r="V158" t="str">
+        <v/>
+      </c>
+      <c r="W158" t="str">
+        <v/>
+      </c>
+      <c r="X158" t="str">
+        <v/>
+      </c>
+      <c r="Y158" t="str">
+        <v/>
+      </c>
+      <c r="Z158" t="str">
+        <v/>
+      </c>
+      <c r="AA158" t="str">
+        <v/>
+      </c>
+      <c r="AB158" t="str">
+        <v/>
+      </c>
+      <c r="AC158" t="str">
+        <v/>
+      </c>
+      <c r="AD158" t="str">
+        <v/>
+      </c>
+      <c r="AE158" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+      </c>
+      <c r="B159" t="str">
+        <v>2025-12-08</v>
+      </c>
+      <c r="C159" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
+      </c>
+      <c r="D159" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E159" t="str">
+        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
+      </c>
+      <c r="F159" t="str">
+        <v/>
+      </c>
+      <c r="G159" t="str">
+        <v/>
+      </c>
+      <c r="H159" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I159" t="str">
+        <v/>
+      </c>
+      <c r="J159" t="str">
+        <v/>
+      </c>
+      <c r="K159" t="str">
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+      </c>
+      <c r="L159" t="str">
+        <v/>
+      </c>
+      <c r="M159" t="str">
+        <v/>
+      </c>
+      <c r="N159" t="str">
+        <v/>
+      </c>
+      <c r="O159" t="str">
+        <v/>
+      </c>
+      <c r="P159" t="str">
+        <v/>
+      </c>
+      <c r="Q159" t="str">
+        <v/>
+      </c>
+      <c r="R159" t="str">
+        <v/>
+      </c>
+      <c r="S159" t="str">
+        <v/>
+      </c>
+      <c r="T159" t="str">
+        <v/>
+      </c>
+      <c r="U159" t="str">
+        <v/>
+      </c>
+      <c r="V159" t="str">
+        <v/>
+      </c>
+      <c r="W159" t="str">
+        <v/>
+      </c>
+      <c r="X159" t="str">
+        <v/>
+      </c>
+      <c r="Y159" t="str">
+        <v/>
+      </c>
+      <c r="Z159" t="str">
+        <v/>
+      </c>
+      <c r="AA159" t="str">
+        <v/>
+      </c>
+      <c r="AB159" t="str">
+        <v/>
+      </c>
+      <c r="AC159" t="str">
+        <v/>
+      </c>
+      <c r="AD159" t="str">
+        <v/>
+      </c>
+      <c r="AE159" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>סטריי קידס DO IT EP</v>
+      </c>
+      <c r="B160" t="str">
+        <v>2025-12-04</v>
+      </c>
+      <c r="C160" t="str">
+        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
+      </c>
+      <c r="D160" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E160" t="str">
+        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
+      </c>
+      <c r="F160" t="str">
+        <v/>
+      </c>
+      <c r="G160" t="str">
+        <v/>
+      </c>
+      <c r="H160" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I160" t="str">
+        <v/>
+      </c>
+      <c r="J160" t="str">
+        <v/>
+      </c>
+      <c r="K160" t="str">
+        <v>סטריי קידס DO IT EP</v>
+      </c>
+      <c r="L160" t="str">
+        <v/>
+      </c>
+      <c r="M160" t="str">
+        <v/>
+      </c>
+      <c r="N160" t="str">
+        <v/>
+      </c>
+      <c r="O160" t="str">
+        <v/>
+      </c>
+      <c r="P160" t="str">
+        <v/>
+      </c>
+      <c r="Q160" t="str">
+        <v/>
+      </c>
+      <c r="R160" t="str">
+        <v/>
+      </c>
+      <c r="S160" t="str">
+        <v/>
+      </c>
+      <c r="T160" t="str">
+        <v/>
+      </c>
+      <c r="U160" t="str">
+        <v/>
+      </c>
+      <c r="V160" t="str">
+        <v/>
+      </c>
+      <c r="W160" t="str">
+        <v/>
+      </c>
+      <c r="X160" t="str">
+        <v/>
+      </c>
+      <c r="Y160" t="str">
+        <v/>
+      </c>
+      <c r="Z160" t="str">
+        <v/>
+      </c>
+      <c r="AA160" t="str">
+        <v/>
+      </c>
+      <c r="AB160" t="str">
+        <v/>
+      </c>
+      <c r="AC160" t="str">
+        <v/>
+      </c>
+      <c r="AD160" t="str">
+        <v/>
+      </c>
+      <c r="AE160" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>דויד ברוזה BROZAJAZZ</v>
+      </c>
+      <c r="B161" t="str">
+        <v>2025-11-30</v>
+      </c>
+      <c r="C161" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
+      </c>
+      <c r="D161" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E161" t="str">
+        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
+      </c>
+      <c r="F161" t="str">
+        <v/>
+      </c>
+      <c r="G161" t="str">
+        <v/>
+      </c>
+      <c r="H161" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I161" t="str">
+        <v/>
+      </c>
+      <c r="J161" t="str">
+        <v/>
+      </c>
+      <c r="K161" t="str">
+        <v>דויד ברוזה BROZAJAZZ</v>
+      </c>
+      <c r="L161" t="str">
+        <v/>
+      </c>
+      <c r="M161" t="str">
+        <v/>
+      </c>
+      <c r="N161" t="str">
+        <v/>
+      </c>
+      <c r="O161" t="str">
+        <v/>
+      </c>
+      <c r="P161" t="str">
+        <v/>
+      </c>
+      <c r="Q161" t="str">
+        <v/>
+      </c>
+      <c r="R161" t="str">
+        <v/>
+      </c>
+      <c r="S161" t="str">
+        <v/>
+      </c>
+      <c r="T161" t="str">
+        <v/>
+      </c>
+      <c r="U161" t="str">
+        <v/>
+      </c>
+      <c r="V161" t="str">
+        <v/>
+      </c>
+      <c r="W161" t="str">
+        <v/>
+      </c>
+      <c r="X161" t="str">
+        <v/>
+      </c>
+      <c r="Y161" t="str">
+        <v/>
+      </c>
+      <c r="Z161" t="str">
+        <v/>
+      </c>
+      <c r="AA161" t="str">
+        <v/>
+      </c>
+      <c r="AB161" t="str">
+        <v/>
+      </c>
+      <c r="AC161" t="str">
+        <v/>
+      </c>
+      <c r="AD161" t="str">
+        <v/>
+      </c>
+      <c r="AE161" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>Five Seconds of Summer – Everyone's A Star</v>
+      </c>
+      <c r="B162" t="str">
+        <v>2025-11-24</v>
+      </c>
+      <c r="C162" t="str">
+        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
+      </c>
+      <c r="D162" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E162" t="str">
+        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
+      </c>
+      <c r="F162" t="str">
+        <v/>
+      </c>
+      <c r="G162" t="str">
+        <v/>
+      </c>
+      <c r="H162" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I162" t="str">
+        <v/>
+      </c>
+      <c r="J162" t="str">
+        <v/>
+      </c>
+      <c r="K162" t="str">
+        <v>Five Seconds of Summer – Everyone's A Star</v>
+      </c>
+      <c r="L162" t="str">
+        <v/>
+      </c>
+      <c r="M162" t="str">
+        <v/>
+      </c>
+      <c r="N162" t="str">
+        <v/>
+      </c>
+      <c r="O162" t="str">
+        <v/>
+      </c>
+      <c r="P162" t="str">
+        <v/>
+      </c>
+      <c r="Q162" t="str">
+        <v/>
+      </c>
+      <c r="R162" t="str">
+        <v/>
+      </c>
+      <c r="S162" t="str">
+        <v/>
+      </c>
+      <c r="T162" t="str">
+        <v/>
+      </c>
+      <c r="U162" t="str">
+        <v/>
+      </c>
+      <c r="V162" t="str">
+        <v/>
+      </c>
+      <c r="W162" t="str">
+        <v/>
+      </c>
+      <c r="X162" t="str">
+        <v/>
+      </c>
+      <c r="Y162" t="str">
+        <v/>
+      </c>
+      <c r="Z162" t="str">
+        <v/>
+      </c>
+      <c r="AA162" t="str">
+        <v/>
+      </c>
+      <c r="AB162" t="str">
+        <v/>
+      </c>
+      <c r="AC162" t="str">
+        <v/>
+      </c>
+      <c r="AD162" t="str">
+        <v/>
+      </c>
+      <c r="AE162" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>התקווה 6 – ויהי אור</v>
+      </c>
+      <c r="B163" t="str">
+        <v>2025-11-20</v>
+      </c>
+      <c r="C163" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
+      </c>
+      <c r="D163" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E163" t="str">
+        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
+      </c>
+      <c r="F163" t="str">
+        <v/>
+      </c>
+      <c r="G163" t="str">
+        <v/>
+      </c>
+      <c r="H163" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I163" t="str">
+        <v/>
+      </c>
+      <c r="J163" t="str">
+        <v/>
+      </c>
+      <c r="K163" t="str">
+        <v>התקווה 6 – ויהי אור</v>
+      </c>
+      <c r="L163" t="str">
+        <v/>
+      </c>
+      <c r="M163" t="str">
+        <v/>
+      </c>
+      <c r="N163" t="str">
+        <v/>
+      </c>
+      <c r="O163" t="str">
+        <v/>
+      </c>
+      <c r="P163" t="str">
+        <v/>
+      </c>
+      <c r="Q163" t="str">
+        <v/>
+      </c>
+      <c r="R163" t="str">
+        <v/>
+      </c>
+      <c r="S163" t="str">
+        <v/>
+      </c>
+      <c r="T163" t="str">
+        <v/>
+      </c>
+      <c r="U163" t="str">
+        <v/>
+      </c>
+      <c r="V163" t="str">
+        <v/>
+      </c>
+      <c r="W163" t="str">
+        <v/>
+      </c>
+      <c r="X163" t="str">
+        <v/>
+      </c>
+      <c r="Y163" t="str">
+        <v/>
+      </c>
+      <c r="Z163" t="str">
+        <v/>
+      </c>
+      <c r="AA163" t="str">
+        <v/>
+      </c>
+      <c r="AB163" t="str">
+        <v/>
+      </c>
+      <c r="AC163" t="str">
+        <v/>
+      </c>
+      <c r="AD163" t="str">
+        <v/>
+      </c>
+      <c r="AE163" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>פלורנס אנד דה משין Everybody Scream</v>
+      </c>
+      <c r="B164" t="str">
+        <v>2025-11-13</v>
+      </c>
+      <c r="C164" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
+      </c>
+      <c r="D164" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E164" t="str">
+        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
+      </c>
+      <c r="F164" t="str">
+        <v/>
+      </c>
+      <c r="G164" t="str">
+        <v/>
+      </c>
+      <c r="H164" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I164" t="str">
+        <v/>
+      </c>
+      <c r="J164" t="str">
+        <v/>
+      </c>
+      <c r="K164" t="str">
+        <v>פלורנס אנד דה משין Everybody Scream</v>
+      </c>
+      <c r="L164" t="str">
+        <v/>
+      </c>
+      <c r="M164" t="str">
+        <v/>
+      </c>
+      <c r="N164" t="str">
+        <v/>
+      </c>
+      <c r="O164" t="str">
+        <v/>
+      </c>
+      <c r="P164" t="str">
+        <v/>
+      </c>
+      <c r="Q164" t="str">
+        <v/>
+      </c>
+      <c r="R164" t="str">
+        <v/>
+      </c>
+      <c r="S164" t="str">
+        <v/>
+      </c>
+      <c r="T164" t="str">
+        <v/>
+      </c>
+      <c r="U164" t="str">
+        <v/>
+      </c>
+      <c r="V164" t="str">
+        <v/>
+      </c>
+      <c r="W164" t="str">
+        <v/>
+      </c>
+      <c r="X164" t="str">
+        <v/>
+      </c>
+      <c r="Y164" t="str">
+        <v/>
+      </c>
+      <c r="Z164" t="str">
+        <v/>
+      </c>
+      <c r="AA164" t="str">
+        <v/>
+      </c>
+      <c r="AB164" t="str">
+        <v/>
+      </c>
+      <c r="AC164" t="str">
+        <v/>
+      </c>
+      <c r="AD164" t="str">
+        <v/>
+      </c>
+      <c r="AE164" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>טיים אימפלה Deadbeat</v>
+      </c>
+      <c r="B165" t="str">
+        <v>2025-11-03</v>
+      </c>
+      <c r="C165" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
+      </c>
+      <c r="D165" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E165" t="str">
+        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
+      </c>
+      <c r="F165" t="str">
+        <v/>
+      </c>
+      <c r="G165" t="str">
+        <v/>
+      </c>
+      <c r="H165" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I165" t="str">
+        <v/>
+      </c>
+      <c r="J165" t="str">
+        <v/>
+      </c>
+      <c r="K165" t="str">
+        <v>טיים אימפלה Deadbeat</v>
+      </c>
+      <c r="L165" t="str">
+        <v/>
+      </c>
+      <c r="M165" t="str">
+        <v/>
+      </c>
+      <c r="N165" t="str">
+        <v/>
+      </c>
+      <c r="O165" t="str">
+        <v/>
+      </c>
+      <c r="P165" t="str">
+        <v/>
+      </c>
+      <c r="Q165" t="str">
+        <v/>
+      </c>
+      <c r="R165" t="str">
+        <v/>
+      </c>
+      <c r="S165" t="str">
+        <v/>
+      </c>
+      <c r="T165" t="str">
+        <v/>
+      </c>
+      <c r="U165" t="str">
+        <v/>
+      </c>
+      <c r="V165" t="str">
+        <v/>
+      </c>
+      <c r="W165" t="str">
+        <v/>
+      </c>
+      <c r="X165" t="str">
+        <v/>
+      </c>
+      <c r="Y165" t="str">
+        <v/>
+      </c>
+      <c r="Z165" t="str">
+        <v/>
+      </c>
+      <c r="AA165" t="str">
+        <v/>
+      </c>
+      <c r="AB165" t="str">
+        <v/>
+      </c>
+      <c r="AC165" t="str">
+        <v/>
+      </c>
+      <c r="AD165" t="str">
+        <v/>
+      </c>
+      <c r="AE165" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+      </c>
+      <c r="B166" t="str">
+        <v>2025-10-20</v>
+      </c>
+      <c r="C166" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
+      </c>
+      <c r="D166" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E166" t="str">
+        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
+      </c>
+      <c r="F166" t="str">
+        <v/>
+      </c>
+      <c r="G166" t="str">
+        <v/>
+      </c>
+      <c r="H166" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I166" t="str">
+        <v/>
+      </c>
+      <c r="J166" t="str">
+        <v/>
+      </c>
+      <c r="K166" t="str">
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+      </c>
+      <c r="L166" t="str">
+        <v/>
+      </c>
+      <c r="M166" t="str">
+        <v/>
+      </c>
+      <c r="N166" t="str">
+        <v/>
+      </c>
+      <c r="O166" t="str">
+        <v/>
+      </c>
+      <c r="P166" t="str">
+        <v/>
+      </c>
+      <c r="Q166" t="str">
+        <v/>
+      </c>
+      <c r="R166" t="str">
+        <v/>
+      </c>
+      <c r="S166" t="str">
+        <v/>
+      </c>
+      <c r="T166" t="str">
+        <v/>
+      </c>
+      <c r="U166" t="str">
+        <v/>
+      </c>
+      <c r="V166" t="str">
+        <v/>
+      </c>
+      <c r="W166" t="str">
+        <v/>
+      </c>
+      <c r="X166" t="str">
+        <v/>
+      </c>
+      <c r="Y166" t="str">
+        <v/>
+      </c>
+      <c r="Z166" t="str">
+        <v/>
+      </c>
+      <c r="AA166" t="str">
+        <v/>
+      </c>
+      <c r="AB166" t="str">
+        <v/>
+      </c>
+      <c r="AC166" t="str">
+        <v/>
+      </c>
+      <c r="AD166" t="str">
+        <v/>
+      </c>
+      <c r="AE166" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>שלמה גרוניך – תודה אהבה</v>
+      </c>
+      <c r="B167" t="str">
+        <v>2025-10-18</v>
+      </c>
+      <c r="C167" t="str">
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
+      </c>
+      <c r="D167" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E167" t="str">
+        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
+      </c>
+      <c r="F167" t="str">
+        <v/>
+      </c>
+      <c r="G167" t="str">
+        <v/>
+      </c>
+      <c r="H167" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I167" t="str">
+        <v/>
+      </c>
+      <c r="J167" t="str">
+        <v/>
+      </c>
+      <c r="K167" t="str">
+        <v>שלמה גרוניך – תודה אהבה</v>
+      </c>
+      <c r="L167" t="str">
+        <v/>
+      </c>
+      <c r="M167" t="str">
+        <v/>
+      </c>
+      <c r="N167" t="str">
+        <v/>
+      </c>
+      <c r="O167" t="str">
+        <v/>
+      </c>
+      <c r="P167" t="str">
+        <v/>
+      </c>
+      <c r="Q167" t="str">
+        <v/>
+      </c>
+      <c r="R167" t="str">
+        <v/>
+      </c>
+      <c r="S167" t="str">
+        <v/>
+      </c>
+      <c r="T167" t="str">
+        <v/>
+      </c>
+      <c r="U167" t="str">
+        <v/>
+      </c>
+      <c r="V167" t="str">
+        <v/>
+      </c>
+      <c r="W167" t="str">
+        <v/>
+      </c>
+      <c r="X167" t="str">
+        <v/>
+      </c>
+      <c r="Y167" t="str">
+        <v/>
+      </c>
+      <c r="Z167" t="str">
+        <v/>
+      </c>
+      <c r="AA167" t="str">
+        <v/>
+      </c>
+      <c r="AB167" t="str">
+        <v/>
+      </c>
+      <c r="AC167" t="str">
+        <v/>
+      </c>
+      <c r="AD167" t="str">
+        <v/>
+      </c>
+      <c r="AE167" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
+      </c>
+      <c r="B168" t="str">
+        <v>2025-10-11</v>
+      </c>
+      <c r="C168" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
+      </c>
+      <c r="D168" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E168" t="str">
+        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
+      </c>
+      <c r="F168" t="str">
+        <v/>
+      </c>
+      <c r="G168" t="str">
+        <v/>
+      </c>
+      <c r="H168" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I168" t="str">
+        <v/>
+      </c>
+      <c r="J168" t="str">
+        <v/>
+      </c>
+      <c r="K168" t="str">
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
+      </c>
+      <c r="L168" t="str">
+        <v/>
+      </c>
+      <c r="M168" t="str">
+        <v/>
+      </c>
+      <c r="N168" t="str">
+        <v/>
+      </c>
+      <c r="O168" t="str">
+        <v/>
+      </c>
+      <c r="P168" t="str">
+        <v/>
+      </c>
+      <c r="Q168" t="str">
+        <v/>
+      </c>
+      <c r="R168" t="str">
+        <v/>
+      </c>
+      <c r="S168" t="str">
+        <v/>
+      </c>
+      <c r="T168" t="str">
+        <v/>
+      </c>
+      <c r="U168" t="str">
+        <v/>
+      </c>
+      <c r="V168" t="str">
+        <v/>
+      </c>
+      <c r="W168" t="str">
+        <v/>
+      </c>
+      <c r="X168" t="str">
+        <v/>
+      </c>
+      <c r="Y168" t="str">
+        <v/>
+      </c>
+      <c r="Z168" t="str">
+        <v/>
+      </c>
+      <c r="AA168" t="str">
+        <v/>
+      </c>
+      <c r="AB168" t="str">
+        <v/>
+      </c>
+      <c r="AC168" t="str">
+        <v/>
+      </c>
+      <c r="AD168" t="str">
+        <v/>
+      </c>
+      <c r="AE168" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>דוג'ה קאט Vie</v>
+      </c>
+      <c r="B169" t="str">
+        <v>2025-10-04</v>
+      </c>
+      <c r="C169" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
+      </c>
+      <c r="D169" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E169" t="str">
+        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
+      </c>
+      <c r="F169" t="str">
+        <v/>
+      </c>
+      <c r="G169" t="str">
+        <v/>
+      </c>
+      <c r="H169" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I169" t="str">
+        <v/>
+      </c>
+      <c r="J169" t="str">
+        <v/>
+      </c>
+      <c r="K169" t="str">
+        <v>דוג'ה קאט Vie</v>
+      </c>
+      <c r="L169" t="str">
+        <v/>
+      </c>
+      <c r="M169" t="str">
+        <v/>
+      </c>
+      <c r="N169" t="str">
+        <v/>
+      </c>
+      <c r="O169" t="str">
+        <v/>
+      </c>
+      <c r="P169" t="str">
+        <v/>
+      </c>
+      <c r="Q169" t="str">
+        <v/>
+      </c>
+      <c r="R169" t="str">
+        <v/>
+      </c>
+      <c r="S169" t="str">
+        <v/>
+      </c>
+      <c r="T169" t="str">
+        <v/>
+      </c>
+      <c r="U169" t="str">
+        <v/>
+      </c>
+      <c r="V169" t="str">
+        <v/>
+      </c>
+      <c r="W169" t="str">
+        <v/>
+      </c>
+      <c r="X169" t="str">
+        <v/>
+      </c>
+      <c r="Y169" t="str">
+        <v/>
+      </c>
+      <c r="Z169" t="str">
+        <v/>
+      </c>
+      <c r="AA169" t="str">
+        <v/>
+      </c>
+      <c r="AB169" t="str">
+        <v/>
+      </c>
+      <c r="AC169" t="str">
+        <v/>
+      </c>
+      <c r="AD169" t="str">
+        <v/>
+      </c>
+      <c r="AE169" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>ג'וי קרוקס Juniper</v>
+      </c>
+      <c r="B170" t="str">
+        <v>2025-10-03</v>
+      </c>
+      <c r="C170" t="str">
+        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
+      </c>
+      <c r="D170" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E170" t="str">
+        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
+      </c>
+      <c r="F170" t="str">
+        <v/>
+      </c>
+      <c r="G170" t="str">
+        <v/>
+      </c>
+      <c r="H170" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I170" t="str">
+        <v/>
+      </c>
+      <c r="J170" t="str">
+        <v/>
+      </c>
+      <c r="K170" t="str">
+        <v>ג'וי קרוקס Juniper</v>
+      </c>
+      <c r="L170" t="str">
+        <v/>
+      </c>
+      <c r="M170" t="str">
+        <v/>
+      </c>
+      <c r="N170" t="str">
+        <v/>
+      </c>
+      <c r="O170" t="str">
+        <v/>
+      </c>
+      <c r="P170" t="str">
+        <v/>
+      </c>
+      <c r="Q170" t="str">
+        <v/>
+      </c>
+      <c r="R170" t="str">
+        <v/>
+      </c>
+      <c r="S170" t="str">
+        <v/>
+      </c>
+      <c r="T170" t="str">
+        <v/>
+      </c>
+      <c r="U170" t="str">
+        <v/>
+      </c>
+      <c r="V170" t="str">
+        <v/>
+      </c>
+      <c r="W170" t="str">
+        <v/>
+      </c>
+      <c r="X170" t="str">
+        <v/>
+      </c>
+      <c r="Y170" t="str">
+        <v/>
+      </c>
+      <c r="Z170" t="str">
+        <v/>
+      </c>
+      <c r="AA170" t="str">
+        <v/>
+      </c>
+      <c r="AB170" t="str">
+        <v/>
+      </c>
+      <c r="AC170" t="str">
+        <v/>
+      </c>
+      <c r="AD170" t="str">
+        <v/>
+      </c>
+      <c r="AE170" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>ביפי קליירו Futique</v>
+      </c>
+      <c r="B171" t="str">
+        <v>2025-09-30</v>
+      </c>
+      <c r="C171" t="str">
+        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
+      </c>
+      <c r="D171" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E171" t="str">
+        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
+      </c>
+      <c r="F171" t="str">
+        <v/>
+      </c>
+      <c r="G171" t="str">
+        <v/>
+      </c>
+      <c r="H171" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I171" t="str">
+        <v/>
+      </c>
+      <c r="J171" t="str">
+        <v/>
+      </c>
+      <c r="K171" t="str">
+        <v>ביפי קליירו Futique</v>
+      </c>
+      <c r="L171" t="str">
+        <v/>
+      </c>
+      <c r="M171" t="str">
+        <v/>
+      </c>
+      <c r="N171" t="str">
+        <v/>
+      </c>
+      <c r="O171" t="str">
+        <v/>
+      </c>
+      <c r="P171" t="str">
+        <v/>
+      </c>
+      <c r="Q171" t="str">
+        <v/>
+      </c>
+      <c r="R171" t="str">
+        <v/>
+      </c>
+      <c r="S171" t="str">
+        <v/>
+      </c>
+      <c r="T171" t="str">
+        <v/>
+      </c>
+      <c r="U171" t="str">
+        <v/>
+      </c>
+      <c r="V171" t="str">
+        <v/>
+      </c>
+      <c r="W171" t="str">
+        <v/>
+      </c>
+      <c r="X171" t="str">
+        <v/>
+      </c>
+      <c r="Y171" t="str">
+        <v/>
+      </c>
+      <c r="Z171" t="str">
+        <v/>
+      </c>
+      <c r="AA171" t="str">
+        <v/>
+      </c>
+      <c r="AB171" t="str">
+        <v/>
+      </c>
+      <c r="AC171" t="str">
+        <v/>
+      </c>
+      <c r="AD171" t="str">
+        <v/>
+      </c>
+      <c r="AE171" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>אד שירן Play</v>
+      </c>
+      <c r="B172" t="str">
+        <v>2025-09-24</v>
+      </c>
+      <c r="C172" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
+      </c>
+      <c r="D172" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E172" t="str">
+        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
+      </c>
+      <c r="F172" t="str">
+        <v/>
+      </c>
+      <c r="G172" t="str">
+        <v/>
+      </c>
+      <c r="H172" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I172" t="str">
+        <v/>
+      </c>
+      <c r="J172" t="str">
+        <v/>
+      </c>
+      <c r="K172" t="str">
+        <v>אד שירן Play</v>
+      </c>
+      <c r="L172" t="str">
+        <v/>
+      </c>
+      <c r="M172" t="str">
+        <v/>
+      </c>
+      <c r="N172" t="str">
+        <v/>
+      </c>
+      <c r="O172" t="str">
+        <v/>
+      </c>
+      <c r="P172" t="str">
+        <v/>
+      </c>
+      <c r="Q172" t="str">
+        <v/>
+      </c>
+      <c r="R172" t="str">
+        <v/>
+      </c>
+      <c r="S172" t="str">
+        <v/>
+      </c>
+      <c r="T172" t="str">
+        <v/>
+      </c>
+      <c r="U172" t="str">
+        <v/>
+      </c>
+      <c r="V172" t="str">
+        <v/>
+      </c>
+      <c r="W172" t="str">
+        <v/>
+      </c>
+      <c r="X172" t="str">
+        <v/>
+      </c>
+      <c r="Y172" t="str">
+        <v/>
+      </c>
+      <c r="Z172" t="str">
+        <v/>
+      </c>
+      <c r="AA172" t="str">
+        <v/>
+      </c>
+      <c r="AB172" t="str">
+        <v/>
+      </c>
+      <c r="AC172" t="str">
+        <v/>
+      </c>
+      <c r="AD172" t="str">
+        <v/>
+      </c>
+      <c r="AE172" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+      </c>
+      <c r="B173" t="str">
+        <v>2025-09-21</v>
+      </c>
+      <c r="C173" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
+      </c>
+      <c r="D173" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E173" t="str">
+        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
+      </c>
+      <c r="F173" t="str">
+        <v/>
+      </c>
+      <c r="G173" t="str">
+        <v/>
+      </c>
+      <c r="H173" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I173" t="str">
+        <v/>
+      </c>
+      <c r="J173" t="str">
+        <v/>
+      </c>
+      <c r="K173" t="str">
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+      </c>
+      <c r="L173" t="str">
+        <v/>
+      </c>
+      <c r="M173" t="str">
+        <v/>
+      </c>
+      <c r="N173" t="str">
+        <v/>
+      </c>
+      <c r="O173" t="str">
+        <v/>
+      </c>
+      <c r="P173" t="str">
+        <v/>
+      </c>
+      <c r="Q173" t="str">
+        <v/>
+      </c>
+      <c r="R173" t="str">
+        <v/>
+      </c>
+      <c r="S173" t="str">
+        <v/>
+      </c>
+      <c r="T173" t="str">
+        <v/>
+      </c>
+      <c r="U173" t="str">
+        <v/>
+      </c>
+      <c r="V173" t="str">
+        <v/>
+      </c>
+      <c r="W173" t="str">
+        <v/>
+      </c>
+      <c r="X173" t="str">
+        <v/>
+      </c>
+      <c r="Y173" t="str">
+        <v/>
+      </c>
+      <c r="Z173" t="str">
+        <v/>
+      </c>
+      <c r="AA173" t="str">
+        <v/>
+      </c>
+      <c r="AB173" t="str">
+        <v/>
+      </c>
+      <c r="AC173" t="str">
+        <v/>
+      </c>
+      <c r="AD173" t="str">
+        <v/>
+      </c>
+      <c r="AE173" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>סוויד Antidepressants</v>
+      </c>
+      <c r="B174" t="str">
+        <v>2025-09-12</v>
+      </c>
+      <c r="C174" t="str">
+        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
+      </c>
+      <c r="D174" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E174" t="str">
+        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
+      </c>
+      <c r="F174" t="str">
+        <v/>
+      </c>
+      <c r="G174" t="str">
+        <v/>
+      </c>
+      <c r="H174" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I174" t="str">
+        <v/>
+      </c>
+      <c r="J174" t="str">
+        <v/>
+      </c>
+      <c r="K174" t="str">
+        <v>סוויד Antidepressants</v>
+      </c>
+      <c r="L174" t="str">
+        <v/>
+      </c>
+      <c r="M174" t="str">
+        <v/>
+      </c>
+      <c r="N174" t="str">
+        <v/>
+      </c>
+      <c r="O174" t="str">
+        <v/>
+      </c>
+      <c r="P174" t="str">
+        <v/>
+      </c>
+      <c r="Q174" t="str">
+        <v/>
+      </c>
+      <c r="R174" t="str">
+        <v/>
+      </c>
+      <c r="S174" t="str">
+        <v/>
+      </c>
+      <c r="T174" t="str">
+        <v/>
+      </c>
+      <c r="U174" t="str">
+        <v/>
+      </c>
+      <c r="V174" t="str">
+        <v/>
+      </c>
+      <c r="W174" t="str">
+        <v/>
+      </c>
+      <c r="X174" t="str">
+        <v/>
+      </c>
+      <c r="Y174" t="str">
+        <v/>
+      </c>
+      <c r="Z174" t="str">
+        <v/>
+      </c>
+      <c r="AA174" t="str">
+        <v/>
+      </c>
+      <c r="AB174" t="str">
+        <v/>
+      </c>
+      <c r="AC174" t="str">
+        <v/>
+      </c>
+      <c r="AD174" t="str">
+        <v/>
+      </c>
+      <c r="AE174" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>וולף אליס The Clearing</v>
+      </c>
+      <c r="B175" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="C175" t="str">
+        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
+      </c>
+      <c r="D175" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E175" t="str">
+        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
+      </c>
+      <c r="F175" t="str">
+        <v/>
+      </c>
+      <c r="G175" t="str">
+        <v/>
+      </c>
+      <c r="H175" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I175" t="str">
+        <v/>
+      </c>
+      <c r="J175" t="str">
+        <v/>
+      </c>
+      <c r="K175" t="str">
+        <v>וולף אליס The Clearing</v>
+      </c>
+      <c r="L175" t="str">
+        <v/>
+      </c>
+      <c r="M175" t="str">
+        <v/>
+      </c>
+      <c r="N175" t="str">
+        <v/>
+      </c>
+      <c r="O175" t="str">
+        <v/>
+      </c>
+      <c r="P175" t="str">
+        <v/>
+      </c>
+      <c r="Q175" t="str">
+        <v/>
+      </c>
+      <c r="R175" t="str">
+        <v/>
+      </c>
+      <c r="S175" t="str">
+        <v/>
+      </c>
+      <c r="T175" t="str">
+        <v/>
+      </c>
+      <c r="U175" t="str">
+        <v/>
+      </c>
+      <c r="V175" t="str">
+        <v/>
+      </c>
+      <c r="W175" t="str">
+        <v/>
+      </c>
+      <c r="X175" t="str">
+        <v/>
+      </c>
+      <c r="Y175" t="str">
+        <v/>
+      </c>
+      <c r="Z175" t="str">
+        <v/>
+      </c>
+      <c r="AA175" t="str">
+        <v/>
+      </c>
+      <c r="AB175" t="str">
+        <v/>
+      </c>
+      <c r="AC175" t="str">
+        <v/>
+      </c>
+      <c r="AD175" t="str">
+        <v/>
+      </c>
+      <c r="AE175" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+      </c>
+      <c r="B176" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="C176" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
+      </c>
+      <c r="D176" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E176" t="str">
+        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
+      </c>
+      <c r="F176" t="str">
+        <v/>
+      </c>
+      <c r="G176" t="str">
+        <v/>
+      </c>
+      <c r="H176" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I176" t="str">
+        <v/>
+      </c>
+      <c r="J176" t="str">
+        <v/>
+      </c>
+      <c r="K176" t="str">
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+      </c>
+      <c r="L176" t="str">
+        <v/>
+      </c>
+      <c r="M176" t="str">
+        <v/>
+      </c>
+      <c r="N176" t="str">
+        <v/>
+      </c>
+      <c r="O176" t="str">
+        <v/>
+      </c>
+      <c r="P176" t="str">
+        <v/>
+      </c>
+      <c r="Q176" t="str">
+        <v/>
+      </c>
+      <c r="R176" t="str">
+        <v/>
+      </c>
+      <c r="S176" t="str">
+        <v/>
+      </c>
+      <c r="T176" t="str">
+        <v/>
+      </c>
+      <c r="U176" t="str">
+        <v/>
+      </c>
+      <c r="V176" t="str">
+        <v/>
+      </c>
+      <c r="W176" t="str">
+        <v/>
+      </c>
+      <c r="X176" t="str">
+        <v/>
+      </c>
+      <c r="Y176" t="str">
+        <v/>
+      </c>
+      <c r="Z176" t="str">
+        <v/>
+      </c>
+      <c r="AA176" t="str">
+        <v/>
+      </c>
+      <c r="AB176" t="str">
+        <v/>
+      </c>
+      <c r="AC176" t="str">
+        <v/>
+      </c>
+      <c r="AD176" t="str">
+        <v/>
+      </c>
+      <c r="AE176" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+      </c>
+      <c r="B177" t="str">
+        <v>2025-08-24</v>
+      </c>
+      <c r="C177" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
+      </c>
+      <c r="D177" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E177" t="str">
+        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
+      </c>
+      <c r="F177" t="str">
+        <v/>
+      </c>
+      <c r="G177" t="str">
+        <v/>
+      </c>
+      <c r="H177" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I177" t="str">
+        <v/>
+      </c>
+      <c r="J177" t="str">
+        <v/>
+      </c>
+      <c r="K177" t="str">
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+      </c>
+      <c r="L177" t="str">
+        <v/>
+      </c>
+      <c r="M177" t="str">
+        <v/>
+      </c>
+      <c r="N177" t="str">
+        <v/>
+      </c>
+      <c r="O177" t="str">
+        <v/>
+      </c>
+      <c r="P177" t="str">
+        <v/>
+      </c>
+      <c r="Q177" t="str">
+        <v/>
+      </c>
+      <c r="R177" t="str">
+        <v/>
+      </c>
+      <c r="S177" t="str">
+        <v/>
+      </c>
+      <c r="T177" t="str">
+        <v/>
+      </c>
+      <c r="U177" t="str">
+        <v/>
+      </c>
+      <c r="V177" t="str">
+        <v/>
+      </c>
+      <c r="W177" t="str">
+        <v/>
+      </c>
+      <c r="X177" t="str">
+        <v/>
+      </c>
+      <c r="Y177" t="str">
+        <v/>
+      </c>
+      <c r="Z177" t="str">
+        <v/>
+      </c>
+      <c r="AA177" t="str">
+        <v/>
+      </c>
+      <c r="AB177" t="str">
+        <v/>
+      </c>
+      <c r="AC177" t="str">
+        <v/>
+      </c>
+      <c r="AD177" t="str">
+        <v/>
+      </c>
+      <c r="AE177" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+      </c>
+      <c r="B178" t="str">
+        <v>2025-08-21</v>
+      </c>
+      <c r="C178" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
+      </c>
+      <c r="D178" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E178" t="str">
+        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
+      </c>
+      <c r="F178" t="str">
+        <v/>
+      </c>
+      <c r="G178" t="str">
+        <v/>
+      </c>
+      <c r="H178" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I178" t="str">
+        <v/>
+      </c>
+      <c r="J178" t="str">
+        <v/>
+      </c>
+      <c r="K178" t="str">
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+      </c>
+      <c r="L178" t="str">
+        <v/>
+      </c>
+      <c r="M178" t="str">
+        <v/>
+      </c>
+      <c r="N178" t="str">
+        <v/>
+      </c>
+      <c r="O178" t="str">
+        <v/>
+      </c>
+      <c r="P178" t="str">
+        <v/>
+      </c>
+      <c r="Q178" t="str">
+        <v/>
+      </c>
+      <c r="R178" t="str">
+        <v/>
+      </c>
+      <c r="S178" t="str">
+        <v/>
+      </c>
+      <c r="T178" t="str">
+        <v/>
+      </c>
+      <c r="U178" t="str">
+        <v/>
+      </c>
+      <c r="V178" t="str">
+        <v/>
+      </c>
+      <c r="W178" t="str">
+        <v/>
+      </c>
+      <c r="X178" t="str">
+        <v/>
+      </c>
+      <c r="Y178" t="str">
+        <v/>
+      </c>
+      <c r="Z178" t="str">
+        <v/>
+      </c>
+      <c r="AA178" t="str">
+        <v/>
+      </c>
+      <c r="AB178" t="str">
+        <v/>
+      </c>
+      <c r="AC178" t="str">
+        <v/>
+      </c>
+      <c r="AD178" t="str">
+        <v/>
+      </c>
+      <c r="AE178" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>אברהם טל – חי</v>
+      </c>
+      <c r="B179" t="str">
+        <v>2025-08-17</v>
+      </c>
+      <c r="C179" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
+      </c>
+      <c r="D179" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E179" t="str">
+        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
+      </c>
+      <c r="F179" t="str">
+        <v/>
+      </c>
+      <c r="G179" t="str">
+        <v/>
+      </c>
+      <c r="H179" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I179" t="str">
+        <v/>
+      </c>
+      <c r="J179" t="str">
+        <v/>
+      </c>
+      <c r="K179" t="str">
+        <v>אברהם טל – חי</v>
+      </c>
+      <c r="L179" t="str">
+        <v/>
+      </c>
+      <c r="M179" t="str">
+        <v/>
+      </c>
+      <c r="N179" t="str">
+        <v/>
+      </c>
+      <c r="O179" t="str">
+        <v/>
+      </c>
+      <c r="P179" t="str">
+        <v/>
+      </c>
+      <c r="Q179" t="str">
+        <v/>
+      </c>
+      <c r="R179" t="str">
+        <v/>
+      </c>
+      <c r="S179" t="str">
+        <v/>
+      </c>
+      <c r="T179" t="str">
+        <v/>
+      </c>
+      <c r="U179" t="str">
+        <v/>
+      </c>
+      <c r="V179" t="str">
+        <v/>
+      </c>
+      <c r="W179" t="str">
+        <v/>
+      </c>
+      <c r="X179" t="str">
+        <v/>
+      </c>
+      <c r="Y179" t="str">
+        <v/>
+      </c>
+      <c r="Z179" t="str">
+        <v/>
+      </c>
+      <c r="AA179" t="str">
+        <v/>
+      </c>
+      <c r="AB179" t="str">
+        <v/>
+      </c>
+      <c r="AC179" t="str">
+        <v/>
+      </c>
+      <c r="AD179" t="str">
+        <v/>
+      </c>
+      <c r="AE179" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>רנה ראפ Bite Me</v>
+      </c>
+      <c r="B180" t="str">
+        <v>2025-08-12</v>
+      </c>
+      <c r="C180" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
+      </c>
+      <c r="D180" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E180" t="str">
+        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
+      </c>
+      <c r="F180" t="str">
+        <v/>
+      </c>
+      <c r="G180" t="str">
+        <v/>
+      </c>
+      <c r="H180" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I180" t="str">
+        <v/>
+      </c>
+      <c r="J180" t="str">
+        <v/>
+      </c>
+      <c r="K180" t="str">
+        <v>רנה ראפ Bite Me</v>
+      </c>
+      <c r="L180" t="str">
+        <v/>
+      </c>
+      <c r="M180" t="str">
+        <v/>
+      </c>
+      <c r="N180" t="str">
+        <v/>
+      </c>
+      <c r="O180" t="str">
+        <v/>
+      </c>
+      <c r="P180" t="str">
+        <v/>
+      </c>
+      <c r="Q180" t="str">
+        <v/>
+      </c>
+      <c r="R180" t="str">
+        <v/>
+      </c>
+      <c r="S180" t="str">
+        <v/>
+      </c>
+      <c r="T180" t="str">
+        <v/>
+      </c>
+      <c r="U180" t="str">
+        <v/>
+      </c>
+      <c r="V180" t="str">
+        <v/>
+      </c>
+      <c r="W180" t="str">
+        <v/>
+      </c>
+      <c r="X180" t="str">
+        <v/>
+      </c>
+      <c r="Y180" t="str">
+        <v/>
+      </c>
+      <c r="Z180" t="str">
+        <v/>
+      </c>
+      <c r="AA180" t="str">
+        <v/>
+      </c>
+      <c r="AB180" t="str">
+        <v/>
+      </c>
+      <c r="AC180" t="str">
+        <v/>
+      </c>
+      <c r="AD180" t="str">
+        <v/>
+      </c>
+      <c r="AE180" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>The K's – Pretty On The Internet</v>
+      </c>
+      <c r="B181" t="str">
+        <v>2025-08-03</v>
+      </c>
+      <c r="C181" t="str">
+        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
+      </c>
+      <c r="D181" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E181" t="str">
+        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
+      </c>
+      <c r="F181" t="str">
+        <v/>
+      </c>
+      <c r="G181" t="str">
+        <v/>
+      </c>
+      <c r="H181" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I181" t="str">
+        <v/>
+      </c>
+      <c r="J181" t="str">
+        <v/>
+      </c>
+      <c r="K181" t="str">
+        <v>The K's – Pretty On The Internet</v>
+      </c>
+      <c r="L181" t="str">
+        <v/>
+      </c>
+      <c r="M181" t="str">
+        <v/>
+      </c>
+      <c r="N181" t="str">
+        <v/>
+      </c>
+      <c r="O181" t="str">
+        <v/>
+      </c>
+      <c r="P181" t="str">
+        <v/>
+      </c>
+      <c r="Q181" t="str">
+        <v/>
+      </c>
+      <c r="R181" t="str">
+        <v/>
+      </c>
+      <c r="S181" t="str">
+        <v/>
+      </c>
+      <c r="T181" t="str">
+        <v/>
+      </c>
+      <c r="U181" t="str">
+        <v/>
+      </c>
+      <c r="V181" t="str">
+        <v/>
+      </c>
+      <c r="W181" t="str">
+        <v/>
+      </c>
+      <c r="X181" t="str">
+        <v/>
+      </c>
+      <c r="Y181" t="str">
+        <v/>
+      </c>
+      <c r="Z181" t="str">
+        <v/>
+      </c>
+      <c r="AA181" t="str">
+        <v/>
+      </c>
+      <c r="AB181" t="str">
+        <v/>
+      </c>
+      <c r="AC181" t="str">
+        <v/>
+      </c>
+      <c r="AD181" t="str">
+        <v/>
+      </c>
+      <c r="AE181" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AA151"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AE181"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE181"/>
+  <dimension ref="A1:AI182"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,19 +436,19 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>פטריק סבג Hotel Mogador</v>
+        <v>עוז זהבי תור זהבי</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-01-13</v>
+        <v>2026-01-18</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
+        <v>https://yosmusic.com/%d7%a2%d7%95%d7%96-%d7%96%d7%94%d7%91%d7%99-%d7%aa%d7%95%d7%a8-%d7%96%d7%94%d7%91%d7%99/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-18</v>
       </c>
       <c r="E2" t="str">
-        <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
+        <v>את ההופעה הזו קיבלתי ביוטיוב (*), שיטה יעילה למי שנפשו לא חשקה לשרך דרכו למועדונים בלילות הקרים. הוידיאו נשלח לרגל יציאת אלבומו "תור זהבי", ששיר הנושא הוא ראפ עצבני בניחוח מזרחי, שיר אגו ביקורתי, אירוני ומודע לעצמו מלא בדאחקות, הגזמות,</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -466,24 +466,24 @@
         <v/>
       </c>
       <c r="K2" t="str">
-        <v>פטריק סבג Hotel Mogador</v>
+        <v>עוז זהבי תור זהבי</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>מארינה מקסימיליאן – ריק בחלל</v>
+        <v>פטריק סבג Hotel Mogador</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C3" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E3" t="str">
-        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
+        <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -501,24 +501,36 @@
         <v/>
       </c>
       <c r="K3" t="str">
-        <v>מארינה מקסימיליאן – ריק בחלל</v>
+        <v>פטריק סבג Hotel Mogador</v>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>אוליביה דין The Art of Loving</v>
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-09</v>
       </c>
       <c r="C4" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
+        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E4" t="str">
-        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
+        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -536,24 +548,36 @@
         <v/>
       </c>
       <c r="K4" t="str">
-        <v>אוליביה דין The Art of Loving</v>
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Geese Getting Killed</v>
+        <v>אוליביה דין The Art of Loving</v>
       </c>
       <c r="B5" t="str">
-        <v>2025-12-29</v>
+        <v>2026-01-04</v>
       </c>
       <c r="C5" t="str">
-        <v>https://yosmusic.com/geese-getting-killed/</v>
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E5" t="str">
-        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
+        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -571,24 +595,36 @@
         <v/>
       </c>
       <c r="K5" t="str">
-        <v>Geese Getting Killed</v>
+        <v>אוליביה דין The Art of Loving</v>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
+        <v/>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>רוסליה Lux</v>
+        <v>Geese Getting Killed</v>
       </c>
       <c r="B6" t="str">
-        <v>2025-12-25</v>
+        <v>2025-12-29</v>
       </c>
       <c r="C6" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
+        <v>https://yosmusic.com/geese-getting-killed/</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E6" t="str">
-        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
+        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -606,24 +642,36 @@
         <v/>
       </c>
       <c r="K6" t="str">
-        <v>רוסליה Lux</v>
+        <v>Geese Getting Killed</v>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
+        <v/>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>יאנגבלאד אירוסמית' one more time</v>
+        <v>רוסליה Lux</v>
       </c>
       <c r="B7" t="str">
-        <v>2025-12-17</v>
+        <v>2025-12-25</v>
       </c>
       <c r="C7" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E7" t="str">
-        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
+        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -641,24 +689,36 @@
         <v/>
       </c>
       <c r="K7" t="str">
-        <v>יאנגבלאד אירוסמית' one more time</v>
+        <v>רוסליה Lux</v>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <v/>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>פינק פלויד Wish You Were Here 50</v>
+        <v>יאנגבלאד אירוסמית' one more time</v>
       </c>
       <c r="B8" t="str">
-        <v>2025-12-14</v>
+        <v>2025-12-17</v>
       </c>
       <c r="C8" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
+        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E8" t="str">
-        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
+        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -676,24 +736,36 @@
         <v/>
       </c>
       <c r="K8" t="str">
-        <v>פינק פלויד Wish You Were Here 50</v>
+        <v>יאנגבלאד אירוסמית' one more time</v>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
+        <v/>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+        <v>פינק פלויד Wish You Were Here 50</v>
       </c>
       <c r="B9" t="str">
-        <v>2025-12-08</v>
+        <v>2025-12-14</v>
       </c>
       <c r="C9" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E9" t="str">
-        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
+        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -711,24 +783,36 @@
         <v/>
       </c>
       <c r="K9" t="str">
-        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+        <v>פינק פלויד Wish You Were Here 50</v>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
+        <v/>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>סטריי קידס DO IT EP</v>
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
       </c>
       <c r="B10" t="str">
-        <v>2025-12-04</v>
+        <v>2025-12-08</v>
       </c>
       <c r="C10" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
+        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E10" t="str">
-        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
+        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -746,24 +830,36 @@
         <v/>
       </c>
       <c r="K10" t="str">
-        <v>סטריי קידס DO IT EP</v>
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>דויד ברוזה BROZAJAZZ</v>
+        <v>סטריי קידס DO IT EP</v>
       </c>
       <c r="B11" t="str">
-        <v>2025-11-30</v>
+        <v>2025-12-04</v>
       </c>
       <c r="C11" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
+        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E11" t="str">
-        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
+        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -781,24 +877,36 @@
         <v/>
       </c>
       <c r="K11" t="str">
-        <v>דויד ברוזה BROZAJAZZ</v>
+        <v>סטריי קידס DO IT EP</v>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
+        <v/>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Five Seconds of Summer – Everyone's A Star</v>
+        <v>דויד ברוזה BROZAJAZZ</v>
       </c>
       <c r="B12" t="str">
-        <v>2025-11-24</v>
+        <v>2025-11-30</v>
       </c>
       <c r="C12" t="str">
-        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E12" t="str">
-        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
+        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -816,24 +924,36 @@
         <v/>
       </c>
       <c r="K12" t="str">
-        <v>Five Seconds of Summer – Everyone's A Star</v>
+        <v>דויד ברוזה BROZAJAZZ</v>
+      </c>
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
+        <v/>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>התקווה 6 – ויהי אור</v>
+        <v>Five Seconds of Summer – Everyone's A Star</v>
       </c>
       <c r="B13" t="str">
-        <v>2025-11-20</v>
+        <v>2025-11-24</v>
       </c>
       <c r="C13" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
+        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E13" t="str">
-        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
+        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
       </c>
       <c r="F13" t="str">
         <v/>
@@ -851,24 +971,36 @@
         <v/>
       </c>
       <c r="K13" t="str">
-        <v>התקווה 6 – ויהי אור</v>
+        <v>Five Seconds of Summer – Everyone's A Star</v>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
+        <v/>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>פלורנס אנד דה משין Everybody Scream</v>
+        <v>התקווה 6 – ויהי אור</v>
       </c>
       <c r="B14" t="str">
-        <v>2025-11-13</v>
+        <v>2025-11-20</v>
       </c>
       <c r="C14" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
+        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E14" t="str">
-        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
+        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
       </c>
       <c r="F14" t="str">
         <v/>
@@ -886,24 +1018,36 @@
         <v/>
       </c>
       <c r="K14" t="str">
-        <v>פלורנס אנד דה משין Everybody Scream</v>
+        <v>התקווה 6 – ויהי אור</v>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
+        <v/>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>טיים אימפלה Deadbeat</v>
+        <v>פלורנס אנד דה משין Everybody Scream</v>
       </c>
       <c r="B15" t="str">
-        <v>2025-11-03</v>
+        <v>2025-11-13</v>
       </c>
       <c r="C15" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E15" t="str">
-        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
+        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
       </c>
       <c r="F15" t="str">
         <v/>
@@ -921,24 +1065,36 @@
         <v/>
       </c>
       <c r="K15" t="str">
-        <v>טיים אימפלה Deadbeat</v>
+        <v>פלורנס אנד דה משין Everybody Scream</v>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+        <v>טיים אימפלה Deadbeat</v>
       </c>
       <c r="B16" t="str">
-        <v>2025-10-20</v>
+        <v>2025-11-03</v>
       </c>
       <c r="C16" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E16" t="str">
-        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
+        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
       </c>
       <c r="F16" t="str">
         <v/>
@@ -956,24 +1112,36 @@
         <v/>
       </c>
       <c r="K16" t="str">
-        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+        <v>טיים אימפלה Deadbeat</v>
+      </c>
+      <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
+        <v/>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>שלמה גרוניך – תודה אהבה</v>
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
       </c>
       <c r="B17" t="str">
-        <v>2025-10-18</v>
+        <v>2025-10-20</v>
       </c>
       <c r="C17" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
+        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E17" t="str">
-        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
+        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
       </c>
       <c r="F17" t="str">
         <v/>
@@ -991,24 +1159,36 @@
         <v/>
       </c>
       <c r="K17" t="str">
-        <v>שלמה גרוניך – תודה אהבה</v>
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+      </c>
+      <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
+        <v/>
+      </c>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>טיילור סוויפט The Life Of A Showgirl</v>
+        <v>שלמה גרוניך – תודה אהבה</v>
       </c>
       <c r="B18" t="str">
-        <v>2025-10-11</v>
+        <v>2025-10-18</v>
       </c>
       <c r="C18" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E18" t="str">
-        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
+        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
       </c>
       <c r="F18" t="str">
         <v/>
@@ -1026,24 +1206,36 @@
         <v/>
       </c>
       <c r="K18" t="str">
-        <v>טיילור סוויפט The Life Of A Showgirl</v>
+        <v>שלמה גרוניך – תודה אהבה</v>
+      </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
+        <v/>
+      </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>דוג'ה קאט Vie</v>
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
       </c>
       <c r="B19" t="str">
-        <v>2025-10-04</v>
+        <v>2025-10-11</v>
       </c>
       <c r="C19" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E19" t="str">
-        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
+        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
       </c>
       <c r="F19" t="str">
         <v/>
@@ -1061,24 +1253,36 @@
         <v/>
       </c>
       <c r="K19" t="str">
-        <v>דוג'ה קאט Vie</v>
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
+      </c>
+      <c r="L19" t="str">
+        <v/>
+      </c>
+      <c r="M19" t="str">
+        <v/>
+      </c>
+      <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ג'וי קרוקס Juniper</v>
+        <v>דוג'ה קאט Vie</v>
       </c>
       <c r="B20" t="str">
-        <v>2025-10-03</v>
+        <v>2025-10-04</v>
       </c>
       <c r="C20" t="str">
-        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E20" t="str">
-        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
+        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
       </c>
       <c r="F20" t="str">
         <v/>
@@ -1096,24 +1300,36 @@
         <v/>
       </c>
       <c r="K20" t="str">
-        <v>ג'וי קרוקס Juniper</v>
+        <v>דוג'ה קאט Vie</v>
+      </c>
+      <c r="L20" t="str">
+        <v/>
+      </c>
+      <c r="M20" t="str">
+        <v/>
+      </c>
+      <c r="N20" t="str">
+        <v/>
+      </c>
+      <c r="O20" t="str">
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ביפי קליירו Futique</v>
+        <v>ג'וי קרוקס Juniper</v>
       </c>
       <c r="B21" t="str">
-        <v>2025-09-30</v>
+        <v>2025-10-03</v>
       </c>
       <c r="C21" t="str">
-        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
+        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E21" t="str">
-        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
+        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
       </c>
       <c r="F21" t="str">
         <v/>
@@ -1131,24 +1347,36 @@
         <v/>
       </c>
       <c r="K21" t="str">
-        <v>ביפי קליירו Futique</v>
+        <v>ג'וי קרוקס Juniper</v>
+      </c>
+      <c r="L21" t="str">
+        <v/>
+      </c>
+      <c r="M21" t="str">
+        <v/>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>אד שירן Play</v>
+        <v>ביפי קליירו Futique</v>
       </c>
       <c r="B22" t="str">
-        <v>2025-09-24</v>
+        <v>2025-09-30</v>
       </c>
       <c r="C22" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
+        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E22" t="str">
-        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
+        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
       </c>
       <c r="F22" t="str">
         <v/>
@@ -1166,24 +1394,36 @@
         <v/>
       </c>
       <c r="K22" t="str">
-        <v>אד שירן Play</v>
+        <v>ביפי קליירו Futique</v>
+      </c>
+      <c r="L22" t="str">
+        <v/>
+      </c>
+      <c r="M22" t="str">
+        <v/>
+      </c>
+      <c r="N22" t="str">
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+        <v>אד שירן Play</v>
       </c>
       <c r="B23" t="str">
-        <v>2025-09-21</v>
+        <v>2025-09-24</v>
       </c>
       <c r="C23" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E23" t="str">
-        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
+        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
       </c>
       <c r="F23" t="str">
         <v/>
@@ -1201,24 +1441,36 @@
         <v/>
       </c>
       <c r="K23" t="str">
-        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+        <v>אד שירן Play</v>
+      </c>
+      <c r="L23" t="str">
+        <v/>
+      </c>
+      <c r="M23" t="str">
+        <v/>
+      </c>
+      <c r="N23" t="str">
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>סוויד Antidepressants</v>
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
       </c>
       <c r="B24" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-21</v>
       </c>
       <c r="C24" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E24" t="str">
-        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
+        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
       </c>
       <c r="F24" t="str">
         <v/>
@@ -1236,24 +1488,36 @@
         <v/>
       </c>
       <c r="K24" t="str">
-        <v>סוויד Antidepressants</v>
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+      </c>
+      <c r="L24" t="str">
+        <v/>
+      </c>
+      <c r="M24" t="str">
+        <v/>
+      </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>וולף אליס The Clearing</v>
+        <v>סוויד Antidepressants</v>
       </c>
       <c r="B25" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-12</v>
       </c>
       <c r="C25" t="str">
-        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
+        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E25" t="str">
-        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
+        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
       </c>
       <c r="F25" t="str">
         <v/>
@@ -1271,24 +1535,36 @@
         <v/>
       </c>
       <c r="K25" t="str">
-        <v>וולף אליס The Clearing</v>
+        <v>סוויד Antidepressants</v>
+      </c>
+      <c r="L25" t="str">
+        <v/>
+      </c>
+      <c r="M25" t="str">
+        <v/>
+      </c>
+      <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+        <v>וולף אליס The Clearing</v>
       </c>
       <c r="B26" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-01</v>
       </c>
       <c r="C26" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
+        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E26" t="str">
-        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
+        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
       </c>
       <c r="F26" t="str">
         <v/>
@@ -1306,24 +1582,36 @@
         <v/>
       </c>
       <c r="K26" t="str">
-        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+        <v>וולף אליס The Clearing</v>
+      </c>
+      <c r="L26" t="str">
+        <v/>
+      </c>
+      <c r="M26" t="str">
+        <v/>
+      </c>
+      <c r="N26" t="str">
+        <v/>
+      </c>
+      <c r="O26" t="str">
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
       </c>
       <c r="B27" t="str">
-        <v>2025-08-24</v>
+        <v>2025-08-29</v>
       </c>
       <c r="C27" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
+        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E27" t="str">
-        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
+        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
       </c>
       <c r="F27" t="str">
         <v/>
@@ -1341,24 +1629,36 @@
         <v/>
       </c>
       <c r="K27" t="str">
-        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+      </c>
+      <c r="L27" t="str">
+        <v/>
+      </c>
+      <c r="M27" t="str">
+        <v/>
+      </c>
+      <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
       </c>
       <c r="B28" t="str">
-        <v>2025-08-21</v>
+        <v>2025-08-24</v>
       </c>
       <c r="C28" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
+        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E28" t="str">
-        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
+        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
       </c>
       <c r="F28" t="str">
         <v/>
@@ -1376,24 +1676,36 @@
         <v/>
       </c>
       <c r="K28" t="str">
-        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+      </c>
+      <c r="L28" t="str">
+        <v/>
+      </c>
+      <c r="M28" t="str">
+        <v/>
+      </c>
+      <c r="N28" t="str">
+        <v/>
+      </c>
+      <c r="O28" t="str">
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>אברהם טל – חי</v>
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
       </c>
       <c r="B29" t="str">
-        <v>2025-08-17</v>
+        <v>2025-08-21</v>
       </c>
       <c r="C29" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E29" t="str">
-        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
+        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
       </c>
       <c r="F29" t="str">
         <v/>
@@ -1411,24 +1723,36 @@
         <v/>
       </c>
       <c r="K29" t="str">
-        <v>אברהם טל – חי</v>
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+      </c>
+      <c r="L29" t="str">
+        <v/>
+      </c>
+      <c r="M29" t="str">
+        <v/>
+      </c>
+      <c r="N29" t="str">
+        <v/>
+      </c>
+      <c r="O29" t="str">
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>רנה ראפ Bite Me</v>
+        <v>אברהם טל – חי</v>
       </c>
       <c r="B30" t="str">
-        <v>2025-08-12</v>
+        <v>2025-08-17</v>
       </c>
       <c r="C30" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E30" t="str">
-        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
+        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
       </c>
       <c r="F30" t="str">
         <v/>
@@ -1446,24 +1770,36 @@
         <v/>
       </c>
       <c r="K30" t="str">
-        <v>רנה ראפ Bite Me</v>
+        <v>אברהם טל – חי</v>
+      </c>
+      <c r="L30" t="str">
+        <v/>
+      </c>
+      <c r="M30" t="str">
+        <v/>
+      </c>
+      <c r="N30" t="str">
+        <v/>
+      </c>
+      <c r="O30" t="str">
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>The K's – Pretty On The Internet</v>
+        <v>רנה ראפ Bite Me</v>
       </c>
       <c r="B31" t="str">
-        <v>2025-08-03</v>
+        <v>2025-08-12</v>
       </c>
       <c r="C31" t="str">
-        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
+        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E31" t="str">
-        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
+        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
       </c>
       <c r="F31" t="str">
         <v/>
@@ -1481,24 +1817,36 @@
         <v/>
       </c>
       <c r="K31" t="str">
-        <v>The K's – Pretty On The Internet</v>
+        <v>רנה ראפ Bite Me</v>
+      </c>
+      <c r="L31" t="str">
+        <v/>
+      </c>
+      <c r="M31" t="str">
+        <v/>
+      </c>
+      <c r="N31" t="str">
+        <v/>
+      </c>
+      <c r="O31" t="str">
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>פטריק סבג Hotel Mogador</v>
+        <v>The K's – Pretty On The Internet</v>
       </c>
       <c r="B32" t="str">
-        <v>2026-01-13</v>
+        <v>2025-08-03</v>
       </c>
       <c r="C32" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
+        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E32" t="str">
-        <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
+        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
       </c>
       <c r="F32" t="str">
         <v/>
@@ -1516,7 +1864,7 @@
         <v/>
       </c>
       <c r="K32" t="str">
-        <v>פטריק סבג Hotel Mogador</v>
+        <v>The K's – Pretty On The Internet</v>
       </c>
       <c r="L32" t="str">
         <v/>
@@ -1533,19 +1881,19 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>מארינה מקסימיליאן – ריק בחלל</v>
+        <v>פטריק סבג Hotel Mogador</v>
       </c>
       <c r="B33" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C33" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E33" t="str">
-        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
+        <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
       </c>
       <c r="F33" t="str">
         <v/>
@@ -1563,7 +1911,7 @@
         <v/>
       </c>
       <c r="K33" t="str">
-        <v>מארינה מקסימיליאן – ריק בחלל</v>
+        <v>פטריק סבג Hotel Mogador</v>
       </c>
       <c r="L33" t="str">
         <v/>
@@ -1575,24 +1923,36 @@
         <v/>
       </c>
       <c r="O33" t="str">
+        <v/>
+      </c>
+      <c r="P33" t="str">
+        <v/>
+      </c>
+      <c r="Q33" t="str">
+        <v/>
+      </c>
+      <c r="R33" t="str">
+        <v/>
+      </c>
+      <c r="S33" t="str">
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>אוליביה דין The Art of Loving</v>
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
       </c>
       <c r="B34" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-09</v>
       </c>
       <c r="C34" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
+        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E34" t="str">
-        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
+        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
       </c>
       <c r="F34" t="str">
         <v/>
@@ -1610,7 +1970,7 @@
         <v/>
       </c>
       <c r="K34" t="str">
-        <v>אוליביה דין The Art of Loving</v>
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
       </c>
       <c r="L34" t="str">
         <v/>
@@ -1622,24 +1982,36 @@
         <v/>
       </c>
       <c r="O34" t="str">
+        <v/>
+      </c>
+      <c r="P34" t="str">
+        <v/>
+      </c>
+      <c r="Q34" t="str">
+        <v/>
+      </c>
+      <c r="R34" t="str">
+        <v/>
+      </c>
+      <c r="S34" t="str">
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Geese Getting Killed</v>
+        <v>אוליביה דין The Art of Loving</v>
       </c>
       <c r="B35" t="str">
-        <v>2025-12-29</v>
+        <v>2026-01-04</v>
       </c>
       <c r="C35" t="str">
-        <v>https://yosmusic.com/geese-getting-killed/</v>
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E35" t="str">
-        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
+        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
       </c>
       <c r="F35" t="str">
         <v/>
@@ -1657,7 +2029,7 @@
         <v/>
       </c>
       <c r="K35" t="str">
-        <v>Geese Getting Killed</v>
+        <v>אוליביה דין The Art of Loving</v>
       </c>
       <c r="L35" t="str">
         <v/>
@@ -1669,24 +2041,36 @@
         <v/>
       </c>
       <c r="O35" t="str">
+        <v/>
+      </c>
+      <c r="P35" t="str">
+        <v/>
+      </c>
+      <c r="Q35" t="str">
+        <v/>
+      </c>
+      <c r="R35" t="str">
+        <v/>
+      </c>
+      <c r="S35" t="str">
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>רוסליה Lux</v>
+        <v>Geese Getting Killed</v>
       </c>
       <c r="B36" t="str">
-        <v>2025-12-25</v>
+        <v>2025-12-29</v>
       </c>
       <c r="C36" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
+        <v>https://yosmusic.com/geese-getting-killed/</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E36" t="str">
-        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
+        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
       </c>
       <c r="F36" t="str">
         <v/>
@@ -1704,7 +2088,7 @@
         <v/>
       </c>
       <c r="K36" t="str">
-        <v>רוסליה Lux</v>
+        <v>Geese Getting Killed</v>
       </c>
       <c r="L36" t="str">
         <v/>
@@ -1716,24 +2100,36 @@
         <v/>
       </c>
       <c r="O36" t="str">
+        <v/>
+      </c>
+      <c r="P36" t="str">
+        <v/>
+      </c>
+      <c r="Q36" t="str">
+        <v/>
+      </c>
+      <c r="R36" t="str">
+        <v/>
+      </c>
+      <c r="S36" t="str">
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>יאנגבלאד אירוסמית' one more time</v>
+        <v>רוסליה Lux</v>
       </c>
       <c r="B37" t="str">
-        <v>2025-12-17</v>
+        <v>2025-12-25</v>
       </c>
       <c r="C37" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E37" t="str">
-        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
+        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
       </c>
       <c r="F37" t="str">
         <v/>
@@ -1751,7 +2147,7 @@
         <v/>
       </c>
       <c r="K37" t="str">
-        <v>יאנגבלאד אירוסמית' one more time</v>
+        <v>רוסליה Lux</v>
       </c>
       <c r="L37" t="str">
         <v/>
@@ -1763,24 +2159,36 @@
         <v/>
       </c>
       <c r="O37" t="str">
+        <v/>
+      </c>
+      <c r="P37" t="str">
+        <v/>
+      </c>
+      <c r="Q37" t="str">
+        <v/>
+      </c>
+      <c r="R37" t="str">
+        <v/>
+      </c>
+      <c r="S37" t="str">
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>פינק פלויד Wish You Were Here 50</v>
+        <v>יאנגבלאד אירוסמית' one more time</v>
       </c>
       <c r="B38" t="str">
-        <v>2025-12-14</v>
+        <v>2025-12-17</v>
       </c>
       <c r="C38" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
+        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E38" t="str">
-        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
+        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
       </c>
       <c r="F38" t="str">
         <v/>
@@ -1798,7 +2206,7 @@
         <v/>
       </c>
       <c r="K38" t="str">
-        <v>פינק פלויד Wish You Were Here 50</v>
+        <v>יאנגבלאד אירוסמית' one more time</v>
       </c>
       <c r="L38" t="str">
         <v/>
@@ -1810,24 +2218,36 @@
         <v/>
       </c>
       <c r="O38" t="str">
+        <v/>
+      </c>
+      <c r="P38" t="str">
+        <v/>
+      </c>
+      <c r="Q38" t="str">
+        <v/>
+      </c>
+      <c r="R38" t="str">
+        <v/>
+      </c>
+      <c r="S38" t="str">
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+        <v>פינק פלויד Wish You Were Here 50</v>
       </c>
       <c r="B39" t="str">
-        <v>2025-12-08</v>
+        <v>2025-12-14</v>
       </c>
       <c r="C39" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E39" t="str">
-        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
+        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
       </c>
       <c r="F39" t="str">
         <v/>
@@ -1845,7 +2265,7 @@
         <v/>
       </c>
       <c r="K39" t="str">
-        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+        <v>פינק פלויד Wish You Were Here 50</v>
       </c>
       <c r="L39" t="str">
         <v/>
@@ -1857,24 +2277,36 @@
         <v/>
       </c>
       <c r="O39" t="str">
+        <v/>
+      </c>
+      <c r="P39" t="str">
+        <v/>
+      </c>
+      <c r="Q39" t="str">
+        <v/>
+      </c>
+      <c r="R39" t="str">
+        <v/>
+      </c>
+      <c r="S39" t="str">
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>סטריי קידס DO IT EP</v>
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
       </c>
       <c r="B40" t="str">
-        <v>2025-12-04</v>
+        <v>2025-12-08</v>
       </c>
       <c r="C40" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
+        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E40" t="str">
-        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
+        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
       </c>
       <c r="F40" t="str">
         <v/>
@@ -1892,7 +2324,7 @@
         <v/>
       </c>
       <c r="K40" t="str">
-        <v>סטריי קידס DO IT EP</v>
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
       </c>
       <c r="L40" t="str">
         <v/>
@@ -1904,24 +2336,36 @@
         <v/>
       </c>
       <c r="O40" t="str">
+        <v/>
+      </c>
+      <c r="P40" t="str">
+        <v/>
+      </c>
+      <c r="Q40" t="str">
+        <v/>
+      </c>
+      <c r="R40" t="str">
+        <v/>
+      </c>
+      <c r="S40" t="str">
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>דויד ברוזה BROZAJAZZ</v>
+        <v>סטריי קידס DO IT EP</v>
       </c>
       <c r="B41" t="str">
-        <v>2025-11-30</v>
+        <v>2025-12-04</v>
       </c>
       <c r="C41" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
+        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E41" t="str">
-        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
+        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
       </c>
       <c r="F41" t="str">
         <v/>
@@ -1939,7 +2383,7 @@
         <v/>
       </c>
       <c r="K41" t="str">
-        <v>דויד ברוזה BROZAJAZZ</v>
+        <v>סטריי קידס DO IT EP</v>
       </c>
       <c r="L41" t="str">
         <v/>
@@ -1951,24 +2395,36 @@
         <v/>
       </c>
       <c r="O41" t="str">
+        <v/>
+      </c>
+      <c r="P41" t="str">
+        <v/>
+      </c>
+      <c r="Q41" t="str">
+        <v/>
+      </c>
+      <c r="R41" t="str">
+        <v/>
+      </c>
+      <c r="S41" t="str">
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Five Seconds of Summer – Everyone's A Star</v>
+        <v>דויד ברוזה BROZAJAZZ</v>
       </c>
       <c r="B42" t="str">
-        <v>2025-11-24</v>
+        <v>2025-11-30</v>
       </c>
       <c r="C42" t="str">
-        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E42" t="str">
-        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
+        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
       </c>
       <c r="F42" t="str">
         <v/>
@@ -1986,7 +2442,7 @@
         <v/>
       </c>
       <c r="K42" t="str">
-        <v>Five Seconds of Summer – Everyone's A Star</v>
+        <v>דויד ברוזה BROZAJAZZ</v>
       </c>
       <c r="L42" t="str">
         <v/>
@@ -1998,24 +2454,36 @@
         <v/>
       </c>
       <c r="O42" t="str">
+        <v/>
+      </c>
+      <c r="P42" t="str">
+        <v/>
+      </c>
+      <c r="Q42" t="str">
+        <v/>
+      </c>
+      <c r="R42" t="str">
+        <v/>
+      </c>
+      <c r="S42" t="str">
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>התקווה 6 – ויהי אור</v>
+        <v>Five Seconds of Summer – Everyone's A Star</v>
       </c>
       <c r="B43" t="str">
-        <v>2025-11-20</v>
+        <v>2025-11-24</v>
       </c>
       <c r="C43" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
+        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E43" t="str">
-        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
+        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
       </c>
       <c r="F43" t="str">
         <v/>
@@ -2033,7 +2501,7 @@
         <v/>
       </c>
       <c r="K43" t="str">
-        <v>התקווה 6 – ויהי אור</v>
+        <v>Five Seconds of Summer – Everyone's A Star</v>
       </c>
       <c r="L43" t="str">
         <v/>
@@ -2045,24 +2513,36 @@
         <v/>
       </c>
       <c r="O43" t="str">
+        <v/>
+      </c>
+      <c r="P43" t="str">
+        <v/>
+      </c>
+      <c r="Q43" t="str">
+        <v/>
+      </c>
+      <c r="R43" t="str">
+        <v/>
+      </c>
+      <c r="S43" t="str">
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>פלורנס אנד דה משין Everybody Scream</v>
+        <v>התקווה 6 – ויהי אור</v>
       </c>
       <c r="B44" t="str">
-        <v>2025-11-13</v>
+        <v>2025-11-20</v>
       </c>
       <c r="C44" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
+        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E44" t="str">
-        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
+        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
       </c>
       <c r="F44" t="str">
         <v/>
@@ -2080,7 +2560,7 @@
         <v/>
       </c>
       <c r="K44" t="str">
-        <v>פלורנס אנד דה משין Everybody Scream</v>
+        <v>התקווה 6 – ויהי אור</v>
       </c>
       <c r="L44" t="str">
         <v/>
@@ -2092,24 +2572,36 @@
         <v/>
       </c>
       <c r="O44" t="str">
+        <v/>
+      </c>
+      <c r="P44" t="str">
+        <v/>
+      </c>
+      <c r="Q44" t="str">
+        <v/>
+      </c>
+      <c r="R44" t="str">
+        <v/>
+      </c>
+      <c r="S44" t="str">
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>טיים אימפלה Deadbeat</v>
+        <v>פלורנס אנד דה משין Everybody Scream</v>
       </c>
       <c r="B45" t="str">
-        <v>2025-11-03</v>
+        <v>2025-11-13</v>
       </c>
       <c r="C45" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E45" t="str">
-        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
+        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
       </c>
       <c r="F45" t="str">
         <v/>
@@ -2127,7 +2619,7 @@
         <v/>
       </c>
       <c r="K45" t="str">
-        <v>טיים אימפלה Deadbeat</v>
+        <v>פלורנס אנד דה משין Everybody Scream</v>
       </c>
       <c r="L45" t="str">
         <v/>
@@ -2139,24 +2631,36 @@
         <v/>
       </c>
       <c r="O45" t="str">
+        <v/>
+      </c>
+      <c r="P45" t="str">
+        <v/>
+      </c>
+      <c r="Q45" t="str">
+        <v/>
+      </c>
+      <c r="R45" t="str">
+        <v/>
+      </c>
+      <c r="S45" t="str">
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+        <v>טיים אימפלה Deadbeat</v>
       </c>
       <c r="B46" t="str">
-        <v>2025-10-20</v>
+        <v>2025-11-03</v>
       </c>
       <c r="C46" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E46" t="str">
-        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
+        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
       </c>
       <c r="F46" t="str">
         <v/>
@@ -2174,7 +2678,7 @@
         <v/>
       </c>
       <c r="K46" t="str">
-        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+        <v>טיים אימפלה Deadbeat</v>
       </c>
       <c r="L46" t="str">
         <v/>
@@ -2186,24 +2690,36 @@
         <v/>
       </c>
       <c r="O46" t="str">
+        <v/>
+      </c>
+      <c r="P46" t="str">
+        <v/>
+      </c>
+      <c r="Q46" t="str">
+        <v/>
+      </c>
+      <c r="R46" t="str">
+        <v/>
+      </c>
+      <c r="S46" t="str">
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>שלמה גרוניך – תודה אהבה</v>
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
       </c>
       <c r="B47" t="str">
-        <v>2025-10-18</v>
+        <v>2025-10-20</v>
       </c>
       <c r="C47" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
+        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E47" t="str">
-        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
+        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
       </c>
       <c r="F47" t="str">
         <v/>
@@ -2221,7 +2737,7 @@
         <v/>
       </c>
       <c r="K47" t="str">
-        <v>שלמה גרוניך – תודה אהבה</v>
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
       </c>
       <c r="L47" t="str">
         <v/>
@@ -2233,24 +2749,36 @@
         <v/>
       </c>
       <c r="O47" t="str">
+        <v/>
+      </c>
+      <c r="P47" t="str">
+        <v/>
+      </c>
+      <c r="Q47" t="str">
+        <v/>
+      </c>
+      <c r="R47" t="str">
+        <v/>
+      </c>
+      <c r="S47" t="str">
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>טיילור סוויפט The Life Of A Showgirl</v>
+        <v>שלמה גרוניך – תודה אהבה</v>
       </c>
       <c r="B48" t="str">
-        <v>2025-10-11</v>
+        <v>2025-10-18</v>
       </c>
       <c r="C48" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E48" t="str">
-        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
+        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
       </c>
       <c r="F48" t="str">
         <v/>
@@ -2268,7 +2796,7 @@
         <v/>
       </c>
       <c r="K48" t="str">
-        <v>טיילור סוויפט The Life Of A Showgirl</v>
+        <v>שלמה גרוניך – תודה אהבה</v>
       </c>
       <c r="L48" t="str">
         <v/>
@@ -2280,24 +2808,36 @@
         <v/>
       </c>
       <c r="O48" t="str">
+        <v/>
+      </c>
+      <c r="P48" t="str">
+        <v/>
+      </c>
+      <c r="Q48" t="str">
+        <v/>
+      </c>
+      <c r="R48" t="str">
+        <v/>
+      </c>
+      <c r="S48" t="str">
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>דוג'ה קאט Vie</v>
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
       </c>
       <c r="B49" t="str">
-        <v>2025-10-04</v>
+        <v>2025-10-11</v>
       </c>
       <c r="C49" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E49" t="str">
-        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
+        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
       </c>
       <c r="F49" t="str">
         <v/>
@@ -2315,7 +2855,7 @@
         <v/>
       </c>
       <c r="K49" t="str">
-        <v>דוג'ה קאט Vie</v>
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
       </c>
       <c r="L49" t="str">
         <v/>
@@ -2327,24 +2867,36 @@
         <v/>
       </c>
       <c r="O49" t="str">
+        <v/>
+      </c>
+      <c r="P49" t="str">
+        <v/>
+      </c>
+      <c r="Q49" t="str">
+        <v/>
+      </c>
+      <c r="R49" t="str">
+        <v/>
+      </c>
+      <c r="S49" t="str">
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ג'וי קרוקס Juniper</v>
+        <v>דוג'ה קאט Vie</v>
       </c>
       <c r="B50" t="str">
-        <v>2025-10-03</v>
+        <v>2025-10-04</v>
       </c>
       <c r="C50" t="str">
-        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E50" t="str">
-        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
+        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
       </c>
       <c r="F50" t="str">
         <v/>
@@ -2362,7 +2914,7 @@
         <v/>
       </c>
       <c r="K50" t="str">
-        <v>ג'וי קרוקס Juniper</v>
+        <v>דוג'ה קאט Vie</v>
       </c>
       <c r="L50" t="str">
         <v/>
@@ -2374,24 +2926,36 @@
         <v/>
       </c>
       <c r="O50" t="str">
+        <v/>
+      </c>
+      <c r="P50" t="str">
+        <v/>
+      </c>
+      <c r="Q50" t="str">
+        <v/>
+      </c>
+      <c r="R50" t="str">
+        <v/>
+      </c>
+      <c r="S50" t="str">
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ביפי קליירו Futique</v>
+        <v>ג'וי קרוקס Juniper</v>
       </c>
       <c r="B51" t="str">
-        <v>2025-09-30</v>
+        <v>2025-10-03</v>
       </c>
       <c r="C51" t="str">
-        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
+        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E51" t="str">
-        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
+        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
       </c>
       <c r="F51" t="str">
         <v/>
@@ -2409,7 +2973,7 @@
         <v/>
       </c>
       <c r="K51" t="str">
-        <v>ביפי קליירו Futique</v>
+        <v>ג'וי קרוקס Juniper</v>
       </c>
       <c r="L51" t="str">
         <v/>
@@ -2421,24 +2985,36 @@
         <v/>
       </c>
       <c r="O51" t="str">
+        <v/>
+      </c>
+      <c r="P51" t="str">
+        <v/>
+      </c>
+      <c r="Q51" t="str">
+        <v/>
+      </c>
+      <c r="R51" t="str">
+        <v/>
+      </c>
+      <c r="S51" t="str">
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>אד שירן Play</v>
+        <v>ביפי קליירו Futique</v>
       </c>
       <c r="B52" t="str">
-        <v>2025-09-24</v>
+        <v>2025-09-30</v>
       </c>
       <c r="C52" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
+        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E52" t="str">
-        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
+        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
       </c>
       <c r="F52" t="str">
         <v/>
@@ -2456,7 +3032,7 @@
         <v/>
       </c>
       <c r="K52" t="str">
-        <v>אד שירן Play</v>
+        <v>ביפי קליירו Futique</v>
       </c>
       <c r="L52" t="str">
         <v/>
@@ -2468,24 +3044,36 @@
         <v/>
       </c>
       <c r="O52" t="str">
+        <v/>
+      </c>
+      <c r="P52" t="str">
+        <v/>
+      </c>
+      <c r="Q52" t="str">
+        <v/>
+      </c>
+      <c r="R52" t="str">
+        <v/>
+      </c>
+      <c r="S52" t="str">
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+        <v>אד שירן Play</v>
       </c>
       <c r="B53" t="str">
-        <v>2025-09-21</v>
+        <v>2025-09-24</v>
       </c>
       <c r="C53" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E53" t="str">
-        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
+        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
       </c>
       <c r="F53" t="str">
         <v/>
@@ -2503,7 +3091,7 @@
         <v/>
       </c>
       <c r="K53" t="str">
-        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+        <v>אד שירן Play</v>
       </c>
       <c r="L53" t="str">
         <v/>
@@ -2515,24 +3103,36 @@
         <v/>
       </c>
       <c r="O53" t="str">
+        <v/>
+      </c>
+      <c r="P53" t="str">
+        <v/>
+      </c>
+      <c r="Q53" t="str">
+        <v/>
+      </c>
+      <c r="R53" t="str">
+        <v/>
+      </c>
+      <c r="S53" t="str">
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>סוויד Antidepressants</v>
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
       </c>
       <c r="B54" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-21</v>
       </c>
       <c r="C54" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E54" t="str">
-        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
+        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
       </c>
       <c r="F54" t="str">
         <v/>
@@ -2550,7 +3150,7 @@
         <v/>
       </c>
       <c r="K54" t="str">
-        <v>סוויד Antidepressants</v>
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
       </c>
       <c r="L54" t="str">
         <v/>
@@ -2562,24 +3162,36 @@
         <v/>
       </c>
       <c r="O54" t="str">
+        <v/>
+      </c>
+      <c r="P54" t="str">
+        <v/>
+      </c>
+      <c r="Q54" t="str">
+        <v/>
+      </c>
+      <c r="R54" t="str">
+        <v/>
+      </c>
+      <c r="S54" t="str">
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>וולף אליס The Clearing</v>
+        <v>סוויד Antidepressants</v>
       </c>
       <c r="B55" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-12</v>
       </c>
       <c r="C55" t="str">
-        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
+        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E55" t="str">
-        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
+        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
       </c>
       <c r="F55" t="str">
         <v/>
@@ -2597,7 +3209,7 @@
         <v/>
       </c>
       <c r="K55" t="str">
-        <v>וולף אליס The Clearing</v>
+        <v>סוויד Antidepressants</v>
       </c>
       <c r="L55" t="str">
         <v/>
@@ -2609,24 +3221,36 @@
         <v/>
       </c>
       <c r="O55" t="str">
+        <v/>
+      </c>
+      <c r="P55" t="str">
+        <v/>
+      </c>
+      <c r="Q55" t="str">
+        <v/>
+      </c>
+      <c r="R55" t="str">
+        <v/>
+      </c>
+      <c r="S55" t="str">
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+        <v>וולף אליס The Clearing</v>
       </c>
       <c r="B56" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-01</v>
       </c>
       <c r="C56" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
+        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E56" t="str">
-        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
+        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
       </c>
       <c r="F56" t="str">
         <v/>
@@ -2644,7 +3268,7 @@
         <v/>
       </c>
       <c r="K56" t="str">
-        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+        <v>וולף אליס The Clearing</v>
       </c>
       <c r="L56" t="str">
         <v/>
@@ -2656,24 +3280,36 @@
         <v/>
       </c>
       <c r="O56" t="str">
+        <v/>
+      </c>
+      <c r="P56" t="str">
+        <v/>
+      </c>
+      <c r="Q56" t="str">
+        <v/>
+      </c>
+      <c r="R56" t="str">
+        <v/>
+      </c>
+      <c r="S56" t="str">
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
       </c>
       <c r="B57" t="str">
-        <v>2025-08-24</v>
+        <v>2025-08-29</v>
       </c>
       <c r="C57" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
+        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E57" t="str">
-        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
+        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
       </c>
       <c r="F57" t="str">
         <v/>
@@ -2691,7 +3327,7 @@
         <v/>
       </c>
       <c r="K57" t="str">
-        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
       </c>
       <c r="L57" t="str">
         <v/>
@@ -2703,24 +3339,36 @@
         <v/>
       </c>
       <c r="O57" t="str">
+        <v/>
+      </c>
+      <c r="P57" t="str">
+        <v/>
+      </c>
+      <c r="Q57" t="str">
+        <v/>
+      </c>
+      <c r="R57" t="str">
+        <v/>
+      </c>
+      <c r="S57" t="str">
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
       </c>
       <c r="B58" t="str">
-        <v>2025-08-21</v>
+        <v>2025-08-24</v>
       </c>
       <c r="C58" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
+        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E58" t="str">
-        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
+        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
       </c>
       <c r="F58" t="str">
         <v/>
@@ -2738,7 +3386,7 @@
         <v/>
       </c>
       <c r="K58" t="str">
-        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
       </c>
       <c r="L58" t="str">
         <v/>
@@ -2750,24 +3398,36 @@
         <v/>
       </c>
       <c r="O58" t="str">
+        <v/>
+      </c>
+      <c r="P58" t="str">
+        <v/>
+      </c>
+      <c r="Q58" t="str">
+        <v/>
+      </c>
+      <c r="R58" t="str">
+        <v/>
+      </c>
+      <c r="S58" t="str">
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>אברהם טל – חי</v>
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
       </c>
       <c r="B59" t="str">
-        <v>2025-08-17</v>
+        <v>2025-08-21</v>
       </c>
       <c r="C59" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E59" t="str">
-        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
+        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
       </c>
       <c r="F59" t="str">
         <v/>
@@ -2785,7 +3445,7 @@
         <v/>
       </c>
       <c r="K59" t="str">
-        <v>אברהם טל – חי</v>
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
       </c>
       <c r="L59" t="str">
         <v/>
@@ -2797,24 +3457,36 @@
         <v/>
       </c>
       <c r="O59" t="str">
+        <v/>
+      </c>
+      <c r="P59" t="str">
+        <v/>
+      </c>
+      <c r="Q59" t="str">
+        <v/>
+      </c>
+      <c r="R59" t="str">
+        <v/>
+      </c>
+      <c r="S59" t="str">
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>רנה ראפ Bite Me</v>
+        <v>אברהם טל – חי</v>
       </c>
       <c r="B60" t="str">
-        <v>2025-08-12</v>
+        <v>2025-08-17</v>
       </c>
       <c r="C60" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E60" t="str">
-        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
+        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
       </c>
       <c r="F60" t="str">
         <v/>
@@ -2832,7 +3504,7 @@
         <v/>
       </c>
       <c r="K60" t="str">
-        <v>רנה ראפ Bite Me</v>
+        <v>אברהם טל – חי</v>
       </c>
       <c r="L60" t="str">
         <v/>
@@ -2844,24 +3516,36 @@
         <v/>
       </c>
       <c r="O60" t="str">
+        <v/>
+      </c>
+      <c r="P60" t="str">
+        <v/>
+      </c>
+      <c r="Q60" t="str">
+        <v/>
+      </c>
+      <c r="R60" t="str">
+        <v/>
+      </c>
+      <c r="S60" t="str">
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>The K's – Pretty On The Internet</v>
+        <v>רנה ראפ Bite Me</v>
       </c>
       <c r="B61" t="str">
-        <v>2025-08-03</v>
+        <v>2025-08-12</v>
       </c>
       <c r="C61" t="str">
-        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
+        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E61" t="str">
-        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
+        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
       </c>
       <c r="F61" t="str">
         <v/>
@@ -2879,7 +3563,7 @@
         <v/>
       </c>
       <c r="K61" t="str">
-        <v>The K's – Pretty On The Internet</v>
+        <v>רנה ראפ Bite Me</v>
       </c>
       <c r="L61" t="str">
         <v/>
@@ -2891,24 +3575,36 @@
         <v/>
       </c>
       <c r="O61" t="str">
+        <v/>
+      </c>
+      <c r="P61" t="str">
+        <v/>
+      </c>
+      <c r="Q61" t="str">
+        <v/>
+      </c>
+      <c r="R61" t="str">
+        <v/>
+      </c>
+      <c r="S61" t="str">
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>פטריק סבג Hotel Mogador</v>
+        <v>The K's – Pretty On The Internet</v>
       </c>
       <c r="B62" t="str">
-        <v>2026-01-13</v>
+        <v>2025-08-03</v>
       </c>
       <c r="C62" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
+        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E62" t="str">
-        <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
+        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
       </c>
       <c r="F62" t="str">
         <v/>
@@ -2926,7 +3622,7 @@
         <v/>
       </c>
       <c r="K62" t="str">
-        <v>פטריק סבג Hotel Mogador</v>
+        <v>The K's – Pretty On The Internet</v>
       </c>
       <c r="L62" t="str">
         <v/>
@@ -2955,19 +3651,19 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>מארינה מקסימיליאן – ריק בחלל</v>
+        <v>פטריק סבג Hotel Mogador</v>
       </c>
       <c r="B63" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C63" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E63" t="str">
-        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
+        <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
       </c>
       <c r="F63" t="str">
         <v/>
@@ -2985,7 +3681,7 @@
         <v/>
       </c>
       <c r="K63" t="str">
-        <v>מארינה מקסימיליאן – ריק בחלל</v>
+        <v>פטריק סבג Hotel Mogador</v>
       </c>
       <c r="L63" t="str">
         <v/>
@@ -3009,24 +3705,36 @@
         <v/>
       </c>
       <c r="S63" t="str">
+        <v/>
+      </c>
+      <c r="T63" t="str">
+        <v/>
+      </c>
+      <c r="U63" t="str">
+        <v/>
+      </c>
+      <c r="V63" t="str">
+        <v/>
+      </c>
+      <c r="W63" t="str">
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>אוליביה דין The Art of Loving</v>
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
       </c>
       <c r="B64" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-09</v>
       </c>
       <c r="C64" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
+        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E64" t="str">
-        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
+        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
       </c>
       <c r="F64" t="str">
         <v/>
@@ -3044,7 +3752,7 @@
         <v/>
       </c>
       <c r="K64" t="str">
-        <v>אוליביה דין The Art of Loving</v>
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
       </c>
       <c r="L64" t="str">
         <v/>
@@ -3068,24 +3776,36 @@
         <v/>
       </c>
       <c r="S64" t="str">
+        <v/>
+      </c>
+      <c r="T64" t="str">
+        <v/>
+      </c>
+      <c r="U64" t="str">
+        <v/>
+      </c>
+      <c r="V64" t="str">
+        <v/>
+      </c>
+      <c r="W64" t="str">
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Geese Getting Killed</v>
+        <v>אוליביה דין The Art of Loving</v>
       </c>
       <c r="B65" t="str">
-        <v>2025-12-29</v>
+        <v>2026-01-04</v>
       </c>
       <c r="C65" t="str">
-        <v>https://yosmusic.com/geese-getting-killed/</v>
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E65" t="str">
-        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
+        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
       </c>
       <c r="F65" t="str">
         <v/>
@@ -3103,7 +3823,7 @@
         <v/>
       </c>
       <c r="K65" t="str">
-        <v>Geese Getting Killed</v>
+        <v>אוליביה דין The Art of Loving</v>
       </c>
       <c r="L65" t="str">
         <v/>
@@ -3127,24 +3847,36 @@
         <v/>
       </c>
       <c r="S65" t="str">
+        <v/>
+      </c>
+      <c r="T65" t="str">
+        <v/>
+      </c>
+      <c r="U65" t="str">
+        <v/>
+      </c>
+      <c r="V65" t="str">
+        <v/>
+      </c>
+      <c r="W65" t="str">
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>רוסליה Lux</v>
+        <v>Geese Getting Killed</v>
       </c>
       <c r="B66" t="str">
-        <v>2025-12-25</v>
+        <v>2025-12-29</v>
       </c>
       <c r="C66" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
+        <v>https://yosmusic.com/geese-getting-killed/</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E66" t="str">
-        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
+        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
       </c>
       <c r="F66" t="str">
         <v/>
@@ -3162,7 +3894,7 @@
         <v/>
       </c>
       <c r="K66" t="str">
-        <v>רוסליה Lux</v>
+        <v>Geese Getting Killed</v>
       </c>
       <c r="L66" t="str">
         <v/>
@@ -3186,24 +3918,36 @@
         <v/>
       </c>
       <c r="S66" t="str">
+        <v/>
+      </c>
+      <c r="T66" t="str">
+        <v/>
+      </c>
+      <c r="U66" t="str">
+        <v/>
+      </c>
+      <c r="V66" t="str">
+        <v/>
+      </c>
+      <c r="W66" t="str">
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>יאנגבלאד אירוסמית' one more time</v>
+        <v>רוסליה Lux</v>
       </c>
       <c r="B67" t="str">
-        <v>2025-12-17</v>
+        <v>2025-12-25</v>
       </c>
       <c r="C67" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E67" t="str">
-        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
+        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
       </c>
       <c r="F67" t="str">
         <v/>
@@ -3221,7 +3965,7 @@
         <v/>
       </c>
       <c r="K67" t="str">
-        <v>יאנגבלאד אירוסמית' one more time</v>
+        <v>רוסליה Lux</v>
       </c>
       <c r="L67" t="str">
         <v/>
@@ -3245,24 +3989,36 @@
         <v/>
       </c>
       <c r="S67" t="str">
+        <v/>
+      </c>
+      <c r="T67" t="str">
+        <v/>
+      </c>
+      <c r="U67" t="str">
+        <v/>
+      </c>
+      <c r="V67" t="str">
+        <v/>
+      </c>
+      <c r="W67" t="str">
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>פינק פלויד Wish You Were Here 50</v>
+        <v>יאנגבלאד אירוסמית' one more time</v>
       </c>
       <c r="B68" t="str">
-        <v>2025-12-14</v>
+        <v>2025-12-17</v>
       </c>
       <c r="C68" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
+        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E68" t="str">
-        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
+        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
       </c>
       <c r="F68" t="str">
         <v/>
@@ -3280,7 +4036,7 @@
         <v/>
       </c>
       <c r="K68" t="str">
-        <v>פינק פלויד Wish You Were Here 50</v>
+        <v>יאנגבלאד אירוסמית' one more time</v>
       </c>
       <c r="L68" t="str">
         <v/>
@@ -3304,24 +4060,36 @@
         <v/>
       </c>
       <c r="S68" t="str">
+        <v/>
+      </c>
+      <c r="T68" t="str">
+        <v/>
+      </c>
+      <c r="U68" t="str">
+        <v/>
+      </c>
+      <c r="V68" t="str">
+        <v/>
+      </c>
+      <c r="W68" t="str">
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+        <v>פינק פלויד Wish You Were Here 50</v>
       </c>
       <c r="B69" t="str">
-        <v>2025-12-08</v>
+        <v>2025-12-14</v>
       </c>
       <c r="C69" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E69" t="str">
-        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
+        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
       </c>
       <c r="F69" t="str">
         <v/>
@@ -3339,7 +4107,7 @@
         <v/>
       </c>
       <c r="K69" t="str">
-        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+        <v>פינק פלויד Wish You Were Here 50</v>
       </c>
       <c r="L69" t="str">
         <v/>
@@ -3363,24 +4131,36 @@
         <v/>
       </c>
       <c r="S69" t="str">
+        <v/>
+      </c>
+      <c r="T69" t="str">
+        <v/>
+      </c>
+      <c r="U69" t="str">
+        <v/>
+      </c>
+      <c r="V69" t="str">
+        <v/>
+      </c>
+      <c r="W69" t="str">
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>סטריי קידס DO IT EP</v>
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
       </c>
       <c r="B70" t="str">
-        <v>2025-12-04</v>
+        <v>2025-12-08</v>
       </c>
       <c r="C70" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
+        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E70" t="str">
-        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
+        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
       </c>
       <c r="F70" t="str">
         <v/>
@@ -3398,7 +4178,7 @@
         <v/>
       </c>
       <c r="K70" t="str">
-        <v>סטריי קידס DO IT EP</v>
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
       </c>
       <c r="L70" t="str">
         <v/>
@@ -3422,24 +4202,36 @@
         <v/>
       </c>
       <c r="S70" t="str">
+        <v/>
+      </c>
+      <c r="T70" t="str">
+        <v/>
+      </c>
+      <c r="U70" t="str">
+        <v/>
+      </c>
+      <c r="V70" t="str">
+        <v/>
+      </c>
+      <c r="W70" t="str">
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>דויד ברוזה BROZAJAZZ</v>
+        <v>סטריי קידס DO IT EP</v>
       </c>
       <c r="B71" t="str">
-        <v>2025-11-30</v>
+        <v>2025-12-04</v>
       </c>
       <c r="C71" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
+        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E71" t="str">
-        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
+        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
       </c>
       <c r="F71" t="str">
         <v/>
@@ -3457,7 +4249,7 @@
         <v/>
       </c>
       <c r="K71" t="str">
-        <v>דויד ברוזה BROZAJAZZ</v>
+        <v>סטריי קידס DO IT EP</v>
       </c>
       <c r="L71" t="str">
         <v/>
@@ -3481,24 +4273,36 @@
         <v/>
       </c>
       <c r="S71" t="str">
+        <v/>
+      </c>
+      <c r="T71" t="str">
+        <v/>
+      </c>
+      <c r="U71" t="str">
+        <v/>
+      </c>
+      <c r="V71" t="str">
+        <v/>
+      </c>
+      <c r="W71" t="str">
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Five Seconds of Summer – Everyone's A Star</v>
+        <v>דויד ברוזה BROZAJAZZ</v>
       </c>
       <c r="B72" t="str">
-        <v>2025-11-24</v>
+        <v>2025-11-30</v>
       </c>
       <c r="C72" t="str">
-        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E72" t="str">
-        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
+        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
       </c>
       <c r="F72" t="str">
         <v/>
@@ -3516,7 +4320,7 @@
         <v/>
       </c>
       <c r="K72" t="str">
-        <v>Five Seconds of Summer – Everyone's A Star</v>
+        <v>דויד ברוזה BROZAJAZZ</v>
       </c>
       <c r="L72" t="str">
         <v/>
@@ -3540,24 +4344,36 @@
         <v/>
       </c>
       <c r="S72" t="str">
+        <v/>
+      </c>
+      <c r="T72" t="str">
+        <v/>
+      </c>
+      <c r="U72" t="str">
+        <v/>
+      </c>
+      <c r="V72" t="str">
+        <v/>
+      </c>
+      <c r="W72" t="str">
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>התקווה 6 – ויהי אור</v>
+        <v>Five Seconds of Summer – Everyone's A Star</v>
       </c>
       <c r="B73" t="str">
-        <v>2025-11-20</v>
+        <v>2025-11-24</v>
       </c>
       <c r="C73" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
+        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E73" t="str">
-        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
+        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
       </c>
       <c r="F73" t="str">
         <v/>
@@ -3575,7 +4391,7 @@
         <v/>
       </c>
       <c r="K73" t="str">
-        <v>התקווה 6 – ויהי אור</v>
+        <v>Five Seconds of Summer – Everyone's A Star</v>
       </c>
       <c r="L73" t="str">
         <v/>
@@ -3599,24 +4415,36 @@
         <v/>
       </c>
       <c r="S73" t="str">
+        <v/>
+      </c>
+      <c r="T73" t="str">
+        <v/>
+      </c>
+      <c r="U73" t="str">
+        <v/>
+      </c>
+      <c r="V73" t="str">
+        <v/>
+      </c>
+      <c r="W73" t="str">
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>פלורנס אנד דה משין Everybody Scream</v>
+        <v>התקווה 6 – ויהי אור</v>
       </c>
       <c r="B74" t="str">
-        <v>2025-11-13</v>
+        <v>2025-11-20</v>
       </c>
       <c r="C74" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
+        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E74" t="str">
-        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
+        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
       </c>
       <c r="F74" t="str">
         <v/>
@@ -3634,7 +4462,7 @@
         <v/>
       </c>
       <c r="K74" t="str">
-        <v>פלורנס אנד דה משין Everybody Scream</v>
+        <v>התקווה 6 – ויהי אור</v>
       </c>
       <c r="L74" t="str">
         <v/>
@@ -3658,24 +4486,36 @@
         <v/>
       </c>
       <c r="S74" t="str">
+        <v/>
+      </c>
+      <c r="T74" t="str">
+        <v/>
+      </c>
+      <c r="U74" t="str">
+        <v/>
+      </c>
+      <c r="V74" t="str">
+        <v/>
+      </c>
+      <c r="W74" t="str">
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>טיים אימפלה Deadbeat</v>
+        <v>פלורנס אנד דה משין Everybody Scream</v>
       </c>
       <c r="B75" t="str">
-        <v>2025-11-03</v>
+        <v>2025-11-13</v>
       </c>
       <c r="C75" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E75" t="str">
-        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
+        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
       </c>
       <c r="F75" t="str">
         <v/>
@@ -3693,7 +4533,7 @@
         <v/>
       </c>
       <c r="K75" t="str">
-        <v>טיים אימפלה Deadbeat</v>
+        <v>פלורנס אנד דה משין Everybody Scream</v>
       </c>
       <c r="L75" t="str">
         <v/>
@@ -3717,24 +4557,36 @@
         <v/>
       </c>
       <c r="S75" t="str">
+        <v/>
+      </c>
+      <c r="T75" t="str">
+        <v/>
+      </c>
+      <c r="U75" t="str">
+        <v/>
+      </c>
+      <c r="V75" t="str">
+        <v/>
+      </c>
+      <c r="W75" t="str">
         <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+        <v>טיים אימפלה Deadbeat</v>
       </c>
       <c r="B76" t="str">
-        <v>2025-10-20</v>
+        <v>2025-11-03</v>
       </c>
       <c r="C76" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E76" t="str">
-        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
+        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
       </c>
       <c r="F76" t="str">
         <v/>
@@ -3752,7 +4604,7 @@
         <v/>
       </c>
       <c r="K76" t="str">
-        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+        <v>טיים אימפלה Deadbeat</v>
       </c>
       <c r="L76" t="str">
         <v/>
@@ -3776,24 +4628,36 @@
         <v/>
       </c>
       <c r="S76" t="str">
+        <v/>
+      </c>
+      <c r="T76" t="str">
+        <v/>
+      </c>
+      <c r="U76" t="str">
+        <v/>
+      </c>
+      <c r="V76" t="str">
+        <v/>
+      </c>
+      <c r="W76" t="str">
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>שלמה גרוניך – תודה אהבה</v>
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
       </c>
       <c r="B77" t="str">
-        <v>2025-10-18</v>
+        <v>2025-10-20</v>
       </c>
       <c r="C77" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
+        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E77" t="str">
-        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
+        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
       </c>
       <c r="F77" t="str">
         <v/>
@@ -3811,7 +4675,7 @@
         <v/>
       </c>
       <c r="K77" t="str">
-        <v>שלמה גרוניך – תודה אהבה</v>
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
       </c>
       <c r="L77" t="str">
         <v/>
@@ -3835,24 +4699,36 @@
         <v/>
       </c>
       <c r="S77" t="str">
+        <v/>
+      </c>
+      <c r="T77" t="str">
+        <v/>
+      </c>
+      <c r="U77" t="str">
+        <v/>
+      </c>
+      <c r="V77" t="str">
+        <v/>
+      </c>
+      <c r="W77" t="str">
         <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>טיילור סוויפט The Life Of A Showgirl</v>
+        <v>שלמה גרוניך – תודה אהבה</v>
       </c>
       <c r="B78" t="str">
-        <v>2025-10-11</v>
+        <v>2025-10-18</v>
       </c>
       <c r="C78" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E78" t="str">
-        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
+        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
       </c>
       <c r="F78" t="str">
         <v/>
@@ -3870,7 +4746,7 @@
         <v/>
       </c>
       <c r="K78" t="str">
-        <v>טיילור סוויפט The Life Of A Showgirl</v>
+        <v>שלמה גרוניך – תודה אהבה</v>
       </c>
       <c r="L78" t="str">
         <v/>
@@ -3894,24 +4770,36 @@
         <v/>
       </c>
       <c r="S78" t="str">
+        <v/>
+      </c>
+      <c r="T78" t="str">
+        <v/>
+      </c>
+      <c r="U78" t="str">
+        <v/>
+      </c>
+      <c r="V78" t="str">
+        <v/>
+      </c>
+      <c r="W78" t="str">
         <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>דוג'ה קאט Vie</v>
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
       </c>
       <c r="B79" t="str">
-        <v>2025-10-04</v>
+        <v>2025-10-11</v>
       </c>
       <c r="C79" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E79" t="str">
-        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
+        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
       </c>
       <c r="F79" t="str">
         <v/>
@@ -3929,7 +4817,7 @@
         <v/>
       </c>
       <c r="K79" t="str">
-        <v>דוג'ה קאט Vie</v>
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
       </c>
       <c r="L79" t="str">
         <v/>
@@ -3953,24 +4841,36 @@
         <v/>
       </c>
       <c r="S79" t="str">
+        <v/>
+      </c>
+      <c r="T79" t="str">
+        <v/>
+      </c>
+      <c r="U79" t="str">
+        <v/>
+      </c>
+      <c r="V79" t="str">
+        <v/>
+      </c>
+      <c r="W79" t="str">
         <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>ג'וי קרוקס Juniper</v>
+        <v>דוג'ה קאט Vie</v>
       </c>
       <c r="B80" t="str">
-        <v>2025-10-03</v>
+        <v>2025-10-04</v>
       </c>
       <c r="C80" t="str">
-        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E80" t="str">
-        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
+        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
       </c>
       <c r="F80" t="str">
         <v/>
@@ -3988,7 +4888,7 @@
         <v/>
       </c>
       <c r="K80" t="str">
-        <v>ג'וי קרוקס Juniper</v>
+        <v>דוג'ה קאט Vie</v>
       </c>
       <c r="L80" t="str">
         <v/>
@@ -4012,24 +4912,36 @@
         <v/>
       </c>
       <c r="S80" t="str">
+        <v/>
+      </c>
+      <c r="T80" t="str">
+        <v/>
+      </c>
+      <c r="U80" t="str">
+        <v/>
+      </c>
+      <c r="V80" t="str">
+        <v/>
+      </c>
+      <c r="W80" t="str">
         <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>ביפי קליירו Futique</v>
+        <v>ג'וי קרוקס Juniper</v>
       </c>
       <c r="B81" t="str">
-        <v>2025-09-30</v>
+        <v>2025-10-03</v>
       </c>
       <c r="C81" t="str">
-        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
+        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E81" t="str">
-        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
+        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
       </c>
       <c r="F81" t="str">
         <v/>
@@ -4047,7 +4959,7 @@
         <v/>
       </c>
       <c r="K81" t="str">
-        <v>ביפי קליירו Futique</v>
+        <v>ג'וי קרוקס Juniper</v>
       </c>
       <c r="L81" t="str">
         <v/>
@@ -4071,24 +4983,36 @@
         <v/>
       </c>
       <c r="S81" t="str">
+        <v/>
+      </c>
+      <c r="T81" t="str">
+        <v/>
+      </c>
+      <c r="U81" t="str">
+        <v/>
+      </c>
+      <c r="V81" t="str">
+        <v/>
+      </c>
+      <c r="W81" t="str">
         <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>אד שירן Play</v>
+        <v>ביפי קליירו Futique</v>
       </c>
       <c r="B82" t="str">
-        <v>2025-09-24</v>
+        <v>2025-09-30</v>
       </c>
       <c r="C82" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
+        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E82" t="str">
-        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
+        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
       </c>
       <c r="F82" t="str">
         <v/>
@@ -4106,7 +5030,7 @@
         <v/>
       </c>
       <c r="K82" t="str">
-        <v>אד שירן Play</v>
+        <v>ביפי קליירו Futique</v>
       </c>
       <c r="L82" t="str">
         <v/>
@@ -4130,24 +5054,36 @@
         <v/>
       </c>
       <c r="S82" t="str">
+        <v/>
+      </c>
+      <c r="T82" t="str">
+        <v/>
+      </c>
+      <c r="U82" t="str">
+        <v/>
+      </c>
+      <c r="V82" t="str">
+        <v/>
+      </c>
+      <c r="W82" t="str">
         <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+        <v>אד שירן Play</v>
       </c>
       <c r="B83" t="str">
-        <v>2025-09-21</v>
+        <v>2025-09-24</v>
       </c>
       <c r="C83" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E83" t="str">
-        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
+        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
       </c>
       <c r="F83" t="str">
         <v/>
@@ -4165,7 +5101,7 @@
         <v/>
       </c>
       <c r="K83" t="str">
-        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+        <v>אד שירן Play</v>
       </c>
       <c r="L83" t="str">
         <v/>
@@ -4189,24 +5125,36 @@
         <v/>
       </c>
       <c r="S83" t="str">
+        <v/>
+      </c>
+      <c r="T83" t="str">
+        <v/>
+      </c>
+      <c r="U83" t="str">
+        <v/>
+      </c>
+      <c r="V83" t="str">
+        <v/>
+      </c>
+      <c r="W83" t="str">
         <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>סוויד Antidepressants</v>
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
       </c>
       <c r="B84" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-21</v>
       </c>
       <c r="C84" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E84" t="str">
-        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
+        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
       </c>
       <c r="F84" t="str">
         <v/>
@@ -4224,7 +5172,7 @@
         <v/>
       </c>
       <c r="K84" t="str">
-        <v>סוויד Antidepressants</v>
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
       </c>
       <c r="L84" t="str">
         <v/>
@@ -4248,24 +5196,36 @@
         <v/>
       </c>
       <c r="S84" t="str">
+        <v/>
+      </c>
+      <c r="T84" t="str">
+        <v/>
+      </c>
+      <c r="U84" t="str">
+        <v/>
+      </c>
+      <c r="V84" t="str">
+        <v/>
+      </c>
+      <c r="W84" t="str">
         <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>וולף אליס The Clearing</v>
+        <v>סוויד Antidepressants</v>
       </c>
       <c r="B85" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-12</v>
       </c>
       <c r="C85" t="str">
-        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
+        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E85" t="str">
-        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
+        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
       </c>
       <c r="F85" t="str">
         <v/>
@@ -4283,7 +5243,7 @@
         <v/>
       </c>
       <c r="K85" t="str">
-        <v>וולף אליס The Clearing</v>
+        <v>סוויד Antidepressants</v>
       </c>
       <c r="L85" t="str">
         <v/>
@@ -4307,24 +5267,36 @@
         <v/>
       </c>
       <c r="S85" t="str">
+        <v/>
+      </c>
+      <c r="T85" t="str">
+        <v/>
+      </c>
+      <c r="U85" t="str">
+        <v/>
+      </c>
+      <c r="V85" t="str">
+        <v/>
+      </c>
+      <c r="W85" t="str">
         <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+        <v>וולף אליס The Clearing</v>
       </c>
       <c r="B86" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-01</v>
       </c>
       <c r="C86" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
+        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E86" t="str">
-        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
+        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
       </c>
       <c r="F86" t="str">
         <v/>
@@ -4342,7 +5314,7 @@
         <v/>
       </c>
       <c r="K86" t="str">
-        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+        <v>וולף אליס The Clearing</v>
       </c>
       <c r="L86" t="str">
         <v/>
@@ -4366,24 +5338,36 @@
         <v/>
       </c>
       <c r="S86" t="str">
+        <v/>
+      </c>
+      <c r="T86" t="str">
+        <v/>
+      </c>
+      <c r="U86" t="str">
+        <v/>
+      </c>
+      <c r="V86" t="str">
+        <v/>
+      </c>
+      <c r="W86" t="str">
         <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
       </c>
       <c r="B87" t="str">
-        <v>2025-08-24</v>
+        <v>2025-08-29</v>
       </c>
       <c r="C87" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
+        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E87" t="str">
-        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
+        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
       </c>
       <c r="F87" t="str">
         <v/>
@@ -4401,7 +5385,7 @@
         <v/>
       </c>
       <c r="K87" t="str">
-        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
       </c>
       <c r="L87" t="str">
         <v/>
@@ -4425,24 +5409,36 @@
         <v/>
       </c>
       <c r="S87" t="str">
+        <v/>
+      </c>
+      <c r="T87" t="str">
+        <v/>
+      </c>
+      <c r="U87" t="str">
+        <v/>
+      </c>
+      <c r="V87" t="str">
+        <v/>
+      </c>
+      <c r="W87" t="str">
         <v/>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
       </c>
       <c r="B88" t="str">
-        <v>2025-08-21</v>
+        <v>2025-08-24</v>
       </c>
       <c r="C88" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
+        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E88" t="str">
-        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
+        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
       </c>
       <c r="F88" t="str">
         <v/>
@@ -4460,7 +5456,7 @@
         <v/>
       </c>
       <c r="K88" t="str">
-        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
       </c>
       <c r="L88" t="str">
         <v/>
@@ -4484,24 +5480,36 @@
         <v/>
       </c>
       <c r="S88" t="str">
+        <v/>
+      </c>
+      <c r="T88" t="str">
+        <v/>
+      </c>
+      <c r="U88" t="str">
+        <v/>
+      </c>
+      <c r="V88" t="str">
+        <v/>
+      </c>
+      <c r="W88" t="str">
         <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>אברהם טל – חי</v>
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
       </c>
       <c r="B89" t="str">
-        <v>2025-08-17</v>
+        <v>2025-08-21</v>
       </c>
       <c r="C89" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E89" t="str">
-        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
+        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
       </c>
       <c r="F89" t="str">
         <v/>
@@ -4519,7 +5527,7 @@
         <v/>
       </c>
       <c r="K89" t="str">
-        <v>אברהם טל – חי</v>
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
       </c>
       <c r="L89" t="str">
         <v/>
@@ -4543,24 +5551,36 @@
         <v/>
       </c>
       <c r="S89" t="str">
+        <v/>
+      </c>
+      <c r="T89" t="str">
+        <v/>
+      </c>
+      <c r="U89" t="str">
+        <v/>
+      </c>
+      <c r="V89" t="str">
+        <v/>
+      </c>
+      <c r="W89" t="str">
         <v/>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>רנה ראפ Bite Me</v>
+        <v>אברהם טל – חי</v>
       </c>
       <c r="B90" t="str">
-        <v>2025-08-12</v>
+        <v>2025-08-17</v>
       </c>
       <c r="C90" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E90" t="str">
-        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
+        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
       </c>
       <c r="F90" t="str">
         <v/>
@@ -4578,7 +5598,7 @@
         <v/>
       </c>
       <c r="K90" t="str">
-        <v>רנה ראפ Bite Me</v>
+        <v>אברהם טל – חי</v>
       </c>
       <c r="L90" t="str">
         <v/>
@@ -4602,24 +5622,36 @@
         <v/>
       </c>
       <c r="S90" t="str">
+        <v/>
+      </c>
+      <c r="T90" t="str">
+        <v/>
+      </c>
+      <c r="U90" t="str">
+        <v/>
+      </c>
+      <c r="V90" t="str">
+        <v/>
+      </c>
+      <c r="W90" t="str">
         <v/>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>The K's – Pretty On The Internet</v>
+        <v>רנה ראפ Bite Me</v>
       </c>
       <c r="B91" t="str">
-        <v>2025-08-03</v>
+        <v>2025-08-12</v>
       </c>
       <c r="C91" t="str">
-        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
+        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E91" t="str">
-        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
+        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
       </c>
       <c r="F91" t="str">
         <v/>
@@ -4637,7 +5669,7 @@
         <v/>
       </c>
       <c r="K91" t="str">
-        <v>The K's – Pretty On The Internet</v>
+        <v>רנה ראפ Bite Me</v>
       </c>
       <c r="L91" t="str">
         <v/>
@@ -4661,24 +5693,36 @@
         <v/>
       </c>
       <c r="S91" t="str">
+        <v/>
+      </c>
+      <c r="T91" t="str">
+        <v/>
+      </c>
+      <c r="U91" t="str">
+        <v/>
+      </c>
+      <c r="V91" t="str">
+        <v/>
+      </c>
+      <c r="W91" t="str">
         <v/>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>פטריק סבג Hotel Mogador</v>
+        <v>The K's – Pretty On The Internet</v>
       </c>
       <c r="B92" t="str">
-        <v>2026-01-13</v>
+        <v>2025-08-03</v>
       </c>
       <c r="C92" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
+        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E92" t="str">
-        <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
+        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
       </c>
       <c r="F92" t="str">
         <v/>
@@ -4696,7 +5740,7 @@
         <v/>
       </c>
       <c r="K92" t="str">
-        <v>פטריק סבג Hotel Mogador</v>
+        <v>The K's – Pretty On The Internet</v>
       </c>
       <c r="L92" t="str">
         <v/>
@@ -4737,19 +5781,19 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>מארינה מקסימיליאן – ריק בחלל</v>
+        <v>פטריק סבג Hotel Mogador</v>
       </c>
       <c r="B93" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C93" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E93" t="str">
-        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
+        <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
       </c>
       <c r="F93" t="str">
         <v/>
@@ -4767,7 +5811,7 @@
         <v/>
       </c>
       <c r="K93" t="str">
-        <v>מארינה מקסימיליאן – ריק בחלל</v>
+        <v>פטריק סבג Hotel Mogador</v>
       </c>
       <c r="L93" t="str">
         <v/>
@@ -4803,24 +5847,36 @@
         <v/>
       </c>
       <c r="W93" t="str">
+        <v/>
+      </c>
+      <c r="X93" t="str">
+        <v/>
+      </c>
+      <c r="Y93" t="str">
+        <v/>
+      </c>
+      <c r="Z93" t="str">
+        <v/>
+      </c>
+      <c r="AA93" t="str">
         <v/>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>אוליביה דין The Art of Loving</v>
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
       </c>
       <c r="B94" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-09</v>
       </c>
       <c r="C94" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
+        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E94" t="str">
-        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
+        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
       </c>
       <c r="F94" t="str">
         <v/>
@@ -4838,7 +5894,7 @@
         <v/>
       </c>
       <c r="K94" t="str">
-        <v>אוליביה דין The Art of Loving</v>
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
       </c>
       <c r="L94" t="str">
         <v/>
@@ -4874,24 +5930,36 @@
         <v/>
       </c>
       <c r="W94" t="str">
+        <v/>
+      </c>
+      <c r="X94" t="str">
+        <v/>
+      </c>
+      <c r="Y94" t="str">
+        <v/>
+      </c>
+      <c r="Z94" t="str">
+        <v/>
+      </c>
+      <c r="AA94" t="str">
         <v/>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Geese Getting Killed</v>
+        <v>אוליביה דין The Art of Loving</v>
       </c>
       <c r="B95" t="str">
-        <v>2025-12-29</v>
+        <v>2026-01-04</v>
       </c>
       <c r="C95" t="str">
-        <v>https://yosmusic.com/geese-getting-killed/</v>
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
       </c>
       <c r="D95" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E95" t="str">
-        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
+        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
       </c>
       <c r="F95" t="str">
         <v/>
@@ -4909,7 +5977,7 @@
         <v/>
       </c>
       <c r="K95" t="str">
-        <v>Geese Getting Killed</v>
+        <v>אוליביה דין The Art of Loving</v>
       </c>
       <c r="L95" t="str">
         <v/>
@@ -4945,24 +6013,36 @@
         <v/>
       </c>
       <c r="W95" t="str">
+        <v/>
+      </c>
+      <c r="X95" t="str">
+        <v/>
+      </c>
+      <c r="Y95" t="str">
+        <v/>
+      </c>
+      <c r="Z95" t="str">
+        <v/>
+      </c>
+      <c r="AA95" t="str">
         <v/>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>רוסליה Lux</v>
+        <v>Geese Getting Killed</v>
       </c>
       <c r="B96" t="str">
-        <v>2025-12-25</v>
+        <v>2025-12-29</v>
       </c>
       <c r="C96" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
+        <v>https://yosmusic.com/geese-getting-killed/</v>
       </c>
       <c r="D96" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E96" t="str">
-        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
+        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
       </c>
       <c r="F96" t="str">
         <v/>
@@ -4980,7 +6060,7 @@
         <v/>
       </c>
       <c r="K96" t="str">
-        <v>רוסליה Lux</v>
+        <v>Geese Getting Killed</v>
       </c>
       <c r="L96" t="str">
         <v/>
@@ -5016,24 +6096,36 @@
         <v/>
       </c>
       <c r="W96" t="str">
+        <v/>
+      </c>
+      <c r="X96" t="str">
+        <v/>
+      </c>
+      <c r="Y96" t="str">
+        <v/>
+      </c>
+      <c r="Z96" t="str">
+        <v/>
+      </c>
+      <c r="AA96" t="str">
         <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>יאנגבלאד אירוסמית' one more time</v>
+        <v>רוסליה Lux</v>
       </c>
       <c r="B97" t="str">
-        <v>2025-12-17</v>
+        <v>2025-12-25</v>
       </c>
       <c r="C97" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
       </c>
       <c r="D97" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E97" t="str">
-        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
+        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
       </c>
       <c r="F97" t="str">
         <v/>
@@ -5051,7 +6143,7 @@
         <v/>
       </c>
       <c r="K97" t="str">
-        <v>יאנגבלאד אירוסמית' one more time</v>
+        <v>רוסליה Lux</v>
       </c>
       <c r="L97" t="str">
         <v/>
@@ -5087,24 +6179,36 @@
         <v/>
       </c>
       <c r="W97" t="str">
+        <v/>
+      </c>
+      <c r="X97" t="str">
+        <v/>
+      </c>
+      <c r="Y97" t="str">
+        <v/>
+      </c>
+      <c r="Z97" t="str">
+        <v/>
+      </c>
+      <c r="AA97" t="str">
         <v/>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>פינק פלויד Wish You Were Here 50</v>
+        <v>יאנגבלאד אירוסמית' one more time</v>
       </c>
       <c r="B98" t="str">
-        <v>2025-12-14</v>
+        <v>2025-12-17</v>
       </c>
       <c r="C98" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
+        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
       </c>
       <c r="D98" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E98" t="str">
-        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
+        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
       </c>
       <c r="F98" t="str">
         <v/>
@@ -5122,7 +6226,7 @@
         <v/>
       </c>
       <c r="K98" t="str">
-        <v>פינק פלויד Wish You Were Here 50</v>
+        <v>יאנגבלאד אירוסמית' one more time</v>
       </c>
       <c r="L98" t="str">
         <v/>
@@ -5158,24 +6262,36 @@
         <v/>
       </c>
       <c r="W98" t="str">
+        <v/>
+      </c>
+      <c r="X98" t="str">
+        <v/>
+      </c>
+      <c r="Y98" t="str">
+        <v/>
+      </c>
+      <c r="Z98" t="str">
+        <v/>
+      </c>
+      <c r="AA98" t="str">
         <v/>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+        <v>פינק פלויד Wish You Were Here 50</v>
       </c>
       <c r="B99" t="str">
-        <v>2025-12-08</v>
+        <v>2025-12-14</v>
       </c>
       <c r="C99" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
       </c>
       <c r="D99" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E99" t="str">
-        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
+        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
       </c>
       <c r="F99" t="str">
         <v/>
@@ -5193,7 +6309,7 @@
         <v/>
       </c>
       <c r="K99" t="str">
-        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+        <v>פינק פלויד Wish You Were Here 50</v>
       </c>
       <c r="L99" t="str">
         <v/>
@@ -5229,24 +6345,36 @@
         <v/>
       </c>
       <c r="W99" t="str">
+        <v/>
+      </c>
+      <c r="X99" t="str">
+        <v/>
+      </c>
+      <c r="Y99" t="str">
+        <v/>
+      </c>
+      <c r="Z99" t="str">
+        <v/>
+      </c>
+      <c r="AA99" t="str">
         <v/>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>סטריי קידס DO IT EP</v>
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
       </c>
       <c r="B100" t="str">
-        <v>2025-12-04</v>
+        <v>2025-12-08</v>
       </c>
       <c r="C100" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
+        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
       </c>
       <c r="D100" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E100" t="str">
-        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
+        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
       </c>
       <c r="F100" t="str">
         <v/>
@@ -5264,7 +6392,7 @@
         <v/>
       </c>
       <c r="K100" t="str">
-        <v>סטריי קידס DO IT EP</v>
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
       </c>
       <c r="L100" t="str">
         <v/>
@@ -5300,24 +6428,36 @@
         <v/>
       </c>
       <c r="W100" t="str">
+        <v/>
+      </c>
+      <c r="X100" t="str">
+        <v/>
+      </c>
+      <c r="Y100" t="str">
+        <v/>
+      </c>
+      <c r="Z100" t="str">
+        <v/>
+      </c>
+      <c r="AA100" t="str">
         <v/>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>דויד ברוזה BROZAJAZZ</v>
+        <v>סטריי קידס DO IT EP</v>
       </c>
       <c r="B101" t="str">
-        <v>2025-11-30</v>
+        <v>2025-12-04</v>
       </c>
       <c r="C101" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
+        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
       </c>
       <c r="D101" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E101" t="str">
-        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
+        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
       </c>
       <c r="F101" t="str">
         <v/>
@@ -5335,7 +6475,7 @@
         <v/>
       </c>
       <c r="K101" t="str">
-        <v>דויד ברוזה BROZAJAZZ</v>
+        <v>סטריי קידס DO IT EP</v>
       </c>
       <c r="L101" t="str">
         <v/>
@@ -5371,24 +6511,36 @@
         <v/>
       </c>
       <c r="W101" t="str">
+        <v/>
+      </c>
+      <c r="X101" t="str">
+        <v/>
+      </c>
+      <c r="Y101" t="str">
+        <v/>
+      </c>
+      <c r="Z101" t="str">
+        <v/>
+      </c>
+      <c r="AA101" t="str">
         <v/>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Five Seconds of Summer – Everyone's A Star</v>
+        <v>דויד ברוזה BROZAJAZZ</v>
       </c>
       <c r="B102" t="str">
-        <v>2025-11-24</v>
+        <v>2025-11-30</v>
       </c>
       <c r="C102" t="str">
-        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
       </c>
       <c r="D102" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E102" t="str">
-        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
+        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
       </c>
       <c r="F102" t="str">
         <v/>
@@ -5406,7 +6558,7 @@
         <v/>
       </c>
       <c r="K102" t="str">
-        <v>Five Seconds of Summer – Everyone's A Star</v>
+        <v>דויד ברוזה BROZAJAZZ</v>
       </c>
       <c r="L102" t="str">
         <v/>
@@ -5442,24 +6594,36 @@
         <v/>
       </c>
       <c r="W102" t="str">
+        <v/>
+      </c>
+      <c r="X102" t="str">
+        <v/>
+      </c>
+      <c r="Y102" t="str">
+        <v/>
+      </c>
+      <c r="Z102" t="str">
+        <v/>
+      </c>
+      <c r="AA102" t="str">
         <v/>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>התקווה 6 – ויהי אור</v>
+        <v>Five Seconds of Summer – Everyone's A Star</v>
       </c>
       <c r="B103" t="str">
-        <v>2025-11-20</v>
+        <v>2025-11-24</v>
       </c>
       <c r="C103" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
+        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
       </c>
       <c r="D103" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E103" t="str">
-        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
+        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
       </c>
       <c r="F103" t="str">
         <v/>
@@ -5477,7 +6641,7 @@
         <v/>
       </c>
       <c r="K103" t="str">
-        <v>התקווה 6 – ויהי אור</v>
+        <v>Five Seconds of Summer – Everyone's A Star</v>
       </c>
       <c r="L103" t="str">
         <v/>
@@ -5513,24 +6677,36 @@
         <v/>
       </c>
       <c r="W103" t="str">
+        <v/>
+      </c>
+      <c r="X103" t="str">
+        <v/>
+      </c>
+      <c r="Y103" t="str">
+        <v/>
+      </c>
+      <c r="Z103" t="str">
+        <v/>
+      </c>
+      <c r="AA103" t="str">
         <v/>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>פלורנס אנד דה משין Everybody Scream</v>
+        <v>התקווה 6 – ויהי אור</v>
       </c>
       <c r="B104" t="str">
-        <v>2025-11-13</v>
+        <v>2025-11-20</v>
       </c>
       <c r="C104" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
+        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
       </c>
       <c r="D104" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E104" t="str">
-        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
+        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
       </c>
       <c r="F104" t="str">
         <v/>
@@ -5548,7 +6724,7 @@
         <v/>
       </c>
       <c r="K104" t="str">
-        <v>פלורנס אנד דה משין Everybody Scream</v>
+        <v>התקווה 6 – ויהי אור</v>
       </c>
       <c r="L104" t="str">
         <v/>
@@ -5584,24 +6760,36 @@
         <v/>
       </c>
       <c r="W104" t="str">
+        <v/>
+      </c>
+      <c r="X104" t="str">
+        <v/>
+      </c>
+      <c r="Y104" t="str">
+        <v/>
+      </c>
+      <c r="Z104" t="str">
+        <v/>
+      </c>
+      <c r="AA104" t="str">
         <v/>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>טיים אימפלה Deadbeat</v>
+        <v>פלורנס אנד דה משין Everybody Scream</v>
       </c>
       <c r="B105" t="str">
-        <v>2025-11-03</v>
+        <v>2025-11-13</v>
       </c>
       <c r="C105" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
       </c>
       <c r="D105" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E105" t="str">
-        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
+        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
       </c>
       <c r="F105" t="str">
         <v/>
@@ -5619,7 +6807,7 @@
         <v/>
       </c>
       <c r="K105" t="str">
-        <v>טיים אימפלה Deadbeat</v>
+        <v>פלורנס אנד דה משין Everybody Scream</v>
       </c>
       <c r="L105" t="str">
         <v/>
@@ -5655,24 +6843,36 @@
         <v/>
       </c>
       <c r="W105" t="str">
+        <v/>
+      </c>
+      <c r="X105" t="str">
+        <v/>
+      </c>
+      <c r="Y105" t="str">
+        <v/>
+      </c>
+      <c r="Z105" t="str">
+        <v/>
+      </c>
+      <c r="AA105" t="str">
         <v/>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+        <v>טיים אימפלה Deadbeat</v>
       </c>
       <c r="B106" t="str">
-        <v>2025-10-20</v>
+        <v>2025-11-03</v>
       </c>
       <c r="C106" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
       </c>
       <c r="D106" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E106" t="str">
-        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
+        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
       </c>
       <c r="F106" t="str">
         <v/>
@@ -5690,7 +6890,7 @@
         <v/>
       </c>
       <c r="K106" t="str">
-        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+        <v>טיים אימפלה Deadbeat</v>
       </c>
       <c r="L106" t="str">
         <v/>
@@ -5726,24 +6926,36 @@
         <v/>
       </c>
       <c r="W106" t="str">
+        <v/>
+      </c>
+      <c r="X106" t="str">
+        <v/>
+      </c>
+      <c r="Y106" t="str">
+        <v/>
+      </c>
+      <c r="Z106" t="str">
+        <v/>
+      </c>
+      <c r="AA106" t="str">
         <v/>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>שלמה גרוניך – תודה אהבה</v>
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
       </c>
       <c r="B107" t="str">
-        <v>2025-10-18</v>
+        <v>2025-10-20</v>
       </c>
       <c r="C107" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
+        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
       </c>
       <c r="D107" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E107" t="str">
-        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
+        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
       </c>
       <c r="F107" t="str">
         <v/>
@@ -5761,7 +6973,7 @@
         <v/>
       </c>
       <c r="K107" t="str">
-        <v>שלמה גרוניך – תודה אהבה</v>
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
       </c>
       <c r="L107" t="str">
         <v/>
@@ -5797,24 +7009,36 @@
         <v/>
       </c>
       <c r="W107" t="str">
+        <v/>
+      </c>
+      <c r="X107" t="str">
+        <v/>
+      </c>
+      <c r="Y107" t="str">
+        <v/>
+      </c>
+      <c r="Z107" t="str">
+        <v/>
+      </c>
+      <c r="AA107" t="str">
         <v/>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>טיילור סוויפט The Life Of A Showgirl</v>
+        <v>שלמה גרוניך – תודה אהבה</v>
       </c>
       <c r="B108" t="str">
-        <v>2025-10-11</v>
+        <v>2025-10-18</v>
       </c>
       <c r="C108" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
       </c>
       <c r="D108" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E108" t="str">
-        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
+        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
       </c>
       <c r="F108" t="str">
         <v/>
@@ -5832,7 +7056,7 @@
         <v/>
       </c>
       <c r="K108" t="str">
-        <v>טיילור סוויפט The Life Of A Showgirl</v>
+        <v>שלמה גרוניך – תודה אהבה</v>
       </c>
       <c r="L108" t="str">
         <v/>
@@ -5868,24 +7092,36 @@
         <v/>
       </c>
       <c r="W108" t="str">
+        <v/>
+      </c>
+      <c r="X108" t="str">
+        <v/>
+      </c>
+      <c r="Y108" t="str">
+        <v/>
+      </c>
+      <c r="Z108" t="str">
+        <v/>
+      </c>
+      <c r="AA108" t="str">
         <v/>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>דוג'ה קאט Vie</v>
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
       </c>
       <c r="B109" t="str">
-        <v>2025-10-04</v>
+        <v>2025-10-11</v>
       </c>
       <c r="C109" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
       </c>
       <c r="D109" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E109" t="str">
-        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
+        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
       </c>
       <c r="F109" t="str">
         <v/>
@@ -5903,7 +7139,7 @@
         <v/>
       </c>
       <c r="K109" t="str">
-        <v>דוג'ה קאט Vie</v>
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
       </c>
       <c r="L109" t="str">
         <v/>
@@ -5939,24 +7175,36 @@
         <v/>
       </c>
       <c r="W109" t="str">
+        <v/>
+      </c>
+      <c r="X109" t="str">
+        <v/>
+      </c>
+      <c r="Y109" t="str">
+        <v/>
+      </c>
+      <c r="Z109" t="str">
+        <v/>
+      </c>
+      <c r="AA109" t="str">
         <v/>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>ג'וי קרוקס Juniper</v>
+        <v>דוג'ה קאט Vie</v>
       </c>
       <c r="B110" t="str">
-        <v>2025-10-03</v>
+        <v>2025-10-04</v>
       </c>
       <c r="C110" t="str">
-        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
       </c>
       <c r="D110" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E110" t="str">
-        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
+        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
       </c>
       <c r="F110" t="str">
         <v/>
@@ -5974,7 +7222,7 @@
         <v/>
       </c>
       <c r="K110" t="str">
-        <v>ג'וי קרוקס Juniper</v>
+        <v>דוג'ה קאט Vie</v>
       </c>
       <c r="L110" t="str">
         <v/>
@@ -6010,24 +7258,36 @@
         <v/>
       </c>
       <c r="W110" t="str">
+        <v/>
+      </c>
+      <c r="X110" t="str">
+        <v/>
+      </c>
+      <c r="Y110" t="str">
+        <v/>
+      </c>
+      <c r="Z110" t="str">
+        <v/>
+      </c>
+      <c r="AA110" t="str">
         <v/>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>ביפי קליירו Futique</v>
+        <v>ג'וי קרוקס Juniper</v>
       </c>
       <c r="B111" t="str">
-        <v>2025-09-30</v>
+        <v>2025-10-03</v>
       </c>
       <c r="C111" t="str">
-        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
+        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
       </c>
       <c r="D111" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E111" t="str">
-        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
+        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
       </c>
       <c r="F111" t="str">
         <v/>
@@ -6045,7 +7305,7 @@
         <v/>
       </c>
       <c r="K111" t="str">
-        <v>ביפי קליירו Futique</v>
+        <v>ג'וי קרוקס Juniper</v>
       </c>
       <c r="L111" t="str">
         <v/>
@@ -6081,24 +7341,36 @@
         <v/>
       </c>
       <c r="W111" t="str">
+        <v/>
+      </c>
+      <c r="X111" t="str">
+        <v/>
+      </c>
+      <c r="Y111" t="str">
+        <v/>
+      </c>
+      <c r="Z111" t="str">
+        <v/>
+      </c>
+      <c r="AA111" t="str">
         <v/>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>אד שירן Play</v>
+        <v>ביפי קליירו Futique</v>
       </c>
       <c r="B112" t="str">
-        <v>2025-09-24</v>
+        <v>2025-09-30</v>
       </c>
       <c r="C112" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
+        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
       </c>
       <c r="D112" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E112" t="str">
-        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
+        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
       </c>
       <c r="F112" t="str">
         <v/>
@@ -6116,7 +7388,7 @@
         <v/>
       </c>
       <c r="K112" t="str">
-        <v>אד שירן Play</v>
+        <v>ביפי קליירו Futique</v>
       </c>
       <c r="L112" t="str">
         <v/>
@@ -6152,24 +7424,36 @@
         <v/>
       </c>
       <c r="W112" t="str">
+        <v/>
+      </c>
+      <c r="X112" t="str">
+        <v/>
+      </c>
+      <c r="Y112" t="str">
+        <v/>
+      </c>
+      <c r="Z112" t="str">
+        <v/>
+      </c>
+      <c r="AA112" t="str">
         <v/>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+        <v>אד שירן Play</v>
       </c>
       <c r="B113" t="str">
-        <v>2025-09-21</v>
+        <v>2025-09-24</v>
       </c>
       <c r="C113" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
       </c>
       <c r="D113" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E113" t="str">
-        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
+        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
       </c>
       <c r="F113" t="str">
         <v/>
@@ -6187,7 +7471,7 @@
         <v/>
       </c>
       <c r="K113" t="str">
-        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+        <v>אד שירן Play</v>
       </c>
       <c r="L113" t="str">
         <v/>
@@ -6223,24 +7507,36 @@
         <v/>
       </c>
       <c r="W113" t="str">
+        <v/>
+      </c>
+      <c r="X113" t="str">
+        <v/>
+      </c>
+      <c r="Y113" t="str">
+        <v/>
+      </c>
+      <c r="Z113" t="str">
+        <v/>
+      </c>
+      <c r="AA113" t="str">
         <v/>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>סוויד Antidepressants</v>
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
       </c>
       <c r="B114" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-21</v>
       </c>
       <c r="C114" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
       </c>
       <c r="D114" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E114" t="str">
-        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
+        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
       </c>
       <c r="F114" t="str">
         <v/>
@@ -6258,7 +7554,7 @@
         <v/>
       </c>
       <c r="K114" t="str">
-        <v>סוויד Antidepressants</v>
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
       </c>
       <c r="L114" t="str">
         <v/>
@@ -6294,24 +7590,36 @@
         <v/>
       </c>
       <c r="W114" t="str">
+        <v/>
+      </c>
+      <c r="X114" t="str">
+        <v/>
+      </c>
+      <c r="Y114" t="str">
+        <v/>
+      </c>
+      <c r="Z114" t="str">
+        <v/>
+      </c>
+      <c r="AA114" t="str">
         <v/>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>וולף אליס The Clearing</v>
+        <v>סוויד Antidepressants</v>
       </c>
       <c r="B115" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-12</v>
       </c>
       <c r="C115" t="str">
-        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
+        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
       </c>
       <c r="D115" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E115" t="str">
-        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
+        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
       </c>
       <c r="F115" t="str">
         <v/>
@@ -6329,7 +7637,7 @@
         <v/>
       </c>
       <c r="K115" t="str">
-        <v>וולף אליס The Clearing</v>
+        <v>סוויד Antidepressants</v>
       </c>
       <c r="L115" t="str">
         <v/>
@@ -6365,24 +7673,36 @@
         <v/>
       </c>
       <c r="W115" t="str">
+        <v/>
+      </c>
+      <c r="X115" t="str">
+        <v/>
+      </c>
+      <c r="Y115" t="str">
+        <v/>
+      </c>
+      <c r="Z115" t="str">
+        <v/>
+      </c>
+      <c r="AA115" t="str">
         <v/>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+        <v>וולף אליס The Clearing</v>
       </c>
       <c r="B116" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-01</v>
       </c>
       <c r="C116" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
+        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
       </c>
       <c r="D116" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E116" t="str">
-        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
+        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
       </c>
       <c r="F116" t="str">
         <v/>
@@ -6400,7 +7720,7 @@
         <v/>
       </c>
       <c r="K116" t="str">
-        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+        <v>וולף אליס The Clearing</v>
       </c>
       <c r="L116" t="str">
         <v/>
@@ -6436,24 +7756,36 @@
         <v/>
       </c>
       <c r="W116" t="str">
+        <v/>
+      </c>
+      <c r="X116" t="str">
+        <v/>
+      </c>
+      <c r="Y116" t="str">
+        <v/>
+      </c>
+      <c r="Z116" t="str">
+        <v/>
+      </c>
+      <c r="AA116" t="str">
         <v/>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
       </c>
       <c r="B117" t="str">
-        <v>2025-08-24</v>
+        <v>2025-08-29</v>
       </c>
       <c r="C117" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
+        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
       </c>
       <c r="D117" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E117" t="str">
-        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
+        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
       </c>
       <c r="F117" t="str">
         <v/>
@@ -6471,7 +7803,7 @@
         <v/>
       </c>
       <c r="K117" t="str">
-        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
       </c>
       <c r="L117" t="str">
         <v/>
@@ -6507,24 +7839,36 @@
         <v/>
       </c>
       <c r="W117" t="str">
+        <v/>
+      </c>
+      <c r="X117" t="str">
+        <v/>
+      </c>
+      <c r="Y117" t="str">
+        <v/>
+      </c>
+      <c r="Z117" t="str">
+        <v/>
+      </c>
+      <c r="AA117" t="str">
         <v/>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
       </c>
       <c r="B118" t="str">
-        <v>2025-08-21</v>
+        <v>2025-08-24</v>
       </c>
       <c r="C118" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
+        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
       </c>
       <c r="D118" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E118" t="str">
-        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
+        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
       </c>
       <c r="F118" t="str">
         <v/>
@@ -6542,7 +7886,7 @@
         <v/>
       </c>
       <c r="K118" t="str">
-        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
       </c>
       <c r="L118" t="str">
         <v/>
@@ -6578,24 +7922,36 @@
         <v/>
       </c>
       <c r="W118" t="str">
+        <v/>
+      </c>
+      <c r="X118" t="str">
+        <v/>
+      </c>
+      <c r="Y118" t="str">
+        <v/>
+      </c>
+      <c r="Z118" t="str">
+        <v/>
+      </c>
+      <c r="AA118" t="str">
         <v/>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>אברהם טל – חי</v>
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
       </c>
       <c r="B119" t="str">
-        <v>2025-08-17</v>
+        <v>2025-08-21</v>
       </c>
       <c r="C119" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
       </c>
       <c r="D119" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E119" t="str">
-        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
+        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
       </c>
       <c r="F119" t="str">
         <v/>
@@ -6613,7 +7969,7 @@
         <v/>
       </c>
       <c r="K119" t="str">
-        <v>אברהם טל – חי</v>
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
       </c>
       <c r="L119" t="str">
         <v/>
@@ -6649,24 +8005,36 @@
         <v/>
       </c>
       <c r="W119" t="str">
+        <v/>
+      </c>
+      <c r="X119" t="str">
+        <v/>
+      </c>
+      <c r="Y119" t="str">
+        <v/>
+      </c>
+      <c r="Z119" t="str">
+        <v/>
+      </c>
+      <c r="AA119" t="str">
         <v/>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>רנה ראפ Bite Me</v>
+        <v>אברהם טל – חי</v>
       </c>
       <c r="B120" t="str">
-        <v>2025-08-12</v>
+        <v>2025-08-17</v>
       </c>
       <c r="C120" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
       </c>
       <c r="D120" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E120" t="str">
-        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
+        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
       </c>
       <c r="F120" t="str">
         <v/>
@@ -6684,7 +8052,7 @@
         <v/>
       </c>
       <c r="K120" t="str">
-        <v>רנה ראפ Bite Me</v>
+        <v>אברהם טל – חי</v>
       </c>
       <c r="L120" t="str">
         <v/>
@@ -6720,24 +8088,36 @@
         <v/>
       </c>
       <c r="W120" t="str">
+        <v/>
+      </c>
+      <c r="X120" t="str">
+        <v/>
+      </c>
+      <c r="Y120" t="str">
+        <v/>
+      </c>
+      <c r="Z120" t="str">
+        <v/>
+      </c>
+      <c r="AA120" t="str">
         <v/>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>The K's – Pretty On The Internet</v>
+        <v>רנה ראפ Bite Me</v>
       </c>
       <c r="B121" t="str">
-        <v>2025-08-03</v>
+        <v>2025-08-12</v>
       </c>
       <c r="C121" t="str">
-        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
+        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
       </c>
       <c r="D121" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E121" t="str">
-        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
+        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
       </c>
       <c r="F121" t="str">
         <v/>
@@ -6755,7 +8135,7 @@
         <v/>
       </c>
       <c r="K121" t="str">
-        <v>The K's – Pretty On The Internet</v>
+        <v>רנה ראפ Bite Me</v>
       </c>
       <c r="L121" t="str">
         <v/>
@@ -6791,24 +8171,36 @@
         <v/>
       </c>
       <c r="W121" t="str">
+        <v/>
+      </c>
+      <c r="X121" t="str">
+        <v/>
+      </c>
+      <c r="Y121" t="str">
+        <v/>
+      </c>
+      <c r="Z121" t="str">
+        <v/>
+      </c>
+      <c r="AA121" t="str">
         <v/>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>פטריק סבג Hotel Mogador</v>
+        <v>The K's – Pretty On The Internet</v>
       </c>
       <c r="B122" t="str">
-        <v>2026-01-13</v>
+        <v>2025-08-03</v>
       </c>
       <c r="C122" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
+        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
       </c>
       <c r="D122" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E122" t="str">
-        <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
+        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
       </c>
       <c r="F122" t="str">
         <v/>
@@ -6826,7 +8218,7 @@
         <v/>
       </c>
       <c r="K122" t="str">
-        <v>פטריק סבג Hotel Mogador</v>
+        <v>The K's – Pretty On The Internet</v>
       </c>
       <c r="L122" t="str">
         <v/>
@@ -6879,19 +8271,19 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>מארינה מקסימיליאן – ריק בחלל</v>
+        <v>פטריק סבג Hotel Mogador</v>
       </c>
       <c r="B123" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C123" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
       </c>
       <c r="D123" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E123" t="str">
-        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
+        <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
       </c>
       <c r="F123" t="str">
         <v/>
@@ -6909,7 +8301,7 @@
         <v/>
       </c>
       <c r="K123" t="str">
-        <v>מארינה מקסימיליאן – ריק בחלל</v>
+        <v>פטריק סבג Hotel Mogador</v>
       </c>
       <c r="L123" t="str">
         <v/>
@@ -6957,24 +8349,36 @@
         <v/>
       </c>
       <c r="AA123" t="str">
+        <v/>
+      </c>
+      <c r="AB123" t="str">
+        <v/>
+      </c>
+      <c r="AC123" t="str">
+        <v/>
+      </c>
+      <c r="AD123" t="str">
+        <v/>
+      </c>
+      <c r="AE123" t="str">
         <v/>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>אוליביה דין The Art of Loving</v>
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
       </c>
       <c r="B124" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-09</v>
       </c>
       <c r="C124" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
+        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
       </c>
       <c r="D124" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E124" t="str">
-        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
+        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
       </c>
       <c r="F124" t="str">
         <v/>
@@ -6992,7 +8396,7 @@
         <v/>
       </c>
       <c r="K124" t="str">
-        <v>אוליביה דין The Art of Loving</v>
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
       </c>
       <c r="L124" t="str">
         <v/>
@@ -7040,24 +8444,36 @@
         <v/>
       </c>
       <c r="AA124" t="str">
+        <v/>
+      </c>
+      <c r="AB124" t="str">
+        <v/>
+      </c>
+      <c r="AC124" t="str">
+        <v/>
+      </c>
+      <c r="AD124" t="str">
+        <v/>
+      </c>
+      <c r="AE124" t="str">
         <v/>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Geese Getting Killed</v>
+        <v>אוליביה דין The Art of Loving</v>
       </c>
       <c r="B125" t="str">
-        <v>2025-12-29</v>
+        <v>2026-01-04</v>
       </c>
       <c r="C125" t="str">
-        <v>https://yosmusic.com/geese-getting-killed/</v>
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
       </c>
       <c r="D125" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E125" t="str">
-        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
+        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
       </c>
       <c r="F125" t="str">
         <v/>
@@ -7075,7 +8491,7 @@
         <v/>
       </c>
       <c r="K125" t="str">
-        <v>Geese Getting Killed</v>
+        <v>אוליביה דין The Art of Loving</v>
       </c>
       <c r="L125" t="str">
         <v/>
@@ -7123,24 +8539,36 @@
         <v/>
       </c>
       <c r="AA125" t="str">
+        <v/>
+      </c>
+      <c r="AB125" t="str">
+        <v/>
+      </c>
+      <c r="AC125" t="str">
+        <v/>
+      </c>
+      <c r="AD125" t="str">
+        <v/>
+      </c>
+      <c r="AE125" t="str">
         <v/>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>רוסליה Lux</v>
+        <v>Geese Getting Killed</v>
       </c>
       <c r="B126" t="str">
-        <v>2025-12-25</v>
+        <v>2025-12-29</v>
       </c>
       <c r="C126" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
+        <v>https://yosmusic.com/geese-getting-killed/</v>
       </c>
       <c r="D126" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E126" t="str">
-        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
+        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
       </c>
       <c r="F126" t="str">
         <v/>
@@ -7158,7 +8586,7 @@
         <v/>
       </c>
       <c r="K126" t="str">
-        <v>רוסליה Lux</v>
+        <v>Geese Getting Killed</v>
       </c>
       <c r="L126" t="str">
         <v/>
@@ -7206,24 +8634,36 @@
         <v/>
       </c>
       <c r="AA126" t="str">
+        <v/>
+      </c>
+      <c r="AB126" t="str">
+        <v/>
+      </c>
+      <c r="AC126" t="str">
+        <v/>
+      </c>
+      <c r="AD126" t="str">
+        <v/>
+      </c>
+      <c r="AE126" t="str">
         <v/>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>יאנגבלאד אירוסמית' one more time</v>
+        <v>רוסליה Lux</v>
       </c>
       <c r="B127" t="str">
-        <v>2025-12-17</v>
+        <v>2025-12-25</v>
       </c>
       <c r="C127" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
       </c>
       <c r="D127" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E127" t="str">
-        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
+        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
       </c>
       <c r="F127" t="str">
         <v/>
@@ -7241,7 +8681,7 @@
         <v/>
       </c>
       <c r="K127" t="str">
-        <v>יאנגבלאד אירוסמית' one more time</v>
+        <v>רוסליה Lux</v>
       </c>
       <c r="L127" t="str">
         <v/>
@@ -7289,24 +8729,36 @@
         <v/>
       </c>
       <c r="AA127" t="str">
+        <v/>
+      </c>
+      <c r="AB127" t="str">
+        <v/>
+      </c>
+      <c r="AC127" t="str">
+        <v/>
+      </c>
+      <c r="AD127" t="str">
+        <v/>
+      </c>
+      <c r="AE127" t="str">
         <v/>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>פינק פלויד Wish You Were Here 50</v>
+        <v>יאנגבלאד אירוסמית' one more time</v>
       </c>
       <c r="B128" t="str">
-        <v>2025-12-14</v>
+        <v>2025-12-17</v>
       </c>
       <c r="C128" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
+        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
       </c>
       <c r="D128" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E128" t="str">
-        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
+        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
       </c>
       <c r="F128" t="str">
         <v/>
@@ -7324,7 +8776,7 @@
         <v/>
       </c>
       <c r="K128" t="str">
-        <v>פינק פלויד Wish You Were Here 50</v>
+        <v>יאנגבלאד אירוסמית' one more time</v>
       </c>
       <c r="L128" t="str">
         <v/>
@@ -7372,24 +8824,36 @@
         <v/>
       </c>
       <c r="AA128" t="str">
+        <v/>
+      </c>
+      <c r="AB128" t="str">
+        <v/>
+      </c>
+      <c r="AC128" t="str">
+        <v/>
+      </c>
+      <c r="AD128" t="str">
+        <v/>
+      </c>
+      <c r="AE128" t="str">
         <v/>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+        <v>פינק פלויד Wish You Were Here 50</v>
       </c>
       <c r="B129" t="str">
-        <v>2025-12-08</v>
+        <v>2025-12-14</v>
       </c>
       <c r="C129" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
       </c>
       <c r="D129" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E129" t="str">
-        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
+        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
       </c>
       <c r="F129" t="str">
         <v/>
@@ -7407,7 +8871,7 @@
         <v/>
       </c>
       <c r="K129" t="str">
-        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+        <v>פינק פלויד Wish You Were Here 50</v>
       </c>
       <c r="L129" t="str">
         <v/>
@@ -7455,24 +8919,36 @@
         <v/>
       </c>
       <c r="AA129" t="str">
+        <v/>
+      </c>
+      <c r="AB129" t="str">
+        <v/>
+      </c>
+      <c r="AC129" t="str">
+        <v/>
+      </c>
+      <c r="AD129" t="str">
+        <v/>
+      </c>
+      <c r="AE129" t="str">
         <v/>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>סטריי קידס DO IT EP</v>
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
       </c>
       <c r="B130" t="str">
-        <v>2025-12-04</v>
+        <v>2025-12-08</v>
       </c>
       <c r="C130" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
+        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
       </c>
       <c r="D130" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E130" t="str">
-        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
+        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
       </c>
       <c r="F130" t="str">
         <v/>
@@ -7490,7 +8966,7 @@
         <v/>
       </c>
       <c r="K130" t="str">
-        <v>סטריי קידס DO IT EP</v>
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
       </c>
       <c r="L130" t="str">
         <v/>
@@ -7538,24 +9014,36 @@
         <v/>
       </c>
       <c r="AA130" t="str">
+        <v/>
+      </c>
+      <c r="AB130" t="str">
+        <v/>
+      </c>
+      <c r="AC130" t="str">
+        <v/>
+      </c>
+      <c r="AD130" t="str">
+        <v/>
+      </c>
+      <c r="AE130" t="str">
         <v/>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>דויד ברוזה BROZAJAZZ</v>
+        <v>סטריי קידס DO IT EP</v>
       </c>
       <c r="B131" t="str">
-        <v>2025-11-30</v>
+        <v>2025-12-04</v>
       </c>
       <c r="C131" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
+        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
       </c>
       <c r="D131" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E131" t="str">
-        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
+        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
       </c>
       <c r="F131" t="str">
         <v/>
@@ -7573,7 +9061,7 @@
         <v/>
       </c>
       <c r="K131" t="str">
-        <v>דויד ברוזה BROZAJAZZ</v>
+        <v>סטריי קידס DO IT EP</v>
       </c>
       <c r="L131" t="str">
         <v/>
@@ -7621,24 +9109,36 @@
         <v/>
       </c>
       <c r="AA131" t="str">
+        <v/>
+      </c>
+      <c r="AB131" t="str">
+        <v/>
+      </c>
+      <c r="AC131" t="str">
+        <v/>
+      </c>
+      <c r="AD131" t="str">
+        <v/>
+      </c>
+      <c r="AE131" t="str">
         <v/>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Five Seconds of Summer – Everyone's A Star</v>
+        <v>דויד ברוזה BROZAJAZZ</v>
       </c>
       <c r="B132" t="str">
-        <v>2025-11-24</v>
+        <v>2025-11-30</v>
       </c>
       <c r="C132" t="str">
-        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
       </c>
       <c r="D132" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E132" t="str">
-        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
+        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
       </c>
       <c r="F132" t="str">
         <v/>
@@ -7656,7 +9156,7 @@
         <v/>
       </c>
       <c r="K132" t="str">
-        <v>Five Seconds of Summer – Everyone's A Star</v>
+        <v>דויד ברוזה BROZAJAZZ</v>
       </c>
       <c r="L132" t="str">
         <v/>
@@ -7704,24 +9204,36 @@
         <v/>
       </c>
       <c r="AA132" t="str">
+        <v/>
+      </c>
+      <c r="AB132" t="str">
+        <v/>
+      </c>
+      <c r="AC132" t="str">
+        <v/>
+      </c>
+      <c r="AD132" t="str">
+        <v/>
+      </c>
+      <c r="AE132" t="str">
         <v/>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>התקווה 6 – ויהי אור</v>
+        <v>Five Seconds of Summer – Everyone's A Star</v>
       </c>
       <c r="B133" t="str">
-        <v>2025-11-20</v>
+        <v>2025-11-24</v>
       </c>
       <c r="C133" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
+        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
       </c>
       <c r="D133" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E133" t="str">
-        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
+        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
       </c>
       <c r="F133" t="str">
         <v/>
@@ -7739,7 +9251,7 @@
         <v/>
       </c>
       <c r="K133" t="str">
-        <v>התקווה 6 – ויהי אור</v>
+        <v>Five Seconds of Summer – Everyone's A Star</v>
       </c>
       <c r="L133" t="str">
         <v/>
@@ -7787,24 +9299,36 @@
         <v/>
       </c>
       <c r="AA133" t="str">
+        <v/>
+      </c>
+      <c r="AB133" t="str">
+        <v/>
+      </c>
+      <c r="AC133" t="str">
+        <v/>
+      </c>
+      <c r="AD133" t="str">
+        <v/>
+      </c>
+      <c r="AE133" t="str">
         <v/>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>פלורנס אנד דה משין Everybody Scream</v>
+        <v>התקווה 6 – ויהי אור</v>
       </c>
       <c r="B134" t="str">
-        <v>2025-11-13</v>
+        <v>2025-11-20</v>
       </c>
       <c r="C134" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
+        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
       </c>
       <c r="D134" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E134" t="str">
-        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
+        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
       </c>
       <c r="F134" t="str">
         <v/>
@@ -7822,7 +9346,7 @@
         <v/>
       </c>
       <c r="K134" t="str">
-        <v>פלורנס אנד דה משין Everybody Scream</v>
+        <v>התקווה 6 – ויהי אור</v>
       </c>
       <c r="L134" t="str">
         <v/>
@@ -7870,24 +9394,36 @@
         <v/>
       </c>
       <c r="AA134" t="str">
+        <v/>
+      </c>
+      <c r="AB134" t="str">
+        <v/>
+      </c>
+      <c r="AC134" t="str">
+        <v/>
+      </c>
+      <c r="AD134" t="str">
+        <v/>
+      </c>
+      <c r="AE134" t="str">
         <v/>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>טיים אימפלה Deadbeat</v>
+        <v>פלורנס אנד דה משין Everybody Scream</v>
       </c>
       <c r="B135" t="str">
-        <v>2025-11-03</v>
+        <v>2025-11-13</v>
       </c>
       <c r="C135" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
       </c>
       <c r="D135" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E135" t="str">
-        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
+        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
       </c>
       <c r="F135" t="str">
         <v/>
@@ -7905,7 +9441,7 @@
         <v/>
       </c>
       <c r="K135" t="str">
-        <v>טיים אימפלה Deadbeat</v>
+        <v>פלורנס אנד דה משין Everybody Scream</v>
       </c>
       <c r="L135" t="str">
         <v/>
@@ -7953,24 +9489,36 @@
         <v/>
       </c>
       <c r="AA135" t="str">
+        <v/>
+      </c>
+      <c r="AB135" t="str">
+        <v/>
+      </c>
+      <c r="AC135" t="str">
+        <v/>
+      </c>
+      <c r="AD135" t="str">
+        <v/>
+      </c>
+      <c r="AE135" t="str">
         <v/>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+        <v>טיים אימפלה Deadbeat</v>
       </c>
       <c r="B136" t="str">
-        <v>2025-10-20</v>
+        <v>2025-11-03</v>
       </c>
       <c r="C136" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
       </c>
       <c r="D136" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E136" t="str">
-        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
+        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
       </c>
       <c r="F136" t="str">
         <v/>
@@ -7988,7 +9536,7 @@
         <v/>
       </c>
       <c r="K136" t="str">
-        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+        <v>טיים אימפלה Deadbeat</v>
       </c>
       <c r="L136" t="str">
         <v/>
@@ -8036,24 +9584,36 @@
         <v/>
       </c>
       <c r="AA136" t="str">
+        <v/>
+      </c>
+      <c r="AB136" t="str">
+        <v/>
+      </c>
+      <c r="AC136" t="str">
+        <v/>
+      </c>
+      <c r="AD136" t="str">
+        <v/>
+      </c>
+      <c r="AE136" t="str">
         <v/>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>שלמה גרוניך – תודה אהבה</v>
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
       </c>
       <c r="B137" t="str">
-        <v>2025-10-18</v>
+        <v>2025-10-20</v>
       </c>
       <c r="C137" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
+        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
       </c>
       <c r="D137" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E137" t="str">
-        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
+        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
       </c>
       <c r="F137" t="str">
         <v/>
@@ -8071,7 +9631,7 @@
         <v/>
       </c>
       <c r="K137" t="str">
-        <v>שלמה גרוניך – תודה אהבה</v>
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
       </c>
       <c r="L137" t="str">
         <v/>
@@ -8119,24 +9679,36 @@
         <v/>
       </c>
       <c r="AA137" t="str">
+        <v/>
+      </c>
+      <c r="AB137" t="str">
+        <v/>
+      </c>
+      <c r="AC137" t="str">
+        <v/>
+      </c>
+      <c r="AD137" t="str">
+        <v/>
+      </c>
+      <c r="AE137" t="str">
         <v/>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>טיילור סוויפט The Life Of A Showgirl</v>
+        <v>שלמה גרוניך – תודה אהבה</v>
       </c>
       <c r="B138" t="str">
-        <v>2025-10-11</v>
+        <v>2025-10-18</v>
       </c>
       <c r="C138" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
       </c>
       <c r="D138" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E138" t="str">
-        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
+        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
       </c>
       <c r="F138" t="str">
         <v/>
@@ -8154,7 +9726,7 @@
         <v/>
       </c>
       <c r="K138" t="str">
-        <v>טיילור סוויפט The Life Of A Showgirl</v>
+        <v>שלמה גרוניך – תודה אהבה</v>
       </c>
       <c r="L138" t="str">
         <v/>
@@ -8202,24 +9774,36 @@
         <v/>
       </c>
       <c r="AA138" t="str">
+        <v/>
+      </c>
+      <c r="AB138" t="str">
+        <v/>
+      </c>
+      <c r="AC138" t="str">
+        <v/>
+      </c>
+      <c r="AD138" t="str">
+        <v/>
+      </c>
+      <c r="AE138" t="str">
         <v/>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>דוג'ה קאט Vie</v>
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
       </c>
       <c r="B139" t="str">
-        <v>2025-10-04</v>
+        <v>2025-10-11</v>
       </c>
       <c r="C139" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
       </c>
       <c r="D139" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E139" t="str">
-        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
+        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
       </c>
       <c r="F139" t="str">
         <v/>
@@ -8237,7 +9821,7 @@
         <v/>
       </c>
       <c r="K139" t="str">
-        <v>דוג'ה קאט Vie</v>
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
       </c>
       <c r="L139" t="str">
         <v/>
@@ -8285,24 +9869,36 @@
         <v/>
       </c>
       <c r="AA139" t="str">
+        <v/>
+      </c>
+      <c r="AB139" t="str">
+        <v/>
+      </c>
+      <c r="AC139" t="str">
+        <v/>
+      </c>
+      <c r="AD139" t="str">
+        <v/>
+      </c>
+      <c r="AE139" t="str">
         <v/>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>ג'וי קרוקס Juniper</v>
+        <v>דוג'ה קאט Vie</v>
       </c>
       <c r="B140" t="str">
-        <v>2025-10-03</v>
+        <v>2025-10-04</v>
       </c>
       <c r="C140" t="str">
-        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
       </c>
       <c r="D140" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E140" t="str">
-        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
+        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
       </c>
       <c r="F140" t="str">
         <v/>
@@ -8320,7 +9916,7 @@
         <v/>
       </c>
       <c r="K140" t="str">
-        <v>ג'וי קרוקס Juniper</v>
+        <v>דוג'ה קאט Vie</v>
       </c>
       <c r="L140" t="str">
         <v/>
@@ -8368,24 +9964,36 @@
         <v/>
       </c>
       <c r="AA140" t="str">
+        <v/>
+      </c>
+      <c r="AB140" t="str">
+        <v/>
+      </c>
+      <c r="AC140" t="str">
+        <v/>
+      </c>
+      <c r="AD140" t="str">
+        <v/>
+      </c>
+      <c r="AE140" t="str">
         <v/>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>ביפי קליירו Futique</v>
+        <v>ג'וי קרוקס Juniper</v>
       </c>
       <c r="B141" t="str">
-        <v>2025-09-30</v>
+        <v>2025-10-03</v>
       </c>
       <c r="C141" t="str">
-        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
+        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
       </c>
       <c r="D141" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E141" t="str">
-        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
+        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
       </c>
       <c r="F141" t="str">
         <v/>
@@ -8403,7 +10011,7 @@
         <v/>
       </c>
       <c r="K141" t="str">
-        <v>ביפי קליירו Futique</v>
+        <v>ג'וי קרוקס Juniper</v>
       </c>
       <c r="L141" t="str">
         <v/>
@@ -8451,24 +10059,36 @@
         <v/>
       </c>
       <c r="AA141" t="str">
+        <v/>
+      </c>
+      <c r="AB141" t="str">
+        <v/>
+      </c>
+      <c r="AC141" t="str">
+        <v/>
+      </c>
+      <c r="AD141" t="str">
+        <v/>
+      </c>
+      <c r="AE141" t="str">
         <v/>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>אד שירן Play</v>
+        <v>ביפי קליירו Futique</v>
       </c>
       <c r="B142" t="str">
-        <v>2025-09-24</v>
+        <v>2025-09-30</v>
       </c>
       <c r="C142" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
+        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
       </c>
       <c r="D142" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E142" t="str">
-        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
+        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
       </c>
       <c r="F142" t="str">
         <v/>
@@ -8486,7 +10106,7 @@
         <v/>
       </c>
       <c r="K142" t="str">
-        <v>אד שירן Play</v>
+        <v>ביפי קליירו Futique</v>
       </c>
       <c r="L142" t="str">
         <v/>
@@ -8534,24 +10154,36 @@
         <v/>
       </c>
       <c r="AA142" t="str">
+        <v/>
+      </c>
+      <c r="AB142" t="str">
+        <v/>
+      </c>
+      <c r="AC142" t="str">
+        <v/>
+      </c>
+      <c r="AD142" t="str">
+        <v/>
+      </c>
+      <c r="AE142" t="str">
         <v/>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+        <v>אד שירן Play</v>
       </c>
       <c r="B143" t="str">
-        <v>2025-09-21</v>
+        <v>2025-09-24</v>
       </c>
       <c r="C143" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
       </c>
       <c r="D143" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E143" t="str">
-        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
+        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
       </c>
       <c r="F143" t="str">
         <v/>
@@ -8569,7 +10201,7 @@
         <v/>
       </c>
       <c r="K143" t="str">
-        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+        <v>אד שירן Play</v>
       </c>
       <c r="L143" t="str">
         <v/>
@@ -8617,24 +10249,36 @@
         <v/>
       </c>
       <c r="AA143" t="str">
+        <v/>
+      </c>
+      <c r="AB143" t="str">
+        <v/>
+      </c>
+      <c r="AC143" t="str">
+        <v/>
+      </c>
+      <c r="AD143" t="str">
+        <v/>
+      </c>
+      <c r="AE143" t="str">
         <v/>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>סוויד Antidepressants</v>
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
       </c>
       <c r="B144" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-21</v>
       </c>
       <c r="C144" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
       </c>
       <c r="D144" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E144" t="str">
-        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
+        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
       </c>
       <c r="F144" t="str">
         <v/>
@@ -8652,7 +10296,7 @@
         <v/>
       </c>
       <c r="K144" t="str">
-        <v>סוויד Antidepressants</v>
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
       </c>
       <c r="L144" t="str">
         <v/>
@@ -8700,24 +10344,36 @@
         <v/>
       </c>
       <c r="AA144" t="str">
+        <v/>
+      </c>
+      <c r="AB144" t="str">
+        <v/>
+      </c>
+      <c r="AC144" t="str">
+        <v/>
+      </c>
+      <c r="AD144" t="str">
+        <v/>
+      </c>
+      <c r="AE144" t="str">
         <v/>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>וולף אליס The Clearing</v>
+        <v>סוויד Antidepressants</v>
       </c>
       <c r="B145" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-12</v>
       </c>
       <c r="C145" t="str">
-        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
+        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
       </c>
       <c r="D145" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E145" t="str">
-        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
+        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
       </c>
       <c r="F145" t="str">
         <v/>
@@ -8735,7 +10391,7 @@
         <v/>
       </c>
       <c r="K145" t="str">
-        <v>וולף אליס The Clearing</v>
+        <v>סוויד Antidepressants</v>
       </c>
       <c r="L145" t="str">
         <v/>
@@ -8783,24 +10439,36 @@
         <v/>
       </c>
       <c r="AA145" t="str">
+        <v/>
+      </c>
+      <c r="AB145" t="str">
+        <v/>
+      </c>
+      <c r="AC145" t="str">
+        <v/>
+      </c>
+      <c r="AD145" t="str">
+        <v/>
+      </c>
+      <c r="AE145" t="str">
         <v/>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+        <v>וולף אליס The Clearing</v>
       </c>
       <c r="B146" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-01</v>
       </c>
       <c r="C146" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
+        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
       </c>
       <c r="D146" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E146" t="str">
-        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
+        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
       </c>
       <c r="F146" t="str">
         <v/>
@@ -8818,7 +10486,7 @@
         <v/>
       </c>
       <c r="K146" t="str">
-        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+        <v>וולף אליס The Clearing</v>
       </c>
       <c r="L146" t="str">
         <v/>
@@ -8866,24 +10534,36 @@
         <v/>
       </c>
       <c r="AA146" t="str">
+        <v/>
+      </c>
+      <c r="AB146" t="str">
+        <v/>
+      </c>
+      <c r="AC146" t="str">
+        <v/>
+      </c>
+      <c r="AD146" t="str">
+        <v/>
+      </c>
+      <c r="AE146" t="str">
         <v/>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
       </c>
       <c r="B147" t="str">
-        <v>2025-08-24</v>
+        <v>2025-08-29</v>
       </c>
       <c r="C147" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
+        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
       </c>
       <c r="D147" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E147" t="str">
-        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
+        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
       </c>
       <c r="F147" t="str">
         <v/>
@@ -8901,7 +10581,7 @@
         <v/>
       </c>
       <c r="K147" t="str">
-        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
       </c>
       <c r="L147" t="str">
         <v/>
@@ -8949,24 +10629,36 @@
         <v/>
       </c>
       <c r="AA147" t="str">
+        <v/>
+      </c>
+      <c r="AB147" t="str">
+        <v/>
+      </c>
+      <c r="AC147" t="str">
+        <v/>
+      </c>
+      <c r="AD147" t="str">
+        <v/>
+      </c>
+      <c r="AE147" t="str">
         <v/>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
       </c>
       <c r="B148" t="str">
-        <v>2025-08-21</v>
+        <v>2025-08-24</v>
       </c>
       <c r="C148" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
+        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
       </c>
       <c r="D148" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E148" t="str">
-        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
+        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
       </c>
       <c r="F148" t="str">
         <v/>
@@ -8984,7 +10676,7 @@
         <v/>
       </c>
       <c r="K148" t="str">
-        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
       </c>
       <c r="L148" t="str">
         <v/>
@@ -9032,24 +10724,36 @@
         <v/>
       </c>
       <c r="AA148" t="str">
+        <v/>
+      </c>
+      <c r="AB148" t="str">
+        <v/>
+      </c>
+      <c r="AC148" t="str">
+        <v/>
+      </c>
+      <c r="AD148" t="str">
+        <v/>
+      </c>
+      <c r="AE148" t="str">
         <v/>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>אברהם טל – חי</v>
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
       </c>
       <c r="B149" t="str">
-        <v>2025-08-17</v>
+        <v>2025-08-21</v>
       </c>
       <c r="C149" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
       </c>
       <c r="D149" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E149" t="str">
-        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
+        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
       </c>
       <c r="F149" t="str">
         <v/>
@@ -9067,7 +10771,7 @@
         <v/>
       </c>
       <c r="K149" t="str">
-        <v>אברהם טל – חי</v>
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
       </c>
       <c r="L149" t="str">
         <v/>
@@ -9115,24 +10819,36 @@
         <v/>
       </c>
       <c r="AA149" t="str">
+        <v/>
+      </c>
+      <c r="AB149" t="str">
+        <v/>
+      </c>
+      <c r="AC149" t="str">
+        <v/>
+      </c>
+      <c r="AD149" t="str">
+        <v/>
+      </c>
+      <c r="AE149" t="str">
         <v/>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>רנה ראפ Bite Me</v>
+        <v>אברהם טל – חי</v>
       </c>
       <c r="B150" t="str">
-        <v>2025-08-12</v>
+        <v>2025-08-17</v>
       </c>
       <c r="C150" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
       </c>
       <c r="D150" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E150" t="str">
-        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
+        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
       </c>
       <c r="F150" t="str">
         <v/>
@@ -9150,7 +10866,7 @@
         <v/>
       </c>
       <c r="K150" t="str">
-        <v>רנה ראפ Bite Me</v>
+        <v>אברהם טל – חי</v>
       </c>
       <c r="L150" t="str">
         <v/>
@@ -9198,24 +10914,36 @@
         <v/>
       </c>
       <c r="AA150" t="str">
+        <v/>
+      </c>
+      <c r="AB150" t="str">
+        <v/>
+      </c>
+      <c r="AC150" t="str">
+        <v/>
+      </c>
+      <c r="AD150" t="str">
+        <v/>
+      </c>
+      <c r="AE150" t="str">
         <v/>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>The K's – Pretty On The Internet</v>
+        <v>רנה ראפ Bite Me</v>
       </c>
       <c r="B151" t="str">
-        <v>2025-08-03</v>
+        <v>2025-08-12</v>
       </c>
       <c r="C151" t="str">
-        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
+        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
       </c>
       <c r="D151" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E151" t="str">
-        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
+        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
       </c>
       <c r="F151" t="str">
         <v/>
@@ -9233,7 +10961,7 @@
         <v/>
       </c>
       <c r="K151" t="str">
-        <v>The K's – Pretty On The Internet</v>
+        <v>רנה ראפ Bite Me</v>
       </c>
       <c r="L151" t="str">
         <v/>
@@ -9281,24 +11009,36 @@
         <v/>
       </c>
       <c r="AA151" t="str">
+        <v/>
+      </c>
+      <c r="AB151" t="str">
+        <v/>
+      </c>
+      <c r="AC151" t="str">
+        <v/>
+      </c>
+      <c r="AD151" t="str">
+        <v/>
+      </c>
+      <c r="AE151" t="str">
         <v/>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>פטריק סבג Hotel Mogador</v>
+        <v>The K's – Pretty On The Internet</v>
       </c>
       <c r="B152" t="str">
-        <v>2026-01-13</v>
+        <v>2025-08-03</v>
       </c>
       <c r="C152" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
+        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
       </c>
       <c r="D152" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E152" t="str">
-        <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
+        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
       </c>
       <c r="F152" t="str">
         <v/>
@@ -9316,7 +11056,7 @@
         <v/>
       </c>
       <c r="K152" t="str">
-        <v>פטריק סבג Hotel Mogador</v>
+        <v>The K's – Pretty On The Internet</v>
       </c>
       <c r="L152" t="str">
         <v/>
@@ -9381,19 +11121,19 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>מארינה מקסימיליאן – ריק בחלל</v>
+        <v>פטריק סבג Hotel Mogador</v>
       </c>
       <c r="B153" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C153" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
       </c>
       <c r="D153" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E153" t="str">
-        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
+        <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
       </c>
       <c r="F153" t="str">
         <v/>
@@ -9411,7 +11151,7 @@
         <v/>
       </c>
       <c r="K153" t="str">
-        <v>מארינה מקסימיליאן – ריק בחלל</v>
+        <v>פטריק סבג Hotel Mogador</v>
       </c>
       <c r="L153" t="str">
         <v/>
@@ -9471,24 +11211,36 @@
         <v/>
       </c>
       <c r="AE153" t="str">
+        <v/>
+      </c>
+      <c r="AF153" t="str">
+        <v/>
+      </c>
+      <c r="AG153" t="str">
+        <v/>
+      </c>
+      <c r="AH153" t="str">
+        <v/>
+      </c>
+      <c r="AI153" t="str">
         <v/>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>אוליביה דין The Art of Loving</v>
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
       </c>
       <c r="B154" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-09</v>
       </c>
       <c r="C154" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
+        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
       </c>
       <c r="D154" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E154" t="str">
-        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
+        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
       </c>
       <c r="F154" t="str">
         <v/>
@@ -9506,7 +11258,7 @@
         <v/>
       </c>
       <c r="K154" t="str">
-        <v>אוליביה דין The Art of Loving</v>
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
       </c>
       <c r="L154" t="str">
         <v/>
@@ -9566,24 +11318,36 @@
         <v/>
       </c>
       <c r="AE154" t="str">
+        <v/>
+      </c>
+      <c r="AF154" t="str">
+        <v/>
+      </c>
+      <c r="AG154" t="str">
+        <v/>
+      </c>
+      <c r="AH154" t="str">
+        <v/>
+      </c>
+      <c r="AI154" t="str">
         <v/>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Geese Getting Killed</v>
+        <v>אוליביה דין The Art of Loving</v>
       </c>
       <c r="B155" t="str">
-        <v>2025-12-29</v>
+        <v>2026-01-04</v>
       </c>
       <c r="C155" t="str">
-        <v>https://yosmusic.com/geese-getting-killed/</v>
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
       </c>
       <c r="D155" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E155" t="str">
-        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
+        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
       </c>
       <c r="F155" t="str">
         <v/>
@@ -9601,7 +11365,7 @@
         <v/>
       </c>
       <c r="K155" t="str">
-        <v>Geese Getting Killed</v>
+        <v>אוליביה דין The Art of Loving</v>
       </c>
       <c r="L155" t="str">
         <v/>
@@ -9661,24 +11425,36 @@
         <v/>
       </c>
       <c r="AE155" t="str">
+        <v/>
+      </c>
+      <c r="AF155" t="str">
+        <v/>
+      </c>
+      <c r="AG155" t="str">
+        <v/>
+      </c>
+      <c r="AH155" t="str">
+        <v/>
+      </c>
+      <c r="AI155" t="str">
         <v/>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>רוסליה Lux</v>
+        <v>Geese Getting Killed</v>
       </c>
       <c r="B156" t="str">
-        <v>2025-12-25</v>
+        <v>2025-12-29</v>
       </c>
       <c r="C156" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
+        <v>https://yosmusic.com/geese-getting-killed/</v>
       </c>
       <c r="D156" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E156" t="str">
-        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
+        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
       </c>
       <c r="F156" t="str">
         <v/>
@@ -9696,7 +11472,7 @@
         <v/>
       </c>
       <c r="K156" t="str">
-        <v>רוסליה Lux</v>
+        <v>Geese Getting Killed</v>
       </c>
       <c r="L156" t="str">
         <v/>
@@ -9756,24 +11532,36 @@
         <v/>
       </c>
       <c r="AE156" t="str">
+        <v/>
+      </c>
+      <c r="AF156" t="str">
+        <v/>
+      </c>
+      <c r="AG156" t="str">
+        <v/>
+      </c>
+      <c r="AH156" t="str">
+        <v/>
+      </c>
+      <c r="AI156" t="str">
         <v/>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>יאנגבלאד אירוסמית' one more time</v>
+        <v>רוסליה Lux</v>
       </c>
       <c r="B157" t="str">
-        <v>2025-12-17</v>
+        <v>2025-12-25</v>
       </c>
       <c r="C157" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
       </c>
       <c r="D157" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E157" t="str">
-        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
+        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
       </c>
       <c r="F157" t="str">
         <v/>
@@ -9791,7 +11579,7 @@
         <v/>
       </c>
       <c r="K157" t="str">
-        <v>יאנגבלאד אירוסמית' one more time</v>
+        <v>רוסליה Lux</v>
       </c>
       <c r="L157" t="str">
         <v/>
@@ -9851,24 +11639,36 @@
         <v/>
       </c>
       <c r="AE157" t="str">
+        <v/>
+      </c>
+      <c r="AF157" t="str">
+        <v/>
+      </c>
+      <c r="AG157" t="str">
+        <v/>
+      </c>
+      <c r="AH157" t="str">
+        <v/>
+      </c>
+      <c r="AI157" t="str">
         <v/>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>פינק פלויד Wish You Were Here 50</v>
+        <v>יאנגבלאד אירוסמית' one more time</v>
       </c>
       <c r="B158" t="str">
-        <v>2025-12-14</v>
+        <v>2025-12-17</v>
       </c>
       <c r="C158" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
+        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
       </c>
       <c r="D158" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E158" t="str">
-        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
+        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
       </c>
       <c r="F158" t="str">
         <v/>
@@ -9886,7 +11686,7 @@
         <v/>
       </c>
       <c r="K158" t="str">
-        <v>פינק פלויד Wish You Were Here 50</v>
+        <v>יאנגבלאד אירוסמית' one more time</v>
       </c>
       <c r="L158" t="str">
         <v/>
@@ -9946,24 +11746,36 @@
         <v/>
       </c>
       <c r="AE158" t="str">
+        <v/>
+      </c>
+      <c r="AF158" t="str">
+        <v/>
+      </c>
+      <c r="AG158" t="str">
+        <v/>
+      </c>
+      <c r="AH158" t="str">
+        <v/>
+      </c>
+      <c r="AI158" t="str">
         <v/>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+        <v>פינק פלויד Wish You Were Here 50</v>
       </c>
       <c r="B159" t="str">
-        <v>2025-12-08</v>
+        <v>2025-12-14</v>
       </c>
       <c r="C159" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
       </c>
       <c r="D159" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E159" t="str">
-        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
+        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
       </c>
       <c r="F159" t="str">
         <v/>
@@ -9981,7 +11793,7 @@
         <v/>
       </c>
       <c r="K159" t="str">
-        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+        <v>פינק פלויד Wish You Were Here 50</v>
       </c>
       <c r="L159" t="str">
         <v/>
@@ -10041,24 +11853,36 @@
         <v/>
       </c>
       <c r="AE159" t="str">
+        <v/>
+      </c>
+      <c r="AF159" t="str">
+        <v/>
+      </c>
+      <c r="AG159" t="str">
+        <v/>
+      </c>
+      <c r="AH159" t="str">
+        <v/>
+      </c>
+      <c r="AI159" t="str">
         <v/>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>סטריי קידס DO IT EP</v>
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
       </c>
       <c r="B160" t="str">
-        <v>2025-12-04</v>
+        <v>2025-12-08</v>
       </c>
       <c r="C160" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
+        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
       </c>
       <c r="D160" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E160" t="str">
-        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
+        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
       </c>
       <c r="F160" t="str">
         <v/>
@@ -10076,7 +11900,7 @@
         <v/>
       </c>
       <c r="K160" t="str">
-        <v>סטריי קידס DO IT EP</v>
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
       </c>
       <c r="L160" t="str">
         <v/>
@@ -10136,24 +11960,36 @@
         <v/>
       </c>
       <c r="AE160" t="str">
+        <v/>
+      </c>
+      <c r="AF160" t="str">
+        <v/>
+      </c>
+      <c r="AG160" t="str">
+        <v/>
+      </c>
+      <c r="AH160" t="str">
+        <v/>
+      </c>
+      <c r="AI160" t="str">
         <v/>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>דויד ברוזה BROZAJAZZ</v>
+        <v>סטריי קידס DO IT EP</v>
       </c>
       <c r="B161" t="str">
-        <v>2025-11-30</v>
+        <v>2025-12-04</v>
       </c>
       <c r="C161" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
+        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
       </c>
       <c r="D161" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E161" t="str">
-        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
+        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
       </c>
       <c r="F161" t="str">
         <v/>
@@ -10171,7 +12007,7 @@
         <v/>
       </c>
       <c r="K161" t="str">
-        <v>דויד ברוזה BROZAJAZZ</v>
+        <v>סטריי קידס DO IT EP</v>
       </c>
       <c r="L161" t="str">
         <v/>
@@ -10231,24 +12067,36 @@
         <v/>
       </c>
       <c r="AE161" t="str">
+        <v/>
+      </c>
+      <c r="AF161" t="str">
+        <v/>
+      </c>
+      <c r="AG161" t="str">
+        <v/>
+      </c>
+      <c r="AH161" t="str">
+        <v/>
+      </c>
+      <c r="AI161" t="str">
         <v/>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Five Seconds of Summer – Everyone's A Star</v>
+        <v>דויד ברוזה BROZAJAZZ</v>
       </c>
       <c r="B162" t="str">
-        <v>2025-11-24</v>
+        <v>2025-11-30</v>
       </c>
       <c r="C162" t="str">
-        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
       </c>
       <c r="D162" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E162" t="str">
-        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
+        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
       </c>
       <c r="F162" t="str">
         <v/>
@@ -10266,7 +12114,7 @@
         <v/>
       </c>
       <c r="K162" t="str">
-        <v>Five Seconds of Summer – Everyone's A Star</v>
+        <v>דויד ברוזה BROZAJAZZ</v>
       </c>
       <c r="L162" t="str">
         <v/>
@@ -10326,24 +12174,36 @@
         <v/>
       </c>
       <c r="AE162" t="str">
+        <v/>
+      </c>
+      <c r="AF162" t="str">
+        <v/>
+      </c>
+      <c r="AG162" t="str">
+        <v/>
+      </c>
+      <c r="AH162" t="str">
+        <v/>
+      </c>
+      <c r="AI162" t="str">
         <v/>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>התקווה 6 – ויהי אור</v>
+        <v>Five Seconds of Summer – Everyone's A Star</v>
       </c>
       <c r="B163" t="str">
-        <v>2025-11-20</v>
+        <v>2025-11-24</v>
       </c>
       <c r="C163" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
+        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
       </c>
       <c r="D163" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E163" t="str">
-        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
+        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
       </c>
       <c r="F163" t="str">
         <v/>
@@ -10361,7 +12221,7 @@
         <v/>
       </c>
       <c r="K163" t="str">
-        <v>התקווה 6 – ויהי אור</v>
+        <v>Five Seconds of Summer – Everyone's A Star</v>
       </c>
       <c r="L163" t="str">
         <v/>
@@ -10421,24 +12281,36 @@
         <v/>
       </c>
       <c r="AE163" t="str">
+        <v/>
+      </c>
+      <c r="AF163" t="str">
+        <v/>
+      </c>
+      <c r="AG163" t="str">
+        <v/>
+      </c>
+      <c r="AH163" t="str">
+        <v/>
+      </c>
+      <c r="AI163" t="str">
         <v/>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>פלורנס אנד דה משין Everybody Scream</v>
+        <v>התקווה 6 – ויהי אור</v>
       </c>
       <c r="B164" t="str">
-        <v>2025-11-13</v>
+        <v>2025-11-20</v>
       </c>
       <c r="C164" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
+        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
       </c>
       <c r="D164" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E164" t="str">
-        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
+        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
       </c>
       <c r="F164" t="str">
         <v/>
@@ -10456,7 +12328,7 @@
         <v/>
       </c>
       <c r="K164" t="str">
-        <v>פלורנס אנד דה משין Everybody Scream</v>
+        <v>התקווה 6 – ויהי אור</v>
       </c>
       <c r="L164" t="str">
         <v/>
@@ -10516,24 +12388,36 @@
         <v/>
       </c>
       <c r="AE164" t="str">
+        <v/>
+      </c>
+      <c r="AF164" t="str">
+        <v/>
+      </c>
+      <c r="AG164" t="str">
+        <v/>
+      </c>
+      <c r="AH164" t="str">
+        <v/>
+      </c>
+      <c r="AI164" t="str">
         <v/>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>טיים אימפלה Deadbeat</v>
+        <v>פלורנס אנד דה משין Everybody Scream</v>
       </c>
       <c r="B165" t="str">
-        <v>2025-11-03</v>
+        <v>2025-11-13</v>
       </c>
       <c r="C165" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
       </c>
       <c r="D165" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E165" t="str">
-        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
+        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
       </c>
       <c r="F165" t="str">
         <v/>
@@ -10551,7 +12435,7 @@
         <v/>
       </c>
       <c r="K165" t="str">
-        <v>טיים אימפלה Deadbeat</v>
+        <v>פלורנס אנד דה משין Everybody Scream</v>
       </c>
       <c r="L165" t="str">
         <v/>
@@ -10611,24 +12495,36 @@
         <v/>
       </c>
       <c r="AE165" t="str">
+        <v/>
+      </c>
+      <c r="AF165" t="str">
+        <v/>
+      </c>
+      <c r="AG165" t="str">
+        <v/>
+      </c>
+      <c r="AH165" t="str">
+        <v/>
+      </c>
+      <c r="AI165" t="str">
         <v/>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+        <v>טיים אימפלה Deadbeat</v>
       </c>
       <c r="B166" t="str">
-        <v>2025-10-20</v>
+        <v>2025-11-03</v>
       </c>
       <c r="C166" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
       </c>
       <c r="D166" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E166" t="str">
-        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
+        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
       </c>
       <c r="F166" t="str">
         <v/>
@@ -10646,7 +12542,7 @@
         <v/>
       </c>
       <c r="K166" t="str">
-        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+        <v>טיים אימפלה Deadbeat</v>
       </c>
       <c r="L166" t="str">
         <v/>
@@ -10706,24 +12602,36 @@
         <v/>
       </c>
       <c r="AE166" t="str">
+        <v/>
+      </c>
+      <c r="AF166" t="str">
+        <v/>
+      </c>
+      <c r="AG166" t="str">
+        <v/>
+      </c>
+      <c r="AH166" t="str">
+        <v/>
+      </c>
+      <c r="AI166" t="str">
         <v/>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>שלמה גרוניך – תודה אהבה</v>
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
       </c>
       <c r="B167" t="str">
-        <v>2025-10-18</v>
+        <v>2025-10-20</v>
       </c>
       <c r="C167" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
+        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
       </c>
       <c r="D167" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E167" t="str">
-        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
+        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
       </c>
       <c r="F167" t="str">
         <v/>
@@ -10741,7 +12649,7 @@
         <v/>
       </c>
       <c r="K167" t="str">
-        <v>שלמה גרוניך – תודה אהבה</v>
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
       </c>
       <c r="L167" t="str">
         <v/>
@@ -10801,24 +12709,36 @@
         <v/>
       </c>
       <c r="AE167" t="str">
+        <v/>
+      </c>
+      <c r="AF167" t="str">
+        <v/>
+      </c>
+      <c r="AG167" t="str">
+        <v/>
+      </c>
+      <c r="AH167" t="str">
+        <v/>
+      </c>
+      <c r="AI167" t="str">
         <v/>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>טיילור סוויפט The Life Of A Showgirl</v>
+        <v>שלמה גרוניך – תודה אהבה</v>
       </c>
       <c r="B168" t="str">
-        <v>2025-10-11</v>
+        <v>2025-10-18</v>
       </c>
       <c r="C168" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
       </c>
       <c r="D168" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E168" t="str">
-        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
+        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
       </c>
       <c r="F168" t="str">
         <v/>
@@ -10836,7 +12756,7 @@
         <v/>
       </c>
       <c r="K168" t="str">
-        <v>טיילור סוויפט The Life Of A Showgirl</v>
+        <v>שלמה גרוניך – תודה אהבה</v>
       </c>
       <c r="L168" t="str">
         <v/>
@@ -10896,24 +12816,36 @@
         <v/>
       </c>
       <c r="AE168" t="str">
+        <v/>
+      </c>
+      <c r="AF168" t="str">
+        <v/>
+      </c>
+      <c r="AG168" t="str">
+        <v/>
+      </c>
+      <c r="AH168" t="str">
+        <v/>
+      </c>
+      <c r="AI168" t="str">
         <v/>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>דוג'ה קאט Vie</v>
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
       </c>
       <c r="B169" t="str">
-        <v>2025-10-04</v>
+        <v>2025-10-11</v>
       </c>
       <c r="C169" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
       </c>
       <c r="D169" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E169" t="str">
-        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
+        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
       </c>
       <c r="F169" t="str">
         <v/>
@@ -10931,7 +12863,7 @@
         <v/>
       </c>
       <c r="K169" t="str">
-        <v>דוג'ה קאט Vie</v>
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
       </c>
       <c r="L169" t="str">
         <v/>
@@ -10991,24 +12923,36 @@
         <v/>
       </c>
       <c r="AE169" t="str">
+        <v/>
+      </c>
+      <c r="AF169" t="str">
+        <v/>
+      </c>
+      <c r="AG169" t="str">
+        <v/>
+      </c>
+      <c r="AH169" t="str">
+        <v/>
+      </c>
+      <c r="AI169" t="str">
         <v/>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>ג'וי קרוקס Juniper</v>
+        <v>דוג'ה קאט Vie</v>
       </c>
       <c r="B170" t="str">
-        <v>2025-10-03</v>
+        <v>2025-10-04</v>
       </c>
       <c r="C170" t="str">
-        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
       </c>
       <c r="D170" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E170" t="str">
-        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
+        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
       </c>
       <c r="F170" t="str">
         <v/>
@@ -11026,7 +12970,7 @@
         <v/>
       </c>
       <c r="K170" t="str">
-        <v>ג'וי קרוקס Juniper</v>
+        <v>דוג'ה קאט Vie</v>
       </c>
       <c r="L170" t="str">
         <v/>
@@ -11086,24 +13030,36 @@
         <v/>
       </c>
       <c r="AE170" t="str">
+        <v/>
+      </c>
+      <c r="AF170" t="str">
+        <v/>
+      </c>
+      <c r="AG170" t="str">
+        <v/>
+      </c>
+      <c r="AH170" t="str">
+        <v/>
+      </c>
+      <c r="AI170" t="str">
         <v/>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>ביפי קליירו Futique</v>
+        <v>ג'וי קרוקס Juniper</v>
       </c>
       <c r="B171" t="str">
-        <v>2025-09-30</v>
+        <v>2025-10-03</v>
       </c>
       <c r="C171" t="str">
-        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
+        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
       </c>
       <c r="D171" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E171" t="str">
-        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
+        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
       </c>
       <c r="F171" t="str">
         <v/>
@@ -11121,7 +13077,7 @@
         <v/>
       </c>
       <c r="K171" t="str">
-        <v>ביפי קליירו Futique</v>
+        <v>ג'וי קרוקס Juniper</v>
       </c>
       <c r="L171" t="str">
         <v/>
@@ -11181,24 +13137,36 @@
         <v/>
       </c>
       <c r="AE171" t="str">
+        <v/>
+      </c>
+      <c r="AF171" t="str">
+        <v/>
+      </c>
+      <c r="AG171" t="str">
+        <v/>
+      </c>
+      <c r="AH171" t="str">
+        <v/>
+      </c>
+      <c r="AI171" t="str">
         <v/>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>אד שירן Play</v>
+        <v>ביפי קליירו Futique</v>
       </c>
       <c r="B172" t="str">
-        <v>2025-09-24</v>
+        <v>2025-09-30</v>
       </c>
       <c r="C172" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
+        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
       </c>
       <c r="D172" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E172" t="str">
-        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
+        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
       </c>
       <c r="F172" t="str">
         <v/>
@@ -11216,7 +13184,7 @@
         <v/>
       </c>
       <c r="K172" t="str">
-        <v>אד שירן Play</v>
+        <v>ביפי קליירו Futique</v>
       </c>
       <c r="L172" t="str">
         <v/>
@@ -11276,24 +13244,36 @@
         <v/>
       </c>
       <c r="AE172" t="str">
+        <v/>
+      </c>
+      <c r="AF172" t="str">
+        <v/>
+      </c>
+      <c r="AG172" t="str">
+        <v/>
+      </c>
+      <c r="AH172" t="str">
+        <v/>
+      </c>
+      <c r="AI172" t="str">
         <v/>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+        <v>אד שירן Play</v>
       </c>
       <c r="B173" t="str">
-        <v>2025-09-21</v>
+        <v>2025-09-24</v>
       </c>
       <c r="C173" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
       </c>
       <c r="D173" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E173" t="str">
-        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
+        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
       </c>
       <c r="F173" t="str">
         <v/>
@@ -11311,7 +13291,7 @@
         <v/>
       </c>
       <c r="K173" t="str">
-        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+        <v>אד שירן Play</v>
       </c>
       <c r="L173" t="str">
         <v/>
@@ -11371,24 +13351,36 @@
         <v/>
       </c>
       <c r="AE173" t="str">
+        <v/>
+      </c>
+      <c r="AF173" t="str">
+        <v/>
+      </c>
+      <c r="AG173" t="str">
+        <v/>
+      </c>
+      <c r="AH173" t="str">
+        <v/>
+      </c>
+      <c r="AI173" t="str">
         <v/>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>סוויד Antidepressants</v>
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
       </c>
       <c r="B174" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-21</v>
       </c>
       <c r="C174" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
       </c>
       <c r="D174" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E174" t="str">
-        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
+        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
       </c>
       <c r="F174" t="str">
         <v/>
@@ -11406,7 +13398,7 @@
         <v/>
       </c>
       <c r="K174" t="str">
-        <v>סוויד Antidepressants</v>
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
       </c>
       <c r="L174" t="str">
         <v/>
@@ -11466,24 +13458,36 @@
         <v/>
       </c>
       <c r="AE174" t="str">
+        <v/>
+      </c>
+      <c r="AF174" t="str">
+        <v/>
+      </c>
+      <c r="AG174" t="str">
+        <v/>
+      </c>
+      <c r="AH174" t="str">
+        <v/>
+      </c>
+      <c r="AI174" t="str">
         <v/>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>וולף אליס The Clearing</v>
+        <v>סוויד Antidepressants</v>
       </c>
       <c r="B175" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-12</v>
       </c>
       <c r="C175" t="str">
-        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
+        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
       </c>
       <c r="D175" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E175" t="str">
-        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
+        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
       </c>
       <c r="F175" t="str">
         <v/>
@@ -11501,7 +13505,7 @@
         <v/>
       </c>
       <c r="K175" t="str">
-        <v>וולף אליס The Clearing</v>
+        <v>סוויד Antidepressants</v>
       </c>
       <c r="L175" t="str">
         <v/>
@@ -11561,24 +13565,36 @@
         <v/>
       </c>
       <c r="AE175" t="str">
+        <v/>
+      </c>
+      <c r="AF175" t="str">
+        <v/>
+      </c>
+      <c r="AG175" t="str">
+        <v/>
+      </c>
+      <c r="AH175" t="str">
+        <v/>
+      </c>
+      <c r="AI175" t="str">
         <v/>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+        <v>וולף אליס The Clearing</v>
       </c>
       <c r="B176" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-01</v>
       </c>
       <c r="C176" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
+        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
       </c>
       <c r="D176" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E176" t="str">
-        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
+        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
       </c>
       <c r="F176" t="str">
         <v/>
@@ -11596,7 +13612,7 @@
         <v/>
       </c>
       <c r="K176" t="str">
-        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+        <v>וולף אליס The Clearing</v>
       </c>
       <c r="L176" t="str">
         <v/>
@@ -11656,24 +13672,36 @@
         <v/>
       </c>
       <c r="AE176" t="str">
+        <v/>
+      </c>
+      <c r="AF176" t="str">
+        <v/>
+      </c>
+      <c r="AG176" t="str">
+        <v/>
+      </c>
+      <c r="AH176" t="str">
+        <v/>
+      </c>
+      <c r="AI176" t="str">
         <v/>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
       </c>
       <c r="B177" t="str">
-        <v>2025-08-24</v>
+        <v>2025-08-29</v>
       </c>
       <c r="C177" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
+        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
       </c>
       <c r="D177" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E177" t="str">
-        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
+        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
       </c>
       <c r="F177" t="str">
         <v/>
@@ -11691,7 +13719,7 @@
         <v/>
       </c>
       <c r="K177" t="str">
-        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
       </c>
       <c r="L177" t="str">
         <v/>
@@ -11751,24 +13779,36 @@
         <v/>
       </c>
       <c r="AE177" t="str">
+        <v/>
+      </c>
+      <c r="AF177" t="str">
+        <v/>
+      </c>
+      <c r="AG177" t="str">
+        <v/>
+      </c>
+      <c r="AH177" t="str">
+        <v/>
+      </c>
+      <c r="AI177" t="str">
         <v/>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
       </c>
       <c r="B178" t="str">
-        <v>2025-08-21</v>
+        <v>2025-08-24</v>
       </c>
       <c r="C178" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
+        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
       </c>
       <c r="D178" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E178" t="str">
-        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
+        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
       </c>
       <c r="F178" t="str">
         <v/>
@@ -11786,7 +13826,7 @@
         <v/>
       </c>
       <c r="K178" t="str">
-        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
       </c>
       <c r="L178" t="str">
         <v/>
@@ -11846,24 +13886,36 @@
         <v/>
       </c>
       <c r="AE178" t="str">
+        <v/>
+      </c>
+      <c r="AF178" t="str">
+        <v/>
+      </c>
+      <c r="AG178" t="str">
+        <v/>
+      </c>
+      <c r="AH178" t="str">
+        <v/>
+      </c>
+      <c r="AI178" t="str">
         <v/>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>אברהם טל – חי</v>
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
       </c>
       <c r="B179" t="str">
-        <v>2025-08-17</v>
+        <v>2025-08-21</v>
       </c>
       <c r="C179" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
       </c>
       <c r="D179" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E179" t="str">
-        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
+        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
       </c>
       <c r="F179" t="str">
         <v/>
@@ -11881,7 +13933,7 @@
         <v/>
       </c>
       <c r="K179" t="str">
-        <v>אברהם טל – חי</v>
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
       </c>
       <c r="L179" t="str">
         <v/>
@@ -11941,24 +13993,36 @@
         <v/>
       </c>
       <c r="AE179" t="str">
+        <v/>
+      </c>
+      <c r="AF179" t="str">
+        <v/>
+      </c>
+      <c r="AG179" t="str">
+        <v/>
+      </c>
+      <c r="AH179" t="str">
+        <v/>
+      </c>
+      <c r="AI179" t="str">
         <v/>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>רנה ראפ Bite Me</v>
+        <v>אברהם טל – חי</v>
       </c>
       <c r="B180" t="str">
-        <v>2025-08-12</v>
+        <v>2025-08-17</v>
       </c>
       <c r="C180" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
       </c>
       <c r="D180" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="E180" t="str">
-        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
+        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
       </c>
       <c r="F180" t="str">
         <v/>
@@ -11976,7 +14040,7 @@
         <v/>
       </c>
       <c r="K180" t="str">
-        <v>רנה ראפ Bite Me</v>
+        <v>אברהם טל – חי</v>
       </c>
       <c r="L180" t="str">
         <v/>
@@ -12036,107 +14100,238 @@
         <v/>
       </c>
       <c r="AE180" t="str">
+        <v/>
+      </c>
+      <c r="AF180" t="str">
+        <v/>
+      </c>
+      <c r="AG180" t="str">
+        <v/>
+      </c>
+      <c r="AH180" t="str">
+        <v/>
+      </c>
+      <c r="AI180" t="str">
         <v/>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
+        <v>רנה ראפ Bite Me</v>
+      </c>
+      <c r="B181" t="str">
+        <v>2025-08-12</v>
+      </c>
+      <c r="C181" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
+      </c>
+      <c r="D181" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E181" t="str">
+        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
+      </c>
+      <c r="F181" t="str">
+        <v/>
+      </c>
+      <c r="G181" t="str">
+        <v/>
+      </c>
+      <c r="H181" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I181" t="str">
+        <v/>
+      </c>
+      <c r="J181" t="str">
+        <v/>
+      </c>
+      <c r="K181" t="str">
+        <v>רנה ראפ Bite Me</v>
+      </c>
+      <c r="L181" t="str">
+        <v/>
+      </c>
+      <c r="M181" t="str">
+        <v/>
+      </c>
+      <c r="N181" t="str">
+        <v/>
+      </c>
+      <c r="O181" t="str">
+        <v/>
+      </c>
+      <c r="P181" t="str">
+        <v/>
+      </c>
+      <c r="Q181" t="str">
+        <v/>
+      </c>
+      <c r="R181" t="str">
+        <v/>
+      </c>
+      <c r="S181" t="str">
+        <v/>
+      </c>
+      <c r="T181" t="str">
+        <v/>
+      </c>
+      <c r="U181" t="str">
+        <v/>
+      </c>
+      <c r="V181" t="str">
+        <v/>
+      </c>
+      <c r="W181" t="str">
+        <v/>
+      </c>
+      <c r="X181" t="str">
+        <v/>
+      </c>
+      <c r="Y181" t="str">
+        <v/>
+      </c>
+      <c r="Z181" t="str">
+        <v/>
+      </c>
+      <c r="AA181" t="str">
+        <v/>
+      </c>
+      <c r="AB181" t="str">
+        <v/>
+      </c>
+      <c r="AC181" t="str">
+        <v/>
+      </c>
+      <c r="AD181" t="str">
+        <v/>
+      </c>
+      <c r="AE181" t="str">
+        <v/>
+      </c>
+      <c r="AF181" t="str">
+        <v/>
+      </c>
+      <c r="AG181" t="str">
+        <v/>
+      </c>
+      <c r="AH181" t="str">
+        <v/>
+      </c>
+      <c r="AI181" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
         <v>The K's – Pretty On The Internet</v>
       </c>
-      <c r="B181" t="str">
+      <c r="B182" t="str">
         <v>2025-08-03</v>
       </c>
-      <c r="C181" t="str">
+      <c r="C182" t="str">
         <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
       </c>
-      <c r="D181" t="str">
-        <v>2026-01-16</v>
-      </c>
-      <c r="E181" t="str">
+      <c r="D182" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E182" t="str">
         <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
       </c>
-      <c r="F181" t="str">
-        <v/>
-      </c>
-      <c r="G181" t="str">
-        <v/>
-      </c>
-      <c r="H181" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="I181" t="str">
-        <v/>
-      </c>
-      <c r="J181" t="str">
-        <v/>
-      </c>
-      <c r="K181" t="str">
+      <c r="F182" t="str">
+        <v/>
+      </c>
+      <c r="G182" t="str">
+        <v/>
+      </c>
+      <c r="H182" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I182" t="str">
+        <v/>
+      </c>
+      <c r="J182" t="str">
+        <v/>
+      </c>
+      <c r="K182" t="str">
         <v>The K's – Pretty On The Internet</v>
       </c>
-      <c r="L181" t="str">
-        <v/>
-      </c>
-      <c r="M181" t="str">
-        <v/>
-      </c>
-      <c r="N181" t="str">
-        <v/>
-      </c>
-      <c r="O181" t="str">
-        <v/>
-      </c>
-      <c r="P181" t="str">
-        <v/>
-      </c>
-      <c r="Q181" t="str">
-        <v/>
-      </c>
-      <c r="R181" t="str">
-        <v/>
-      </c>
-      <c r="S181" t="str">
-        <v/>
-      </c>
-      <c r="T181" t="str">
-        <v/>
-      </c>
-      <c r="U181" t="str">
-        <v/>
-      </c>
-      <c r="V181" t="str">
-        <v/>
-      </c>
-      <c r="W181" t="str">
-        <v/>
-      </c>
-      <c r="X181" t="str">
-        <v/>
-      </c>
-      <c r="Y181" t="str">
-        <v/>
-      </c>
-      <c r="Z181" t="str">
-        <v/>
-      </c>
-      <c r="AA181" t="str">
-        <v/>
-      </c>
-      <c r="AB181" t="str">
-        <v/>
-      </c>
-      <c r="AC181" t="str">
-        <v/>
-      </c>
-      <c r="AD181" t="str">
-        <v/>
-      </c>
-      <c r="AE181" t="str">
+      <c r="L182" t="str">
+        <v/>
+      </c>
+      <c r="M182" t="str">
+        <v/>
+      </c>
+      <c r="N182" t="str">
+        <v/>
+      </c>
+      <c r="O182" t="str">
+        <v/>
+      </c>
+      <c r="P182" t="str">
+        <v/>
+      </c>
+      <c r="Q182" t="str">
+        <v/>
+      </c>
+      <c r="R182" t="str">
+        <v/>
+      </c>
+      <c r="S182" t="str">
+        <v/>
+      </c>
+      <c r="T182" t="str">
+        <v/>
+      </c>
+      <c r="U182" t="str">
+        <v/>
+      </c>
+      <c r="V182" t="str">
+        <v/>
+      </c>
+      <c r="W182" t="str">
+        <v/>
+      </c>
+      <c r="X182" t="str">
+        <v/>
+      </c>
+      <c r="Y182" t="str">
+        <v/>
+      </c>
+      <c r="Z182" t="str">
+        <v/>
+      </c>
+      <c r="AA182" t="str">
+        <v/>
+      </c>
+      <c r="AB182" t="str">
+        <v/>
+      </c>
+      <c r="AC182" t="str">
+        <v/>
+      </c>
+      <c r="AD182" t="str">
+        <v/>
+      </c>
+      <c r="AE182" t="str">
+        <v/>
+      </c>
+      <c r="AF182" t="str">
+        <v/>
+      </c>
+      <c r="AG182" t="str">
+        <v/>
+      </c>
+      <c r="AH182" t="str">
+        <v/>
+      </c>
+      <c r="AI182" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AE181"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AI182"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI182"/>
+  <dimension ref="A1:AM212"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -445,7 +445,7 @@
         <v>https://yosmusic.com/%d7%a2%d7%95%d7%96-%d7%96%d7%94%d7%91%d7%99-%d7%aa%d7%95%d7%a8-%d7%96%d7%94%d7%91%d7%99/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-18</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E2" t="str">
         <v>את ההופעה הזו קיבלתי ביוטיוב (*), שיטה יעילה למי שנפשו לא חשקה לשרך דרכו למועדונים בלילות הקרים. הוידיאו נשלח לרגל יציאת אלבומו "תור זהבי", ששיר הנושא הוא ראפ עצבני בניחוח מזרחי, שיר אגו ביקורתי, אירוני ומודע לעצמו מלא בדאחקות, הגזמות,</v>
@@ -480,7 +480,7 @@
         <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E3" t="str">
         <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
@@ -502,18 +502,6 @@
       </c>
       <c r="K3" t="str">
         <v>פטריק סבג Hotel Mogador</v>
-      </c>
-      <c r="L3" t="str">
-        <v/>
-      </c>
-      <c r="M3" t="str">
-        <v/>
-      </c>
-      <c r="N3" t="str">
-        <v/>
-      </c>
-      <c r="O3" t="str">
-        <v/>
       </c>
     </row>
     <row r="4">
@@ -527,7 +515,7 @@
         <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E4" t="str">
         <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
@@ -549,18 +537,6 @@
       </c>
       <c r="K4" t="str">
         <v>מארינה מקסימיליאן – ריק בחלל</v>
-      </c>
-      <c r="L4" t="str">
-        <v/>
-      </c>
-      <c r="M4" t="str">
-        <v/>
-      </c>
-      <c r="N4" t="str">
-        <v/>
-      </c>
-      <c r="O4" t="str">
-        <v/>
       </c>
     </row>
     <row r="5">
@@ -574,7 +550,7 @@
         <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E5" t="str">
         <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
@@ -596,18 +572,6 @@
       </c>
       <c r="K5" t="str">
         <v>אוליביה דין The Art of Loving</v>
-      </c>
-      <c r="L5" t="str">
-        <v/>
-      </c>
-      <c r="M5" t="str">
-        <v/>
-      </c>
-      <c r="N5" t="str">
-        <v/>
-      </c>
-      <c r="O5" t="str">
-        <v/>
       </c>
     </row>
     <row r="6">
@@ -621,7 +585,7 @@
         <v>https://yosmusic.com/geese-getting-killed/</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E6" t="str">
         <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
@@ -643,18 +607,6 @@
       </c>
       <c r="K6" t="str">
         <v>Geese Getting Killed</v>
-      </c>
-      <c r="L6" t="str">
-        <v/>
-      </c>
-      <c r="M6" t="str">
-        <v/>
-      </c>
-      <c r="N6" t="str">
-        <v/>
-      </c>
-      <c r="O6" t="str">
-        <v/>
       </c>
     </row>
     <row r="7">
@@ -668,7 +620,7 @@
         <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E7" t="str">
         <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
@@ -690,18 +642,6 @@
       </c>
       <c r="K7" t="str">
         <v>רוסליה Lux</v>
-      </c>
-      <c r="L7" t="str">
-        <v/>
-      </c>
-      <c r="M7" t="str">
-        <v/>
-      </c>
-      <c r="N7" t="str">
-        <v/>
-      </c>
-      <c r="O7" t="str">
-        <v/>
       </c>
     </row>
     <row r="8">
@@ -715,7 +655,7 @@
         <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E8" t="str">
         <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
@@ -737,18 +677,6 @@
       </c>
       <c r="K8" t="str">
         <v>יאנגבלאד אירוסמית' one more time</v>
-      </c>
-      <c r="L8" t="str">
-        <v/>
-      </c>
-      <c r="M8" t="str">
-        <v/>
-      </c>
-      <c r="N8" t="str">
-        <v/>
-      </c>
-      <c r="O8" t="str">
-        <v/>
       </c>
     </row>
     <row r="9">
@@ -762,7 +690,7 @@
         <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E9" t="str">
         <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
@@ -784,18 +712,6 @@
       </c>
       <c r="K9" t="str">
         <v>פינק פלויד Wish You Were Here 50</v>
-      </c>
-      <c r="L9" t="str">
-        <v/>
-      </c>
-      <c r="M9" t="str">
-        <v/>
-      </c>
-      <c r="N9" t="str">
-        <v/>
-      </c>
-      <c r="O9" t="str">
-        <v/>
       </c>
     </row>
     <row r="10">
@@ -809,7 +725,7 @@
         <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E10" t="str">
         <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
@@ -832,22 +748,10 @@
       <c r="K10" t="str">
         <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
       </c>
-      <c r="L10" t="str">
-        <v/>
-      </c>
-      <c r="M10" t="str">
-        <v/>
-      </c>
-      <c r="N10" t="str">
-        <v/>
-      </c>
-      <c r="O10" t="str">
-        <v/>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>סטריי קידס DO IT EP</v>
+        <v>סטריי קידס DO IT (EP)</v>
       </c>
       <c r="B11" t="str">
         <v>2025-12-04</v>
@@ -856,7 +760,7 @@
         <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E11" t="str">
         <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
@@ -877,19 +781,7 @@
         <v/>
       </c>
       <c r="K11" t="str">
-        <v>סטריי קידס DO IT EP</v>
-      </c>
-      <c r="L11" t="str">
-        <v/>
-      </c>
-      <c r="M11" t="str">
-        <v/>
-      </c>
-      <c r="N11" t="str">
-        <v/>
-      </c>
-      <c r="O11" t="str">
-        <v/>
+        <v>סטריי קידס DO IT (EP)</v>
       </c>
     </row>
     <row r="12">
@@ -903,7 +795,7 @@
         <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E12" t="str">
         <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
@@ -925,18 +817,6 @@
       </c>
       <c r="K12" t="str">
         <v>דויד ברוזה BROZAJAZZ</v>
-      </c>
-      <c r="L12" t="str">
-        <v/>
-      </c>
-      <c r="M12" t="str">
-        <v/>
-      </c>
-      <c r="N12" t="str">
-        <v/>
-      </c>
-      <c r="O12" t="str">
-        <v/>
       </c>
     </row>
     <row r="13">
@@ -950,7 +830,7 @@
         <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E13" t="str">
         <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
@@ -972,18 +852,6 @@
       </c>
       <c r="K13" t="str">
         <v>Five Seconds of Summer – Everyone's A Star</v>
-      </c>
-      <c r="L13" t="str">
-        <v/>
-      </c>
-      <c r="M13" t="str">
-        <v/>
-      </c>
-      <c r="N13" t="str">
-        <v/>
-      </c>
-      <c r="O13" t="str">
-        <v/>
       </c>
     </row>
     <row r="14">
@@ -997,7 +865,7 @@
         <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E14" t="str">
         <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
@@ -1019,18 +887,6 @@
       </c>
       <c r="K14" t="str">
         <v>התקווה 6 – ויהי אור</v>
-      </c>
-      <c r="L14" t="str">
-        <v/>
-      </c>
-      <c r="M14" t="str">
-        <v/>
-      </c>
-      <c r="N14" t="str">
-        <v/>
-      </c>
-      <c r="O14" t="str">
-        <v/>
       </c>
     </row>
     <row r="15">
@@ -1044,7 +900,7 @@
         <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E15" t="str">
         <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
@@ -1066,18 +922,6 @@
       </c>
       <c r="K15" t="str">
         <v>פלורנס אנד דה משין Everybody Scream</v>
-      </c>
-      <c r="L15" t="str">
-        <v/>
-      </c>
-      <c r="M15" t="str">
-        <v/>
-      </c>
-      <c r="N15" t="str">
-        <v/>
-      </c>
-      <c r="O15" t="str">
-        <v/>
       </c>
     </row>
     <row r="16">
@@ -1091,7 +935,7 @@
         <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E16" t="str">
         <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
@@ -1113,18 +957,6 @@
       </c>
       <c r="K16" t="str">
         <v>טיים אימפלה Deadbeat</v>
-      </c>
-      <c r="L16" t="str">
-        <v/>
-      </c>
-      <c r="M16" t="str">
-        <v/>
-      </c>
-      <c r="N16" t="str">
-        <v/>
-      </c>
-      <c r="O16" t="str">
-        <v/>
       </c>
     </row>
     <row r="17">
@@ -1138,7 +970,7 @@
         <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E17" t="str">
         <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
@@ -1160,18 +992,6 @@
       </c>
       <c r="K17" t="str">
         <v>דייוויד גילמור The Luck and Strange Concerts</v>
-      </c>
-      <c r="L17" t="str">
-        <v/>
-      </c>
-      <c r="M17" t="str">
-        <v/>
-      </c>
-      <c r="N17" t="str">
-        <v/>
-      </c>
-      <c r="O17" t="str">
-        <v/>
       </c>
     </row>
     <row r="18">
@@ -1185,7 +1005,7 @@
         <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E18" t="str">
         <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
@@ -1207,18 +1027,6 @@
       </c>
       <c r="K18" t="str">
         <v>שלמה גרוניך – תודה אהבה</v>
-      </c>
-      <c r="L18" t="str">
-        <v/>
-      </c>
-      <c r="M18" t="str">
-        <v/>
-      </c>
-      <c r="N18" t="str">
-        <v/>
-      </c>
-      <c r="O18" t="str">
-        <v/>
       </c>
     </row>
     <row r="19">
@@ -1232,7 +1040,7 @@
         <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E19" t="str">
         <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
@@ -1254,18 +1062,6 @@
       </c>
       <c r="K19" t="str">
         <v>טיילור סוויפט The Life Of A Showgirl</v>
-      </c>
-      <c r="L19" t="str">
-        <v/>
-      </c>
-      <c r="M19" t="str">
-        <v/>
-      </c>
-      <c r="N19" t="str">
-        <v/>
-      </c>
-      <c r="O19" t="str">
-        <v/>
       </c>
     </row>
     <row r="20">
@@ -1279,7 +1075,7 @@
         <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E20" t="str">
         <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
@@ -1301,18 +1097,6 @@
       </c>
       <c r="K20" t="str">
         <v>דוג'ה קאט Vie</v>
-      </c>
-      <c r="L20" t="str">
-        <v/>
-      </c>
-      <c r="M20" t="str">
-        <v/>
-      </c>
-      <c r="N20" t="str">
-        <v/>
-      </c>
-      <c r="O20" t="str">
-        <v/>
       </c>
     </row>
     <row r="21">
@@ -1326,7 +1110,7 @@
         <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E21" t="str">
         <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
@@ -1348,18 +1132,6 @@
       </c>
       <c r="K21" t="str">
         <v>ג'וי קרוקס Juniper</v>
-      </c>
-      <c r="L21" t="str">
-        <v/>
-      </c>
-      <c r="M21" t="str">
-        <v/>
-      </c>
-      <c r="N21" t="str">
-        <v/>
-      </c>
-      <c r="O21" t="str">
-        <v/>
       </c>
     </row>
     <row r="22">
@@ -1373,7 +1145,7 @@
         <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E22" t="str">
         <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
@@ -1395,18 +1167,6 @@
       </c>
       <c r="K22" t="str">
         <v>ביפי קליירו Futique</v>
-      </c>
-      <c r="L22" t="str">
-        <v/>
-      </c>
-      <c r="M22" t="str">
-        <v/>
-      </c>
-      <c r="N22" t="str">
-        <v/>
-      </c>
-      <c r="O22" t="str">
-        <v/>
       </c>
     </row>
     <row r="23">
@@ -1420,7 +1180,7 @@
         <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E23" t="str">
         <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
@@ -1442,18 +1202,6 @@
       </c>
       <c r="K23" t="str">
         <v>אד שירן Play</v>
-      </c>
-      <c r="L23" t="str">
-        <v/>
-      </c>
-      <c r="M23" t="str">
-        <v/>
-      </c>
-      <c r="N23" t="str">
-        <v/>
-      </c>
-      <c r="O23" t="str">
-        <v/>
       </c>
     </row>
     <row r="24">
@@ -1467,7 +1215,7 @@
         <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E24" t="str">
         <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
@@ -1489,18 +1237,6 @@
       </c>
       <c r="K24" t="str">
         <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
-      </c>
-      <c r="L24" t="str">
-        <v/>
-      </c>
-      <c r="M24" t="str">
-        <v/>
-      </c>
-      <c r="N24" t="str">
-        <v/>
-      </c>
-      <c r="O24" t="str">
-        <v/>
       </c>
     </row>
     <row r="25">
@@ -1514,7 +1250,7 @@
         <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E25" t="str">
         <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
@@ -1536,18 +1272,6 @@
       </c>
       <c r="K25" t="str">
         <v>סוויד Antidepressants</v>
-      </c>
-      <c r="L25" t="str">
-        <v/>
-      </c>
-      <c r="M25" t="str">
-        <v/>
-      </c>
-      <c r="N25" t="str">
-        <v/>
-      </c>
-      <c r="O25" t="str">
-        <v/>
       </c>
     </row>
     <row r="26">
@@ -1561,7 +1285,7 @@
         <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E26" t="str">
         <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
@@ -1583,18 +1307,6 @@
       </c>
       <c r="K26" t="str">
         <v>וולף אליס The Clearing</v>
-      </c>
-      <c r="L26" t="str">
-        <v/>
-      </c>
-      <c r="M26" t="str">
-        <v/>
-      </c>
-      <c r="N26" t="str">
-        <v/>
-      </c>
-      <c r="O26" t="str">
-        <v/>
       </c>
     </row>
     <row r="27">
@@ -1608,7 +1320,7 @@
         <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E27" t="str">
         <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
@@ -1630,18 +1342,6 @@
       </c>
       <c r="K27" t="str">
         <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
-      </c>
-      <c r="L27" t="str">
-        <v/>
-      </c>
-      <c r="M27" t="str">
-        <v/>
-      </c>
-      <c r="N27" t="str">
-        <v/>
-      </c>
-      <c r="O27" t="str">
-        <v/>
       </c>
     </row>
     <row r="28">
@@ -1655,7 +1355,7 @@
         <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E28" t="str">
         <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
@@ -1677,18 +1377,6 @@
       </c>
       <c r="K28" t="str">
         <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
-      </c>
-      <c r="L28" t="str">
-        <v/>
-      </c>
-      <c r="M28" t="str">
-        <v/>
-      </c>
-      <c r="N28" t="str">
-        <v/>
-      </c>
-      <c r="O28" t="str">
-        <v/>
       </c>
     </row>
     <row r="29">
@@ -1702,7 +1390,7 @@
         <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E29" t="str">
         <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
@@ -1724,18 +1412,6 @@
       </c>
       <c r="K29" t="str">
         <v>טיילר דה קריאייטור Don't Tap The Glass</v>
-      </c>
-      <c r="L29" t="str">
-        <v/>
-      </c>
-      <c r="M29" t="str">
-        <v/>
-      </c>
-      <c r="N29" t="str">
-        <v/>
-      </c>
-      <c r="O29" t="str">
-        <v/>
       </c>
     </row>
     <row r="30">
@@ -1749,7 +1425,7 @@
         <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E30" t="str">
         <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
@@ -1771,18 +1447,6 @@
       </c>
       <c r="K30" t="str">
         <v>אברהם טל – חי</v>
-      </c>
-      <c r="L30" t="str">
-        <v/>
-      </c>
-      <c r="M30" t="str">
-        <v/>
-      </c>
-      <c r="N30" t="str">
-        <v/>
-      </c>
-      <c r="O30" t="str">
-        <v/>
       </c>
     </row>
     <row r="31">
@@ -1796,7 +1460,7 @@
         <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E31" t="str">
         <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
@@ -1819,34 +1483,22 @@
       <c r="K31" t="str">
         <v>רנה ראפ Bite Me</v>
       </c>
-      <c r="L31" t="str">
-        <v/>
-      </c>
-      <c r="M31" t="str">
-        <v/>
-      </c>
-      <c r="N31" t="str">
-        <v/>
-      </c>
-      <c r="O31" t="str">
-        <v/>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>The K's – Pretty On The Internet</v>
+        <v>עוז זהבי תור זהבי</v>
       </c>
       <c r="B32" t="str">
-        <v>2025-08-03</v>
+        <v>2026-01-18</v>
       </c>
       <c r="C32" t="str">
-        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
+        <v>https://yosmusic.com/%d7%a2%d7%95%d7%96-%d7%96%d7%94%d7%91%d7%99-%d7%aa%d7%95%d7%a8-%d7%96%d7%94%d7%91%d7%99/</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-18</v>
       </c>
       <c r="E32" t="str">
-        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
+        <v>את ההופעה הזו קיבלתי ביוטיוב (*), שיטה יעילה למי שנפשו לא חשקה לשרך דרכו למועדונים בלילות הקרים. הוידיאו נשלח לרגל יציאת אלבומו "תור זהבי", ששיר הנושא הוא ראפ עצבני בניחוח מזרחי, שיר אגו ביקורתי, אירוני ומודע לעצמו מלא בדאחקות, הגזמות,</v>
       </c>
       <c r="F32" t="str">
         <v/>
@@ -1864,7 +1516,7 @@
         <v/>
       </c>
       <c r="K32" t="str">
-        <v>The K's – Pretty On The Internet</v>
+        <v>עוז זהבי תור זהבי</v>
       </c>
       <c r="L32" t="str">
         <v/>
@@ -14329,9 +13981,3579 @@
         <v/>
       </c>
     </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>פטריק סבג Hotel Mogador</v>
+      </c>
+      <c r="B183" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C183" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
+      </c>
+      <c r="D183" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E183" t="str">
+        <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
+      </c>
+      <c r="F183" t="str">
+        <v/>
+      </c>
+      <c r="G183" t="str">
+        <v/>
+      </c>
+      <c r="H183" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I183" t="str">
+        <v/>
+      </c>
+      <c r="J183" t="str">
+        <v/>
+      </c>
+      <c r="K183" t="str">
+        <v>פטריק סבג Hotel Mogador</v>
+      </c>
+      <c r="L183" t="str">
+        <v/>
+      </c>
+      <c r="M183" t="str">
+        <v/>
+      </c>
+      <c r="N183" t="str">
+        <v/>
+      </c>
+      <c r="O183" t="str">
+        <v/>
+      </c>
+      <c r="P183" t="str">
+        <v/>
+      </c>
+      <c r="Q183" t="str">
+        <v/>
+      </c>
+      <c r="R183" t="str">
+        <v/>
+      </c>
+      <c r="S183" t="str">
+        <v/>
+      </c>
+      <c r="T183" t="str">
+        <v/>
+      </c>
+      <c r="U183" t="str">
+        <v/>
+      </c>
+      <c r="V183" t="str">
+        <v/>
+      </c>
+      <c r="W183" t="str">
+        <v/>
+      </c>
+      <c r="X183" t="str">
+        <v/>
+      </c>
+      <c r="Y183" t="str">
+        <v/>
+      </c>
+      <c r="Z183" t="str">
+        <v/>
+      </c>
+      <c r="AA183" t="str">
+        <v/>
+      </c>
+      <c r="AB183" t="str">
+        <v/>
+      </c>
+      <c r="AC183" t="str">
+        <v/>
+      </c>
+      <c r="AD183" t="str">
+        <v/>
+      </c>
+      <c r="AE183" t="str">
+        <v/>
+      </c>
+      <c r="AF183" t="str">
+        <v/>
+      </c>
+      <c r="AG183" t="str">
+        <v/>
+      </c>
+      <c r="AH183" t="str">
+        <v/>
+      </c>
+      <c r="AI183" t="str">
+        <v/>
+      </c>
+      <c r="AJ183" t="str">
+        <v/>
+      </c>
+      <c r="AK183" t="str">
+        <v/>
+      </c>
+      <c r="AL183" t="str">
+        <v/>
+      </c>
+      <c r="AM183" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
+      </c>
+      <c r="B184" t="str">
+        <v>2026-01-09</v>
+      </c>
+      <c r="C184" t="str">
+        <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
+      </c>
+      <c r="D184" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E184" t="str">
+        <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
+      </c>
+      <c r="F184" t="str">
+        <v/>
+      </c>
+      <c r="G184" t="str">
+        <v/>
+      </c>
+      <c r="H184" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I184" t="str">
+        <v/>
+      </c>
+      <c r="J184" t="str">
+        <v/>
+      </c>
+      <c r="K184" t="str">
+        <v>מארינה מקסימיליאן – ריק בחלל</v>
+      </c>
+      <c r="L184" t="str">
+        <v/>
+      </c>
+      <c r="M184" t="str">
+        <v/>
+      </c>
+      <c r="N184" t="str">
+        <v/>
+      </c>
+      <c r="O184" t="str">
+        <v/>
+      </c>
+      <c r="P184" t="str">
+        <v/>
+      </c>
+      <c r="Q184" t="str">
+        <v/>
+      </c>
+      <c r="R184" t="str">
+        <v/>
+      </c>
+      <c r="S184" t="str">
+        <v/>
+      </c>
+      <c r="T184" t="str">
+        <v/>
+      </c>
+      <c r="U184" t="str">
+        <v/>
+      </c>
+      <c r="V184" t="str">
+        <v/>
+      </c>
+      <c r="W184" t="str">
+        <v/>
+      </c>
+      <c r="X184" t="str">
+        <v/>
+      </c>
+      <c r="Y184" t="str">
+        <v/>
+      </c>
+      <c r="Z184" t="str">
+        <v/>
+      </c>
+      <c r="AA184" t="str">
+        <v/>
+      </c>
+      <c r="AB184" t="str">
+        <v/>
+      </c>
+      <c r="AC184" t="str">
+        <v/>
+      </c>
+      <c r="AD184" t="str">
+        <v/>
+      </c>
+      <c r="AE184" t="str">
+        <v/>
+      </c>
+      <c r="AF184" t="str">
+        <v/>
+      </c>
+      <c r="AG184" t="str">
+        <v/>
+      </c>
+      <c r="AH184" t="str">
+        <v/>
+      </c>
+      <c r="AI184" t="str">
+        <v/>
+      </c>
+      <c r="AJ184" t="str">
+        <v/>
+      </c>
+      <c r="AK184" t="str">
+        <v/>
+      </c>
+      <c r="AL184" t="str">
+        <v/>
+      </c>
+      <c r="AM184" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>אוליביה דין The Art of Loving</v>
+      </c>
+      <c r="B185" t="str">
+        <v>2026-01-04</v>
+      </c>
+      <c r="C185" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
+      </c>
+      <c r="D185" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E185" t="str">
+        <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
+      </c>
+      <c r="F185" t="str">
+        <v/>
+      </c>
+      <c r="G185" t="str">
+        <v/>
+      </c>
+      <c r="H185" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I185" t="str">
+        <v/>
+      </c>
+      <c r="J185" t="str">
+        <v/>
+      </c>
+      <c r="K185" t="str">
+        <v>אוליביה דין The Art of Loving</v>
+      </c>
+      <c r="L185" t="str">
+        <v/>
+      </c>
+      <c r="M185" t="str">
+        <v/>
+      </c>
+      <c r="N185" t="str">
+        <v/>
+      </c>
+      <c r="O185" t="str">
+        <v/>
+      </c>
+      <c r="P185" t="str">
+        <v/>
+      </c>
+      <c r="Q185" t="str">
+        <v/>
+      </c>
+      <c r="R185" t="str">
+        <v/>
+      </c>
+      <c r="S185" t="str">
+        <v/>
+      </c>
+      <c r="T185" t="str">
+        <v/>
+      </c>
+      <c r="U185" t="str">
+        <v/>
+      </c>
+      <c r="V185" t="str">
+        <v/>
+      </c>
+      <c r="W185" t="str">
+        <v/>
+      </c>
+      <c r="X185" t="str">
+        <v/>
+      </c>
+      <c r="Y185" t="str">
+        <v/>
+      </c>
+      <c r="Z185" t="str">
+        <v/>
+      </c>
+      <c r="AA185" t="str">
+        <v/>
+      </c>
+      <c r="AB185" t="str">
+        <v/>
+      </c>
+      <c r="AC185" t="str">
+        <v/>
+      </c>
+      <c r="AD185" t="str">
+        <v/>
+      </c>
+      <c r="AE185" t="str">
+        <v/>
+      </c>
+      <c r="AF185" t="str">
+        <v/>
+      </c>
+      <c r="AG185" t="str">
+        <v/>
+      </c>
+      <c r="AH185" t="str">
+        <v/>
+      </c>
+      <c r="AI185" t="str">
+        <v/>
+      </c>
+      <c r="AJ185" t="str">
+        <v/>
+      </c>
+      <c r="AK185" t="str">
+        <v/>
+      </c>
+      <c r="AL185" t="str">
+        <v/>
+      </c>
+      <c r="AM185" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>Geese Getting Killed</v>
+      </c>
+      <c r="B186" t="str">
+        <v>2025-12-29</v>
+      </c>
+      <c r="C186" t="str">
+        <v>https://yosmusic.com/geese-getting-killed/</v>
+      </c>
+      <c r="D186" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E186" t="str">
+        <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
+      </c>
+      <c r="F186" t="str">
+        <v/>
+      </c>
+      <c r="G186" t="str">
+        <v/>
+      </c>
+      <c r="H186" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I186" t="str">
+        <v/>
+      </c>
+      <c r="J186" t="str">
+        <v/>
+      </c>
+      <c r="K186" t="str">
+        <v>Geese Getting Killed</v>
+      </c>
+      <c r="L186" t="str">
+        <v/>
+      </c>
+      <c r="M186" t="str">
+        <v/>
+      </c>
+      <c r="N186" t="str">
+        <v/>
+      </c>
+      <c r="O186" t="str">
+        <v/>
+      </c>
+      <c r="P186" t="str">
+        <v/>
+      </c>
+      <c r="Q186" t="str">
+        <v/>
+      </c>
+      <c r="R186" t="str">
+        <v/>
+      </c>
+      <c r="S186" t="str">
+        <v/>
+      </c>
+      <c r="T186" t="str">
+        <v/>
+      </c>
+      <c r="U186" t="str">
+        <v/>
+      </c>
+      <c r="V186" t="str">
+        <v/>
+      </c>
+      <c r="W186" t="str">
+        <v/>
+      </c>
+      <c r="X186" t="str">
+        <v/>
+      </c>
+      <c r="Y186" t="str">
+        <v/>
+      </c>
+      <c r="Z186" t="str">
+        <v/>
+      </c>
+      <c r="AA186" t="str">
+        <v/>
+      </c>
+      <c r="AB186" t="str">
+        <v/>
+      </c>
+      <c r="AC186" t="str">
+        <v/>
+      </c>
+      <c r="AD186" t="str">
+        <v/>
+      </c>
+      <c r="AE186" t="str">
+        <v/>
+      </c>
+      <c r="AF186" t="str">
+        <v/>
+      </c>
+      <c r="AG186" t="str">
+        <v/>
+      </c>
+      <c r="AH186" t="str">
+        <v/>
+      </c>
+      <c r="AI186" t="str">
+        <v/>
+      </c>
+      <c r="AJ186" t="str">
+        <v/>
+      </c>
+      <c r="AK186" t="str">
+        <v/>
+      </c>
+      <c r="AL186" t="str">
+        <v/>
+      </c>
+      <c r="AM186" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>רוסליה Lux</v>
+      </c>
+      <c r="B187" t="str">
+        <v>2025-12-25</v>
+      </c>
+      <c r="C187" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
+      </c>
+      <c r="D187" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E187" t="str">
+        <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
+      </c>
+      <c r="F187" t="str">
+        <v/>
+      </c>
+      <c r="G187" t="str">
+        <v/>
+      </c>
+      <c r="H187" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I187" t="str">
+        <v/>
+      </c>
+      <c r="J187" t="str">
+        <v/>
+      </c>
+      <c r="K187" t="str">
+        <v>רוסליה Lux</v>
+      </c>
+      <c r="L187" t="str">
+        <v/>
+      </c>
+      <c r="M187" t="str">
+        <v/>
+      </c>
+      <c r="N187" t="str">
+        <v/>
+      </c>
+      <c r="O187" t="str">
+        <v/>
+      </c>
+      <c r="P187" t="str">
+        <v/>
+      </c>
+      <c r="Q187" t="str">
+        <v/>
+      </c>
+      <c r="R187" t="str">
+        <v/>
+      </c>
+      <c r="S187" t="str">
+        <v/>
+      </c>
+      <c r="T187" t="str">
+        <v/>
+      </c>
+      <c r="U187" t="str">
+        <v/>
+      </c>
+      <c r="V187" t="str">
+        <v/>
+      </c>
+      <c r="W187" t="str">
+        <v/>
+      </c>
+      <c r="X187" t="str">
+        <v/>
+      </c>
+      <c r="Y187" t="str">
+        <v/>
+      </c>
+      <c r="Z187" t="str">
+        <v/>
+      </c>
+      <c r="AA187" t="str">
+        <v/>
+      </c>
+      <c r="AB187" t="str">
+        <v/>
+      </c>
+      <c r="AC187" t="str">
+        <v/>
+      </c>
+      <c r="AD187" t="str">
+        <v/>
+      </c>
+      <c r="AE187" t="str">
+        <v/>
+      </c>
+      <c r="AF187" t="str">
+        <v/>
+      </c>
+      <c r="AG187" t="str">
+        <v/>
+      </c>
+      <c r="AH187" t="str">
+        <v/>
+      </c>
+      <c r="AI187" t="str">
+        <v/>
+      </c>
+      <c r="AJ187" t="str">
+        <v/>
+      </c>
+      <c r="AK187" t="str">
+        <v/>
+      </c>
+      <c r="AL187" t="str">
+        <v/>
+      </c>
+      <c r="AM187" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>יאנגבלאד אירוסמית' one more time</v>
+      </c>
+      <c r="B188" t="str">
+        <v>2025-12-17</v>
+      </c>
+      <c r="C188" t="str">
+        <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
+      </c>
+      <c r="D188" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E188" t="str">
+        <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
+      </c>
+      <c r="F188" t="str">
+        <v/>
+      </c>
+      <c r="G188" t="str">
+        <v/>
+      </c>
+      <c r="H188" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I188" t="str">
+        <v/>
+      </c>
+      <c r="J188" t="str">
+        <v/>
+      </c>
+      <c r="K188" t="str">
+        <v>יאנגבלאד אירוסמית' one more time</v>
+      </c>
+      <c r="L188" t="str">
+        <v/>
+      </c>
+      <c r="M188" t="str">
+        <v/>
+      </c>
+      <c r="N188" t="str">
+        <v/>
+      </c>
+      <c r="O188" t="str">
+        <v/>
+      </c>
+      <c r="P188" t="str">
+        <v/>
+      </c>
+      <c r="Q188" t="str">
+        <v/>
+      </c>
+      <c r="R188" t="str">
+        <v/>
+      </c>
+      <c r="S188" t="str">
+        <v/>
+      </c>
+      <c r="T188" t="str">
+        <v/>
+      </c>
+      <c r="U188" t="str">
+        <v/>
+      </c>
+      <c r="V188" t="str">
+        <v/>
+      </c>
+      <c r="W188" t="str">
+        <v/>
+      </c>
+      <c r="X188" t="str">
+        <v/>
+      </c>
+      <c r="Y188" t="str">
+        <v/>
+      </c>
+      <c r="Z188" t="str">
+        <v/>
+      </c>
+      <c r="AA188" t="str">
+        <v/>
+      </c>
+      <c r="AB188" t="str">
+        <v/>
+      </c>
+      <c r="AC188" t="str">
+        <v/>
+      </c>
+      <c r="AD188" t="str">
+        <v/>
+      </c>
+      <c r="AE188" t="str">
+        <v/>
+      </c>
+      <c r="AF188" t="str">
+        <v/>
+      </c>
+      <c r="AG188" t="str">
+        <v/>
+      </c>
+      <c r="AH188" t="str">
+        <v/>
+      </c>
+      <c r="AI188" t="str">
+        <v/>
+      </c>
+      <c r="AJ188" t="str">
+        <v/>
+      </c>
+      <c r="AK188" t="str">
+        <v/>
+      </c>
+      <c r="AL188" t="str">
+        <v/>
+      </c>
+      <c r="AM188" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>פינק פלויד Wish You Were Here 50</v>
+      </c>
+      <c r="B189" t="str">
+        <v>2025-12-14</v>
+      </c>
+      <c r="C189" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
+      </c>
+      <c r="D189" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E189" t="str">
+        <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
+      </c>
+      <c r="F189" t="str">
+        <v/>
+      </c>
+      <c r="G189" t="str">
+        <v/>
+      </c>
+      <c r="H189" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I189" t="str">
+        <v/>
+      </c>
+      <c r="J189" t="str">
+        <v/>
+      </c>
+      <c r="K189" t="str">
+        <v>פינק פלויד Wish You Were Here 50</v>
+      </c>
+      <c r="L189" t="str">
+        <v/>
+      </c>
+      <c r="M189" t="str">
+        <v/>
+      </c>
+      <c r="N189" t="str">
+        <v/>
+      </c>
+      <c r="O189" t="str">
+        <v/>
+      </c>
+      <c r="P189" t="str">
+        <v/>
+      </c>
+      <c r="Q189" t="str">
+        <v/>
+      </c>
+      <c r="R189" t="str">
+        <v/>
+      </c>
+      <c r="S189" t="str">
+        <v/>
+      </c>
+      <c r="T189" t="str">
+        <v/>
+      </c>
+      <c r="U189" t="str">
+        <v/>
+      </c>
+      <c r="V189" t="str">
+        <v/>
+      </c>
+      <c r="W189" t="str">
+        <v/>
+      </c>
+      <c r="X189" t="str">
+        <v/>
+      </c>
+      <c r="Y189" t="str">
+        <v/>
+      </c>
+      <c r="Z189" t="str">
+        <v/>
+      </c>
+      <c r="AA189" t="str">
+        <v/>
+      </c>
+      <c r="AB189" t="str">
+        <v/>
+      </c>
+      <c r="AC189" t="str">
+        <v/>
+      </c>
+      <c r="AD189" t="str">
+        <v/>
+      </c>
+      <c r="AE189" t="str">
+        <v/>
+      </c>
+      <c r="AF189" t="str">
+        <v/>
+      </c>
+      <c r="AG189" t="str">
+        <v/>
+      </c>
+      <c r="AH189" t="str">
+        <v/>
+      </c>
+      <c r="AI189" t="str">
+        <v/>
+      </c>
+      <c r="AJ189" t="str">
+        <v/>
+      </c>
+      <c r="AK189" t="str">
+        <v/>
+      </c>
+      <c r="AL189" t="str">
+        <v/>
+      </c>
+      <c r="AM189" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+      </c>
+      <c r="B190" t="str">
+        <v>2025-12-08</v>
+      </c>
+      <c r="C190" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
+      </c>
+      <c r="D190" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E190" t="str">
+        <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
+      </c>
+      <c r="F190" t="str">
+        <v/>
+      </c>
+      <c r="G190" t="str">
+        <v/>
+      </c>
+      <c r="H190" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I190" t="str">
+        <v/>
+      </c>
+      <c r="J190" t="str">
+        <v/>
+      </c>
+      <c r="K190" t="str">
+        <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
+      </c>
+      <c r="L190" t="str">
+        <v/>
+      </c>
+      <c r="M190" t="str">
+        <v/>
+      </c>
+      <c r="N190" t="str">
+        <v/>
+      </c>
+      <c r="O190" t="str">
+        <v/>
+      </c>
+      <c r="P190" t="str">
+        <v/>
+      </c>
+      <c r="Q190" t="str">
+        <v/>
+      </c>
+      <c r="R190" t="str">
+        <v/>
+      </c>
+      <c r="S190" t="str">
+        <v/>
+      </c>
+      <c r="T190" t="str">
+        <v/>
+      </c>
+      <c r="U190" t="str">
+        <v/>
+      </c>
+      <c r="V190" t="str">
+        <v/>
+      </c>
+      <c r="W190" t="str">
+        <v/>
+      </c>
+      <c r="X190" t="str">
+        <v/>
+      </c>
+      <c r="Y190" t="str">
+        <v/>
+      </c>
+      <c r="Z190" t="str">
+        <v/>
+      </c>
+      <c r="AA190" t="str">
+        <v/>
+      </c>
+      <c r="AB190" t="str">
+        <v/>
+      </c>
+      <c r="AC190" t="str">
+        <v/>
+      </c>
+      <c r="AD190" t="str">
+        <v/>
+      </c>
+      <c r="AE190" t="str">
+        <v/>
+      </c>
+      <c r="AF190" t="str">
+        <v/>
+      </c>
+      <c r="AG190" t="str">
+        <v/>
+      </c>
+      <c r="AH190" t="str">
+        <v/>
+      </c>
+      <c r="AI190" t="str">
+        <v/>
+      </c>
+      <c r="AJ190" t="str">
+        <v/>
+      </c>
+      <c r="AK190" t="str">
+        <v/>
+      </c>
+      <c r="AL190" t="str">
+        <v/>
+      </c>
+      <c r="AM190" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>סטריי קידס DO IT EP</v>
+      </c>
+      <c r="B191" t="str">
+        <v>2025-12-04</v>
+      </c>
+      <c r="C191" t="str">
+        <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
+      </c>
+      <c r="D191" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E191" t="str">
+        <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
+      </c>
+      <c r="F191" t="str">
+        <v/>
+      </c>
+      <c r="G191" t="str">
+        <v/>
+      </c>
+      <c r="H191" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I191" t="str">
+        <v/>
+      </c>
+      <c r="J191" t="str">
+        <v/>
+      </c>
+      <c r="K191" t="str">
+        <v>סטריי קידס DO IT EP</v>
+      </c>
+      <c r="L191" t="str">
+        <v/>
+      </c>
+      <c r="M191" t="str">
+        <v/>
+      </c>
+      <c r="N191" t="str">
+        <v/>
+      </c>
+      <c r="O191" t="str">
+        <v/>
+      </c>
+      <c r="P191" t="str">
+        <v/>
+      </c>
+      <c r="Q191" t="str">
+        <v/>
+      </c>
+      <c r="R191" t="str">
+        <v/>
+      </c>
+      <c r="S191" t="str">
+        <v/>
+      </c>
+      <c r="T191" t="str">
+        <v/>
+      </c>
+      <c r="U191" t="str">
+        <v/>
+      </c>
+      <c r="V191" t="str">
+        <v/>
+      </c>
+      <c r="W191" t="str">
+        <v/>
+      </c>
+      <c r="X191" t="str">
+        <v/>
+      </c>
+      <c r="Y191" t="str">
+        <v/>
+      </c>
+      <c r="Z191" t="str">
+        <v/>
+      </c>
+      <c r="AA191" t="str">
+        <v/>
+      </c>
+      <c r="AB191" t="str">
+        <v/>
+      </c>
+      <c r="AC191" t="str">
+        <v/>
+      </c>
+      <c r="AD191" t="str">
+        <v/>
+      </c>
+      <c r="AE191" t="str">
+        <v/>
+      </c>
+      <c r="AF191" t="str">
+        <v/>
+      </c>
+      <c r="AG191" t="str">
+        <v/>
+      </c>
+      <c r="AH191" t="str">
+        <v/>
+      </c>
+      <c r="AI191" t="str">
+        <v/>
+      </c>
+      <c r="AJ191" t="str">
+        <v/>
+      </c>
+      <c r="AK191" t="str">
+        <v/>
+      </c>
+      <c r="AL191" t="str">
+        <v/>
+      </c>
+      <c r="AM191" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>דויד ברוזה BROZAJAZZ</v>
+      </c>
+      <c r="B192" t="str">
+        <v>2025-11-30</v>
+      </c>
+      <c r="C192" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
+      </c>
+      <c r="D192" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E192" t="str">
+        <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
+      </c>
+      <c r="F192" t="str">
+        <v/>
+      </c>
+      <c r="G192" t="str">
+        <v/>
+      </c>
+      <c r="H192" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I192" t="str">
+        <v/>
+      </c>
+      <c r="J192" t="str">
+        <v/>
+      </c>
+      <c r="K192" t="str">
+        <v>דויד ברוזה BROZAJAZZ</v>
+      </c>
+      <c r="L192" t="str">
+        <v/>
+      </c>
+      <c r="M192" t="str">
+        <v/>
+      </c>
+      <c r="N192" t="str">
+        <v/>
+      </c>
+      <c r="O192" t="str">
+        <v/>
+      </c>
+      <c r="P192" t="str">
+        <v/>
+      </c>
+      <c r="Q192" t="str">
+        <v/>
+      </c>
+      <c r="R192" t="str">
+        <v/>
+      </c>
+      <c r="S192" t="str">
+        <v/>
+      </c>
+      <c r="T192" t="str">
+        <v/>
+      </c>
+      <c r="U192" t="str">
+        <v/>
+      </c>
+      <c r="V192" t="str">
+        <v/>
+      </c>
+      <c r="W192" t="str">
+        <v/>
+      </c>
+      <c r="X192" t="str">
+        <v/>
+      </c>
+      <c r="Y192" t="str">
+        <v/>
+      </c>
+      <c r="Z192" t="str">
+        <v/>
+      </c>
+      <c r="AA192" t="str">
+        <v/>
+      </c>
+      <c r="AB192" t="str">
+        <v/>
+      </c>
+      <c r="AC192" t="str">
+        <v/>
+      </c>
+      <c r="AD192" t="str">
+        <v/>
+      </c>
+      <c r="AE192" t="str">
+        <v/>
+      </c>
+      <c r="AF192" t="str">
+        <v/>
+      </c>
+      <c r="AG192" t="str">
+        <v/>
+      </c>
+      <c r="AH192" t="str">
+        <v/>
+      </c>
+      <c r="AI192" t="str">
+        <v/>
+      </c>
+      <c r="AJ192" t="str">
+        <v/>
+      </c>
+      <c r="AK192" t="str">
+        <v/>
+      </c>
+      <c r="AL192" t="str">
+        <v/>
+      </c>
+      <c r="AM192" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>Five Seconds of Summer – Everyone's A Star</v>
+      </c>
+      <c r="B193" t="str">
+        <v>2025-11-24</v>
+      </c>
+      <c r="C193" t="str">
+        <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
+      </c>
+      <c r="D193" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E193" t="str">
+        <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
+      </c>
+      <c r="F193" t="str">
+        <v/>
+      </c>
+      <c r="G193" t="str">
+        <v/>
+      </c>
+      <c r="H193" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I193" t="str">
+        <v/>
+      </c>
+      <c r="J193" t="str">
+        <v/>
+      </c>
+      <c r="K193" t="str">
+        <v>Five Seconds of Summer – Everyone's A Star</v>
+      </c>
+      <c r="L193" t="str">
+        <v/>
+      </c>
+      <c r="M193" t="str">
+        <v/>
+      </c>
+      <c r="N193" t="str">
+        <v/>
+      </c>
+      <c r="O193" t="str">
+        <v/>
+      </c>
+      <c r="P193" t="str">
+        <v/>
+      </c>
+      <c r="Q193" t="str">
+        <v/>
+      </c>
+      <c r="R193" t="str">
+        <v/>
+      </c>
+      <c r="S193" t="str">
+        <v/>
+      </c>
+      <c r="T193" t="str">
+        <v/>
+      </c>
+      <c r="U193" t="str">
+        <v/>
+      </c>
+      <c r="V193" t="str">
+        <v/>
+      </c>
+      <c r="W193" t="str">
+        <v/>
+      </c>
+      <c r="X193" t="str">
+        <v/>
+      </c>
+      <c r="Y193" t="str">
+        <v/>
+      </c>
+      <c r="Z193" t="str">
+        <v/>
+      </c>
+      <c r="AA193" t="str">
+        <v/>
+      </c>
+      <c r="AB193" t="str">
+        <v/>
+      </c>
+      <c r="AC193" t="str">
+        <v/>
+      </c>
+      <c r="AD193" t="str">
+        <v/>
+      </c>
+      <c r="AE193" t="str">
+        <v/>
+      </c>
+      <c r="AF193" t="str">
+        <v/>
+      </c>
+      <c r="AG193" t="str">
+        <v/>
+      </c>
+      <c r="AH193" t="str">
+        <v/>
+      </c>
+      <c r="AI193" t="str">
+        <v/>
+      </c>
+      <c r="AJ193" t="str">
+        <v/>
+      </c>
+      <c r="AK193" t="str">
+        <v/>
+      </c>
+      <c r="AL193" t="str">
+        <v/>
+      </c>
+      <c r="AM193" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>התקווה 6 – ויהי אור</v>
+      </c>
+      <c r="B194" t="str">
+        <v>2025-11-20</v>
+      </c>
+      <c r="C194" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
+      </c>
+      <c r="D194" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E194" t="str">
+        <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
+      </c>
+      <c r="F194" t="str">
+        <v/>
+      </c>
+      <c r="G194" t="str">
+        <v/>
+      </c>
+      <c r="H194" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I194" t="str">
+        <v/>
+      </c>
+      <c r="J194" t="str">
+        <v/>
+      </c>
+      <c r="K194" t="str">
+        <v>התקווה 6 – ויהי אור</v>
+      </c>
+      <c r="L194" t="str">
+        <v/>
+      </c>
+      <c r="M194" t="str">
+        <v/>
+      </c>
+      <c r="N194" t="str">
+        <v/>
+      </c>
+      <c r="O194" t="str">
+        <v/>
+      </c>
+      <c r="P194" t="str">
+        <v/>
+      </c>
+      <c r="Q194" t="str">
+        <v/>
+      </c>
+      <c r="R194" t="str">
+        <v/>
+      </c>
+      <c r="S194" t="str">
+        <v/>
+      </c>
+      <c r="T194" t="str">
+        <v/>
+      </c>
+      <c r="U194" t="str">
+        <v/>
+      </c>
+      <c r="V194" t="str">
+        <v/>
+      </c>
+      <c r="W194" t="str">
+        <v/>
+      </c>
+      <c r="X194" t="str">
+        <v/>
+      </c>
+      <c r="Y194" t="str">
+        <v/>
+      </c>
+      <c r="Z194" t="str">
+        <v/>
+      </c>
+      <c r="AA194" t="str">
+        <v/>
+      </c>
+      <c r="AB194" t="str">
+        <v/>
+      </c>
+      <c r="AC194" t="str">
+        <v/>
+      </c>
+      <c r="AD194" t="str">
+        <v/>
+      </c>
+      <c r="AE194" t="str">
+        <v/>
+      </c>
+      <c r="AF194" t="str">
+        <v/>
+      </c>
+      <c r="AG194" t="str">
+        <v/>
+      </c>
+      <c r="AH194" t="str">
+        <v/>
+      </c>
+      <c r="AI194" t="str">
+        <v/>
+      </c>
+      <c r="AJ194" t="str">
+        <v/>
+      </c>
+      <c r="AK194" t="str">
+        <v/>
+      </c>
+      <c r="AL194" t="str">
+        <v/>
+      </c>
+      <c r="AM194" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>פלורנס אנד דה משין Everybody Scream</v>
+      </c>
+      <c r="B195" t="str">
+        <v>2025-11-13</v>
+      </c>
+      <c r="C195" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
+      </c>
+      <c r="D195" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E195" t="str">
+        <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
+      </c>
+      <c r="F195" t="str">
+        <v/>
+      </c>
+      <c r="G195" t="str">
+        <v/>
+      </c>
+      <c r="H195" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I195" t="str">
+        <v/>
+      </c>
+      <c r="J195" t="str">
+        <v/>
+      </c>
+      <c r="K195" t="str">
+        <v>פלורנס אנד דה משין Everybody Scream</v>
+      </c>
+      <c r="L195" t="str">
+        <v/>
+      </c>
+      <c r="M195" t="str">
+        <v/>
+      </c>
+      <c r="N195" t="str">
+        <v/>
+      </c>
+      <c r="O195" t="str">
+        <v/>
+      </c>
+      <c r="P195" t="str">
+        <v/>
+      </c>
+      <c r="Q195" t="str">
+        <v/>
+      </c>
+      <c r="R195" t="str">
+        <v/>
+      </c>
+      <c r="S195" t="str">
+        <v/>
+      </c>
+      <c r="T195" t="str">
+        <v/>
+      </c>
+      <c r="U195" t="str">
+        <v/>
+      </c>
+      <c r="V195" t="str">
+        <v/>
+      </c>
+      <c r="W195" t="str">
+        <v/>
+      </c>
+      <c r="X195" t="str">
+        <v/>
+      </c>
+      <c r="Y195" t="str">
+        <v/>
+      </c>
+      <c r="Z195" t="str">
+        <v/>
+      </c>
+      <c r="AA195" t="str">
+        <v/>
+      </c>
+      <c r="AB195" t="str">
+        <v/>
+      </c>
+      <c r="AC195" t="str">
+        <v/>
+      </c>
+      <c r="AD195" t="str">
+        <v/>
+      </c>
+      <c r="AE195" t="str">
+        <v/>
+      </c>
+      <c r="AF195" t="str">
+        <v/>
+      </c>
+      <c r="AG195" t="str">
+        <v/>
+      </c>
+      <c r="AH195" t="str">
+        <v/>
+      </c>
+      <c r="AI195" t="str">
+        <v/>
+      </c>
+      <c r="AJ195" t="str">
+        <v/>
+      </c>
+      <c r="AK195" t="str">
+        <v/>
+      </c>
+      <c r="AL195" t="str">
+        <v/>
+      </c>
+      <c r="AM195" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>טיים אימפלה Deadbeat</v>
+      </c>
+      <c r="B196" t="str">
+        <v>2025-11-03</v>
+      </c>
+      <c r="C196" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
+      </c>
+      <c r="D196" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E196" t="str">
+        <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
+      </c>
+      <c r="F196" t="str">
+        <v/>
+      </c>
+      <c r="G196" t="str">
+        <v/>
+      </c>
+      <c r="H196" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I196" t="str">
+        <v/>
+      </c>
+      <c r="J196" t="str">
+        <v/>
+      </c>
+      <c r="K196" t="str">
+        <v>טיים אימפלה Deadbeat</v>
+      </c>
+      <c r="L196" t="str">
+        <v/>
+      </c>
+      <c r="M196" t="str">
+        <v/>
+      </c>
+      <c r="N196" t="str">
+        <v/>
+      </c>
+      <c r="O196" t="str">
+        <v/>
+      </c>
+      <c r="P196" t="str">
+        <v/>
+      </c>
+      <c r="Q196" t="str">
+        <v/>
+      </c>
+      <c r="R196" t="str">
+        <v/>
+      </c>
+      <c r="S196" t="str">
+        <v/>
+      </c>
+      <c r="T196" t="str">
+        <v/>
+      </c>
+      <c r="U196" t="str">
+        <v/>
+      </c>
+      <c r="V196" t="str">
+        <v/>
+      </c>
+      <c r="W196" t="str">
+        <v/>
+      </c>
+      <c r="X196" t="str">
+        <v/>
+      </c>
+      <c r="Y196" t="str">
+        <v/>
+      </c>
+      <c r="Z196" t="str">
+        <v/>
+      </c>
+      <c r="AA196" t="str">
+        <v/>
+      </c>
+      <c r="AB196" t="str">
+        <v/>
+      </c>
+      <c r="AC196" t="str">
+        <v/>
+      </c>
+      <c r="AD196" t="str">
+        <v/>
+      </c>
+      <c r="AE196" t="str">
+        <v/>
+      </c>
+      <c r="AF196" t="str">
+        <v/>
+      </c>
+      <c r="AG196" t="str">
+        <v/>
+      </c>
+      <c r="AH196" t="str">
+        <v/>
+      </c>
+      <c r="AI196" t="str">
+        <v/>
+      </c>
+      <c r="AJ196" t="str">
+        <v/>
+      </c>
+      <c r="AK196" t="str">
+        <v/>
+      </c>
+      <c r="AL196" t="str">
+        <v/>
+      </c>
+      <c r="AM196" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+      </c>
+      <c r="B197" t="str">
+        <v>2025-10-20</v>
+      </c>
+      <c r="C197" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
+      </c>
+      <c r="D197" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E197" t="str">
+        <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
+      </c>
+      <c r="F197" t="str">
+        <v/>
+      </c>
+      <c r="G197" t="str">
+        <v/>
+      </c>
+      <c r="H197" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I197" t="str">
+        <v/>
+      </c>
+      <c r="J197" t="str">
+        <v/>
+      </c>
+      <c r="K197" t="str">
+        <v>דייוויד גילמור The Luck and Strange Concerts</v>
+      </c>
+      <c r="L197" t="str">
+        <v/>
+      </c>
+      <c r="M197" t="str">
+        <v/>
+      </c>
+      <c r="N197" t="str">
+        <v/>
+      </c>
+      <c r="O197" t="str">
+        <v/>
+      </c>
+      <c r="P197" t="str">
+        <v/>
+      </c>
+      <c r="Q197" t="str">
+        <v/>
+      </c>
+      <c r="R197" t="str">
+        <v/>
+      </c>
+      <c r="S197" t="str">
+        <v/>
+      </c>
+      <c r="T197" t="str">
+        <v/>
+      </c>
+      <c r="U197" t="str">
+        <v/>
+      </c>
+      <c r="V197" t="str">
+        <v/>
+      </c>
+      <c r="W197" t="str">
+        <v/>
+      </c>
+      <c r="X197" t="str">
+        <v/>
+      </c>
+      <c r="Y197" t="str">
+        <v/>
+      </c>
+      <c r="Z197" t="str">
+        <v/>
+      </c>
+      <c r="AA197" t="str">
+        <v/>
+      </c>
+      <c r="AB197" t="str">
+        <v/>
+      </c>
+      <c r="AC197" t="str">
+        <v/>
+      </c>
+      <c r="AD197" t="str">
+        <v/>
+      </c>
+      <c r="AE197" t="str">
+        <v/>
+      </c>
+      <c r="AF197" t="str">
+        <v/>
+      </c>
+      <c r="AG197" t="str">
+        <v/>
+      </c>
+      <c r="AH197" t="str">
+        <v/>
+      </c>
+      <c r="AI197" t="str">
+        <v/>
+      </c>
+      <c r="AJ197" t="str">
+        <v/>
+      </c>
+      <c r="AK197" t="str">
+        <v/>
+      </c>
+      <c r="AL197" t="str">
+        <v/>
+      </c>
+      <c r="AM197" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>שלמה גרוניך – תודה אהבה</v>
+      </c>
+      <c r="B198" t="str">
+        <v>2025-10-18</v>
+      </c>
+      <c r="C198" t="str">
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
+      </c>
+      <c r="D198" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E198" t="str">
+        <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
+      </c>
+      <c r="F198" t="str">
+        <v/>
+      </c>
+      <c r="G198" t="str">
+        <v/>
+      </c>
+      <c r="H198" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I198" t="str">
+        <v/>
+      </c>
+      <c r="J198" t="str">
+        <v/>
+      </c>
+      <c r="K198" t="str">
+        <v>שלמה גרוניך – תודה אהבה</v>
+      </c>
+      <c r="L198" t="str">
+        <v/>
+      </c>
+      <c r="M198" t="str">
+        <v/>
+      </c>
+      <c r="N198" t="str">
+        <v/>
+      </c>
+      <c r="O198" t="str">
+        <v/>
+      </c>
+      <c r="P198" t="str">
+        <v/>
+      </c>
+      <c r="Q198" t="str">
+        <v/>
+      </c>
+      <c r="R198" t="str">
+        <v/>
+      </c>
+      <c r="S198" t="str">
+        <v/>
+      </c>
+      <c r="T198" t="str">
+        <v/>
+      </c>
+      <c r="U198" t="str">
+        <v/>
+      </c>
+      <c r="V198" t="str">
+        <v/>
+      </c>
+      <c r="W198" t="str">
+        <v/>
+      </c>
+      <c r="X198" t="str">
+        <v/>
+      </c>
+      <c r="Y198" t="str">
+        <v/>
+      </c>
+      <c r="Z198" t="str">
+        <v/>
+      </c>
+      <c r="AA198" t="str">
+        <v/>
+      </c>
+      <c r="AB198" t="str">
+        <v/>
+      </c>
+      <c r="AC198" t="str">
+        <v/>
+      </c>
+      <c r="AD198" t="str">
+        <v/>
+      </c>
+      <c r="AE198" t="str">
+        <v/>
+      </c>
+      <c r="AF198" t="str">
+        <v/>
+      </c>
+      <c r="AG198" t="str">
+        <v/>
+      </c>
+      <c r="AH198" t="str">
+        <v/>
+      </c>
+      <c r="AI198" t="str">
+        <v/>
+      </c>
+      <c r="AJ198" t="str">
+        <v/>
+      </c>
+      <c r="AK198" t="str">
+        <v/>
+      </c>
+      <c r="AL198" t="str">
+        <v/>
+      </c>
+      <c r="AM198" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
+      </c>
+      <c r="B199" t="str">
+        <v>2025-10-11</v>
+      </c>
+      <c r="C199" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
+      </c>
+      <c r="D199" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E199" t="str">
+        <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
+      </c>
+      <c r="F199" t="str">
+        <v/>
+      </c>
+      <c r="G199" t="str">
+        <v/>
+      </c>
+      <c r="H199" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I199" t="str">
+        <v/>
+      </c>
+      <c r="J199" t="str">
+        <v/>
+      </c>
+      <c r="K199" t="str">
+        <v>טיילור סוויפט The Life Of A Showgirl</v>
+      </c>
+      <c r="L199" t="str">
+        <v/>
+      </c>
+      <c r="M199" t="str">
+        <v/>
+      </c>
+      <c r="N199" t="str">
+        <v/>
+      </c>
+      <c r="O199" t="str">
+        <v/>
+      </c>
+      <c r="P199" t="str">
+        <v/>
+      </c>
+      <c r="Q199" t="str">
+        <v/>
+      </c>
+      <c r="R199" t="str">
+        <v/>
+      </c>
+      <c r="S199" t="str">
+        <v/>
+      </c>
+      <c r="T199" t="str">
+        <v/>
+      </c>
+      <c r="U199" t="str">
+        <v/>
+      </c>
+      <c r="V199" t="str">
+        <v/>
+      </c>
+      <c r="W199" t="str">
+        <v/>
+      </c>
+      <c r="X199" t="str">
+        <v/>
+      </c>
+      <c r="Y199" t="str">
+        <v/>
+      </c>
+      <c r="Z199" t="str">
+        <v/>
+      </c>
+      <c r="AA199" t="str">
+        <v/>
+      </c>
+      <c r="AB199" t="str">
+        <v/>
+      </c>
+      <c r="AC199" t="str">
+        <v/>
+      </c>
+      <c r="AD199" t="str">
+        <v/>
+      </c>
+      <c r="AE199" t="str">
+        <v/>
+      </c>
+      <c r="AF199" t="str">
+        <v/>
+      </c>
+      <c r="AG199" t="str">
+        <v/>
+      </c>
+      <c r="AH199" t="str">
+        <v/>
+      </c>
+      <c r="AI199" t="str">
+        <v/>
+      </c>
+      <c r="AJ199" t="str">
+        <v/>
+      </c>
+      <c r="AK199" t="str">
+        <v/>
+      </c>
+      <c r="AL199" t="str">
+        <v/>
+      </c>
+      <c r="AM199" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>דוג'ה קאט Vie</v>
+      </c>
+      <c r="B200" t="str">
+        <v>2025-10-04</v>
+      </c>
+      <c r="C200" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
+      </c>
+      <c r="D200" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E200" t="str">
+        <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
+      </c>
+      <c r="F200" t="str">
+        <v/>
+      </c>
+      <c r="G200" t="str">
+        <v/>
+      </c>
+      <c r="H200" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I200" t="str">
+        <v/>
+      </c>
+      <c r="J200" t="str">
+        <v/>
+      </c>
+      <c r="K200" t="str">
+        <v>דוג'ה קאט Vie</v>
+      </c>
+      <c r="L200" t="str">
+        <v/>
+      </c>
+      <c r="M200" t="str">
+        <v/>
+      </c>
+      <c r="N200" t="str">
+        <v/>
+      </c>
+      <c r="O200" t="str">
+        <v/>
+      </c>
+      <c r="P200" t="str">
+        <v/>
+      </c>
+      <c r="Q200" t="str">
+        <v/>
+      </c>
+      <c r="R200" t="str">
+        <v/>
+      </c>
+      <c r="S200" t="str">
+        <v/>
+      </c>
+      <c r="T200" t="str">
+        <v/>
+      </c>
+      <c r="U200" t="str">
+        <v/>
+      </c>
+      <c r="V200" t="str">
+        <v/>
+      </c>
+      <c r="W200" t="str">
+        <v/>
+      </c>
+      <c r="X200" t="str">
+        <v/>
+      </c>
+      <c r="Y200" t="str">
+        <v/>
+      </c>
+      <c r="Z200" t="str">
+        <v/>
+      </c>
+      <c r="AA200" t="str">
+        <v/>
+      </c>
+      <c r="AB200" t="str">
+        <v/>
+      </c>
+      <c r="AC200" t="str">
+        <v/>
+      </c>
+      <c r="AD200" t="str">
+        <v/>
+      </c>
+      <c r="AE200" t="str">
+        <v/>
+      </c>
+      <c r="AF200" t="str">
+        <v/>
+      </c>
+      <c r="AG200" t="str">
+        <v/>
+      </c>
+      <c r="AH200" t="str">
+        <v/>
+      </c>
+      <c r="AI200" t="str">
+        <v/>
+      </c>
+      <c r="AJ200" t="str">
+        <v/>
+      </c>
+      <c r="AK200" t="str">
+        <v/>
+      </c>
+      <c r="AL200" t="str">
+        <v/>
+      </c>
+      <c r="AM200" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>ג'וי קרוקס Juniper</v>
+      </c>
+      <c r="B201" t="str">
+        <v>2025-10-03</v>
+      </c>
+      <c r="C201" t="str">
+        <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
+      </c>
+      <c r="D201" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E201" t="str">
+        <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
+      </c>
+      <c r="F201" t="str">
+        <v/>
+      </c>
+      <c r="G201" t="str">
+        <v/>
+      </c>
+      <c r="H201" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I201" t="str">
+        <v/>
+      </c>
+      <c r="J201" t="str">
+        <v/>
+      </c>
+      <c r="K201" t="str">
+        <v>ג'וי קרוקס Juniper</v>
+      </c>
+      <c r="L201" t="str">
+        <v/>
+      </c>
+      <c r="M201" t="str">
+        <v/>
+      </c>
+      <c r="N201" t="str">
+        <v/>
+      </c>
+      <c r="O201" t="str">
+        <v/>
+      </c>
+      <c r="P201" t="str">
+        <v/>
+      </c>
+      <c r="Q201" t="str">
+        <v/>
+      </c>
+      <c r="R201" t="str">
+        <v/>
+      </c>
+      <c r="S201" t="str">
+        <v/>
+      </c>
+      <c r="T201" t="str">
+        <v/>
+      </c>
+      <c r="U201" t="str">
+        <v/>
+      </c>
+      <c r="V201" t="str">
+        <v/>
+      </c>
+      <c r="W201" t="str">
+        <v/>
+      </c>
+      <c r="X201" t="str">
+        <v/>
+      </c>
+      <c r="Y201" t="str">
+        <v/>
+      </c>
+      <c r="Z201" t="str">
+        <v/>
+      </c>
+      <c r="AA201" t="str">
+        <v/>
+      </c>
+      <c r="AB201" t="str">
+        <v/>
+      </c>
+      <c r="AC201" t="str">
+        <v/>
+      </c>
+      <c r="AD201" t="str">
+        <v/>
+      </c>
+      <c r="AE201" t="str">
+        <v/>
+      </c>
+      <c r="AF201" t="str">
+        <v/>
+      </c>
+      <c r="AG201" t="str">
+        <v/>
+      </c>
+      <c r="AH201" t="str">
+        <v/>
+      </c>
+      <c r="AI201" t="str">
+        <v/>
+      </c>
+      <c r="AJ201" t="str">
+        <v/>
+      </c>
+      <c r="AK201" t="str">
+        <v/>
+      </c>
+      <c r="AL201" t="str">
+        <v/>
+      </c>
+      <c r="AM201" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>ביפי קליירו Futique</v>
+      </c>
+      <c r="B202" t="str">
+        <v>2025-09-30</v>
+      </c>
+      <c r="C202" t="str">
+        <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
+      </c>
+      <c r="D202" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E202" t="str">
+        <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
+      </c>
+      <c r="F202" t="str">
+        <v/>
+      </c>
+      <c r="G202" t="str">
+        <v/>
+      </c>
+      <c r="H202" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I202" t="str">
+        <v/>
+      </c>
+      <c r="J202" t="str">
+        <v/>
+      </c>
+      <c r="K202" t="str">
+        <v>ביפי קליירו Futique</v>
+      </c>
+      <c r="L202" t="str">
+        <v/>
+      </c>
+      <c r="M202" t="str">
+        <v/>
+      </c>
+      <c r="N202" t="str">
+        <v/>
+      </c>
+      <c r="O202" t="str">
+        <v/>
+      </c>
+      <c r="P202" t="str">
+        <v/>
+      </c>
+      <c r="Q202" t="str">
+        <v/>
+      </c>
+      <c r="R202" t="str">
+        <v/>
+      </c>
+      <c r="S202" t="str">
+        <v/>
+      </c>
+      <c r="T202" t="str">
+        <v/>
+      </c>
+      <c r="U202" t="str">
+        <v/>
+      </c>
+      <c r="V202" t="str">
+        <v/>
+      </c>
+      <c r="W202" t="str">
+        <v/>
+      </c>
+      <c r="X202" t="str">
+        <v/>
+      </c>
+      <c r="Y202" t="str">
+        <v/>
+      </c>
+      <c r="Z202" t="str">
+        <v/>
+      </c>
+      <c r="AA202" t="str">
+        <v/>
+      </c>
+      <c r="AB202" t="str">
+        <v/>
+      </c>
+      <c r="AC202" t="str">
+        <v/>
+      </c>
+      <c r="AD202" t="str">
+        <v/>
+      </c>
+      <c r="AE202" t="str">
+        <v/>
+      </c>
+      <c r="AF202" t="str">
+        <v/>
+      </c>
+      <c r="AG202" t="str">
+        <v/>
+      </c>
+      <c r="AH202" t="str">
+        <v/>
+      </c>
+      <c r="AI202" t="str">
+        <v/>
+      </c>
+      <c r="AJ202" t="str">
+        <v/>
+      </c>
+      <c r="AK202" t="str">
+        <v/>
+      </c>
+      <c r="AL202" t="str">
+        <v/>
+      </c>
+      <c r="AM202" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>אד שירן Play</v>
+      </c>
+      <c r="B203" t="str">
+        <v>2025-09-24</v>
+      </c>
+      <c r="C203" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
+      </c>
+      <c r="D203" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E203" t="str">
+        <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
+      </c>
+      <c r="F203" t="str">
+        <v/>
+      </c>
+      <c r="G203" t="str">
+        <v/>
+      </c>
+      <c r="H203" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I203" t="str">
+        <v/>
+      </c>
+      <c r="J203" t="str">
+        <v/>
+      </c>
+      <c r="K203" t="str">
+        <v>אד שירן Play</v>
+      </c>
+      <c r="L203" t="str">
+        <v/>
+      </c>
+      <c r="M203" t="str">
+        <v/>
+      </c>
+      <c r="N203" t="str">
+        <v/>
+      </c>
+      <c r="O203" t="str">
+        <v/>
+      </c>
+      <c r="P203" t="str">
+        <v/>
+      </c>
+      <c r="Q203" t="str">
+        <v/>
+      </c>
+      <c r="R203" t="str">
+        <v/>
+      </c>
+      <c r="S203" t="str">
+        <v/>
+      </c>
+      <c r="T203" t="str">
+        <v/>
+      </c>
+      <c r="U203" t="str">
+        <v/>
+      </c>
+      <c r="V203" t="str">
+        <v/>
+      </c>
+      <c r="W203" t="str">
+        <v/>
+      </c>
+      <c r="X203" t="str">
+        <v/>
+      </c>
+      <c r="Y203" t="str">
+        <v/>
+      </c>
+      <c r="Z203" t="str">
+        <v/>
+      </c>
+      <c r="AA203" t="str">
+        <v/>
+      </c>
+      <c r="AB203" t="str">
+        <v/>
+      </c>
+      <c r="AC203" t="str">
+        <v/>
+      </c>
+      <c r="AD203" t="str">
+        <v/>
+      </c>
+      <c r="AE203" t="str">
+        <v/>
+      </c>
+      <c r="AF203" t="str">
+        <v/>
+      </c>
+      <c r="AG203" t="str">
+        <v/>
+      </c>
+      <c r="AH203" t="str">
+        <v/>
+      </c>
+      <c r="AI203" t="str">
+        <v/>
+      </c>
+      <c r="AJ203" t="str">
+        <v/>
+      </c>
+      <c r="AK203" t="str">
+        <v/>
+      </c>
+      <c r="AL203" t="str">
+        <v/>
+      </c>
+      <c r="AM203" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+      </c>
+      <c r="B204" t="str">
+        <v>2025-09-21</v>
+      </c>
+      <c r="C204" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
+      </c>
+      <c r="D204" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E204" t="str">
+        <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
+      </c>
+      <c r="F204" t="str">
+        <v/>
+      </c>
+      <c r="G204" t="str">
+        <v/>
+      </c>
+      <c r="H204" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I204" t="str">
+        <v/>
+      </c>
+      <c r="J204" t="str">
+        <v/>
+      </c>
+      <c r="K204" t="str">
+        <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
+      </c>
+      <c r="L204" t="str">
+        <v/>
+      </c>
+      <c r="M204" t="str">
+        <v/>
+      </c>
+      <c r="N204" t="str">
+        <v/>
+      </c>
+      <c r="O204" t="str">
+        <v/>
+      </c>
+      <c r="P204" t="str">
+        <v/>
+      </c>
+      <c r="Q204" t="str">
+        <v/>
+      </c>
+      <c r="R204" t="str">
+        <v/>
+      </c>
+      <c r="S204" t="str">
+        <v/>
+      </c>
+      <c r="T204" t="str">
+        <v/>
+      </c>
+      <c r="U204" t="str">
+        <v/>
+      </c>
+      <c r="V204" t="str">
+        <v/>
+      </c>
+      <c r="W204" t="str">
+        <v/>
+      </c>
+      <c r="X204" t="str">
+        <v/>
+      </c>
+      <c r="Y204" t="str">
+        <v/>
+      </c>
+      <c r="Z204" t="str">
+        <v/>
+      </c>
+      <c r="AA204" t="str">
+        <v/>
+      </c>
+      <c r="AB204" t="str">
+        <v/>
+      </c>
+      <c r="AC204" t="str">
+        <v/>
+      </c>
+      <c r="AD204" t="str">
+        <v/>
+      </c>
+      <c r="AE204" t="str">
+        <v/>
+      </c>
+      <c r="AF204" t="str">
+        <v/>
+      </c>
+      <c r="AG204" t="str">
+        <v/>
+      </c>
+      <c r="AH204" t="str">
+        <v/>
+      </c>
+      <c r="AI204" t="str">
+        <v/>
+      </c>
+      <c r="AJ204" t="str">
+        <v/>
+      </c>
+      <c r="AK204" t="str">
+        <v/>
+      </c>
+      <c r="AL204" t="str">
+        <v/>
+      </c>
+      <c r="AM204" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>סוויד Antidepressants</v>
+      </c>
+      <c r="B205" t="str">
+        <v>2025-09-12</v>
+      </c>
+      <c r="C205" t="str">
+        <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
+      </c>
+      <c r="D205" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E205" t="str">
+        <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
+      </c>
+      <c r="F205" t="str">
+        <v/>
+      </c>
+      <c r="G205" t="str">
+        <v/>
+      </c>
+      <c r="H205" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I205" t="str">
+        <v/>
+      </c>
+      <c r="J205" t="str">
+        <v/>
+      </c>
+      <c r="K205" t="str">
+        <v>סוויד Antidepressants</v>
+      </c>
+      <c r="L205" t="str">
+        <v/>
+      </c>
+      <c r="M205" t="str">
+        <v/>
+      </c>
+      <c r="N205" t="str">
+        <v/>
+      </c>
+      <c r="O205" t="str">
+        <v/>
+      </c>
+      <c r="P205" t="str">
+        <v/>
+      </c>
+      <c r="Q205" t="str">
+        <v/>
+      </c>
+      <c r="R205" t="str">
+        <v/>
+      </c>
+      <c r="S205" t="str">
+        <v/>
+      </c>
+      <c r="T205" t="str">
+        <v/>
+      </c>
+      <c r="U205" t="str">
+        <v/>
+      </c>
+      <c r="V205" t="str">
+        <v/>
+      </c>
+      <c r="W205" t="str">
+        <v/>
+      </c>
+      <c r="X205" t="str">
+        <v/>
+      </c>
+      <c r="Y205" t="str">
+        <v/>
+      </c>
+      <c r="Z205" t="str">
+        <v/>
+      </c>
+      <c r="AA205" t="str">
+        <v/>
+      </c>
+      <c r="AB205" t="str">
+        <v/>
+      </c>
+      <c r="AC205" t="str">
+        <v/>
+      </c>
+      <c r="AD205" t="str">
+        <v/>
+      </c>
+      <c r="AE205" t="str">
+        <v/>
+      </c>
+      <c r="AF205" t="str">
+        <v/>
+      </c>
+      <c r="AG205" t="str">
+        <v/>
+      </c>
+      <c r="AH205" t="str">
+        <v/>
+      </c>
+      <c r="AI205" t="str">
+        <v/>
+      </c>
+      <c r="AJ205" t="str">
+        <v/>
+      </c>
+      <c r="AK205" t="str">
+        <v/>
+      </c>
+      <c r="AL205" t="str">
+        <v/>
+      </c>
+      <c r="AM205" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>וולף אליס The Clearing</v>
+      </c>
+      <c r="B206" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="C206" t="str">
+        <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
+      </c>
+      <c r="D206" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E206" t="str">
+        <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
+      </c>
+      <c r="F206" t="str">
+        <v/>
+      </c>
+      <c r="G206" t="str">
+        <v/>
+      </c>
+      <c r="H206" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I206" t="str">
+        <v/>
+      </c>
+      <c r="J206" t="str">
+        <v/>
+      </c>
+      <c r="K206" t="str">
+        <v>וולף אליס The Clearing</v>
+      </c>
+      <c r="L206" t="str">
+        <v/>
+      </c>
+      <c r="M206" t="str">
+        <v/>
+      </c>
+      <c r="N206" t="str">
+        <v/>
+      </c>
+      <c r="O206" t="str">
+        <v/>
+      </c>
+      <c r="P206" t="str">
+        <v/>
+      </c>
+      <c r="Q206" t="str">
+        <v/>
+      </c>
+      <c r="R206" t="str">
+        <v/>
+      </c>
+      <c r="S206" t="str">
+        <v/>
+      </c>
+      <c r="T206" t="str">
+        <v/>
+      </c>
+      <c r="U206" t="str">
+        <v/>
+      </c>
+      <c r="V206" t="str">
+        <v/>
+      </c>
+      <c r="W206" t="str">
+        <v/>
+      </c>
+      <c r="X206" t="str">
+        <v/>
+      </c>
+      <c r="Y206" t="str">
+        <v/>
+      </c>
+      <c r="Z206" t="str">
+        <v/>
+      </c>
+      <c r="AA206" t="str">
+        <v/>
+      </c>
+      <c r="AB206" t="str">
+        <v/>
+      </c>
+      <c r="AC206" t="str">
+        <v/>
+      </c>
+      <c r="AD206" t="str">
+        <v/>
+      </c>
+      <c r="AE206" t="str">
+        <v/>
+      </c>
+      <c r="AF206" t="str">
+        <v/>
+      </c>
+      <c r="AG206" t="str">
+        <v/>
+      </c>
+      <c r="AH206" t="str">
+        <v/>
+      </c>
+      <c r="AI206" t="str">
+        <v/>
+      </c>
+      <c r="AJ206" t="str">
+        <v/>
+      </c>
+      <c r="AK206" t="str">
+        <v/>
+      </c>
+      <c r="AL206" t="str">
+        <v/>
+      </c>
+      <c r="AM206" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+      </c>
+      <c r="B207" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="C207" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
+      </c>
+      <c r="D207" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E207" t="str">
+        <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
+      </c>
+      <c r="F207" t="str">
+        <v/>
+      </c>
+      <c r="G207" t="str">
+        <v/>
+      </c>
+      <c r="H207" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I207" t="str">
+        <v/>
+      </c>
+      <c r="J207" t="str">
+        <v/>
+      </c>
+      <c r="K207" t="str">
+        <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
+      </c>
+      <c r="L207" t="str">
+        <v/>
+      </c>
+      <c r="M207" t="str">
+        <v/>
+      </c>
+      <c r="N207" t="str">
+        <v/>
+      </c>
+      <c r="O207" t="str">
+        <v/>
+      </c>
+      <c r="P207" t="str">
+        <v/>
+      </c>
+      <c r="Q207" t="str">
+        <v/>
+      </c>
+      <c r="R207" t="str">
+        <v/>
+      </c>
+      <c r="S207" t="str">
+        <v/>
+      </c>
+      <c r="T207" t="str">
+        <v/>
+      </c>
+      <c r="U207" t="str">
+        <v/>
+      </c>
+      <c r="V207" t="str">
+        <v/>
+      </c>
+      <c r="W207" t="str">
+        <v/>
+      </c>
+      <c r="X207" t="str">
+        <v/>
+      </c>
+      <c r="Y207" t="str">
+        <v/>
+      </c>
+      <c r="Z207" t="str">
+        <v/>
+      </c>
+      <c r="AA207" t="str">
+        <v/>
+      </c>
+      <c r="AB207" t="str">
+        <v/>
+      </c>
+      <c r="AC207" t="str">
+        <v/>
+      </c>
+      <c r="AD207" t="str">
+        <v/>
+      </c>
+      <c r="AE207" t="str">
+        <v/>
+      </c>
+      <c r="AF207" t="str">
+        <v/>
+      </c>
+      <c r="AG207" t="str">
+        <v/>
+      </c>
+      <c r="AH207" t="str">
+        <v/>
+      </c>
+      <c r="AI207" t="str">
+        <v/>
+      </c>
+      <c r="AJ207" t="str">
+        <v/>
+      </c>
+      <c r="AK207" t="str">
+        <v/>
+      </c>
+      <c r="AL207" t="str">
+        <v/>
+      </c>
+      <c r="AM207" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+      </c>
+      <c r="B208" t="str">
+        <v>2025-08-24</v>
+      </c>
+      <c r="C208" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
+      </c>
+      <c r="D208" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E208" t="str">
+        <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
+      </c>
+      <c r="F208" t="str">
+        <v/>
+      </c>
+      <c r="G208" t="str">
+        <v/>
+      </c>
+      <c r="H208" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I208" t="str">
+        <v/>
+      </c>
+      <c r="J208" t="str">
+        <v/>
+      </c>
+      <c r="K208" t="str">
+        <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
+      </c>
+      <c r="L208" t="str">
+        <v/>
+      </c>
+      <c r="M208" t="str">
+        <v/>
+      </c>
+      <c r="N208" t="str">
+        <v/>
+      </c>
+      <c r="O208" t="str">
+        <v/>
+      </c>
+      <c r="P208" t="str">
+        <v/>
+      </c>
+      <c r="Q208" t="str">
+        <v/>
+      </c>
+      <c r="R208" t="str">
+        <v/>
+      </c>
+      <c r="S208" t="str">
+        <v/>
+      </c>
+      <c r="T208" t="str">
+        <v/>
+      </c>
+      <c r="U208" t="str">
+        <v/>
+      </c>
+      <c r="V208" t="str">
+        <v/>
+      </c>
+      <c r="W208" t="str">
+        <v/>
+      </c>
+      <c r="X208" t="str">
+        <v/>
+      </c>
+      <c r="Y208" t="str">
+        <v/>
+      </c>
+      <c r="Z208" t="str">
+        <v/>
+      </c>
+      <c r="AA208" t="str">
+        <v/>
+      </c>
+      <c r="AB208" t="str">
+        <v/>
+      </c>
+      <c r="AC208" t="str">
+        <v/>
+      </c>
+      <c r="AD208" t="str">
+        <v/>
+      </c>
+      <c r="AE208" t="str">
+        <v/>
+      </c>
+      <c r="AF208" t="str">
+        <v/>
+      </c>
+      <c r="AG208" t="str">
+        <v/>
+      </c>
+      <c r="AH208" t="str">
+        <v/>
+      </c>
+      <c r="AI208" t="str">
+        <v/>
+      </c>
+      <c r="AJ208" t="str">
+        <v/>
+      </c>
+      <c r="AK208" t="str">
+        <v/>
+      </c>
+      <c r="AL208" t="str">
+        <v/>
+      </c>
+      <c r="AM208" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+      </c>
+      <c r="B209" t="str">
+        <v>2025-08-21</v>
+      </c>
+      <c r="C209" t="str">
+        <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
+      </c>
+      <c r="D209" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E209" t="str">
+        <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
+      </c>
+      <c r="F209" t="str">
+        <v/>
+      </c>
+      <c r="G209" t="str">
+        <v/>
+      </c>
+      <c r="H209" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I209" t="str">
+        <v/>
+      </c>
+      <c r="J209" t="str">
+        <v/>
+      </c>
+      <c r="K209" t="str">
+        <v>טיילר דה קריאייטור Don't Tap The Glass</v>
+      </c>
+      <c r="L209" t="str">
+        <v/>
+      </c>
+      <c r="M209" t="str">
+        <v/>
+      </c>
+      <c r="N209" t="str">
+        <v/>
+      </c>
+      <c r="O209" t="str">
+        <v/>
+      </c>
+      <c r="P209" t="str">
+        <v/>
+      </c>
+      <c r="Q209" t="str">
+        <v/>
+      </c>
+      <c r="R209" t="str">
+        <v/>
+      </c>
+      <c r="S209" t="str">
+        <v/>
+      </c>
+      <c r="T209" t="str">
+        <v/>
+      </c>
+      <c r="U209" t="str">
+        <v/>
+      </c>
+      <c r="V209" t="str">
+        <v/>
+      </c>
+      <c r="W209" t="str">
+        <v/>
+      </c>
+      <c r="X209" t="str">
+        <v/>
+      </c>
+      <c r="Y209" t="str">
+        <v/>
+      </c>
+      <c r="Z209" t="str">
+        <v/>
+      </c>
+      <c r="AA209" t="str">
+        <v/>
+      </c>
+      <c r="AB209" t="str">
+        <v/>
+      </c>
+      <c r="AC209" t="str">
+        <v/>
+      </c>
+      <c r="AD209" t="str">
+        <v/>
+      </c>
+      <c r="AE209" t="str">
+        <v/>
+      </c>
+      <c r="AF209" t="str">
+        <v/>
+      </c>
+      <c r="AG209" t="str">
+        <v/>
+      </c>
+      <c r="AH209" t="str">
+        <v/>
+      </c>
+      <c r="AI209" t="str">
+        <v/>
+      </c>
+      <c r="AJ209" t="str">
+        <v/>
+      </c>
+      <c r="AK209" t="str">
+        <v/>
+      </c>
+      <c r="AL209" t="str">
+        <v/>
+      </c>
+      <c r="AM209" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>אברהם טל – חי</v>
+      </c>
+      <c r="B210" t="str">
+        <v>2025-08-17</v>
+      </c>
+      <c r="C210" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
+      </c>
+      <c r="D210" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E210" t="str">
+        <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
+      </c>
+      <c r="F210" t="str">
+        <v/>
+      </c>
+      <c r="G210" t="str">
+        <v/>
+      </c>
+      <c r="H210" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I210" t="str">
+        <v/>
+      </c>
+      <c r="J210" t="str">
+        <v/>
+      </c>
+      <c r="K210" t="str">
+        <v>אברהם טל – חי</v>
+      </c>
+      <c r="L210" t="str">
+        <v/>
+      </c>
+      <c r="M210" t="str">
+        <v/>
+      </c>
+      <c r="N210" t="str">
+        <v/>
+      </c>
+      <c r="O210" t="str">
+        <v/>
+      </c>
+      <c r="P210" t="str">
+        <v/>
+      </c>
+      <c r="Q210" t="str">
+        <v/>
+      </c>
+      <c r="R210" t="str">
+        <v/>
+      </c>
+      <c r="S210" t="str">
+        <v/>
+      </c>
+      <c r="T210" t="str">
+        <v/>
+      </c>
+      <c r="U210" t="str">
+        <v/>
+      </c>
+      <c r="V210" t="str">
+        <v/>
+      </c>
+      <c r="W210" t="str">
+        <v/>
+      </c>
+      <c r="X210" t="str">
+        <v/>
+      </c>
+      <c r="Y210" t="str">
+        <v/>
+      </c>
+      <c r="Z210" t="str">
+        <v/>
+      </c>
+      <c r="AA210" t="str">
+        <v/>
+      </c>
+      <c r="AB210" t="str">
+        <v/>
+      </c>
+      <c r="AC210" t="str">
+        <v/>
+      </c>
+      <c r="AD210" t="str">
+        <v/>
+      </c>
+      <c r="AE210" t="str">
+        <v/>
+      </c>
+      <c r="AF210" t="str">
+        <v/>
+      </c>
+      <c r="AG210" t="str">
+        <v/>
+      </c>
+      <c r="AH210" t="str">
+        <v/>
+      </c>
+      <c r="AI210" t="str">
+        <v/>
+      </c>
+      <c r="AJ210" t="str">
+        <v/>
+      </c>
+      <c r="AK210" t="str">
+        <v/>
+      </c>
+      <c r="AL210" t="str">
+        <v/>
+      </c>
+      <c r="AM210" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>רנה ראפ Bite Me</v>
+      </c>
+      <c r="B211" t="str">
+        <v>2025-08-12</v>
+      </c>
+      <c r="C211" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%a0%d7%94-%d7%a8%d7%90%d7%a4-bite-me/</v>
+      </c>
+      <c r="D211" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E211" t="str">
+        <v>אלבום האולפן השני של רנה ראפ, "BITE Me" עוסק בכאוטי והבטוח שבהוויה האישית, בלהיות אותנטי, ללא התנצלות. זהו אלבום על קבלה עצמית בצורתה האמיתית ביותר, וכמו ראפ עצמה, יוצר קרקע לביטוי עצמי לא מסונן. האלבום משלב סגנונות של פופ, R&amp;B,</v>
+      </c>
+      <c r="F211" t="str">
+        <v/>
+      </c>
+      <c r="G211" t="str">
+        <v/>
+      </c>
+      <c r="H211" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I211" t="str">
+        <v/>
+      </c>
+      <c r="J211" t="str">
+        <v/>
+      </c>
+      <c r="K211" t="str">
+        <v>רנה ראפ Bite Me</v>
+      </c>
+      <c r="L211" t="str">
+        <v/>
+      </c>
+      <c r="M211" t="str">
+        <v/>
+      </c>
+      <c r="N211" t="str">
+        <v/>
+      </c>
+      <c r="O211" t="str">
+        <v/>
+      </c>
+      <c r="P211" t="str">
+        <v/>
+      </c>
+      <c r="Q211" t="str">
+        <v/>
+      </c>
+      <c r="R211" t="str">
+        <v/>
+      </c>
+      <c r="S211" t="str">
+        <v/>
+      </c>
+      <c r="T211" t="str">
+        <v/>
+      </c>
+      <c r="U211" t="str">
+        <v/>
+      </c>
+      <c r="V211" t="str">
+        <v/>
+      </c>
+      <c r="W211" t="str">
+        <v/>
+      </c>
+      <c r="X211" t="str">
+        <v/>
+      </c>
+      <c r="Y211" t="str">
+        <v/>
+      </c>
+      <c r="Z211" t="str">
+        <v/>
+      </c>
+      <c r="AA211" t="str">
+        <v/>
+      </c>
+      <c r="AB211" t="str">
+        <v/>
+      </c>
+      <c r="AC211" t="str">
+        <v/>
+      </c>
+      <c r="AD211" t="str">
+        <v/>
+      </c>
+      <c r="AE211" t="str">
+        <v/>
+      </c>
+      <c r="AF211" t="str">
+        <v/>
+      </c>
+      <c r="AG211" t="str">
+        <v/>
+      </c>
+      <c r="AH211" t="str">
+        <v/>
+      </c>
+      <c r="AI211" t="str">
+        <v/>
+      </c>
+      <c r="AJ211" t="str">
+        <v/>
+      </c>
+      <c r="AK211" t="str">
+        <v/>
+      </c>
+      <c r="AL211" t="str">
+        <v/>
+      </c>
+      <c r="AM211" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>The K's – Pretty On The Internet</v>
+      </c>
+      <c r="B212" t="str">
+        <v>2025-08-03</v>
+      </c>
+      <c r="C212" t="str">
+        <v>https://yosmusic.com/the-ks-pretty-on-the-internet/</v>
+      </c>
+      <c r="D212" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E212" t="str">
+        <v>אלבום האולפן השני של להקת The K's מגיע בעקבות הצלחתו של אלבום הבכורה "I Wonder If The World Knows?", שהגיע למקום השלישי במצעד האלבומים הרשמי של בריטניה. האלבוםהופק על ידי זוכה פרס גרמי Jim Lowe, מציג את ההתפתחות של The</v>
+      </c>
+      <c r="F212" t="str">
+        <v/>
+      </c>
+      <c r="G212" t="str">
+        <v/>
+      </c>
+      <c r="H212" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="I212" t="str">
+        <v/>
+      </c>
+      <c r="J212" t="str">
+        <v/>
+      </c>
+      <c r="K212" t="str">
+        <v>The K's – Pretty On The Internet</v>
+      </c>
+      <c r="L212" t="str">
+        <v/>
+      </c>
+      <c r="M212" t="str">
+        <v/>
+      </c>
+      <c r="N212" t="str">
+        <v/>
+      </c>
+      <c r="O212" t="str">
+        <v/>
+      </c>
+      <c r="P212" t="str">
+        <v/>
+      </c>
+      <c r="Q212" t="str">
+        <v/>
+      </c>
+      <c r="R212" t="str">
+        <v/>
+      </c>
+      <c r="S212" t="str">
+        <v/>
+      </c>
+      <c r="T212" t="str">
+        <v/>
+      </c>
+      <c r="U212" t="str">
+        <v/>
+      </c>
+      <c r="V212" t="str">
+        <v/>
+      </c>
+      <c r="W212" t="str">
+        <v/>
+      </c>
+      <c r="X212" t="str">
+        <v/>
+      </c>
+      <c r="Y212" t="str">
+        <v/>
+      </c>
+      <c r="Z212" t="str">
+        <v/>
+      </c>
+      <c r="AA212" t="str">
+        <v/>
+      </c>
+      <c r="AB212" t="str">
+        <v/>
+      </c>
+      <c r="AC212" t="str">
+        <v/>
+      </c>
+      <c r="AD212" t="str">
+        <v/>
+      </c>
+      <c r="AE212" t="str">
+        <v/>
+      </c>
+      <c r="AF212" t="str">
+        <v/>
+      </c>
+      <c r="AG212" t="str">
+        <v/>
+      </c>
+      <c r="AH212" t="str">
+        <v/>
+      </c>
+      <c r="AI212" t="str">
+        <v/>
+      </c>
+      <c r="AJ212" t="str">
+        <v/>
+      </c>
+      <c r="AK212" t="str">
+        <v/>
+      </c>
+      <c r="AL212" t="str">
+        <v/>
+      </c>
+      <c r="AM212" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AI182"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AM212"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -413,7 +413,7 @@
         <v>תאריך סריקה</v>
       </c>
       <c r="E1" t="str">
-        <v>תיאור</v>
+        <v>שעה</v>
       </c>
       <c r="F1" t="str">
         <v>משך</v>
@@ -448,24 +448,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
         <v>רובי וויליאמס הודה בכנות שהוא מעכב את יציאת האלבום בגלל שאינו רוצה להתחרות ב־The Life of a Showgirl של טיילור סוויפט. כעת האלבום הופיע לפתע, ללא הסבר, שבועיים בלבד לתוך ינואר, ככל הנראה משום שלוויליאמס יהיו פחות מתחרים במצעד האלבומים</v>
       </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
       </c>
       <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
         <v>רובי ויליאמס Britpop</v>
       </c>
     </row>
@@ -483,24 +486,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
         <v>את ההופעה הזו קיבלתי ביוטיוב (*), שיטה יעילה למי שנפשו לא חשקה לשרך דרכו למועדונים בלילות הקרים. הוידיאו נשלח לרגל יציאת אלבומו "תור זהבי", ששיר הנושא הוא ראפ עצבני בניחוח מזרחי, שיר אגו ביקורתי, אירוני ומודע לעצמו מלא בדאחקות, הגזמות,</v>
       </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J3" t="str">
         <v/>
       </c>
       <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
         <v>עוז זהבי תור זהבי</v>
       </c>
     </row>
@@ -518,24 +524,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
         <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
       </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J4" t="str">
         <v/>
       </c>
       <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
         <v>פטריק סבג Hotel Mogador</v>
       </c>
     </row>
@@ -553,24 +562,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
         <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
       </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J5" t="str">
         <v/>
       </c>
       <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
         <v>מארינה מקסימיליאן – ריק בחלל</v>
       </c>
     </row>
@@ -588,24 +600,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
         <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
       </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J6" t="str">
         <v/>
       </c>
       <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
         <v>אוליביה דין The Art of Loving</v>
       </c>
     </row>
@@ -623,24 +638,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
         <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
       </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J7" t="str">
         <v/>
       </c>
       <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
         <v>Geese Getting Killed</v>
       </c>
     </row>
@@ -658,24 +676,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
         <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
       </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J8" t="str">
         <v/>
       </c>
       <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
         <v>רוסליה Lux</v>
       </c>
     </row>
@@ -693,24 +714,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
         <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
       </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J9" t="str">
         <v/>
       </c>
       <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
         <v>יאנגבלאד אירוסמית' one more time</v>
       </c>
     </row>
@@ -728,24 +752,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
         <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
       </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J10" t="str">
         <v/>
       </c>
       <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
         <v>פינק פלויד Wish You Were Here 50</v>
       </c>
     </row>
@@ -763,24 +790,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
         <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
       </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I11" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J11" t="str">
         <v/>
       </c>
       <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
         <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
       </c>
     </row>
@@ -798,24 +828,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
         <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
       </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I12" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J12" t="str">
         <v/>
       </c>
       <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
         <v>סטריי קידס DO IT (EP)</v>
       </c>
     </row>
@@ -833,24 +866,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
         <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
       </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I13" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J13" t="str">
         <v/>
       </c>
       <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
         <v>דויד ברוזה BROZAJAZZ</v>
       </c>
     </row>
@@ -868,24 +904,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
         <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
       </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I14" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J14" t="str">
         <v/>
       </c>
       <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
         <v>Five Seconds of Summer – Everyone's A Star</v>
       </c>
     </row>
@@ -903,24 +942,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
         <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
       </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I15" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J15" t="str">
         <v/>
       </c>
       <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
         <v>התקווה 6 – ויהי אור</v>
       </c>
     </row>
@@ -938,24 +980,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
         <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
       </c>
-      <c r="F16" t="str">
-        <v/>
-      </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I16" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J16" t="str">
         <v/>
       </c>
       <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
         <v>פלורנס אנד דה משין Everybody Scream</v>
       </c>
     </row>
@@ -973,24 +1018,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
         <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
       </c>
-      <c r="F17" t="str">
-        <v/>
-      </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I17" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J17" t="str">
         <v/>
       </c>
       <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
         <v>טיים אימפלה Deadbeat</v>
       </c>
     </row>
@@ -1008,24 +1056,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
         <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
       </c>
-      <c r="F18" t="str">
-        <v/>
-      </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I18" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J18" t="str">
         <v/>
       </c>
       <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
         <v>דייוויד גילמור The Luck and Strange Concerts</v>
       </c>
     </row>
@@ -1043,24 +1094,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
         <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
       </c>
-      <c r="F19" t="str">
-        <v/>
-      </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I19" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J19" t="str">
         <v/>
       </c>
       <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
         <v>שלמה גרוניך – תודה אהבה</v>
       </c>
     </row>
@@ -1078,24 +1132,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
         <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
       </c>
-      <c r="F20" t="str">
-        <v/>
-      </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I20" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J20" t="str">
         <v/>
       </c>
       <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
         <v>טיילור סוויפט The Life Of A Showgirl</v>
       </c>
     </row>
@@ -1113,24 +1170,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
         <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
       </c>
-      <c r="F21" t="str">
-        <v/>
-      </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I21" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J21" t="str">
         <v/>
       </c>
       <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
         <v>דוג'ה קאט Vie</v>
       </c>
     </row>
@@ -1148,24 +1208,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
         <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
       </c>
-      <c r="F22" t="str">
-        <v/>
-      </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I22" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J22" t="str">
         <v/>
       </c>
       <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
         <v>ג'וי קרוקס Juniper</v>
       </c>
     </row>
@@ -1183,24 +1246,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
         <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
       </c>
-      <c r="F23" t="str">
-        <v/>
-      </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I23" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J23" t="str">
         <v/>
       </c>
       <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
         <v>ביפי קליירו Futique</v>
       </c>
     </row>
@@ -1218,24 +1284,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
         <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
       </c>
-      <c r="F24" t="str">
-        <v/>
-      </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I24" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J24" t="str">
         <v/>
       </c>
       <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
         <v>אד שירן Play</v>
       </c>
     </row>
@@ -1253,24 +1322,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
         <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
       </c>
-      <c r="F25" t="str">
-        <v/>
-      </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I25" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J25" t="str">
         <v/>
       </c>
       <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
         <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
       </c>
     </row>
@@ -1288,24 +1360,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
         <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
       </c>
-      <c r="F26" t="str">
-        <v/>
-      </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I26" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J26" t="str">
         <v/>
       </c>
       <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
         <v>סוויד Antidepressants</v>
       </c>
     </row>
@@ -1323,24 +1398,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
         <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
       </c>
-      <c r="F27" t="str">
-        <v/>
-      </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I27" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J27" t="str">
         <v/>
       </c>
       <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
         <v>וולף אליס The Clearing</v>
       </c>
     </row>
@@ -1358,24 +1436,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
         <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
       </c>
-      <c r="F28" t="str">
-        <v/>
-      </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I28" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J28" t="str">
         <v/>
       </c>
       <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
         <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
       </c>
     </row>
@@ -1393,24 +1474,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
         <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
       </c>
-      <c r="F29" t="str">
-        <v/>
-      </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I29" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J29" t="str">
         <v/>
       </c>
       <c r="K29" t="str">
+        <v/>
+      </c>
+      <c r="L29" t="str">
         <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
       </c>
     </row>
@@ -1428,24 +1512,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
         <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
       </c>
-      <c r="F30" t="str">
-        <v/>
-      </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I30" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J30" t="str">
         <v/>
       </c>
       <c r="K30" t="str">
+        <v/>
+      </c>
+      <c r="L30" t="str">
         <v>טיילר דה קריאייטור Don't Tap The Glass</v>
       </c>
     </row>
@@ -1463,30 +1550,33 @@
         <v>2026-01-22</v>
       </c>
       <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
         <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
       </c>
-      <c r="F31" t="str">
-        <v/>
-      </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I31" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J31" t="str">
         <v/>
       </c>
       <c r="K31" t="str">
+        <v/>
+      </c>
+      <c r="L31" t="str">
         <v>אברהם טל – חי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://yosmusic.com/%d7%a8%d7%95%d7%91%d7%99-%d7%95%d7%99%d7%9c%d7%99%d7%90%d7%9e%d7%a1-britpop/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://yosmusic.com/%d7%a2%d7%95%d7%96-%d7%96%d7%94%d7%91%d7%99-%d7%aa%d7%95%d7%a8-%d7%96%d7%94%d7%91%d7%99/</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://yosmusic.com/geese-getting-killed/</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E31" t="str">
         <v/>

--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://yosmusic.com/%d7%a8%d7%95%d7%91%d7%99-%d7%95%d7%99%d7%9c%d7%99%d7%90%d7%9e%d7%a1-britpop/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://yosmusic.com/%d7%a2%d7%95%d7%96-%d7%96%d7%94%d7%91%d7%99-%d7%aa%d7%95%d7%a8-%d7%96%d7%94%d7%91%d7%99/</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://yosmusic.com/geese-getting-killed/</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E31" t="str">
         <v/>

--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Wet Leg Moisturizer אלבום הרוק האלטרנטיבי של 2025</v>
+        <v>חנן בן ארי לא המשוגע היחידי</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-01-31</v>
+        <v>2026-02-01</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/wet-leg-moisturizer/</v>
+        <v>https://yosmusic.com/%d7%97%d7%a0%d7%9f-%d7%91%d7%9f-%d7%90%d7%a8%d7%99-%d7%9c%d7%90-%d7%94%d7%9e%d7%a9%d7%95%d7%92%d7%a2-%d7%94%d7%99%d7%97%d7%99%d7%93%d7%99/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-31</v>
+        <v>2026-02-01</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>להקת Wet Leg לא הוציאה קרם לחות (Moisturizer) כמוצר טיפוח. במקום זאת, "Moisturizer" הוא שמו של האלבום השני והחדש שלהם. במרכז –  צמד אינדי-רוק המורכב מהחברות ריין טיסדייל והסטר צ'יימברס. אלבום הבכורה הנושא את שמה, הגיע למקום הראשון במצעד האלבומים</v>
+        <v>חנן בן ארי לא מנסה להמציא את עצמו מחדש – אלא מעז להסיר שכבות. זהו אלבום שמעדיף אמת על פני פוזה, פגיעות על פני הצהרה, ושאלות פתוחות על פני תשובות מהודקות. בין תפילה להמנון, בין בלדת נשמה לפולק־רוק אמריקאי ובין</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Wet Leg Moisturizer אלבום הרוק האלטרנטיבי של 2025</v>
+        <v>חנן בן ארי לא המשוגע היחידי</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>חנן בן ארי לא המשוגע היחידי</v>
+        <v>לואיס טומלינסון How Did I Get Here</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-03</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%97%d7%a0%d7%9f-%d7%91%d7%9f-%d7%90%d7%a8%d7%99-%d7%9c%d7%90-%d7%94%d7%9e%d7%a9%d7%95%d7%92%d7%a2-%d7%94%d7%99%d7%97%d7%99%d7%93%d7%99/</v>
+        <v>https://yosmusic.com/%d7%9c%d7%95%d7%90%d7%99%d7%a1-%d7%98%d7%95%d7%9e%d7%9c%d7%99%d7%a0%d7%a1%d7%95%d7%9f-how-did-i-get-here/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>חנן בן ארי לא מנסה להמציא את עצמו מחדש – אלא מעז להסיר שכבות. זהו אלבום שמעדיף אמת על פני פוזה, פגיעות על פני הצהרה, ושאלות פתוחות על פני תשובות מהודקות. בין תפילה להמנון, בין בלדת נשמה לפולק־רוק אמריקאי ובין</v>
+        <v>מוזיקת פופ היא עניין דו־צדדי: מצד אחד, היא לא הייתה נקראת פופ אם לא הייתה מכוונת לקהל רחב ככל האפשר, ומצד שני – בשל המהות שלה והאופן שבו היא נוצרת – היא זוכה לא פעם ליחס ספקני מצד מבקרי מוזיקה.</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>חנן בן ארי לא המשוגע היחידי</v>
+        <v>לואיס טומלינסון How Did I Get Here</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>לואיס טומלינסון How Did I Get Here</v>
+        <v>ליידי גאגא MAYHEM אלבום הפופ הווקאלי הטוב ביותר בגראמי</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-07</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9c%d7%95%d7%90%d7%99%d7%a1-%d7%98%d7%95%d7%9e%d7%9c%d7%99%d7%a0%d7%a1%d7%95%d7%9f-how-did-i-get-here/</v>
+        <v>https://yosmusic.com/%d7%9c%d7%99%d7%99%d7%93%d7%99-%d7%92%d7%90%d7%92%d7%90-mayhem/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-07</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>מוזיקת פופ היא עניין דו־צדדי: מצד אחד, היא לא הייתה נקראת פופ אם לא הייתה מכוונת לקהל רחב ככל האפשר, ומצד שני – בשל המהות שלה והאופן שבו היא נוצרת – היא זוכה לא פעם ליחס ספקני מצד מבקרי מוזיקה.</v>
+        <v>כשליידי גאגא הכריזה לראשונה על 'Mayhem' בינואר, היא אמרה שזה "התחיל כשהתמודדתי עם הפחד שלי לחזור למוזיקת ​​הפופ שהמעריצים הראשונים שלי אהבו". היא לא ממש ניסתה לשחזר את הצליל של 2008 אבל גאגא התחברה לאזוור הרגשי הזה מחדש. "פנטום רחבת</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>לואיס טומלינסון How Did I Get Here</v>
+        <v>ליידי גאגא MAYHEM אלבום הפופ הווקאלי הטוב ביותר בגראמי</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ליידי גאגא MAYHEM אלבום הפופ הווקאלי הטוב ביותר בגראמי</v>
+        <v>NEVER ENOUGH של טרנסטייל הוכתר כאלבום הרוק הטוב ביותר בגראמי</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-07</v>
+        <v>2026-02-09</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9c%d7%99%d7%99%d7%93%d7%99-%d7%92%d7%90%d7%92%d7%90-mayhem/</v>
+        <v>https://yosmusic.com/never-enough-%d7%a9%d7%9c-%d7%98%d7%a8%d7%a0%d7%a1%d7%98%d7%99%d7%99%d7%9c-%d7%94%d7%95%d7%9b%d7%aa%d7%a8-%d7%9b%d7%90%d7%9c%d7%91%d7%95%d7%9d-%d7%94%d7%a8%d7%95%d7%a7-%d7%94%d7%98%d7%95%d7%91-%d7%91/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-07</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>כשליידי גאגא הכריזה לראשונה על 'Mayhem' בינואר, היא אמרה שזה "התחיל כשהתמודדתי עם הפחד שלי לחזור למוזיקת ​​הפופ שהמעריצים הראשונים שלי אהבו". היא לא ממש ניסתה לשחזר את הצליל של 2008 אבל גאגא התחברה לאזוור הרגשי הזה מחדש. "פנטום רחבת</v>
+        <v>האלבום רחב היריעה הוא התפתחות חסרת מנוחה ומלהיבה של הצליל שובר־הז’אנרים של הלהקה. זהו מסע טרנספורמטיבי – חסר פחד ומלא חיים – של אחת הלהקות החדשניות והמשפיעות ביותר בדור שלה. טרנסטייל (Turnstile) מגיעים מהארדקור של בולטימור, אבל ב־NEVER ENOUGH הם</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ליידי גאגא MAYHEM אלבום הפופ הווקאלי הטוב ביותר בגראמי</v>
+        <v>NEVER ENOUGH של טרנסטייל הוכתר כאלבום הרוק הטוב ביותר בגראמי</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>NEVER ENOUGH של טרנסטייל הוכתר כאלבום הרוק הטוב ביותר בגראמי</v>
+        <v>עברי לידר – אין לך מילה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-11</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/never-enough-%d7%a9%d7%9c-%d7%98%d7%a8%d7%a0%d7%a1%d7%98%d7%99%d7%99%d7%9c-%d7%94%d7%95%d7%9b%d7%aa%d7%a8-%d7%9b%d7%90%d7%9c%d7%91%d7%95%d7%9d-%d7%94%d7%a8%d7%95%d7%a7-%d7%94%d7%98%d7%95%d7%91-%d7%91/</v>
+        <v>https://yosmusic.com/%d7%a2%d7%91%d7%a8%d7%99-%d7%9c%d7%99%d7%93%d7%a8-%d7%90%d7%99%d7%9f-%d7%9c%d7%9a-%d7%9e%d7%99%d7%9c%d7%94/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>האלבום רחב היריעה הוא התפתחות חסרת מנוחה ומלהיבה של הצליל שובר־הז’אנרים של הלהקה. זהו מסע טרנספורמטיבי – חסר פחד ומלא חיים – של אחת הלהקות החדשניות והמשפיעות ביותר בדור שלה. טרנסטייל (Turnstile) מגיעים מהארדקור של בולטימור, אבל ב־NEVER ENOUGH הם</v>
+        <v>ה-EP "אין לך מילה" של עברי לידר הוא מהלך אמנותי חריג ומשמעותי בקריירה שלו – גם בגלל הוויתור על כתיבה אישית לטובת טל קסטיאל, וגם בגלל האימוץ המלא של קול נשי כנקודת מוצא רגשית. זה לא “רק” שינוי טקסטואלי –</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>NEVER ENOUGH של טרנסטייל הוכתר כאלבום הרוק הטוב ביותר בגראמי</v>
+        <v>עברי לידר – אין לך מילה</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>דודו טסה – אי</v>
+        <v>שלומי שבן חי בגימל בהיכל התרבות</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-20</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%93%d7%95-%d7%98%d7%a1%d7%94-%d7%90%d7%99/</v>
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%95%d7%9e%d7%99-%d7%a9%d7%91%d7%9f-%d7%97%d7%99-%d7%91%d7%92%d7%99%d7%9e%d7%9c-%d7%91%d7%94%d7%99%d7%9b%d7%9c-%d7%94%d7%aa%d7%a8%d7%91%d7%95%d7%aa/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>מי מוציא היום אלבום של 18 שירים? התשובה: דודו טסה. הוא עזב את הכאוס המקומי, יצא לאי ביוון עם עלמה זוהר ויונתן דסקל, והנה התוצאה. שווה היה להתנתק. הנה מה שהאי הוליד. שווה מאוד להקשיב. האלבום נפתח ב"עמנואל" – לא</v>
+        <v>יש סיבה לחזור להיכל התרבות הריק מאדם למפגשי הקורונה של שלומי שבן.  האלבום "חי בגימל בהיכל התרבות" של שלומי שבן שנולד בתקופת הסגרים בקורונה, הוא לא עוד פרויקט קאברים – הוא תיעוד של מצב תרבותי חריג: אין קהל, אין להקה,</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>דודו טסה – אי</v>
+        <v>שלומי שבן חי בגימל בהיכל התרבות</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שלומי שבן חי בגימל בהיכל התרבות</v>
+        <v>Wuthering Heights צ'רלי XCX</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-23</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%95%d7%9e%d7%99-%d7%a9%d7%91%d7%9f-%d7%97%d7%99-%d7%91%d7%92%d7%99%d7%9e%d7%9c-%d7%91%d7%94%d7%99%d7%9b%d7%9c-%d7%94%d7%aa%d7%a8%d7%91%d7%95%d7%aa/</v>
+        <v>https://yosmusic.com/wuthering-heights-%d7%a6%d7%a8%d7%9c%d7%99-xcx/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>יש סיבה לחזור להיכל התרבות הריק מאדם למפגשי הקורונה של שלומי שבן.  האלבום "חי בגימל בהיכל התרבות" של שלומי שבן שנולד בתקופת הסגרים בקורונה, הוא לא עוד פרויקט קאברים – הוא תיעוד של מצב תרבותי חריג: אין קהל, אין להקה,</v>
+        <v>Wuthering Heights הוא אלבום האולפן השביעי של צ'רלי XCX. האלבום נוצר כאלבום קונספט ופסקול נלווה לעיבוד הקולנועי של אמרלד פנל לרומן הקלאסי "אנקת גבהים" (מאת אמילי ברונטה), בכיכובם של מרגו רובי וג'ייקוב אלורד מדובר בשינוי כיוון דרסטי מבחינתה מעבר מאסתטיקה של פופ</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שלומי שבן חי בגימל בהיכל התרבות</v>
+        <v>Wuthering Heights צ'רלי XCX</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Wuthering Heights צ'רלי XCX</v>
+        <v>עומר אדם – חלק מהנצח</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-27</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/wuthering-heights-%d7%a6%d7%a8%d7%9c%d7%99-xcx/</v>
+        <v>https://yosmusic.com/%d7%a2%d7%95%d7%9e%d7%a8-%d7%90%d7%93%d7%9d-%d7%97%d7%9c%d7%a7-%d7%9e%d7%94%d7%a0%d7%a6%d7%97/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>Wuthering Heights הוא אלבום האולפן השביעי של צ'רלי XCX. האלבום נוצר כאלבום קונספט ופסקול נלווה לעיבוד הקולנועי של אמרלד פנל לרומן הקלאסי "אנקת גבהים" (מאת אמילי ברונטה), בכיכובם של מרגו רובי וג'ייקוב אלורד מדובר בשינוי כיוון דרסטי מבחינתה מעבר מאסתטיקה של פופ</v>
+        <v>"משפחה וכבוד" הפותח את אלבומו העשירי  של עומר אדם מציב הצהרה אמנותית: זו אינה רק בלדת אהבה, אלא בלדה על מחיר ההצלחה. השיר יושב על קו התפר שבין עולם חומרי נוצץ לבין נאמנות פנימית, בין אהבה הרסנית לבין ערכי יסוד.</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Wuthering Heights צ'רלי XCX</v>
+        <v>עומר אדם – חלק מהנצח</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עומר אדם – חלק מהנצח</v>
+        <v>ג'ייקוב אלון In Limerence</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-27</v>
+        <v>2026-03-03</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a2%d7%95%d7%9e%d7%a8-%d7%90%d7%93%d7%9d-%d7%97%d7%9c%d7%a7-%d7%9e%d7%94%d7%a0%d7%a6%d7%97/</v>
+        <v>https://yosmusic.com/%d7%92%d7%99%d7%99%d7%a7%d7%95%d7%91-%d7%90%d7%9c%d7%95%d7%9f-in-limerence/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-27</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"משפחה וכבוד" הפותח את אלבומו העשירי  של עומר אדם מציב הצהרה אמנותית: זו אינה רק בלדת אהבה, אלא בלדה על מחיר ההצלחה. השיר יושב על קו התפר שבין עולם חומרי נוצץ לבין נאמנות פנימית, בין אהבה הרסנית לבין ערכי יסוד.</v>
+        <v>מדי פעם מופיע קול חדש עם השילוב האלכימי של יופי שברירי ופואטיות – כזה שיש לו את הכוח לגרום לזמן להיראות כאילו עצר מלכת. זהו אותו קסם שהפך את עמודי התווך של המוזיקה האלטרנטיבית, ג׳ף באקלי ולורה מרלינג, למה שהם,</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עומר אדם – חלק מהנצח</v>
+        <v>ג'ייקוב אלון In Limerence</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ג'ייקוב אלון In Limerence</v>
+        <v>הארי סטיילס Kiss All The Time. Disco Occasionally</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-07</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%92%d7%99%d7%99%d7%a7%d7%95%d7%91-%d7%90%d7%9c%d7%95%d7%9f-in-limerence/</v>
+        <v>https://yosmusic.com/%d7%94%d7%90%d7%a8%d7%99-%d7%a1%d7%98%d7%99%d7%99%d7%9c%d7%a1-kiss-all-the-time-disco-occasionally/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>מדי פעם מופיע קול חדש עם השילוב האלכימי של יופי שברירי ופואטיות – כזה שיש לו את הכוח לגרום לזמן להיראות כאילו עצר מלכת. זהו אותו קסם שהפך את עמודי התווך של המוזיקה האלטרנטיבית, ג׳ף באקלי ולורה מרלינג, למה שהם,</v>
+        <v>מאז האלבום האחרון של הארי סטיילס, “Harry’s House” מ-2022, כוכב הפופ עשה כמה שינויים בחייו. האלבום ההוא יצא בתקופה של רכילות והשערות בלתי פוסקות סביב חייו האישיים, ובשנים שעברו מאז הוא ניסה להשיב לעצמו שליטה על הפרטיות שלו, כשהוא מנצל</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ג'ייקוב אלון In Limerence</v>
+        <v>הארי סטיילס Kiss All The Time. Disco Occasionally</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>הארי סטיילס Kiss All The Time. Disco Occasionally</v>
+        <v>יבבה Jean</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-07</v>
+        <v>2026-03-10</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%90%d7%a8%d7%99-%d7%a1%d7%98%d7%99%d7%99%d7%9c%d7%a1-kiss-all-the-time-disco-occasionally/</v>
+        <v>https://yosmusic.com/%d7%99%d7%91%d7%91%d7%94-jean/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-07</v>
+        <v>2026-03-10</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>מאז האלבום האחרון של הארי סטיילס, “Harry’s House” מ-2022, כוכב הפופ עשה כמה שינויים בחייו. האלבום ההוא יצא בתקופה של רכילות והשערות בלתי פוסקות סביב חייו האישיים, ובשנים שעברו מאז הוא ניסה להשיב לעצמו שליטה על הפרטיות שלו, כשהוא מנצל</v>
+        <v>זה אלבומה השני של יבבה (Yebba) הזמרת-יוצרת, ילידת ארקנסו המוכרת מהשיר הנפלא October Sky.  זהו  אוסף שירים בעל ניחוח פולקי עם השפעות גוספל – יצירה בוגרת יותר בסגנון פופ עכשווי שמגיעה אחרי אלבום הבכורה שלה Dawn. האלבום נקרא על שם</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>הארי סטיילס Kiss All The Time. Disco Occasionally</v>
+        <v>יבבה Jean</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יבבה Jean</v>
+        <v>גורילז The Mountain</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%91%d7%91%d7%94-jean/</v>
+        <v>https://yosmusic.com/%d7%92%d7%95%d7%a8%d7%99%d7%9c%d7%96-the-mountain/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>זה אלבומה השני של יבבה (Yebba) הזמרת-יוצרת, ילידת ארקנסו המוכרת מהשיר הנפלא October Sky.  זהו  אוסף שירים בעל ניחוח פולקי עם השפעות גוספל – יצירה בוגרת יותר בסגנון פופ עכשווי שמגיעה אחרי אלבום הבכורה שלה Dawn. האלבום נקרא על שם</v>
+        <v>בשלב מסוים במהלך השיר Orange County הבנתי שאני לא רק נהנה מהאלבום The Mountain, אלא שאני גם קצת המום מהייחוד שלו. לאורך 15 שירים מאזינים לתערובת מסחררת של מצבי רוח, סגנונות, תרבויות, שפות ותקופות The Mountain הוא אלבום האולפן התשיעי</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יבבה Jean</v>
+        <v>גורילז The Mountain</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>גורילז The Mountain</v>
+        <v>ג'יימס בלייק Trying Time</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-13</v>
+        <v>2026-03-18</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%92%d7%95%d7%a8%d7%99%d7%9c%d7%96-the-mountain/</v>
+        <v>https://yosmusic.com/%d7%92%d7%99%d7%99%d7%9e%d7%a1-%d7%91%d7%9c%d7%99%d7%99%d7%a7-trying-time/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-13</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>בשלב מסוים במהלך השיר Orange County הבנתי שאני לא רק נהנה מהאלבום The Mountain, אלא שאני גם קצת המום מהייחוד שלו. לאורך 15 שירים מאזינים לתערובת מסחררת של מצבי רוח, סגנונות, תרבויות, שפות ותקופות The Mountain הוא אלבום האולפן התשיעי</v>
+        <v>מבין כל הדברים שאפשר לצפות מאלבום של ג'יימס בלייק James Blake – מינימליזם מעודן, עיוותים ווקאליים מלאי כאב, ואורחים מעולם ההיפ-הופ מהשורה הראשונה – פרשנות סוציו־פוליטית מעמיקה היא כנראה לא אחד מהם. אבל כפי שמרמז השם, המצוקה הנוכחית שלנו היא</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>גורילז The Mountain</v>
+        <v>ג'יימס בלייק Trying Time</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ג'יימס בלייק Trying Time</v>
+        <v>הילה רוח – שחור זוהר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-25</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%92%d7%99%d7%99%d7%9e%d7%a1-%d7%91%d7%9c%d7%99%d7%99%d7%a7-trying-time/</v>
+        <v>https://yosmusic.com/%d7%94%d7%99%d7%9c%d7%94-%d7%a8%d7%95%d7%97-%d7%a9%d7%97%d7%95%d7%a8-%d7%96%d7%95%d7%94%d7%a8/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>מבין כל הדברים שאפשר לצפות מאלבום של ג'יימס בלייק James Blake – מינימליזם מעודן, עיוותים ווקאליים מלאי כאב, ואורחים מעולם ההיפ-הופ מהשורה הראשונה – פרשנות סוציו־פוליטית מעמיקה היא כנראה לא אחד מהם. אבל כפי שמרמז השם, המצוקה הנוכחית שלנו היא</v>
+        <v>"שחור זוהר" של הילה רוח הוא יצירה בת 15 שירים שמנסה להלך על קו עדין בין פופ נגיש לבין אמירה כמעט אוונגרדית.  זה לא אלבום שמבקש לרצות אלא  להטרי, לעורר, ולפעמים גם לבלבל. הסינגלים "טבע" ו־"זאת השנה" מתפקדים כשער כניסה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ג'יימס בלייק Trying Time</v>
+        <v>הילה רוח – שחור זוהר</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>הילה רוח – שחור זוהר</v>
+        <v>רובין Sexistential</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-28</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%99%d7%9c%d7%94-%d7%a8%d7%95%d7%97-%d7%a9%d7%97%d7%95%d7%a8-%d7%96%d7%95%d7%94%d7%a8/</v>
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%91%d7%99%d7%9f-sexistential/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"שחור זוהר" של הילה רוח הוא יצירה בת 15 שירים שמנסה להלך על קו עדין בין פופ נגיש לבין אמירה כמעט אוונגרדית.  זה לא אלבום שמבקש לרצות אלא  להטרי, לעורר, ולפעמים גם לבלבל. הסינגלים "טבע" ו־"זאת השנה" מתפקדים כשער כניסה</v>
+        <v>בקריירה שנמשכת כבר שני עשורים, רובין (Robyn), הזמרת השוודית, יצרה כמה מהלהיטים הבולטים בפופ – ובראשם “Dancing On My Own”, המנון נצחי ואיקוני על מציאת הדרך האישית מתוך שברון לב. אך באלבומה התשיעי “Sexistential”, אנו פוגשים אותה חסרת עוגן ותוהה,</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>הילה רוח – שחור זוהר</v>
+        <v>רובין Sexistential</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>BTS Arirang</v>
+        <v>ריי – This Music May Contain Hope</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-03</v>
+        <v>2026-04-07</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/bts-arirang/</v>
+        <v>https://yosmusic.com/%d7%a8%d7%99%d7%99-this-music-may-contain-hope/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-03</v>
+        <v>2026-04-07</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>האלבום Arirang של BTS (שיצא במרץ 2026) הפך בתוך שבועות ספורים לאחד התקליטים המבוקשים בעולם גם פיזית (ויניל/מהדורות אספנים) וגם סטרימינג, וזה לא במקרה. מדובר בשילוב נדיר של אירוע תרבותי, מהלך מוזיקלי מחושב, ורגע רגשי של קאמבק. בעיני המעריצים, זה</v>
+        <v>האלבום "This Music May Contain Hope" של  ריי RAYE הוא יצירה טעונה רגשית, שממשיכה את הקו האישי והחשוף שהיא ביססה מאז הפריצה העצמאית שלה. כבר בשם יש פרובוקציה עדינה: במקום אזהרה שלילית (“עלול להכיל תכנים קשים”), היא מציעה אפשרות הפוכה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>BTS Arirang</v>
+        <v>ריי – This Music May Contain Hope</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ריי – This Music May Contain Hope</v>
+        <v>מלאני מרטינז – Hades</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-07</v>
+        <v>2026-04-10</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%99%d7%99-this-music-may-contain-hope/</v>
+        <v>https://yosmusic.com/%d7%9e%d7%9c%d7%90%d7%a0%d7%99-%d7%9e%d7%a8%d7%98%d7%99%d7%a0%d7%96-hades/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-07</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>האלבום "This Music May Contain Hope" של  ריי RAYE הוא יצירה טעונה רגשית, שממשיכה את הקו האישי והחשוף שהיא ביססה מאז הפריצה העצמאית שלה. כבר בשם יש פרובוקציה עדינה: במקום אזהרה שלילית (“עלול להכיל תכנים קשים”), היא מציעה אפשרות הפוכה</v>
+        <v>מלאני מרטינז Melanie Martinez היא הכוכבת הכי לא־נלהבת מההצלחה גם אחרי שמילאה שני ערבים רצופים סולד אאוט באולם מדיסון סקוור גרדן. גם כשהיא עלתה לתהילה כנערה בתוכנית The Voice לפני יותר מעשור, והגיעה למעמד פלטינה עם האלבומים הראשונים שלה, היא</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ריי – This Music May Contain Hope</v>
+        <v>מלאני מרטינז – Hades</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מלאני מרטינז – Hades</v>
+        <v>פלי Honora</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-15</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%9c%d7%90%d7%a0%d7%99-%d7%9e%d7%a8%d7%98%d7%99%d7%a0%d7%96-hades/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%99-honora/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-15</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>מלאני מרטינז Melanie Martinez היא הכוכבת הכי לא־נלהבת מההצלחה גם אחרי שמילאה שני ערבים רצופים סולד אאוט באולם מדיסון סקוור גרדן. גם כשהיא עלתה לתהילה כנערה בתוכנית The Voice לפני יותר מעשור, והגיעה למעמד פלטינה עם האלבומים הראשונים שלה, היא</v>
+        <v>רד הוט צ'ילי פפרס מצליחים להמציא את עצמם מחדש? ממש לא! אבל פלי Flea ממש כן – כנגן חצוצרה ג׳אז, בעזרת מעט עזרה מתום יורק, ניק קייב וג׳ף פארקר. נראה כמעט בלתי אפשרי שנגן הבס הוורקוהוליק  אדם שהוציא מוזיקה חדשה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מלאני מרטינז – Hades</v>
+        <v>פלי Honora</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>פלי Honora</v>
+        <v>מייקל ג'קסון Songs From The Motion Picture</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-24</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%99-honora/</v>
+        <v>https://yosmusic.com/%d7%9e%d7%99%d7%99%d7%a7%d7%9c-%d7%92%d7%a7%d7%a1%d7%95%d7%9f-songs-from-the-motion-picture/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>רד הוט צ'ילי פפרס מצליחים להמציא את עצמם מחדש? ממש לא! אבל פלי Flea ממש כן – כנגן חצוצרה ג׳אז, בעזרת מעט עזרה מתום יורק, ניק קייב וג׳ף פארקר. נראה כמעט בלתי אפשרי שנגן הבס הוורקוהוליק  אדם שהוציא מוזיקה חדשה</v>
+        <v>האלבום Michael – Songs From The Motion Picture” (2026), שמלווה את הסרט הביוגרפי על מייקל ג'קסון, עומד בפני אתגר מורכב בהרבה מפסקול רגיל: הוא לא רק צריך לשרת סרט, אלא גם לייצג מורשת מוזיקלית מהגדולות בהיסטוריה. לכן הוא נע בין</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>פלי Honora</v>
+        <v>מייקל ג'קסון Songs From The Motion Picture</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מייקל ג'קסון Songs From The Motion Picture</v>
+        <v>ינון מועלם Aegina's Secret</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%99%d7%99%d7%a7%d7%9c-%d7%92%d7%a7%d7%a1%d7%95%d7%9f-songs-from-the-motion-picture/</v>
+        <v>https://yosmusic.com/%d7%99%d7%a0%d7%95%d7%9f-%d7%9e%d7%95%d7%a2%d7%9c%d7%9d-aeginas-secret/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>האלבום Michael – Songs From The Motion Picture” (2026), שמלווה את הסרט הביוגרפי על מייקל ג'קסון, עומד בפני אתגר מורכב בהרבה מפסקול רגיל: הוא לא רק צריך לשרת סרט, אלא גם לייצג מורשת מוזיקלית מהגדולות בהיסטוריה. לכן הוא נע בין</v>
+        <v>הרעיון ל־Aegina’s Secret נולד אצל המוסיקאי ינון מועלם לאחר ביקור באי אגינה, אחד מאיי סרוניקוס הסמוכים לאתונה. המפגשים שחווה שם, האנשים המגוונים שפגש והאווירה הייחודית של האי העניקו לו השראה ליצור מוסיקה. האלבום מורכב בעיקר מיצירות מקוריות לצד כמה קאברים</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מייקל ג'קסון Songs From The Motion Picture</v>
+        <v>ינון מועלם Aegina's Secret</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ינון מועלם Aegina's Secret</v>
+        <v>פו פייטרס Your Favorite Toy</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-27</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%a0%d7%95%d7%9f-%d7%9e%d7%95%d7%a2%d7%9c%d7%9d-aeginas-secret/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%95-%d7%a4%d7%99%d7%99%d7%98%d7%a8%d7%a1-your-favorite-toy/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הרעיון ל־Aegina’s Secret נולד אצל המוסיקאי ינון מועלם לאחר ביקור באי אגינה, אחד מאיי סרוניקוס הסמוכים לאתונה. המפגשים שחווה שם, האנשים המגוונים שפגש והאווירה הייחודית של האי העניקו לו השראה ליצור מוסיקה. האלבום מורכב בעיקר מיצירות מקוריות לצד כמה קאברים</v>
+        <v>במשך שני העשורים האחרונים, דייב גרוהל Dave Grohl תמיד מצא רעיון מרכזי שעליו נשען כל אלבום חדש של פו פייטרס Foo Fighters.האלבום In Your Honor היה אלבום כפול שהתפצל בין צד "קשוח” לצד "רך”, ואילו האלבום שאחריו, Echoes, Silence, Patience</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ינון מועלם Aegina's Secret</v>
+        <v>פו פייטרס Your Favorite Toy</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>פו פייטרס Your Favorite Toy</v>
+        <v>סקינרד You got this</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-27</v>
+        <v>2026-05-01</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%95-%d7%a4%d7%99%d7%99%d7%98%d7%a8%d7%a1-your-favorite-toy/</v>
+        <v>https://yosmusic.com/%d7%a1%d7%a7%d7%99%d7%a0%d7%a8%d7%93-you-got-this/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-27</v>
+        <v>2026-05-01</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>במשך שני העשורים האחרונים, דייב גרוהל Dave Grohl תמיד מצא רעיון מרכזי שעליו נשען כל אלבום חדש של פו פייטרס Foo Fighters.האלבום In Your Honor היה אלבום כפול שהתפצל בין צד "קשוח” לצד "רך”, ואילו האלבום שאחריו, Echoes, Silence, Patience</v>
+        <v>הרכב הרגאיי-מטאל מניופורט, סקינרד Skindred, מוכרים כלהקה חיה סוחפת במיוחד, אבל האלבום “Smile” מ-2023 שינה את כללי המשחק. הוא הגיע למקום השני במצעדים בבריטניה, הוביל להופעת סולד אאוט באולם וומבלי ארנה, ולזכייה גאה בפרס להקת האלטרנטיב הטובה ביותר בטקס פרסי</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>פו פייטרס Your Favorite Toy</v>
+        <v>סקינרד You got this</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>סקינרד You got this</v>
+        <v>נואה קאהן The Great Divide</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-05</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%a7%d7%99%d7%a0%d7%a8%d7%93-you-got-this/</v>
+        <v>https://yosmusic.com/%d7%a0%d7%95%d7%90%d7%94-%d7%a7%d7%90%d7%94%d7%9f-the-great-divide/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הרכב הרגאיי-מטאל מניופורט, סקינרד Skindred, מוכרים כלהקה חיה סוחפת במיוחד, אבל האלבום “Smile” מ-2023 שינה את כללי המשחק. הוא הגיע למקום השני במצעדים בבריטניה, הוביל להופעת סולד אאוט באולם וומבלי ארנה, ולזכייה גאה בפרס להקת האלטרנטיב הטובה ביותר בטקס פרסי</v>
+        <v>נואה קאהן פרסם ב־X: “מבקרים שאומרים שהאלבום ארוך מדי — לעזאזל, אני לא חושב שהוא מספיק ארוך.”בהתחשב בכך ש־The Great Divide נמשך לא פחות מ־77 דקות על פני 17 שירים, אפשר להבין מנין הביקורת מגיעה. אורך כשלעצמו אינו דבר רע.</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>סקינרד You got this</v>
+        <v>נואה קאהן The Great Divide</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נואה קאהן The Great Divide</v>
+        <v>אריק סיני – כל השירים היפים באמת</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-10</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%95%d7%90%d7%94-%d7%a7%d7%90%d7%94%d7%9f-the-great-divide/</v>
+        <v>https://yosmusic.com/%d7%90%d7%a8%d7%99%d7%a7-%d7%a1%d7%99%d7%a0%d7%99-%d7%9b%d7%9c-%d7%94%d7%a9%d7%99%d7%a8%d7%99%d7%9d-%d7%94%d7%99%d7%a4%d7%99%d7%9d-%d7%91%d7%90%d7%9e%d7%aa/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>נואה קאהן פרסם ב־X: “מבקרים שאומרים שהאלבום ארוך מדי — לעזאזל, אני לא חושב שהוא מספיק ארוך.”בהתחשב בכך ש־The Great Divide נמשך לא פחות מ־77 דקות על פני 17 שירים, אפשר להבין מנין הביקורת מגיעה. אורך כשלעצמו אינו דבר רע.</v>
+        <v>האלבום "כל השירים היפים באמת” של אריק סיני הוא לא סתם אוסף קאברים אלא אלבום פרשנות. סיני לא מנסה “לעדכן” את השירים בכוח או להתחרות בביצועים המקוריים, אלא להפוך אותם לחלק מהעולם הפנימי והקולי שלו. זה אלבום שמבוסס פחות על</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נואה קאהן The Great Divide</v>
+        <v>אריק סיני – כל השירים היפים באמת</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אריק סיני – כל השירים היפים באמת</v>
+        <v>זארה לארסון Midnight Sun</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-13</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%a8%d7%99%d7%a7-%d7%a1%d7%99%d7%a0%d7%99-%d7%9b%d7%9c-%d7%94%d7%a9%d7%99%d7%a8%d7%99%d7%9d-%d7%94%d7%99%d7%a4%d7%99%d7%9d-%d7%91%d7%90%d7%9e%d7%aa/</v>
+        <v>https://yosmusic.com/%d7%96%d7%90%d7%a8%d7%94-%d7%9c%d7%90%d7%a8%d7%a1%d7%95%d7%9f-midnight-sun/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>האלבום "כל השירים היפים באמת” של אריק סיני הוא לא סתם אוסף קאברים אלא אלבום פרשנות. סיני לא מנסה “לעדכן” את השירים בכוח או להתחרות בביצועים המקוריים, אלא להפוך אותם לחלק מהעולם הפנימי והקולי שלו. זה אלבום שמבוסס פחות על</v>
+        <v>״אמרתי שעד גיל 20 אמלא אצטדיונים״,  שרה זארה לארסון ב־Midnight Sun, ואילו ב״Saturn’s Return״ אחד השרים היפים באלבום – . ״זה לא קרה, אז פשוט דחיתי את הדדליין״ השילוב המושך הזה בין נחישות לפגיעוּת זורם לאורך אלבום הדאנס־פופ המסחרר של</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אריק סיני – כל השירים היפים באמת</v>
+        <v>זארה לארסון Midnight Sun</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>זארה לארסון Midnight Sun</v>
+        <v>יוני רכטר – סגור פתוח סגור</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-28</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%96%d7%90%d7%a8%d7%94-%d7%9c%d7%90%d7%a8%d7%a1%d7%95%d7%9f-midnight-sun/</v>
+        <v>https://yosmusic.com/%d7%99%d7%95%d7%a0%d7%99-%d7%a8%d7%9b%d7%98%d7%a8-%d7%a1%d7%92%d7%95%d7%a8-%d7%a4%d7%aa%d7%95%d7%97-%d7%a1%d7%92%d7%95%d7%a8/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>״אמרתי שעד גיל 20 אמלא אצטדיונים״,  שרה זארה לארסון ב־Midnight Sun, ואילו ב״Saturn’s Return״ אחד השרים היפים באלבום – . ״זה לא קרה, אז פשוט דחיתי את הדדליין״ השילוב המושך הזה בין נחישות לפגיעוּת זורם לאורך אלבום הדאנס־פופ המסחרר של</v>
+        <v>יוני רכטר לא הקליט אלבום אינסטרומנטלי מאז האלבום 'ממש עכשיו – מנגנים יוני רכטר' (1991). ההזדמנות להקליט אחד כזה פעם נוספת התאפשרה בעקבות הטריו שהקים לפני מספר שנים, שכולל מלבדו בפסנתר את נגן הקונטרבס ברק מורי והמתופפת רוני כספי. הקטע</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>זארה לארסון Midnight Sun</v>
+        <v>יוני רכטר – סגור פתוח סגור</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יוני רכטר – סגור פתוח סגור</v>
+        <v>פול מקרטני The Boys Of Dungeon Lane</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-31</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%95%d7%a0%d7%99-%d7%a8%d7%9b%d7%98%d7%a8-%d7%a1%d7%92%d7%95%d7%a8-%d7%a4%d7%aa%d7%95%d7%97-%d7%a1%d7%92%d7%95%d7%a8/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%95%d7%9c-%d7%9e%d7%a7%d7%a8%d7%98%d7%a0%d7%99-the-boys-of-dungeon-lane/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-31</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>יוני רכטר לא הקליט אלבום אינסטרומנטלי מאז האלבום 'ממש עכשיו – מנגנים יוני רכטר' (1991). ההזדמנות להקליט אחד כזה פעם נוספת התאפשרה בעקבות הטריו שהקים לפני מספר שנים, שכולל מלבדו בפסנתר את נגן הקונטרבס ברק מורי והמתופפת רוני כספי. הקטע</v>
+        <v>יש מי שהגדיר את האלבום החדש שת פול מקרטני "סיור מודרך בדרך הארוכה והמפותלת" (a guided tour of the long and winding road Paul)  בנוסח שירו המוכר. המניה של מקרטני לא הייתה בשיא כזה מאז בערך 1966. מוזר ככל שזה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יוני רכטר – סגור פתוח סגור</v>
+        <v>פול מקרטני The Boys Of Dungeon Lane</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>פול מקרטני The Boys Of Dungeon Lane</v>
+        <v>מייזי פיטרס Florescence</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-31</v>
+        <v>2026-06-03</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%95%d7%9c-%d7%9e%d7%a7%d7%a8%d7%98%d7%a0%d7%99-the-boys-of-dungeon-lane/</v>
+        <v>https://yosmusic.com/%d7%9e%d7%99%d7%99%d7%96%d7%99-%d7%a4%d7%99%d7%98%d7%a8%d7%a1-florescence/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-31</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>יש מי שהגדיר את האלבום החדש שת פול מקרטני "סיור מודרך בדרך הארוכה והמפותלת" (a guided tour of the long and winding road Paul)  בנוסח שירו המוכר. המניה של מקרטני לא הייתה בשיא כזה מאז בערך 1966. מוזר ככל שזה</v>
+        <v>החיים נראים מעט אחרת עבור מייזי פיטרס. מאז יציאת  אלבומה השני, "The Good Witch" מ-2023.  באלבומה השלישי, כוכבת הפופ הבריטית משחררת את הכאב ומוצאת שלווה באהבת אמת. בדיוק כשהקריירה שלה צברה תאוצה לקראת סוף 2024, הזמרת שנבחרה לחמם את ההופעות</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>פול מקרטני The Boys Of Dungeon Lane</v>
+        <v>מייזי פיטרס Florescence</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מייזי פיטרס Florescence</v>
+        <v>אלבום הפסקול הרשמי של גביע העולם בכדורגל 2026 של פיפ"א</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%99%d7%99%d7%96%d7%99-%d7%a4%d7%99%d7%98%d7%a8%d7%a1-florescence/</v>
+        <v>https://yosmusic.com/%d7%90%d7%9c%d7%91%d7%95%d7%9d-%d7%94%d7%a4%d7%a1%d7%a7%d7%95%d7%9c-%d7%94%d7%a8%d7%a9%d7%9e%d7%99-%d7%a9%d7%9c-%d7%92%d7%91%d7%99%d7%a2-%d7%94%d7%a2%d7%95%d7%9c%d7%9d-%d7%91%d7%9b%d7%93%d7%95%d7%a8/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>החיים נראים מעט אחרת עבור מייזי פיטרס. מאז יציאת  אלבומה השני, "The Good Witch" מ-2023.  באלבומה השלישי, כוכבת הפופ הבריטית משחררת את הכאב ומוצאת שלווה באהבת אמת. בדיוק כשהקריירה שלה צברה תאוצה לקראת סוף 2024, הזמרת שנבחרה לחמם את ההופעות</v>
+        <v>זהן אוסף בן שעה אחת ו־18 רצועות, המורכב ברובו משיתופי פעולה בין אמנים שנעים בין סטורמזי ושאקירה לבין ג'לי רול והרולינג סטונז? לאורך השנים נוצרה הרבה מוזיקה בהשראת כדורגל. אבל האם נמצא ממנה משהו כאן שהופך את האוסף למיוחד בסוגו?</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מייזי פיטרס Florescence</v>
+        <v>אלבום הפסקול הרשמי של גביע העולם בכדורגל 2026 של פיפ"א</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אלבום הפסקול הרשמי של גביע העולם בכדורגל 2026 של פיפ"א</v>
+        <v>נינט טייב – אני נינה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-11</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%9c%d7%91%d7%95%d7%9d-%d7%94%d7%a4%d7%a1%d7%a7%d7%95%d7%9c-%d7%94%d7%a8%d7%a9%d7%9e%d7%99-%d7%a9%d7%9c-%d7%92%d7%91%d7%99%d7%a2-%d7%94%d7%a2%d7%95%d7%9c%d7%9d-%d7%91%d7%9b%d7%93%d7%95%d7%a8/</v>
+        <v>https://yosmusic.com/%d7%a0%d7%99%d7%a0%d7%98-%d7%98%d7%99%d7%99%d7%91-%d7%90%d7%a0%d7%99-%d7%a0%d7%99%d7%a0%d7%94/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>זהן אוסף בן שעה אחת ו־18 רצועות, המורכב ברובו משיתופי פעולה בין אמנים שנעים בין סטורמזי ושאקירה לבין ג'לי רול והרולינג סטונז? לאורך השנים נוצרה הרבה מוזיקה בהשראת כדורגל. אבל האם נמצא ממנה משהו כאן שהופך את האוסף למיוחד בסוגו?</v>
+        <v>"אני נינה" של נינט טייב מהווה צומת דרכים מכונן בקריירה של אחת הזמרות-יוצרות הבולטות בישראל. הטקסטים של שירי האלבום מתארים תהליך של פירוק והרכבה מחדש, שבו נינט מתרחקת מהדימוי הציבורי הישן שלה ומגדירה את זהותה מחדש כאמנית חופשיה, בוגרת, רוקיסטית</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אלבום הפסקול הרשמי של גביע העולם בכדורגל 2026 של פיפ"א</v>
+        <v>נינט טייב – אני נינה</v>
       </c>
     </row>
   </sheetData>
